--- a/src/data/ruse-blocks.xlsx
+++ b/src/data/ruse-blocks.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2718" uniqueCount="1675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2719" uniqueCount="1676">
   <si>
     <t>Дружба 1</t>
   </si>
@@ -5039,13 +5039,16 @@
   </si>
   <si>
     <t>ул. Бели Брези 103</t>
+  </si>
+  <si>
+    <t>БЛОК 15 ГО НЯМА В ДАННИТЕ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -5053,8 +5056,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5064,6 +5073,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5080,9 +5095,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5414,7 +5430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C986"/>
+  <dimension ref="A1:D986"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -8062,7 +8078,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="241" spans="1:3">
+    <row r="241" spans="1:4">
       <c r="A241" t="s">
         <v>8</v>
       </c>
@@ -8073,7 +8089,7 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="242" spans="1:3">
+    <row r="242" spans="1:4">
       <c r="A242" t="s">
         <v>8</v>
       </c>
@@ -8084,7 +8100,7 @@
         <v>1493</v>
       </c>
     </row>
-    <row r="243" spans="1:3">
+    <row r="243" spans="1:4">
       <c r="A243" t="s">
         <v>8</v>
       </c>
@@ -8095,7 +8111,7 @@
         <v>1497</v>
       </c>
     </row>
-    <row r="244" spans="1:3">
+    <row r="244" spans="1:4">
       <c r="A244" t="s">
         <v>8</v>
       </c>
@@ -8106,18 +8122,21 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="245" spans="1:3">
+    <row r="245" spans="1:4">
       <c r="A245" t="s">
         <v>8</v>
       </c>
-      <c r="B245">
+      <c r="B245" s="2">
         <v>15</v>
       </c>
       <c r="C245" t="s">
         <v>1503</v>
       </c>
-    </row>
-    <row r="246" spans="1:3">
+      <c r="D245" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4">
       <c r="A246" t="s">
         <v>8</v>
       </c>
@@ -8128,7 +8147,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="247" spans="1:3">
+    <row r="247" spans="1:4">
       <c r="A247" t="s">
         <v>8</v>
       </c>
@@ -8139,7 +8158,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="248" spans="1:3">
+    <row r="248" spans="1:4">
       <c r="A248" t="s">
         <v>8</v>
       </c>
@@ -8150,7 +8169,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="249" spans="1:3">
+    <row r="249" spans="1:4">
       <c r="A249" t="s">
         <v>8</v>
       </c>
@@ -8161,7 +8180,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="250" spans="1:3">
+    <row r="250" spans="1:4">
       <c r="A250" t="s">
         <v>8</v>
       </c>
@@ -8172,7 +8191,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="251" spans="1:3">
+    <row r="251" spans="1:4">
       <c r="A251" t="s">
         <v>8</v>
       </c>
@@ -8183,7 +8202,7 @@
         <v>1517</v>
       </c>
     </row>
-    <row r="252" spans="1:3">
+    <row r="252" spans="1:4">
       <c r="A252" t="s">
         <v>8</v>
       </c>
@@ -8194,7 +8213,7 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="253" spans="1:3">
+    <row r="253" spans="1:4">
       <c r="A253" t="s">
         <v>8</v>
       </c>
@@ -8205,7 +8224,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="254" spans="1:3">
+    <row r="254" spans="1:4">
       <c r="A254" t="s">
         <v>8</v>
       </c>
@@ -8216,7 +8235,7 @@
         <v>1524</v>
       </c>
     </row>
-    <row r="255" spans="1:3">
+    <row r="255" spans="1:4">
       <c r="A255" t="s">
         <v>8</v>
       </c>
@@ -8227,7 +8246,7 @@
         <v>1526</v>
       </c>
     </row>
-    <row r="256" spans="1:3">
+    <row r="256" spans="1:4">
       <c r="A256" t="s">
         <v>8</v>
       </c>

--- a/src/data/ruse-blocks.xlsx
+++ b/src/data/ruse-blocks.xlsx
@@ -7994,7 +7994,7 @@
       <c r="A233" t="s">
         <v>8</v>
       </c>
-      <c r="B233">
+      <c r="B233" s="1">
         <v>3</v>
       </c>
       <c r="C233" t="s">
@@ -8005,7 +8005,7 @@
       <c r="A234" t="s">
         <v>8</v>
       </c>
-      <c r="B234">
+      <c r="B234" s="1">
         <v>4</v>
       </c>
       <c r="C234" t="s">
@@ -8016,7 +8016,7 @@
       <c r="A235" t="s">
         <v>8</v>
       </c>
-      <c r="B235">
+      <c r="B235" s="1">
         <v>5</v>
       </c>
       <c r="C235" t="s">
@@ -8038,7 +8038,7 @@
       <c r="A237" t="s">
         <v>8</v>
       </c>
-      <c r="B237">
+      <c r="B237" s="1">
         <v>7</v>
       </c>
       <c r="C237" t="s">
@@ -8049,7 +8049,7 @@
       <c r="A238" t="s">
         <v>8</v>
       </c>
-      <c r="B238">
+      <c r="B238" s="1">
         <v>8</v>
       </c>
       <c r="C238" t="s">
@@ -8082,7 +8082,7 @@
       <c r="A241" t="s">
         <v>8</v>
       </c>
-      <c r="B241">
+      <c r="B241" s="1">
         <v>11</v>
       </c>
       <c r="C241" t="s">
@@ -8195,7 +8195,7 @@
       <c r="A251" t="s">
         <v>8</v>
       </c>
-      <c r="B251">
+      <c r="B251" s="1">
         <v>21</v>
       </c>
       <c r="C251" t="s">
@@ -8206,7 +8206,7 @@
       <c r="A252" t="s">
         <v>8</v>
       </c>
-      <c r="B252">
+      <c r="B252" s="1">
         <v>22</v>
       </c>
       <c r="C252" t="s">
@@ -8283,7 +8283,7 @@
       <c r="A259" t="s">
         <v>8</v>
       </c>
-      <c r="B259">
+      <c r="B259" s="1">
         <v>30</v>
       </c>
       <c r="C259" t="s">
@@ -8294,7 +8294,7 @@
       <c r="A260" t="s">
         <v>8</v>
       </c>
-      <c r="B260">
+      <c r="B260" s="1">
         <v>31</v>
       </c>
       <c r="C260" t="s">
@@ -8305,7 +8305,7 @@
       <c r="A261" t="s">
         <v>8</v>
       </c>
-      <c r="B261">
+      <c r="B261" s="1">
         <v>34</v>
       </c>
       <c r="C261" t="s">
@@ -8327,7 +8327,7 @@
       <c r="A263" t="s">
         <v>8</v>
       </c>
-      <c r="B263">
+      <c r="B263" s="1">
         <v>36</v>
       </c>
       <c r="C263" t="s">
@@ -8338,7 +8338,7 @@
       <c r="A264" t="s">
         <v>8</v>
       </c>
-      <c r="B264">
+      <c r="B264" s="1">
         <v>38</v>
       </c>
       <c r="C264" t="s">
@@ -8349,7 +8349,7 @@
       <c r="A265" t="s">
         <v>8</v>
       </c>
-      <c r="B265">
+      <c r="B265" s="1">
         <v>39</v>
       </c>
       <c r="C265" t="s">
@@ -8360,7 +8360,7 @@
       <c r="A266" t="s">
         <v>8</v>
       </c>
-      <c r="B266">
+      <c r="B266" s="1">
         <v>40</v>
       </c>
       <c r="C266" t="s">
@@ -8371,7 +8371,7 @@
       <c r="A267" t="s">
         <v>8</v>
       </c>
-      <c r="B267">
+      <c r="B267" s="1">
         <v>41</v>
       </c>
       <c r="C267" t="s">
@@ -8404,7 +8404,7 @@
       <c r="A270" t="s">
         <v>8</v>
       </c>
-      <c r="B270">
+      <c r="B270" s="1">
         <v>44</v>
       </c>
       <c r="C270" t="s">
@@ -8415,7 +8415,7 @@
       <c r="A271" t="s">
         <v>8</v>
       </c>
-      <c r="B271">
+      <c r="B271" s="1">
         <v>45</v>
       </c>
       <c r="C271" t="s">
@@ -8426,7 +8426,7 @@
       <c r="A272" t="s">
         <v>8</v>
       </c>
-      <c r="B272">
+      <c r="B272" s="1">
         <v>46</v>
       </c>
       <c r="C272" t="s">
@@ -8437,7 +8437,7 @@
       <c r="A273" t="s">
         <v>8</v>
       </c>
-      <c r="B273">
+      <c r="B273" s="1">
         <v>47</v>
       </c>
       <c r="C273" t="s">
@@ -8448,7 +8448,7 @@
       <c r="A274" t="s">
         <v>8</v>
       </c>
-      <c r="B274">
+      <c r="B274" s="1">
         <v>48</v>
       </c>
       <c r="C274" t="s">
@@ -8558,7 +8558,7 @@
       <c r="A284" t="s">
         <v>8</v>
       </c>
-      <c r="B284">
+      <c r="B284" s="1">
         <v>63</v>
       </c>
       <c r="C284" t="s">
@@ -8569,7 +8569,7 @@
       <c r="A285" t="s">
         <v>8</v>
       </c>
-      <c r="B285">
+      <c r="B285" s="1">
         <v>65</v>
       </c>
       <c r="C285" t="s">
@@ -8822,7 +8822,7 @@
       <c r="A308" t="s">
         <v>8</v>
       </c>
-      <c r="B308">
+      <c r="B308" s="1">
         <v>131</v>
       </c>
       <c r="C308" t="s">

--- a/src/data/ruse-blocks.xlsx
+++ b/src/data/ruse-blocks.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2719" uniqueCount="1676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2730" uniqueCount="1682">
   <si>
     <t>Дружба 1</t>
   </si>
@@ -5038,10 +5038,28 @@
     <t>Бели Брези</t>
   </si>
   <si>
-    <t>ул. Бели Брези 103</t>
-  </si>
-  <si>
-    <t>БЛОК 15 ГО НЯМА В ДАННИТЕ</t>
+    <t>ул. Юндола 1</t>
+  </si>
+  <si>
+    <t>ул. Юндола 3</t>
+  </si>
+  <si>
+    <t>бл. Гагарин</t>
+  </si>
+  <si>
+    <t>бл. Пощенец</t>
+  </si>
+  <si>
+    <t>Гагарин</t>
+  </si>
+  <si>
+    <t>ул. Бели Брези 100</t>
+  </si>
+  <si>
+    <t>В-1</t>
+  </si>
+  <si>
+    <t>ул. Бели хризантеми 9</t>
   </si>
 </sst>
 </file>
@@ -5078,7 +5096,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5095,10 +5113,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5430,12 +5451,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D986"/>
+  <dimension ref="A1:D990"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
     <col min="2" max="2" width="22.09765625" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="12.09765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8027,7 +8049,7 @@
       <c r="A236" t="s">
         <v>8</v>
       </c>
-      <c r="B236">
+      <c r="B236" s="1">
         <v>6</v>
       </c>
       <c r="C236" t="s">
@@ -8060,7 +8082,7 @@
       <c r="A239" t="s">
         <v>8</v>
       </c>
-      <c r="B239">
+      <c r="B239" s="1">
         <v>9</v>
       </c>
       <c r="C239" t="s">
@@ -8071,14 +8093,14 @@
       <c r="A240" t="s">
         <v>8</v>
       </c>
-      <c r="B240">
+      <c r="B240" s="1">
         <v>10</v>
       </c>
       <c r="C240" t="s">
         <v>1486</v>
       </c>
     </row>
-    <row r="241" spans="1:4">
+    <row r="241" spans="1:3">
       <c r="A241" t="s">
         <v>8</v>
       </c>
@@ -8089,40 +8111,40 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="242" spans="1:4">
+    <row r="242" spans="1:3">
       <c r="A242" t="s">
         <v>8</v>
       </c>
-      <c r="B242">
+      <c r="B242" s="1">
         <v>12</v>
       </c>
       <c r="C242" t="s">
         <v>1493</v>
       </c>
     </row>
-    <row r="243" spans="1:4">
+    <row r="243" spans="1:3">
       <c r="A243" t="s">
         <v>8</v>
       </c>
-      <c r="B243">
+      <c r="B243" s="1">
         <v>13</v>
       </c>
       <c r="C243" t="s">
         <v>1497</v>
       </c>
     </row>
-    <row r="244" spans="1:4">
+    <row r="244" spans="1:3">
       <c r="A244" t="s">
         <v>8</v>
       </c>
-      <c r="B244">
+      <c r="B244" s="1">
         <v>14</v>
       </c>
       <c r="C244" t="s">
         <v>1500</v>
       </c>
     </row>
-    <row r="245" spans="1:4">
+    <row r="245" spans="1:3">
       <c r="A245" t="s">
         <v>8</v>
       </c>
@@ -8132,66 +8154,63 @@
       <c r="C245" t="s">
         <v>1503</v>
       </c>
-      <c r="D245" t="s">
-        <v>1675</v>
-      </c>
-    </row>
-    <row r="246" spans="1:4">
+    </row>
+    <row r="246" spans="1:3">
       <c r="A246" t="s">
         <v>8</v>
       </c>
-      <c r="B246">
+      <c r="B246" s="1">
         <v>16</v>
       </c>
       <c r="C246" t="s">
         <v>1506</v>
       </c>
     </row>
-    <row r="247" spans="1:4">
+    <row r="247" spans="1:3">
       <c r="A247" t="s">
         <v>8</v>
       </c>
-      <c r="B247">
+      <c r="B247" s="1">
         <v>17</v>
       </c>
       <c r="C247" t="s">
         <v>1508</v>
       </c>
     </row>
-    <row r="248" spans="1:4">
+    <row r="248" spans="1:3">
       <c r="A248" t="s">
         <v>8</v>
       </c>
-      <c r="B248">
+      <c r="B248" s="1">
         <v>18</v>
       </c>
       <c r="C248" t="s">
         <v>1510</v>
       </c>
     </row>
-    <row r="249" spans="1:4">
+    <row r="249" spans="1:3">
       <c r="A249" t="s">
         <v>8</v>
       </c>
-      <c r="B249">
+      <c r="B249" s="1">
         <v>19</v>
       </c>
       <c r="C249" t="s">
         <v>1512</v>
       </c>
     </row>
-    <row r="250" spans="1:4">
+    <row r="250" spans="1:3">
       <c r="A250" t="s">
         <v>8</v>
       </c>
-      <c r="B250">
+      <c r="B250" s="1">
         <v>20</v>
       </c>
       <c r="C250" t="s">
         <v>1514</v>
       </c>
     </row>
-    <row r="251" spans="1:4">
+    <row r="251" spans="1:3">
       <c r="A251" t="s">
         <v>8</v>
       </c>
@@ -8202,7 +8221,7 @@
         <v>1517</v>
       </c>
     </row>
-    <row r="252" spans="1:4">
+    <row r="252" spans="1:3">
       <c r="A252" t="s">
         <v>8</v>
       </c>
@@ -8213,44 +8232,44 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="253" spans="1:4">
+    <row r="253" spans="1:3">
       <c r="A253" t="s">
         <v>8</v>
       </c>
-      <c r="B253">
+      <c r="B253" s="1">
         <v>23</v>
       </c>
       <c r="C253" t="s">
         <v>1522</v>
       </c>
     </row>
-    <row r="254" spans="1:4">
+    <row r="254" spans="1:3">
       <c r="A254" t="s">
         <v>8</v>
       </c>
-      <c r="B254">
+      <c r="B254" s="1">
         <v>24</v>
       </c>
       <c r="C254" t="s">
         <v>1524</v>
       </c>
     </row>
-    <row r="255" spans="1:4">
+    <row r="255" spans="1:3">
       <c r="A255" t="s">
         <v>8</v>
       </c>
-      <c r="B255">
+      <c r="B255" s="1">
         <v>25</v>
       </c>
       <c r="C255" t="s">
         <v>1526</v>
       </c>
     </row>
-    <row r="256" spans="1:4">
+    <row r="256" spans="1:3">
       <c r="A256" t="s">
         <v>8</v>
       </c>
-      <c r="B256">
+      <c r="B256" s="1">
         <v>27</v>
       </c>
       <c r="C256" t="s">
@@ -8261,7 +8280,7 @@
       <c r="A257" t="s">
         <v>8</v>
       </c>
-      <c r="B257">
+      <c r="B257" s="1">
         <v>28</v>
       </c>
       <c r="C257" t="s">
@@ -8272,7 +8291,7 @@
       <c r="A258" t="s">
         <v>8</v>
       </c>
-      <c r="B258">
+      <c r="B258" s="1">
         <v>29</v>
       </c>
       <c r="C258" t="s">
@@ -8316,7 +8335,7 @@
       <c r="A262" t="s">
         <v>8</v>
       </c>
-      <c r="B262">
+      <c r="B262" s="1">
         <v>35</v>
       </c>
       <c r="C262" t="s">
@@ -8433,7 +8452,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="273" spans="1:3">
+    <row r="273" spans="1:4">
       <c r="A273" t="s">
         <v>8</v>
       </c>
@@ -8444,7 +8463,7 @@
         <v>1567</v>
       </c>
     </row>
-    <row r="274" spans="1:3">
+    <row r="274" spans="1:4">
       <c r="A274" t="s">
         <v>8</v>
       </c>
@@ -8455,40 +8474,40 @@
         <v>1569</v>
       </c>
     </row>
-    <row r="275" spans="1:3">
+    <row r="275" spans="1:4">
       <c r="A275" t="s">
         <v>8</v>
       </c>
-      <c r="B275">
+      <c r="B275" s="1">
         <v>49</v>
       </c>
       <c r="C275" t="s">
         <v>1571</v>
       </c>
     </row>
-    <row r="276" spans="1:3">
+    <row r="276" spans="1:4">
       <c r="A276" t="s">
         <v>8</v>
       </c>
-      <c r="B276">
+      <c r="B276" s="1">
         <v>50</v>
       </c>
       <c r="C276" t="s">
         <v>1573</v>
       </c>
     </row>
-    <row r="277" spans="1:3">
+    <row r="277" spans="1:4">
       <c r="A277" t="s">
         <v>8</v>
       </c>
-      <c r="B277">
+      <c r="B277" s="1">
         <v>51</v>
       </c>
       <c r="C277" t="s">
         <v>1575</v>
       </c>
     </row>
-    <row r="278" spans="1:3">
+    <row r="278" spans="1:4">
       <c r="A278" t="s">
         <v>8</v>
       </c>
@@ -8499,7 +8518,7 @@
         <v>1577</v>
       </c>
     </row>
-    <row r="279" spans="1:3">
+    <row r="279" spans="1:4">
       <c r="A279" t="s">
         <v>8</v>
       </c>
@@ -8510,7 +8529,7 @@
         <v>1580</v>
       </c>
     </row>
-    <row r="280" spans="1:3">
+    <row r="280" spans="1:4">
       <c r="A280" t="s">
         <v>8</v>
       </c>
@@ -8521,7 +8540,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="281" spans="1:3">
+    <row r="281" spans="1:4">
       <c r="A281" t="s">
         <v>8</v>
       </c>
@@ -8532,7 +8551,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="282" spans="1:3">
+    <row r="282" spans="1:4">
       <c r="A282" t="s">
         <v>8</v>
       </c>
@@ -8543,7 +8562,7 @@
         <v>1584</v>
       </c>
     </row>
-    <row r="283" spans="1:3">
+    <row r="283" spans="1:4">
       <c r="A283" t="s">
         <v>8</v>
       </c>
@@ -8554,7 +8573,7 @@
         <v>1585</v>
       </c>
     </row>
-    <row r="284" spans="1:3">
+    <row r="284" spans="1:4">
       <c r="A284" t="s">
         <v>8</v>
       </c>
@@ -8565,7 +8584,7 @@
         <v>1586</v>
       </c>
     </row>
-    <row r="285" spans="1:3">
+    <row r="285" spans="1:4">
       <c r="A285" t="s">
         <v>8</v>
       </c>
@@ -8576,18 +8595,18 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="286" spans="1:3">
+    <row r="286" spans="1:4">
       <c r="A286" t="s">
         <v>8</v>
       </c>
-      <c r="B286">
+      <c r="B286" s="2">
         <v>68</v>
       </c>
       <c r="C286" t="s">
         <v>1588</v>
       </c>
     </row>
-    <row r="287" spans="1:3">
+    <row r="287" spans="1:4">
       <c r="A287" t="s">
         <v>8</v>
       </c>
@@ -8598,15 +8617,18 @@
         <v>1589</v>
       </c>
     </row>
-    <row r="288" spans="1:3">
-      <c r="A288" t="s">
+    <row r="288" spans="1:4">
+      <c r="A288" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B288">
+      <c r="B288" s="3">
         <v>71</v>
       </c>
-      <c r="C288" t="s">
+      <c r="C288" s="3" t="s">
         <v>1590</v>
+      </c>
+      <c r="D288" t="s">
+        <v>1677</v>
       </c>
     </row>
     <row r="289" spans="1:3">
@@ -8785,180 +8807,183 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="305" spans="1:3">
+    <row r="305" spans="1:4">
       <c r="A305" t="s">
         <v>8</v>
       </c>
-      <c r="B305">
-        <v>109</v>
+      <c r="B305" s="1">
+        <v>107</v>
       </c>
       <c r="C305" t="s">
-        <v>1616</v>
-      </c>
-    </row>
-    <row r="306" spans="1:3">
+        <v>1674</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4">
       <c r="A306" t="s">
         <v>8</v>
       </c>
-      <c r="B306">
-        <v>110</v>
+      <c r="B306" s="1">
+        <v>108</v>
       </c>
       <c r="C306" t="s">
-        <v>1618</v>
-      </c>
-    </row>
-    <row r="307" spans="1:3">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4">
       <c r="A307" t="s">
         <v>8</v>
       </c>
-      <c r="B307">
-        <v>111</v>
+      <c r="B307" s="1">
+        <v>109</v>
       </c>
       <c r="C307" t="s">
-        <v>1619</v>
-      </c>
-    </row>
-    <row r="308" spans="1:3">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4">
       <c r="A308" t="s">
         <v>8</v>
       </c>
       <c r="B308" s="1">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="C308" t="s">
-        <v>1632</v>
-      </c>
-    </row>
-    <row r="309" spans="1:3">
+        <v>1618</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4">
       <c r="A309" t="s">
         <v>8</v>
       </c>
-      <c r="B309">
-        <v>133</v>
+      <c r="B309" s="1">
+        <v>111</v>
       </c>
       <c r="C309" t="s">
-        <v>1633</v>
-      </c>
-    </row>
-    <row r="310" spans="1:3">
+        <v>1619</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4">
       <c r="A310" t="s">
         <v>8</v>
       </c>
-      <c r="B310">
-        <v>141</v>
+      <c r="B310" s="1">
+        <v>131</v>
       </c>
       <c r="C310" t="s">
-        <v>1634</v>
-      </c>
-    </row>
-    <row r="311" spans="1:3">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4">
       <c r="A311" t="s">
         <v>8</v>
       </c>
-      <c r="B311" t="s">
-        <v>1671</v>
+      <c r="B311" s="1">
+        <v>133</v>
       </c>
       <c r="C311" t="s">
-        <v>1672</v>
-      </c>
-    </row>
-    <row r="312" spans="1:3">
-      <c r="A312" t="s">
+        <v>1633</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4">
+      <c r="A312" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B312" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C312" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="313" spans="1:3">
+      <c r="B312" s="3">
+        <v>141</v>
+      </c>
+      <c r="C312" s="3" t="s">
+        <v>1634</v>
+      </c>
+      <c r="D312" t="s">
+        <v>1676</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4">
       <c r="A313" t="s">
         <v>8</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>78</v>
+        <v>1671</v>
       </c>
       <c r="C313" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="314" spans="1:3">
+        <v>1672</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4">
       <c r="A314" t="s">
         <v>8</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>1673</v>
+        <v>76</v>
       </c>
       <c r="C314" t="s">
-        <v>1674</v>
-      </c>
-    </row>
-    <row r="315" spans="1:3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4">
       <c r="A315" t="s">
         <v>8</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>144</v>
+        <v>78</v>
       </c>
       <c r="C315" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="316" spans="1:3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4">
       <c r="A316" t="s">
         <v>8</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>636</v>
+        <v>1673</v>
       </c>
       <c r="C316" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="317" spans="1:3">
-      <c r="A317" t="s">
+        <v>1679</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4">
+      <c r="A317" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>827</v>
+        <v>144</v>
       </c>
       <c r="C317" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="318" spans="1:3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4">
       <c r="A318" t="s">
         <v>8</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>917</v>
+        <v>1680</v>
       </c>
       <c r="C318" t="s">
-        <v>918</v>
-      </c>
-    </row>
-    <row r="319" spans="1:3">
-      <c r="A319" t="s">
+        <v>1681</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4">
+      <c r="A319" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>944</v>
-      </c>
-      <c r="C319" t="s">
-        <v>945</v>
-      </c>
-    </row>
-    <row r="320" spans="1:3">
+        <v>1678</v>
+      </c>
+      <c r="C319" s="4" t="s">
+        <v>1634</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4">
       <c r="A320" t="s">
         <v>8</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>1045</v>
+        <v>636</v>
       </c>
       <c r="C320" t="s">
-        <v>1046</v>
+        <v>637</v>
       </c>
     </row>
     <row r="321" spans="1:3">
@@ -8966,10 +8991,10 @@
         <v>8</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>1051</v>
+        <v>827</v>
       </c>
       <c r="C321" t="s">
-        <v>1590</v>
+        <v>828</v>
       </c>
     </row>
     <row r="322" spans="1:3">
@@ -8977,10 +9002,10 @@
         <v>8</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>1181</v>
+        <v>917</v>
       </c>
       <c r="C322" t="s">
-        <v>1182</v>
+        <v>918</v>
       </c>
     </row>
     <row r="323" spans="1:3">
@@ -8988,10 +9013,10 @@
         <v>8</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>1258</v>
+        <v>944</v>
       </c>
       <c r="C323" t="s">
-        <v>1259</v>
+        <v>945</v>
       </c>
     </row>
     <row r="324" spans="1:3">
@@ -8999,10 +9024,10 @@
         <v>8</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>1269</v>
+        <v>1045</v>
       </c>
       <c r="C324" t="s">
-        <v>1270</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="325" spans="1:3">
@@ -9010,54 +9035,54 @@
         <v>8</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>1271</v>
+        <v>1051</v>
       </c>
       <c r="C325" t="s">
-        <v>1272</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="326" spans="1:3">
       <c r="A326" t="s">
-        <v>117</v>
-      </c>
-      <c r="B326" t="s">
-        <v>118</v>
+        <v>8</v>
+      </c>
+      <c r="B326" s="1" t="s">
+        <v>1181</v>
       </c>
       <c r="C326" t="s">
-        <v>119</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="327" spans="1:3">
       <c r="A327" t="s">
-        <v>117</v>
-      </c>
-      <c r="B327" t="s">
-        <v>394</v>
+        <v>8</v>
+      </c>
+      <c r="B327" s="1" t="s">
+        <v>1258</v>
       </c>
       <c r="C327" t="s">
-        <v>395</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="328" spans="1:3">
       <c r="A328" t="s">
-        <v>117</v>
-      </c>
-      <c r="B328" t="s">
-        <v>816</v>
+        <v>8</v>
+      </c>
+      <c r="B328" s="1" t="s">
+        <v>1269</v>
       </c>
       <c r="C328" t="s">
-        <v>817</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="329" spans="1:3">
       <c r="A329" t="s">
-        <v>117</v>
-      </c>
-      <c r="B329" t="s">
-        <v>888</v>
+        <v>8</v>
+      </c>
+      <c r="B329" s="1" t="s">
+        <v>1271</v>
       </c>
       <c r="C329" t="s">
-        <v>889</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="330" spans="1:3">
@@ -9065,10 +9090,10 @@
         <v>117</v>
       </c>
       <c r="B330" t="s">
-        <v>990</v>
+        <v>118</v>
       </c>
       <c r="C330" t="s">
-        <v>991</v>
+        <v>119</v>
       </c>
     </row>
     <row r="331" spans="1:3">
@@ -9076,10 +9101,10 @@
         <v>117</v>
       </c>
       <c r="B331" t="s">
-        <v>1018</v>
+        <v>394</v>
       </c>
       <c r="C331" t="s">
-        <v>1019</v>
+        <v>395</v>
       </c>
     </row>
     <row r="332" spans="1:3">
@@ -9087,10 +9112,10 @@
         <v>117</v>
       </c>
       <c r="B332" t="s">
-        <v>1102</v>
+        <v>816</v>
       </c>
       <c r="C332" t="s">
-        <v>1103</v>
+        <v>817</v>
       </c>
     </row>
     <row r="333" spans="1:3">
@@ -9098,10 +9123,10 @@
         <v>117</v>
       </c>
       <c r="B333" t="s">
-        <v>1106</v>
+        <v>888</v>
       </c>
       <c r="C333" t="s">
-        <v>1107</v>
+        <v>889</v>
       </c>
     </row>
     <row r="334" spans="1:3">
@@ -9109,10 +9134,10 @@
         <v>117</v>
       </c>
       <c r="B334" t="s">
-        <v>1126</v>
+        <v>990</v>
       </c>
       <c r="C334" t="s">
-        <v>1127</v>
+        <v>991</v>
       </c>
     </row>
     <row r="335" spans="1:3">
@@ -9120,10 +9145,10 @@
         <v>117</v>
       </c>
       <c r="B335" t="s">
-        <v>1130</v>
+        <v>1018</v>
       </c>
       <c r="C335" t="s">
-        <v>1131</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="336" spans="1:3">
@@ -9131,54 +9156,54 @@
         <v>117</v>
       </c>
       <c r="B336" t="s">
-        <v>1386</v>
+        <v>1102</v>
       </c>
       <c r="C336" t="s">
-        <v>1387</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="337" spans="1:3">
       <c r="A337" t="s">
-        <v>550</v>
+        <v>117</v>
       </c>
       <c r="B337" t="s">
-        <v>551</v>
+        <v>1106</v>
       </c>
       <c r="C337" t="s">
-        <v>552</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="338" spans="1:3">
       <c r="A338" t="s">
-        <v>550</v>
+        <v>117</v>
       </c>
       <c r="B338" t="s">
-        <v>553</v>
+        <v>1126</v>
       </c>
       <c r="C338" t="s">
-        <v>554</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="339" spans="1:3">
       <c r="A339" t="s">
-        <v>550</v>
+        <v>117</v>
       </c>
       <c r="B339" t="s">
-        <v>692</v>
+        <v>1130</v>
       </c>
       <c r="C339" t="s">
-        <v>693</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="340" spans="1:3">
       <c r="A340" t="s">
-        <v>550</v>
+        <v>117</v>
       </c>
       <c r="B340" t="s">
-        <v>1016</v>
+        <v>1386</v>
       </c>
       <c r="C340" t="s">
-        <v>1017</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="341" spans="1:3">
@@ -9186,10 +9211,10 @@
         <v>550</v>
       </c>
       <c r="B341" t="s">
-        <v>1047</v>
+        <v>551</v>
       </c>
       <c r="C341" t="s">
-        <v>1048</v>
+        <v>552</v>
       </c>
     </row>
     <row r="342" spans="1:3">
@@ -9197,10 +9222,10 @@
         <v>550</v>
       </c>
       <c r="B342" t="s">
-        <v>1049</v>
+        <v>553</v>
       </c>
       <c r="C342" t="s">
-        <v>1050</v>
+        <v>554</v>
       </c>
     </row>
     <row r="343" spans="1:3">
@@ -9208,54 +9233,54 @@
         <v>550</v>
       </c>
       <c r="B343" t="s">
-        <v>1074</v>
+        <v>692</v>
       </c>
       <c r="C343" t="s">
-        <v>1075</v>
+        <v>693</v>
       </c>
     </row>
     <row r="344" spans="1:3">
       <c r="A344" t="s">
-        <v>45</v>
-      </c>
-      <c r="B344" s="1" t="s">
-        <v>46</v>
+        <v>550</v>
+      </c>
+      <c r="B344" t="s">
+        <v>1016</v>
       </c>
       <c r="C344" t="s">
-        <v>47</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="345" spans="1:3">
       <c r="A345" t="s">
-        <v>45</v>
-      </c>
-      <c r="B345" s="1" t="s">
-        <v>74</v>
+        <v>550</v>
+      </c>
+      <c r="B345" t="s">
+        <v>1047</v>
       </c>
       <c r="C345" t="s">
-        <v>75</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="346" spans="1:3">
       <c r="A346" t="s">
-        <v>45</v>
-      </c>
-      <c r="B346" s="1" t="s">
-        <v>94</v>
+        <v>550</v>
+      </c>
+      <c r="B346" t="s">
+        <v>1049</v>
       </c>
       <c r="C346" t="s">
-        <v>95</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="347" spans="1:3">
       <c r="A347" t="s">
-        <v>45</v>
-      </c>
-      <c r="B347" s="1" t="s">
-        <v>128</v>
+        <v>550</v>
+      </c>
+      <c r="B347" t="s">
+        <v>1074</v>
       </c>
       <c r="C347" t="s">
-        <v>129</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="348" spans="1:3">
@@ -9263,10 +9288,10 @@
         <v>45</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>142</v>
+        <v>46</v>
       </c>
       <c r="C348" t="s">
-        <v>143</v>
+        <v>47</v>
       </c>
     </row>
     <row r="349" spans="1:3">
@@ -9274,10 +9299,10 @@
         <v>45</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>189</v>
+        <v>74</v>
       </c>
       <c r="C349" t="s">
-        <v>190</v>
+        <v>75</v>
       </c>
     </row>
     <row r="350" spans="1:3">
@@ -9285,10 +9310,10 @@
         <v>45</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>192</v>
+        <v>94</v>
       </c>
       <c r="C350" t="s">
-        <v>193</v>
+        <v>95</v>
       </c>
     </row>
     <row r="351" spans="1:3">
@@ -9296,10 +9321,10 @@
         <v>45</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>198</v>
+        <v>128</v>
       </c>
       <c r="C351" t="s">
-        <v>199</v>
+        <v>129</v>
       </c>
     </row>
     <row r="352" spans="1:3">
@@ -9307,10 +9332,10 @@
         <v>45</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>211</v>
+        <v>142</v>
       </c>
       <c r="C352" t="s">
-        <v>212</v>
+        <v>143</v>
       </c>
     </row>
     <row r="353" spans="1:3">
@@ -9318,10 +9343,10 @@
         <v>45</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>238</v>
+        <v>189</v>
       </c>
       <c r="C353" t="s">
-        <v>239</v>
+        <v>190</v>
       </c>
     </row>
     <row r="354" spans="1:3">
@@ -9329,10 +9354,10 @@
         <v>45</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>354</v>
+        <v>192</v>
       </c>
       <c r="C354" t="s">
-        <v>355</v>
+        <v>193</v>
       </c>
     </row>
     <row r="355" spans="1:3">
@@ -9340,10 +9365,10 @@
         <v>45</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>358</v>
+        <v>198</v>
       </c>
       <c r="C355" t="s">
-        <v>359</v>
+        <v>199</v>
       </c>
     </row>
     <row r="356" spans="1:3">
@@ -9351,10 +9376,10 @@
         <v>45</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>360</v>
+        <v>211</v>
       </c>
       <c r="C356" t="s">
-        <v>361</v>
+        <v>212</v>
       </c>
     </row>
     <row r="357" spans="1:3">
@@ -9362,10 +9387,10 @@
         <v>45</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>382</v>
+        <v>238</v>
       </c>
       <c r="C357" t="s">
-        <v>385</v>
+        <v>239</v>
       </c>
     </row>
     <row r="358" spans="1:3">
@@ -9373,10 +9398,10 @@
         <v>45</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>386</v>
+        <v>354</v>
       </c>
       <c r="C358" t="s">
-        <v>387</v>
+        <v>355</v>
       </c>
     </row>
     <row r="359" spans="1:3">
@@ -9384,10 +9409,10 @@
         <v>45</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>403</v>
+        <v>358</v>
       </c>
       <c r="C359" t="s">
-        <v>404</v>
+        <v>359</v>
       </c>
     </row>
     <row r="360" spans="1:3">
@@ -9395,10 +9420,10 @@
         <v>45</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>405</v>
+        <v>360</v>
       </c>
       <c r="C360" t="s">
-        <v>406</v>
+        <v>361</v>
       </c>
     </row>
     <row r="361" spans="1:3">
@@ -9406,10 +9431,10 @@
         <v>45</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>462</v>
+        <v>382</v>
       </c>
       <c r="C361" t="s">
-        <v>463</v>
+        <v>385</v>
       </c>
     </row>
     <row r="362" spans="1:3">
@@ -9417,10 +9442,10 @@
         <v>45</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>480</v>
+        <v>386</v>
       </c>
       <c r="C362" t="s">
-        <v>481</v>
+        <v>387</v>
       </c>
     </row>
     <row r="363" spans="1:3">
@@ -9428,10 +9453,10 @@
         <v>45</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>482</v>
+        <v>403</v>
       </c>
       <c r="C363" t="s">
-        <v>483</v>
+        <v>404</v>
       </c>
     </row>
     <row r="364" spans="1:3">
@@ -9439,10 +9464,10 @@
         <v>45</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>500</v>
+        <v>405</v>
       </c>
       <c r="C364" t="s">
-        <v>501</v>
+        <v>406</v>
       </c>
     </row>
     <row r="365" spans="1:3">
@@ -9450,10 +9475,10 @@
         <v>45</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>504</v>
+        <v>462</v>
       </c>
       <c r="C365" t="s">
-        <v>129</v>
+        <v>463</v>
       </c>
     </row>
     <row r="366" spans="1:3">
@@ -9461,10 +9486,10 @@
         <v>45</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>505</v>
+        <v>480</v>
       </c>
       <c r="C366" t="s">
-        <v>506</v>
+        <v>481</v>
       </c>
     </row>
     <row r="367" spans="1:3">
@@ -9472,10 +9497,10 @@
         <v>45</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>537</v>
+        <v>482</v>
       </c>
       <c r="C367" t="s">
-        <v>538</v>
+        <v>483</v>
       </c>
     </row>
     <row r="368" spans="1:3">
@@ -9483,10 +9508,10 @@
         <v>45</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>559</v>
+        <v>500</v>
       </c>
       <c r="C368" t="s">
-        <v>560</v>
+        <v>501</v>
       </c>
     </row>
     <row r="369" spans="1:3">
@@ -9494,10 +9519,10 @@
         <v>45</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>570</v>
+        <v>504</v>
       </c>
       <c r="C369" t="s">
-        <v>571</v>
+        <v>129</v>
       </c>
     </row>
     <row r="370" spans="1:3">
@@ -9505,10 +9530,10 @@
         <v>45</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>574</v>
+        <v>505</v>
       </c>
       <c r="C370" t="s">
-        <v>575</v>
+        <v>506</v>
       </c>
     </row>
     <row r="371" spans="1:3">
@@ -9516,10 +9541,10 @@
         <v>45</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>594</v>
+        <v>537</v>
       </c>
       <c r="C371" t="s">
-        <v>595</v>
+        <v>538</v>
       </c>
     </row>
     <row r="372" spans="1:3">
@@ -9527,10 +9552,10 @@
         <v>45</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>596</v>
+        <v>559</v>
       </c>
       <c r="C372" t="s">
-        <v>597</v>
+        <v>560</v>
       </c>
     </row>
     <row r="373" spans="1:3">
@@ -9538,10 +9563,10 @@
         <v>45</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>600</v>
+        <v>570</v>
       </c>
       <c r="C373" t="s">
-        <v>601</v>
+        <v>571</v>
       </c>
     </row>
     <row r="374" spans="1:3">
@@ -9549,10 +9574,10 @@
         <v>45</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>672</v>
+        <v>574</v>
       </c>
       <c r="C374" t="s">
-        <v>673</v>
+        <v>575</v>
       </c>
     </row>
     <row r="375" spans="1:3">
@@ -9560,10 +9585,10 @@
         <v>45</v>
       </c>
       <c r="B375" s="1" t="s">
-        <v>688</v>
+        <v>594</v>
       </c>
       <c r="C375" t="s">
-        <v>689</v>
+        <v>595</v>
       </c>
     </row>
     <row r="376" spans="1:3">
@@ -9571,10 +9596,10 @@
         <v>45</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>696</v>
+        <v>596</v>
       </c>
       <c r="C376" t="s">
-        <v>697</v>
+        <v>597</v>
       </c>
     </row>
     <row r="377" spans="1:3">
@@ -9582,10 +9607,10 @@
         <v>45</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>702</v>
+        <v>600</v>
       </c>
       <c r="C377" t="s">
-        <v>703</v>
+        <v>601</v>
       </c>
     </row>
     <row r="378" spans="1:3">
@@ -9593,10 +9618,10 @@
         <v>45</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>792</v>
+        <v>672</v>
       </c>
       <c r="C378" t="s">
-        <v>793</v>
+        <v>673</v>
       </c>
     </row>
     <row r="379" spans="1:3">
@@ -9604,10 +9629,10 @@
         <v>45</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>798</v>
+        <v>688</v>
       </c>
       <c r="C379" t="s">
-        <v>799</v>
+        <v>689</v>
       </c>
     </row>
     <row r="380" spans="1:3">
@@ -9615,10 +9640,10 @@
         <v>45</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>812</v>
+        <v>696</v>
       </c>
       <c r="C380" t="s">
-        <v>813</v>
+        <v>697</v>
       </c>
     </row>
     <row r="381" spans="1:3">
@@ -9626,10 +9651,10 @@
         <v>45</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>822</v>
+        <v>702</v>
       </c>
       <c r="C381" t="s">
-        <v>823</v>
+        <v>703</v>
       </c>
     </row>
     <row r="382" spans="1:3">
@@ -9637,10 +9662,10 @@
         <v>45</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>881</v>
+        <v>792</v>
       </c>
       <c r="C382" t="s">
-        <v>882</v>
+        <v>793</v>
       </c>
     </row>
     <row r="383" spans="1:3">
@@ -9648,10 +9673,10 @@
         <v>45</v>
       </c>
       <c r="B383" s="1" t="s">
-        <v>886</v>
+        <v>798</v>
       </c>
       <c r="C383" t="s">
-        <v>887</v>
+        <v>799</v>
       </c>
     </row>
     <row r="384" spans="1:3">
@@ -9659,10 +9684,10 @@
         <v>45</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>893</v>
+        <v>812</v>
       </c>
       <c r="C384" t="s">
-        <v>894</v>
+        <v>813</v>
       </c>
     </row>
     <row r="385" spans="1:3">
@@ -9670,10 +9695,10 @@
         <v>45</v>
       </c>
       <c r="B385" s="1" t="s">
-        <v>913</v>
+        <v>822</v>
       </c>
       <c r="C385" t="s">
-        <v>914</v>
+        <v>823</v>
       </c>
     </row>
     <row r="386" spans="1:3">
@@ -9681,10 +9706,10 @@
         <v>45</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>926</v>
+        <v>881</v>
       </c>
       <c r="C386" t="s">
-        <v>927</v>
+        <v>882</v>
       </c>
     </row>
     <row r="387" spans="1:3">
@@ -9692,10 +9717,10 @@
         <v>45</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>932</v>
+        <v>886</v>
       </c>
       <c r="C387" t="s">
-        <v>933</v>
+        <v>887</v>
       </c>
     </row>
     <row r="388" spans="1:3">
@@ -9703,10 +9728,10 @@
         <v>45</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>971</v>
+        <v>893</v>
       </c>
       <c r="C388" t="s">
-        <v>972</v>
+        <v>894</v>
       </c>
     </row>
     <row r="389" spans="1:3">
@@ -9714,10 +9739,10 @@
         <v>45</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>988</v>
+        <v>913</v>
       </c>
       <c r="C389" t="s">
-        <v>989</v>
+        <v>914</v>
       </c>
     </row>
     <row r="390" spans="1:3">
@@ -9725,10 +9750,10 @@
         <v>45</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>1008</v>
+        <v>926</v>
       </c>
       <c r="C390" t="s">
-        <v>1009</v>
+        <v>927</v>
       </c>
     </row>
     <row r="391" spans="1:3">
@@ -9736,10 +9761,10 @@
         <v>45</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>1053</v>
+        <v>932</v>
       </c>
       <c r="C391" t="s">
-        <v>1054</v>
+        <v>933</v>
       </c>
     </row>
     <row r="392" spans="1:3">
@@ -9747,10 +9772,10 @@
         <v>45</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>1087</v>
+        <v>971</v>
       </c>
       <c r="C392" t="s">
-        <v>1088</v>
+        <v>972</v>
       </c>
     </row>
     <row r="393" spans="1:3">
@@ -9758,10 +9783,10 @@
         <v>45</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>1093</v>
+        <v>988</v>
       </c>
       <c r="C393" t="s">
-        <v>1094</v>
+        <v>989</v>
       </c>
     </row>
     <row r="394" spans="1:3">
@@ -9769,10 +9794,10 @@
         <v>45</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>1128</v>
+        <v>1008</v>
       </c>
       <c r="C394" t="s">
-        <v>1129</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="395" spans="1:3">
@@ -9780,10 +9805,10 @@
         <v>45</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>1187</v>
+        <v>1053</v>
       </c>
       <c r="C395" t="s">
-        <v>1188</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="396" spans="1:3">
@@ -9791,10 +9816,10 @@
         <v>45</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>1199</v>
+        <v>1087</v>
       </c>
       <c r="C396" t="s">
-        <v>1200</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="397" spans="1:3">
@@ -9802,10 +9827,10 @@
         <v>45</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>1208</v>
+        <v>1093</v>
       </c>
       <c r="C397" t="s">
-        <v>1209</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="398" spans="1:3">
@@ -9813,10 +9838,10 @@
         <v>45</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>1218</v>
+        <v>1128</v>
       </c>
       <c r="C398" t="s">
-        <v>1219</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="399" spans="1:3">
@@ -9824,10 +9849,10 @@
         <v>45</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>1236</v>
+        <v>1187</v>
       </c>
       <c r="C399" t="s">
-        <v>1237</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="400" spans="1:3">
@@ -9835,10 +9860,10 @@
         <v>45</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>1315</v>
+        <v>1199</v>
       </c>
       <c r="C400" t="s">
-        <v>1316</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="401" spans="1:3">
@@ -9846,10 +9871,10 @@
         <v>45</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>1333</v>
+        <v>1208</v>
       </c>
       <c r="C401" t="s">
-        <v>1334</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="402" spans="1:3">
@@ -9857,10 +9882,10 @@
         <v>45</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>1357</v>
+        <v>1218</v>
       </c>
       <c r="C402" t="s">
-        <v>1358</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="403" spans="1:3">
@@ -9868,10 +9893,10 @@
         <v>45</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>1365</v>
+        <v>1236</v>
       </c>
       <c r="C403" t="s">
-        <v>1366</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="404" spans="1:3">
@@ -9879,10 +9904,10 @@
         <v>45</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>1367</v>
+        <v>1315</v>
       </c>
       <c r="C404" t="s">
-        <v>1368</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="405" spans="1:3">
@@ -9890,10 +9915,10 @@
         <v>45</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>1370</v>
+        <v>1333</v>
       </c>
       <c r="C405" t="s">
-        <v>1371</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="406" spans="1:3">
@@ -9901,10 +9926,10 @@
         <v>45</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>1378</v>
+        <v>1357</v>
       </c>
       <c r="C406" t="s">
-        <v>1379</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="407" spans="1:3">
@@ -9912,10 +9937,10 @@
         <v>45</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>1406</v>
+        <v>1365</v>
       </c>
       <c r="C407" t="s">
-        <v>1407</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="408" spans="1:3">
@@ -9923,54 +9948,54 @@
         <v>45</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>1424</v>
+        <v>1367</v>
       </c>
       <c r="C408" t="s">
-        <v>1425</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="409" spans="1:3">
       <c r="A409" t="s">
-        <v>4</v>
-      </c>
-      <c r="B409">
-        <v>1</v>
+        <v>45</v>
+      </c>
+      <c r="B409" s="1" t="s">
+        <v>1370</v>
       </c>
       <c r="C409" t="s">
-        <v>1430</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="410" spans="1:3">
       <c r="A410" t="s">
-        <v>4</v>
-      </c>
-      <c r="B410">
-        <v>2</v>
+        <v>45</v>
+      </c>
+      <c r="B410" s="1" t="s">
+        <v>1378</v>
       </c>
       <c r="C410" t="s">
-        <v>1430</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="411" spans="1:3">
       <c r="A411" t="s">
-        <v>4</v>
-      </c>
-      <c r="B411">
-        <v>5</v>
+        <v>45</v>
+      </c>
+      <c r="B411" s="1" t="s">
+        <v>1406</v>
       </c>
       <c r="C411" t="s">
-        <v>1459</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="412" spans="1:3">
       <c r="A412" t="s">
-        <v>4</v>
-      </c>
-      <c r="B412">
-        <v>6</v>
+        <v>45</v>
+      </c>
+      <c r="B412" s="1" t="s">
+        <v>1424</v>
       </c>
       <c r="C412" t="s">
-        <v>1466</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="413" spans="1:3">
@@ -9978,65 +10003,65 @@
         <v>4</v>
       </c>
       <c r="B413">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C413" t="s">
-        <v>1473</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="414" spans="1:3">
       <c r="A414" t="s">
         <v>4</v>
       </c>
-      <c r="B414" t="s">
-        <v>394</v>
+      <c r="B414">
+        <v>2</v>
       </c>
       <c r="C414" t="s">
-        <v>396</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="415" spans="1:3">
       <c r="A415" t="s">
-        <v>31</v>
-      </c>
-      <c r="B415" t="s">
-        <v>32</v>
+        <v>4</v>
+      </c>
+      <c r="B415">
+        <v>5</v>
       </c>
       <c r="C415" t="s">
-        <v>33</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="416" spans="1:3">
       <c r="A416" t="s">
-        <v>31</v>
-      </c>
-      <c r="B416" t="s">
-        <v>55</v>
+        <v>4</v>
+      </c>
+      <c r="B416">
+        <v>6</v>
       </c>
       <c r="C416" t="s">
-        <v>57</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="417" spans="1:3">
       <c r="A417" t="s">
-        <v>31</v>
-      </c>
-      <c r="B417" t="s">
-        <v>173</v>
+        <v>4</v>
+      </c>
+      <c r="B417">
+        <v>7</v>
       </c>
       <c r="C417" t="s">
-        <v>174</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="418" spans="1:3">
       <c r="A418" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="B418" t="s">
-        <v>449</v>
+        <v>394</v>
       </c>
       <c r="C418" t="s">
-        <v>450</v>
+        <v>396</v>
       </c>
     </row>
     <row r="419" spans="1:3">
@@ -10044,10 +10069,10 @@
         <v>31</v>
       </c>
       <c r="B419" t="s">
-        <v>472</v>
+        <v>32</v>
       </c>
       <c r="C419" t="s">
-        <v>473</v>
+        <v>33</v>
       </c>
     </row>
     <row r="420" spans="1:3">
@@ -10055,10 +10080,10 @@
         <v>31</v>
       </c>
       <c r="B420" t="s">
-        <v>502</v>
+        <v>55</v>
       </c>
       <c r="C420" t="s">
-        <v>503</v>
+        <v>57</v>
       </c>
     </row>
     <row r="421" spans="1:3">
@@ -10066,10 +10091,10 @@
         <v>31</v>
       </c>
       <c r="B421" t="s">
-        <v>561</v>
+        <v>173</v>
       </c>
       <c r="C421" t="s">
-        <v>562</v>
+        <v>174</v>
       </c>
     </row>
     <row r="422" spans="1:3">
@@ -10077,10 +10102,10 @@
         <v>31</v>
       </c>
       <c r="B422" t="s">
-        <v>572</v>
+        <v>449</v>
       </c>
       <c r="C422" t="s">
-        <v>573</v>
+        <v>450</v>
       </c>
     </row>
     <row r="423" spans="1:3">
@@ -10088,10 +10113,10 @@
         <v>31</v>
       </c>
       <c r="B423" t="s">
-        <v>676</v>
+        <v>472</v>
       </c>
       <c r="C423" t="s">
-        <v>677</v>
+        <v>473</v>
       </c>
     </row>
     <row r="424" spans="1:3">
@@ -10099,10 +10124,10 @@
         <v>31</v>
       </c>
       <c r="B424" t="s">
-        <v>31</v>
+        <v>502</v>
       </c>
       <c r="C424" t="s">
-        <v>811</v>
+        <v>503</v>
       </c>
     </row>
     <row r="425" spans="1:3">
@@ -10110,10 +10135,10 @@
         <v>31</v>
       </c>
       <c r="B425" t="s">
-        <v>831</v>
+        <v>561</v>
       </c>
       <c r="C425" t="s">
-        <v>832</v>
+        <v>562</v>
       </c>
     </row>
     <row r="426" spans="1:3">
@@ -10121,10 +10146,10 @@
         <v>31</v>
       </c>
       <c r="B426" t="s">
-        <v>847</v>
+        <v>572</v>
       </c>
       <c r="C426" t="s">
-        <v>848</v>
+        <v>573</v>
       </c>
     </row>
     <row r="427" spans="1:3">
@@ -10132,10 +10157,10 @@
         <v>31</v>
       </c>
       <c r="B427" t="s">
-        <v>1051</v>
+        <v>676</v>
       </c>
       <c r="C427" t="s">
-        <v>503</v>
+        <v>677</v>
       </c>
     </row>
     <row r="428" spans="1:3">
@@ -10143,10 +10168,10 @@
         <v>31</v>
       </c>
       <c r="B428" t="s">
-        <v>1100</v>
+        <v>31</v>
       </c>
       <c r="C428" t="s">
-        <v>1101</v>
+        <v>811</v>
       </c>
     </row>
     <row r="429" spans="1:3">
@@ -10154,10 +10179,10 @@
         <v>31</v>
       </c>
       <c r="B429" t="s">
-        <v>1138</v>
+        <v>831</v>
       </c>
       <c r="C429" t="s">
-        <v>1139</v>
+        <v>832</v>
       </c>
     </row>
     <row r="430" spans="1:3">
@@ -10165,10 +10190,10 @@
         <v>31</v>
       </c>
       <c r="B430" t="s">
-        <v>1264</v>
+        <v>847</v>
       </c>
       <c r="C430" t="s">
-        <v>1265</v>
+        <v>848</v>
       </c>
     </row>
     <row r="431" spans="1:3">
@@ -10176,10 +10201,10 @@
         <v>31</v>
       </c>
       <c r="B431" t="s">
-        <v>1295</v>
+        <v>1051</v>
       </c>
       <c r="C431" t="s">
-        <v>1296</v>
+        <v>503</v>
       </c>
     </row>
     <row r="432" spans="1:3">
@@ -10187,10 +10212,10 @@
         <v>31</v>
       </c>
       <c r="B432" t="s">
-        <v>1343</v>
+        <v>1100</v>
       </c>
       <c r="C432" t="s">
-        <v>1344</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="433" spans="1:3">
@@ -10198,54 +10223,54 @@
         <v>31</v>
       </c>
       <c r="B433" t="s">
-        <v>1374</v>
+        <v>1138</v>
       </c>
       <c r="C433" t="s">
-        <v>1376</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="434" spans="1:3">
       <c r="A434" t="s">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="B434" t="s">
-        <v>83</v>
+        <v>1264</v>
       </c>
       <c r="C434" t="s">
-        <v>84</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="435" spans="1:3">
       <c r="A435" t="s">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="B435" t="s">
-        <v>134</v>
+        <v>1295</v>
       </c>
       <c r="C435" t="s">
-        <v>135</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="436" spans="1:3">
       <c r="A436" t="s">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="B436" t="s">
-        <v>217</v>
+        <v>1343</v>
       </c>
       <c r="C436" t="s">
-        <v>218</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="437" spans="1:3">
       <c r="A437" t="s">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="B437" t="s">
-        <v>341</v>
+        <v>1374</v>
       </c>
       <c r="C437" t="s">
-        <v>135</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="438" spans="1:3">
@@ -10253,10 +10278,10 @@
         <v>82</v>
       </c>
       <c r="B438" t="s">
-        <v>397</v>
+        <v>83</v>
       </c>
       <c r="C438" t="s">
-        <v>398</v>
+        <v>84</v>
       </c>
     </row>
     <row r="439" spans="1:3">
@@ -10264,7 +10289,7 @@
         <v>82</v>
       </c>
       <c r="B439" t="s">
-        <v>442</v>
+        <v>134</v>
       </c>
       <c r="C439" t="s">
         <v>135</v>
@@ -10275,10 +10300,10 @@
         <v>82</v>
       </c>
       <c r="B440" t="s">
-        <v>523</v>
+        <v>217</v>
       </c>
       <c r="C440" t="s">
-        <v>524</v>
+        <v>218</v>
       </c>
     </row>
     <row r="441" spans="1:3">
@@ -10286,10 +10311,10 @@
         <v>82</v>
       </c>
       <c r="B441" t="s">
-        <v>547</v>
+        <v>341</v>
       </c>
       <c r="C441" t="s">
-        <v>548</v>
+        <v>135</v>
       </c>
     </row>
     <row r="442" spans="1:3">
@@ -10297,10 +10322,10 @@
         <v>82</v>
       </c>
       <c r="B442" t="s">
-        <v>584</v>
+        <v>397</v>
       </c>
       <c r="C442" t="s">
-        <v>585</v>
+        <v>398</v>
       </c>
     </row>
     <row r="443" spans="1:3">
@@ -10308,10 +10333,10 @@
         <v>82</v>
       </c>
       <c r="B443" t="s">
-        <v>586</v>
+        <v>442</v>
       </c>
       <c r="C443" t="s">
-        <v>587</v>
+        <v>135</v>
       </c>
     </row>
     <row r="444" spans="1:3">
@@ -10319,10 +10344,10 @@
         <v>82</v>
       </c>
       <c r="B444" t="s">
-        <v>598</v>
+        <v>523</v>
       </c>
       <c r="C444" t="s">
-        <v>599</v>
+        <v>524</v>
       </c>
     </row>
     <row r="445" spans="1:3">
@@ -10330,10 +10355,10 @@
         <v>82</v>
       </c>
       <c r="B445" t="s">
-        <v>610</v>
+        <v>547</v>
       </c>
       <c r="C445" t="s">
-        <v>611</v>
+        <v>548</v>
       </c>
     </row>
     <row r="446" spans="1:3">
@@ -10341,10 +10366,10 @@
         <v>82</v>
       </c>
       <c r="B446" t="s">
-        <v>644</v>
+        <v>584</v>
       </c>
       <c r="C446" t="s">
-        <v>645</v>
+        <v>585</v>
       </c>
     </row>
     <row r="447" spans="1:3">
@@ -10352,10 +10377,10 @@
         <v>82</v>
       </c>
       <c r="B447" t="s">
-        <v>831</v>
+        <v>586</v>
       </c>
       <c r="C447" t="s">
-        <v>135</v>
+        <v>587</v>
       </c>
     </row>
     <row r="448" spans="1:3">
@@ -10363,10 +10388,10 @@
         <v>82</v>
       </c>
       <c r="B448" t="s">
-        <v>853</v>
+        <v>598</v>
       </c>
       <c r="C448" t="s">
-        <v>854</v>
+        <v>599</v>
       </c>
     </row>
     <row r="449" spans="1:3">
@@ -10374,10 +10399,10 @@
         <v>82</v>
       </c>
       <c r="B449" t="s">
-        <v>855</v>
+        <v>610</v>
       </c>
       <c r="C449" t="s">
-        <v>856</v>
+        <v>611</v>
       </c>
     </row>
     <row r="450" spans="1:3">
@@ -10385,10 +10410,10 @@
         <v>82</v>
       </c>
       <c r="B450" t="s">
-        <v>891</v>
+        <v>644</v>
       </c>
       <c r="C450" t="s">
-        <v>892</v>
+        <v>645</v>
       </c>
     </row>
     <row r="451" spans="1:3">
@@ -10396,10 +10421,10 @@
         <v>82</v>
       </c>
       <c r="B451" t="s">
-        <v>1022</v>
+        <v>831</v>
       </c>
       <c r="C451" t="s">
-        <v>1023</v>
+        <v>135</v>
       </c>
     </row>
     <row r="452" spans="1:3">
@@ -10407,10 +10432,10 @@
         <v>82</v>
       </c>
       <c r="B452" t="s">
-        <v>1024</v>
+        <v>853</v>
       </c>
       <c r="C452" t="s">
-        <v>1025</v>
+        <v>854</v>
       </c>
     </row>
     <row r="453" spans="1:3">
@@ -10418,10 +10443,10 @@
         <v>82</v>
       </c>
       <c r="B453" t="s">
-        <v>1034</v>
+        <v>855</v>
       </c>
       <c r="C453" t="s">
-        <v>1035</v>
+        <v>856</v>
       </c>
     </row>
     <row r="454" spans="1:3">
@@ -10429,10 +10454,10 @@
         <v>82</v>
       </c>
       <c r="B454" t="s">
-        <v>1146</v>
+        <v>891</v>
       </c>
       <c r="C454" t="s">
-        <v>1147</v>
+        <v>892</v>
       </c>
     </row>
     <row r="455" spans="1:3">
@@ -10440,10 +10465,10 @@
         <v>82</v>
       </c>
       <c r="B455" t="s">
-        <v>1279</v>
+        <v>1022</v>
       </c>
       <c r="C455" t="s">
-        <v>1280</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="456" spans="1:3">
@@ -10451,10 +10476,10 @@
         <v>82</v>
       </c>
       <c r="B456" t="s">
-        <v>1281</v>
+        <v>1024</v>
       </c>
       <c r="C456" t="s">
-        <v>1282</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="457" spans="1:3">
@@ -10462,54 +10487,54 @@
         <v>82</v>
       </c>
       <c r="B457" t="s">
-        <v>1372</v>
+        <v>1034</v>
       </c>
       <c r="C457" t="s">
-        <v>1373</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="458" spans="1:3">
       <c r="A458" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="B458" t="s">
-        <v>114</v>
+        <v>1146</v>
       </c>
       <c r="C458" t="s">
-        <v>115</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="459" spans="1:3">
       <c r="A459" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="B459" t="s">
-        <v>136</v>
+        <v>1279</v>
       </c>
       <c r="C459" t="s">
-        <v>137</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="460" spans="1:3">
       <c r="A460" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="B460" t="s">
-        <v>219</v>
+        <v>1281</v>
       </c>
       <c r="C460" t="s">
-        <v>220</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="461" spans="1:3">
       <c r="A461" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="B461" t="s">
-        <v>251</v>
+        <v>1372</v>
       </c>
       <c r="C461" t="s">
-        <v>252</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="462" spans="1:3">
@@ -10517,10 +10542,10 @@
         <v>113</v>
       </c>
       <c r="B462" t="s">
-        <v>267</v>
+        <v>114</v>
       </c>
       <c r="C462" t="s">
-        <v>268</v>
+        <v>115</v>
       </c>
     </row>
     <row r="463" spans="1:3">
@@ -10528,10 +10553,10 @@
         <v>113</v>
       </c>
       <c r="B463" t="s">
-        <v>364</v>
+        <v>136</v>
       </c>
       <c r="C463" t="s">
-        <v>365</v>
+        <v>137</v>
       </c>
     </row>
     <row r="464" spans="1:3">
@@ -10539,10 +10564,10 @@
         <v>113</v>
       </c>
       <c r="B464" t="s">
-        <v>426</v>
+        <v>219</v>
       </c>
       <c r="C464" t="s">
-        <v>427</v>
+        <v>220</v>
       </c>
     </row>
     <row r="465" spans="1:3">
@@ -10550,10 +10575,10 @@
         <v>113</v>
       </c>
       <c r="B465" t="s">
-        <v>624</v>
+        <v>251</v>
       </c>
       <c r="C465" t="s">
-        <v>625</v>
+        <v>252</v>
       </c>
     </row>
     <row r="466" spans="1:3">
@@ -10561,10 +10586,10 @@
         <v>113</v>
       </c>
       <c r="B466" t="s">
-        <v>626</v>
+        <v>267</v>
       </c>
       <c r="C466" t="s">
-        <v>627</v>
+        <v>268</v>
       </c>
     </row>
     <row r="467" spans="1:3">
@@ -10572,10 +10597,10 @@
         <v>113</v>
       </c>
       <c r="B467" t="s">
-        <v>630</v>
+        <v>364</v>
       </c>
       <c r="C467" t="s">
-        <v>631</v>
+        <v>365</v>
       </c>
     </row>
     <row r="468" spans="1:3">
@@ -10583,10 +10608,10 @@
         <v>113</v>
       </c>
       <c r="B468" t="s">
-        <v>650</v>
+        <v>426</v>
       </c>
       <c r="C468" t="s">
-        <v>651</v>
+        <v>427</v>
       </c>
     </row>
     <row r="469" spans="1:3">
@@ -10594,10 +10619,10 @@
         <v>113</v>
       </c>
       <c r="B469" t="s">
-        <v>747</v>
+        <v>624</v>
       </c>
       <c r="C469" t="s">
-        <v>748</v>
+        <v>625</v>
       </c>
     </row>
     <row r="470" spans="1:3">
@@ -10605,10 +10630,10 @@
         <v>113</v>
       </c>
       <c r="B470" t="s">
-        <v>757</v>
+        <v>626</v>
       </c>
       <c r="C470" t="s">
-        <v>758</v>
+        <v>627</v>
       </c>
     </row>
     <row r="471" spans="1:3">
@@ -10616,10 +10641,10 @@
         <v>113</v>
       </c>
       <c r="B471" t="s">
-        <v>763</v>
+        <v>630</v>
       </c>
       <c r="C471" t="s">
-        <v>764</v>
+        <v>631</v>
       </c>
     </row>
     <row r="472" spans="1:3">
@@ -10627,10 +10652,10 @@
         <v>113</v>
       </c>
       <c r="B472" t="s">
-        <v>780</v>
+        <v>650</v>
       </c>
       <c r="C472" t="s">
-        <v>781</v>
+        <v>651</v>
       </c>
     </row>
     <row r="473" spans="1:3">
@@ -10638,10 +10663,10 @@
         <v>113</v>
       </c>
       <c r="B473" t="s">
-        <v>802</v>
+        <v>747</v>
       </c>
       <c r="C473" t="s">
-        <v>803</v>
+        <v>748</v>
       </c>
     </row>
     <row r="474" spans="1:3">
@@ -10649,10 +10674,10 @@
         <v>113</v>
       </c>
       <c r="B474" t="s">
-        <v>804</v>
+        <v>757</v>
       </c>
       <c r="C474" t="s">
-        <v>805</v>
+        <v>758</v>
       </c>
     </row>
     <row r="475" spans="1:3">
@@ -10660,10 +10685,10 @@
         <v>113</v>
       </c>
       <c r="B475" t="s">
-        <v>809</v>
+        <v>763</v>
       </c>
       <c r="C475" t="s">
-        <v>810</v>
+        <v>764</v>
       </c>
     </row>
     <row r="476" spans="1:3">
@@ -10671,10 +10696,10 @@
         <v>113</v>
       </c>
       <c r="B476" t="s">
-        <v>940</v>
+        <v>780</v>
       </c>
       <c r="C476" t="s">
-        <v>941</v>
+        <v>781</v>
       </c>
     </row>
     <row r="477" spans="1:3">
@@ -10682,10 +10707,10 @@
         <v>113</v>
       </c>
       <c r="B477" t="s">
-        <v>973</v>
+        <v>802</v>
       </c>
       <c r="C477" t="s">
-        <v>974</v>
+        <v>803</v>
       </c>
     </row>
     <row r="478" spans="1:3">
@@ -10693,10 +10718,10 @@
         <v>113</v>
       </c>
       <c r="B478" t="s">
-        <v>1148</v>
+        <v>804</v>
       </c>
       <c r="C478" t="s">
-        <v>1149</v>
+        <v>805</v>
       </c>
     </row>
     <row r="479" spans="1:3">
@@ -10704,10 +10729,10 @@
         <v>113</v>
       </c>
       <c r="B479" t="s">
-        <v>1193</v>
+        <v>809</v>
       </c>
       <c r="C479" t="s">
-        <v>1194</v>
+        <v>810</v>
       </c>
     </row>
     <row r="480" spans="1:3">
@@ -10715,10 +10740,10 @@
         <v>113</v>
       </c>
       <c r="B480" t="s">
-        <v>1232</v>
+        <v>940</v>
       </c>
       <c r="C480" t="s">
-        <v>1233</v>
+        <v>941</v>
       </c>
     </row>
     <row r="481" spans="1:3">
@@ -10726,10 +10751,10 @@
         <v>113</v>
       </c>
       <c r="B481" t="s">
-        <v>1252</v>
+        <v>973</v>
       </c>
       <c r="C481" t="s">
-        <v>1253</v>
+        <v>974</v>
       </c>
     </row>
     <row r="482" spans="1:3">
@@ -10737,54 +10762,54 @@
         <v>113</v>
       </c>
       <c r="B482" t="s">
-        <v>1267</v>
+        <v>1148</v>
       </c>
       <c r="C482" t="s">
-        <v>1268</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="483" spans="1:3">
       <c r="A483" t="s">
-        <v>24</v>
+        <v>113</v>
       </c>
       <c r="B483" t="s">
-        <v>25</v>
+        <v>1193</v>
       </c>
       <c r="C483" t="s">
-        <v>26</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="484" spans="1:3">
       <c r="A484" t="s">
-        <v>24</v>
+        <v>113</v>
       </c>
       <c r="B484" t="s">
-        <v>27</v>
+        <v>1232</v>
       </c>
       <c r="C484" t="s">
-        <v>28</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="485" spans="1:3">
       <c r="A485" t="s">
-        <v>24</v>
+        <v>113</v>
       </c>
       <c r="B485" t="s">
-        <v>120</v>
+        <v>1252</v>
       </c>
       <c r="C485" t="s">
-        <v>121</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="486" spans="1:3">
       <c r="A486" t="s">
-        <v>24</v>
+        <v>113</v>
       </c>
       <c r="B486" t="s">
-        <v>175</v>
+        <v>1267</v>
       </c>
       <c r="C486" t="s">
-        <v>176</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="487" spans="1:3">
@@ -10792,10 +10817,10 @@
         <v>24</v>
       </c>
       <c r="B487" t="s">
-        <v>196</v>
+        <v>25</v>
       </c>
       <c r="C487" t="s">
-        <v>197</v>
+        <v>26</v>
       </c>
     </row>
     <row r="488" spans="1:3">
@@ -10803,10 +10828,10 @@
         <v>24</v>
       </c>
       <c r="B488" t="s">
-        <v>221</v>
+        <v>27</v>
       </c>
       <c r="C488" t="s">
-        <v>222</v>
+        <v>28</v>
       </c>
     </row>
     <row r="489" spans="1:3">
@@ -10814,10 +10839,10 @@
         <v>24</v>
       </c>
       <c r="B489" t="s">
-        <v>227</v>
+        <v>120</v>
       </c>
       <c r="C489" t="s">
-        <v>228</v>
+        <v>121</v>
       </c>
     </row>
     <row r="490" spans="1:3">
@@ -10825,10 +10850,10 @@
         <v>24</v>
       </c>
       <c r="B490" t="s">
-        <v>283</v>
+        <v>175</v>
       </c>
       <c r="C490" t="s">
-        <v>284</v>
+        <v>176</v>
       </c>
     </row>
     <row r="491" spans="1:3">
@@ -10836,10 +10861,10 @@
         <v>24</v>
       </c>
       <c r="B491" t="s">
-        <v>346</v>
+        <v>196</v>
       </c>
       <c r="C491" t="s">
-        <v>347</v>
+        <v>197</v>
       </c>
     </row>
     <row r="492" spans="1:3">
@@ -10847,10 +10872,10 @@
         <v>24</v>
       </c>
       <c r="B492" t="s">
-        <v>369</v>
+        <v>221</v>
       </c>
       <c r="C492" t="s">
-        <v>370</v>
+        <v>222</v>
       </c>
     </row>
     <row r="493" spans="1:3">
@@ -10858,10 +10883,10 @@
         <v>24</v>
       </c>
       <c r="B493" t="s">
-        <v>464</v>
+        <v>227</v>
       </c>
       <c r="C493" t="s">
-        <v>465</v>
+        <v>228</v>
       </c>
     </row>
     <row r="494" spans="1:3">
@@ -10869,10 +10894,10 @@
         <v>24</v>
       </c>
       <c r="B494" t="s">
-        <v>494</v>
+        <v>283</v>
       </c>
       <c r="C494" t="s">
-        <v>495</v>
+        <v>284</v>
       </c>
     </row>
     <row r="495" spans="1:3">
@@ -10880,10 +10905,10 @@
         <v>24</v>
       </c>
       <c r="B495" t="s">
-        <v>545</v>
+        <v>346</v>
       </c>
       <c r="C495" t="s">
-        <v>546</v>
+        <v>347</v>
       </c>
     </row>
     <row r="496" spans="1:3">
@@ -10891,10 +10916,10 @@
         <v>24</v>
       </c>
       <c r="B496" t="s">
-        <v>605</v>
+        <v>369</v>
       </c>
       <c r="C496" t="s">
-        <v>606</v>
+        <v>370</v>
       </c>
     </row>
     <row r="497" spans="1:3">
@@ -10902,10 +10927,10 @@
         <v>24</v>
       </c>
       <c r="B497" t="s">
-        <v>618</v>
+        <v>464</v>
       </c>
       <c r="C497" t="s">
-        <v>619</v>
+        <v>465</v>
       </c>
     </row>
     <row r="498" spans="1:3">
@@ -10913,10 +10938,10 @@
         <v>24</v>
       </c>
       <c r="B498" t="s">
-        <v>662</v>
+        <v>494</v>
       </c>
       <c r="C498" t="s">
-        <v>663</v>
+        <v>495</v>
       </c>
     </row>
     <row r="499" spans="1:3">
@@ -10924,10 +10949,10 @@
         <v>24</v>
       </c>
       <c r="B499" t="s">
-        <v>670</v>
+        <v>545</v>
       </c>
       <c r="C499" t="s">
-        <v>671</v>
+        <v>546</v>
       </c>
     </row>
     <row r="500" spans="1:3">
@@ -10935,10 +10960,10 @@
         <v>24</v>
       </c>
       <c r="B500" t="s">
-        <v>903</v>
+        <v>605</v>
       </c>
       <c r="C500" t="s">
-        <v>904</v>
+        <v>606</v>
       </c>
     </row>
     <row r="501" spans="1:3">
@@ -10946,10 +10971,10 @@
         <v>24</v>
       </c>
       <c r="B501" t="s">
-        <v>986</v>
+        <v>618</v>
       </c>
       <c r="C501" t="s">
-        <v>987</v>
+        <v>619</v>
       </c>
     </row>
     <row r="502" spans="1:3">
@@ -10957,10 +10982,10 @@
         <v>24</v>
       </c>
       <c r="B502" t="s">
-        <v>992</v>
+        <v>662</v>
       </c>
       <c r="C502" t="s">
-        <v>993</v>
+        <v>663</v>
       </c>
     </row>
     <row r="503" spans="1:3">
@@ -10968,10 +10993,10 @@
         <v>24</v>
       </c>
       <c r="B503" t="s">
-        <v>1006</v>
+        <v>670</v>
       </c>
       <c r="C503" t="s">
-        <v>1007</v>
+        <v>671</v>
       </c>
     </row>
     <row r="504" spans="1:3">
@@ -10979,10 +11004,10 @@
         <v>24</v>
       </c>
       <c r="B504" t="s">
-        <v>1111</v>
+        <v>903</v>
       </c>
       <c r="C504" t="s">
-        <v>1112</v>
+        <v>904</v>
       </c>
     </row>
     <row r="505" spans="1:3">
@@ -10990,10 +11015,10 @@
         <v>24</v>
       </c>
       <c r="B505" t="s">
-        <v>1132</v>
+        <v>986</v>
       </c>
       <c r="C505" t="s">
-        <v>1133</v>
+        <v>987</v>
       </c>
     </row>
     <row r="506" spans="1:3">
@@ -11001,10 +11026,10 @@
         <v>24</v>
       </c>
       <c r="B506" t="s">
-        <v>1202</v>
+        <v>992</v>
       </c>
       <c r="C506" t="s">
-        <v>1203</v>
+        <v>993</v>
       </c>
     </row>
     <row r="507" spans="1:3">
@@ -11012,10 +11037,10 @@
         <v>24</v>
       </c>
       <c r="B507" t="s">
-        <v>1234</v>
+        <v>1006</v>
       </c>
       <c r="C507" t="s">
-        <v>1235</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="508" spans="1:3">
@@ -11023,10 +11048,10 @@
         <v>24</v>
       </c>
       <c r="B508" t="s">
-        <v>1248</v>
+        <v>1111</v>
       </c>
       <c r="C508" t="s">
-        <v>1249</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="509" spans="1:3">
@@ -11034,10 +11059,10 @@
         <v>24</v>
       </c>
       <c r="B509" t="s">
-        <v>1260</v>
+        <v>1132</v>
       </c>
       <c r="C509" t="s">
-        <v>1261</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="510" spans="1:3">
@@ -11045,10 +11070,10 @@
         <v>24</v>
       </c>
       <c r="B510" t="s">
-        <v>1304</v>
+        <v>1202</v>
       </c>
       <c r="C510" t="s">
-        <v>1305</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="511" spans="1:3">
@@ -11056,10 +11081,10 @@
         <v>24</v>
       </c>
       <c r="B511" t="s">
-        <v>1321</v>
+        <v>1234</v>
       </c>
       <c r="C511" t="s">
-        <v>1322</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="512" spans="1:3">
@@ -11067,10 +11092,10 @@
         <v>24</v>
       </c>
       <c r="B512" t="s">
-        <v>1323</v>
+        <v>1248</v>
       </c>
       <c r="C512" t="s">
-        <v>1324</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="513" spans="1:3">
@@ -11078,10 +11103,10 @@
         <v>24</v>
       </c>
       <c r="B513" t="s">
-        <v>1325</v>
+        <v>1260</v>
       </c>
       <c r="C513" t="s">
-        <v>1326</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="514" spans="1:3">
@@ -11089,10 +11114,10 @@
         <v>24</v>
       </c>
       <c r="B514" t="s">
-        <v>1327</v>
+        <v>1304</v>
       </c>
       <c r="C514" t="s">
-        <v>1328</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="515" spans="1:3">
@@ -11100,109 +11125,109 @@
         <v>24</v>
       </c>
       <c r="B515" t="s">
-        <v>1380</v>
+        <v>1321</v>
       </c>
       <c r="C515" t="s">
-        <v>1381</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="516" spans="1:3">
       <c r="A516" t="s">
-        <v>5</v>
-      </c>
-      <c r="B516">
-        <v>1</v>
+        <v>24</v>
+      </c>
+      <c r="B516" t="s">
+        <v>1323</v>
       </c>
       <c r="C516" t="s">
-        <v>1431</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="517" spans="1:3">
       <c r="A517" t="s">
-        <v>5</v>
-      </c>
-      <c r="B517">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="B517" t="s">
+        <v>1325</v>
       </c>
       <c r="C517" t="s">
-        <v>1437</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="518" spans="1:3">
       <c r="A518" t="s">
-        <v>5</v>
-      </c>
-      <c r="B518">
-        <v>3</v>
+        <v>24</v>
+      </c>
+      <c r="B518" t="s">
+        <v>1327</v>
       </c>
       <c r="C518" t="s">
-        <v>1445</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="519" spans="1:3">
       <c r="A519" t="s">
-        <v>5</v>
-      </c>
-      <c r="B519">
-        <v>8</v>
+        <v>24</v>
+      </c>
+      <c r="B519" t="s">
+        <v>1380</v>
       </c>
       <c r="C519" t="s">
-        <v>1477</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="520" spans="1:3">
       <c r="A520" t="s">
         <v>5</v>
       </c>
-      <c r="B520" t="s">
-        <v>1341</v>
+      <c r="B520">
+        <v>1</v>
       </c>
       <c r="C520" t="s">
-        <v>1342</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="521" spans="1:3">
       <c r="A521" t="s">
-        <v>530</v>
-      </c>
-      <c r="B521" t="s">
-        <v>531</v>
+        <v>5</v>
+      </c>
+      <c r="B521">
+        <v>2</v>
       </c>
       <c r="C521" t="s">
-        <v>532</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="522" spans="1:3">
       <c r="A522" t="s">
-        <v>530</v>
-      </c>
-      <c r="B522" t="s">
-        <v>977</v>
+        <v>5</v>
+      </c>
+      <c r="B522">
+        <v>3</v>
       </c>
       <c r="C522" t="s">
-        <v>978</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="523" spans="1:3">
       <c r="A523" t="s">
-        <v>530</v>
-      </c>
-      <c r="B523" t="s">
-        <v>979</v>
+        <v>5</v>
+      </c>
+      <c r="B523">
+        <v>8</v>
       </c>
       <c r="C523" t="s">
-        <v>978</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="524" spans="1:3">
       <c r="A524" t="s">
-        <v>530</v>
+        <v>5</v>
       </c>
       <c r="B524" t="s">
-        <v>980</v>
+        <v>1341</v>
       </c>
       <c r="C524" t="s">
-        <v>981</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="525" spans="1:3">
@@ -11210,54 +11235,54 @@
         <v>530</v>
       </c>
       <c r="B525" t="s">
-        <v>1189</v>
+        <v>531</v>
       </c>
       <c r="C525" t="s">
-        <v>1190</v>
+        <v>532</v>
       </c>
     </row>
     <row r="526" spans="1:3">
       <c r="A526" t="s">
-        <v>6</v>
-      </c>
-      <c r="B526">
-        <v>1</v>
+        <v>530</v>
+      </c>
+      <c r="B526" t="s">
+        <v>977</v>
       </c>
       <c r="C526" t="s">
-        <v>1432</v>
+        <v>978</v>
       </c>
     </row>
     <row r="527" spans="1:3">
       <c r="A527" t="s">
-        <v>6</v>
-      </c>
-      <c r="B527">
-        <v>2</v>
+        <v>530</v>
+      </c>
+      <c r="B527" t="s">
+        <v>979</v>
       </c>
       <c r="C527" t="s">
-        <v>1438</v>
+        <v>978</v>
       </c>
     </row>
     <row r="528" spans="1:3">
       <c r="A528" t="s">
-        <v>6</v>
-      </c>
-      <c r="B528">
-        <v>3</v>
+        <v>530</v>
+      </c>
+      <c r="B528" t="s">
+        <v>980</v>
       </c>
       <c r="C528" t="s">
-        <v>1446</v>
+        <v>981</v>
       </c>
     </row>
     <row r="529" spans="1:3">
       <c r="A529" t="s">
-        <v>6</v>
-      </c>
-      <c r="B529">
-        <v>4</v>
+        <v>530</v>
+      </c>
+      <c r="B529" t="s">
+        <v>1189</v>
       </c>
       <c r="C529" t="s">
-        <v>1452</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="530" spans="1:3">
@@ -11265,10 +11290,10 @@
         <v>6</v>
       </c>
       <c r="B530">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C530" t="s">
-        <v>1460</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="531" spans="1:3">
@@ -11276,10 +11301,10 @@
         <v>6</v>
       </c>
       <c r="B531">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C531" t="s">
-        <v>1467</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="532" spans="1:3">
@@ -11287,10 +11312,10 @@
         <v>6</v>
       </c>
       <c r="B532">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C532" t="s">
-        <v>1478</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="533" spans="1:3">
@@ -11298,10 +11323,10 @@
         <v>6</v>
       </c>
       <c r="B533">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C533" t="s">
-        <v>1487</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="534" spans="1:3">
@@ -11309,10 +11334,10 @@
         <v>6</v>
       </c>
       <c r="B534">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C534" t="s">
-        <v>1494</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="535" spans="1:3">
@@ -11320,10 +11345,10 @@
         <v>6</v>
       </c>
       <c r="B535">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="C535" t="s">
-        <v>1527</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="536" spans="1:3">
@@ -11331,10 +11356,10 @@
         <v>6</v>
       </c>
       <c r="B536">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="C536" t="s">
-        <v>1528</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="537" spans="1:3">
@@ -11342,10 +11367,10 @@
         <v>6</v>
       </c>
       <c r="B537">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="C537" t="s">
-        <v>1533</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="538" spans="1:3">
@@ -11353,10 +11378,10 @@
         <v>6</v>
       </c>
       <c r="B538">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C538" t="s">
-        <v>1536</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="539" spans="1:3">
@@ -11364,10 +11389,10 @@
         <v>6</v>
       </c>
       <c r="B539">
-        <v>118</v>
+        <v>25</v>
       </c>
       <c r="C539" t="s">
-        <v>1628</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="540" spans="1:3">
@@ -11375,54 +11400,54 @@
         <v>6</v>
       </c>
       <c r="B540">
-        <v>120</v>
+        <v>26</v>
       </c>
       <c r="C540" t="s">
-        <v>1631</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="541" spans="1:3">
       <c r="A541" t="s">
         <v>6</v>
       </c>
-      <c r="B541" t="s">
-        <v>14</v>
+      <c r="B541">
+        <v>28</v>
       </c>
       <c r="C541" t="s">
-        <v>15</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="542" spans="1:3">
       <c r="A542" t="s">
         <v>6</v>
       </c>
-      <c r="B542" t="s">
-        <v>67</v>
+      <c r="B542">
+        <v>29</v>
       </c>
       <c r="C542" t="s">
-        <v>68</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="543" spans="1:3">
       <c r="A543" t="s">
         <v>6</v>
       </c>
-      <c r="B543" t="s">
-        <v>72</v>
+      <c r="B543">
+        <v>118</v>
       </c>
       <c r="C543" t="s">
-        <v>73</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="544" spans="1:3">
       <c r="A544" t="s">
         <v>6</v>
       </c>
-      <c r="B544" t="s">
-        <v>132</v>
+      <c r="B544">
+        <v>120</v>
       </c>
       <c r="C544" t="s">
-        <v>133</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="545" spans="1:3">
@@ -11430,10 +11455,10 @@
         <v>6</v>
       </c>
       <c r="B545" t="s">
-        <v>163</v>
+        <v>14</v>
       </c>
       <c r="C545" t="s">
-        <v>164</v>
+        <v>15</v>
       </c>
     </row>
     <row r="546" spans="1:3">
@@ -11441,10 +11466,10 @@
         <v>6</v>
       </c>
       <c r="B546" t="s">
-        <v>165</v>
+        <v>67</v>
       </c>
       <c r="C546" t="s">
-        <v>166</v>
+        <v>68</v>
       </c>
     </row>
     <row r="547" spans="1:3">
@@ -11452,10 +11477,10 @@
         <v>6</v>
       </c>
       <c r="B547" t="s">
-        <v>167</v>
+        <v>72</v>
       </c>
       <c r="C547" t="s">
-        <v>168</v>
+        <v>73</v>
       </c>
     </row>
     <row r="548" spans="1:3">
@@ -11463,10 +11488,10 @@
         <v>6</v>
       </c>
       <c r="B548" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="C548" t="s">
-        <v>170</v>
+        <v>133</v>
       </c>
     </row>
     <row r="549" spans="1:3">
@@ -11474,10 +11499,10 @@
         <v>6</v>
       </c>
       <c r="B549" t="s">
-        <v>287</v>
+        <v>163</v>
       </c>
       <c r="C549" t="s">
-        <v>288</v>
+        <v>164</v>
       </c>
     </row>
     <row r="550" spans="1:3">
@@ -11485,10 +11510,10 @@
         <v>6</v>
       </c>
       <c r="B550" t="s">
-        <v>490</v>
+        <v>165</v>
       </c>
       <c r="C550" t="s">
-        <v>491</v>
+        <v>166</v>
       </c>
     </row>
     <row r="551" spans="1:3">
@@ -11496,10 +11521,10 @@
         <v>6</v>
       </c>
       <c r="B551" t="s">
-        <v>511</v>
+        <v>167</v>
       </c>
       <c r="C551" t="s">
-        <v>512</v>
+        <v>168</v>
       </c>
     </row>
     <row r="552" spans="1:3">
@@ -11507,10 +11532,10 @@
         <v>6</v>
       </c>
       <c r="B552" t="s">
-        <v>662</v>
+        <v>169</v>
       </c>
       <c r="C552" t="s">
-        <v>664</v>
+        <v>170</v>
       </c>
     </row>
     <row r="553" spans="1:3">
@@ -11518,10 +11543,10 @@
         <v>6</v>
       </c>
       <c r="B553" t="s">
-        <v>694</v>
+        <v>287</v>
       </c>
       <c r="C553" t="s">
-        <v>695</v>
+        <v>288</v>
       </c>
     </row>
     <row r="554" spans="1:3">
@@ -11529,10 +11554,10 @@
         <v>6</v>
       </c>
       <c r="B554" t="s">
-        <v>715</v>
+        <v>490</v>
       </c>
       <c r="C554" t="s">
-        <v>716</v>
+        <v>491</v>
       </c>
     </row>
     <row r="555" spans="1:3">
@@ -11540,10 +11565,10 @@
         <v>6</v>
       </c>
       <c r="B555" t="s">
-        <v>721</v>
+        <v>511</v>
       </c>
       <c r="C555" t="s">
-        <v>722</v>
+        <v>512</v>
       </c>
     </row>
     <row r="556" spans="1:3">
@@ -11551,10 +11576,10 @@
         <v>6</v>
       </c>
       <c r="B556" t="s">
-        <v>741</v>
+        <v>662</v>
       </c>
       <c r="C556" t="s">
-        <v>742</v>
+        <v>664</v>
       </c>
     </row>
     <row r="557" spans="1:3">
@@ -11562,10 +11587,10 @@
         <v>6</v>
       </c>
       <c r="B557" t="s">
-        <v>743</v>
+        <v>694</v>
       </c>
       <c r="C557" t="s">
-        <v>744</v>
+        <v>695</v>
       </c>
     </row>
     <row r="558" spans="1:3">
@@ -11573,10 +11598,10 @@
         <v>6</v>
       </c>
       <c r="B558" t="s">
-        <v>754</v>
+        <v>715</v>
       </c>
       <c r="C558" t="s">
-        <v>756</v>
+        <v>716</v>
       </c>
     </row>
     <row r="559" spans="1:3">
@@ -11584,10 +11609,10 @@
         <v>6</v>
       </c>
       <c r="B559" t="s">
-        <v>942</v>
+        <v>721</v>
       </c>
       <c r="C559" t="s">
-        <v>943</v>
+        <v>722</v>
       </c>
     </row>
     <row r="560" spans="1:3">
@@ -11595,10 +11620,10 @@
         <v>6</v>
       </c>
       <c r="B560" t="s">
-        <v>1018</v>
+        <v>741</v>
       </c>
       <c r="C560" t="s">
-        <v>1020</v>
+        <v>742</v>
       </c>
     </row>
     <row r="561" spans="1:3">
@@ -11606,10 +11631,10 @@
         <v>6</v>
       </c>
       <c r="B561" t="s">
-        <v>1104</v>
+        <v>743</v>
       </c>
       <c r="C561" t="s">
-        <v>1105</v>
+        <v>744</v>
       </c>
     </row>
     <row r="562" spans="1:3">
@@ -11617,10 +11642,10 @@
         <v>6</v>
       </c>
       <c r="B562" t="s">
-        <v>1273</v>
+        <v>754</v>
       </c>
       <c r="C562" t="s">
-        <v>1274</v>
+        <v>756</v>
       </c>
     </row>
     <row r="563" spans="1:3">
@@ -11628,10 +11653,10 @@
         <v>6</v>
       </c>
       <c r="B563" t="s">
-        <v>1288</v>
+        <v>942</v>
       </c>
       <c r="C563" t="s">
-        <v>1290</v>
+        <v>943</v>
       </c>
     </row>
     <row r="564" spans="1:3">
@@ -11639,10 +11664,10 @@
         <v>6</v>
       </c>
       <c r="B564" t="s">
-        <v>1297</v>
+        <v>1018</v>
       </c>
       <c r="C564" t="s">
-        <v>1298</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="565" spans="1:3">
@@ -11650,54 +11675,54 @@
         <v>6</v>
       </c>
       <c r="B565" t="s">
-        <v>1301</v>
+        <v>1104</v>
       </c>
       <c r="C565" t="s">
-        <v>1303</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="566" spans="1:3">
       <c r="A566" t="s">
-        <v>9</v>
-      </c>
-      <c r="B566">
         <v>6</v>
       </c>
+      <c r="B566" t="s">
+        <v>1273</v>
+      </c>
       <c r="C566" t="s">
-        <v>1468</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="567" spans="1:3">
       <c r="A567" t="s">
-        <v>9</v>
-      </c>
-      <c r="B567">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="B567" t="s">
+        <v>1288</v>
       </c>
       <c r="C567" t="s">
-        <v>1474</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="568" spans="1:3">
       <c r="A568" t="s">
-        <v>9</v>
-      </c>
-      <c r="B568">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="B568" t="s">
+        <v>1297</v>
       </c>
       <c r="C568" t="s">
-        <v>1479</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="569" spans="1:3">
       <c r="A569" t="s">
-        <v>9</v>
-      </c>
-      <c r="B569">
-        <v>9</v>
+        <v>6</v>
+      </c>
+      <c r="B569" t="s">
+        <v>1301</v>
       </c>
       <c r="C569" t="s">
-        <v>1483</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="570" spans="1:3">
@@ -11705,10 +11730,10 @@
         <v>9</v>
       </c>
       <c r="B570">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C570" t="s">
-        <v>1491</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="571" spans="1:3">
@@ -11716,10 +11741,10 @@
         <v>9</v>
       </c>
       <c r="B571">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C571" t="s">
-        <v>1495</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="572" spans="1:3">
@@ -11727,10 +11752,10 @@
         <v>9</v>
       </c>
       <c r="B572">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C572" t="s">
-        <v>1498</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="573" spans="1:3">
@@ -11738,10 +11763,10 @@
         <v>9</v>
       </c>
       <c r="B573">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C573" t="s">
-        <v>1501</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="574" spans="1:3">
@@ -11749,10 +11774,10 @@
         <v>9</v>
       </c>
       <c r="B574">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C574" t="s">
-        <v>1504</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="575" spans="1:3">
@@ -11760,10 +11785,10 @@
         <v>9</v>
       </c>
       <c r="B575">
-        <v>106</v>
+        <v>12</v>
       </c>
       <c r="C575" t="s">
-        <v>1612</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="576" spans="1:3">
@@ -11771,10 +11796,10 @@
         <v>9</v>
       </c>
       <c r="B576">
-        <v>115</v>
+        <v>13</v>
       </c>
       <c r="C576" t="s">
-        <v>1624</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="577" spans="1:3">
@@ -11782,54 +11807,54 @@
         <v>9</v>
       </c>
       <c r="B577">
-        <v>202</v>
+        <v>14</v>
       </c>
       <c r="C577" t="s">
-        <v>1636</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="578" spans="1:3">
       <c r="A578" t="s">
         <v>9</v>
       </c>
-      <c r="B578" t="s">
-        <v>1667</v>
+      <c r="B578">
+        <v>15</v>
       </c>
       <c r="C578" t="s">
-        <v>1668</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="579" spans="1:3">
       <c r="A579" t="s">
         <v>9</v>
       </c>
-      <c r="B579" t="s">
-        <v>1669</v>
+      <c r="B579">
+        <v>106</v>
       </c>
       <c r="C579" t="s">
-        <v>1670</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="580" spans="1:3">
       <c r="A580" t="s">
         <v>9</v>
       </c>
-      <c r="B580" t="s">
-        <v>10</v>
+      <c r="B580">
+        <v>115</v>
       </c>
       <c r="C580" t="s">
-        <v>11</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="581" spans="1:3">
       <c r="A581" t="s">
         <v>9</v>
       </c>
-      <c r="B581" t="s">
-        <v>12</v>
+      <c r="B581">
+        <v>202</v>
       </c>
       <c r="C581" t="s">
-        <v>13</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="582" spans="1:3">
@@ -11837,10 +11862,10 @@
         <v>9</v>
       </c>
       <c r="B582" t="s">
-        <v>18</v>
+        <v>1667</v>
       </c>
       <c r="C582" t="s">
-        <v>19</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="583" spans="1:3">
@@ -11848,10 +11873,10 @@
         <v>9</v>
       </c>
       <c r="B583" t="s">
-        <v>20</v>
+        <v>1669</v>
       </c>
       <c r="C583" t="s">
-        <v>21</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="584" spans="1:3">
@@ -11859,10 +11884,10 @@
         <v>9</v>
       </c>
       <c r="B584" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C584" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="585" spans="1:3">
@@ -11870,10 +11895,10 @@
         <v>9</v>
       </c>
       <c r="B585" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C585" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="586" spans="1:3">
@@ -11881,10 +11906,10 @@
         <v>9</v>
       </c>
       <c r="B586" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="C586" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="587" spans="1:3">
@@ -11892,10 +11917,10 @@
         <v>9</v>
       </c>
       <c r="B587" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="C587" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
     <row r="588" spans="1:3">
@@ -11903,10 +11928,10 @@
         <v>9</v>
       </c>
       <c r="B588" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="C588" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
     </row>
     <row r="589" spans="1:3">
@@ -11914,10 +11939,10 @@
         <v>9</v>
       </c>
       <c r="B589" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="C589" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
     </row>
     <row r="590" spans="1:3">
@@ -11925,10 +11950,10 @@
         <v>9</v>
       </c>
       <c r="B590" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C590" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
     </row>
     <row r="591" spans="1:3">
@@ -11936,10 +11961,10 @@
         <v>9</v>
       </c>
       <c r="B591" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C591" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="592" spans="1:3">
@@ -11947,10 +11972,10 @@
         <v>9</v>
       </c>
       <c r="B592" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C592" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
     </row>
     <row r="593" spans="1:3">
@@ -11958,10 +11983,10 @@
         <v>9</v>
       </c>
       <c r="B593" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="C593" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
     </row>
     <row r="594" spans="1:3">
@@ -11969,10 +11994,10 @@
         <v>9</v>
       </c>
       <c r="B594" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C594" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="595" spans="1:3">
@@ -11980,10 +12005,10 @@
         <v>9</v>
       </c>
       <c r="B595" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C595" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="596" spans="1:3">
@@ -11991,10 +12016,10 @@
         <v>9</v>
       </c>
       <c r="B596" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="C596" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
     </row>
     <row r="597" spans="1:3">
@@ -12002,10 +12027,10 @@
         <v>9</v>
       </c>
       <c r="B597" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C597" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="598" spans="1:3">
@@ -12013,10 +12038,10 @@
         <v>9</v>
       </c>
       <c r="B598" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C598" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="599" spans="1:3">
@@ -12024,10 +12049,10 @@
         <v>9</v>
       </c>
       <c r="B599" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="C599" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
     </row>
     <row r="600" spans="1:3">
@@ -12035,10 +12060,10 @@
         <v>9</v>
       </c>
       <c r="B600" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="C600" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
     </row>
     <row r="601" spans="1:3">
@@ -12046,10 +12071,10 @@
         <v>9</v>
       </c>
       <c r="B601" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="C601" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
     </row>
     <row r="602" spans="1:3">
@@ -12057,10 +12082,10 @@
         <v>9</v>
       </c>
       <c r="B602" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="C602" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
     </row>
     <row r="603" spans="1:3">
@@ -12068,10 +12093,10 @@
         <v>9</v>
       </c>
       <c r="B603" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="C603" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
     </row>
     <row r="604" spans="1:3">
@@ -12079,10 +12104,10 @@
         <v>9</v>
       </c>
       <c r="B604" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="C604" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
     </row>
     <row r="605" spans="1:3">
@@ -12090,10 +12115,10 @@
         <v>9</v>
       </c>
       <c r="B605" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="C605" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
     </row>
     <row r="606" spans="1:3">
@@ -12101,10 +12126,10 @@
         <v>9</v>
       </c>
       <c r="B606" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="C606" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="607" spans="1:3">
@@ -12112,10 +12137,10 @@
         <v>9</v>
       </c>
       <c r="B607" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="C607" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
     </row>
     <row r="608" spans="1:3">
@@ -12123,10 +12148,10 @@
         <v>9</v>
       </c>
       <c r="B608" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C608" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
     </row>
     <row r="609" spans="1:3">
@@ -12134,10 +12159,10 @@
         <v>9</v>
       </c>
       <c r="B609" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="C609" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
     </row>
     <row r="610" spans="1:3">
@@ -12145,10 +12170,10 @@
         <v>9</v>
       </c>
       <c r="B610" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="C610" t="s">
-        <v>19</v>
+        <v>101</v>
       </c>
     </row>
     <row r="611" spans="1:3">
@@ -12156,10 +12181,10 @@
         <v>9</v>
       </c>
       <c r="B611" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="C611" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
     </row>
     <row r="612" spans="1:3">
@@ -12167,10 +12192,10 @@
         <v>9</v>
       </c>
       <c r="B612" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="C612" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
     </row>
     <row r="613" spans="1:3">
@@ -12178,10 +12203,10 @@
         <v>9</v>
       </c>
       <c r="B613" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="C613" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
     </row>
     <row r="614" spans="1:3">
@@ -12189,10 +12214,10 @@
         <v>9</v>
       </c>
       <c r="B614" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="C614" t="s">
-        <v>131</v>
+        <v>19</v>
       </c>
     </row>
     <row r="615" spans="1:3">
@@ -12200,10 +12225,10 @@
         <v>9</v>
       </c>
       <c r="B615" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="C615" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
     </row>
     <row r="616" spans="1:3">
@@ -12211,10 +12236,10 @@
         <v>9</v>
       </c>
       <c r="B616" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="C616" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
     </row>
     <row r="617" spans="1:3">
@@ -12222,10 +12247,10 @@
         <v>9</v>
       </c>
       <c r="B617" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="C617" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
     </row>
     <row r="618" spans="1:3">
@@ -12233,10 +12258,10 @@
         <v>9</v>
       </c>
       <c r="B618" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="C618" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
     </row>
     <row r="619" spans="1:3">
@@ -12244,10 +12269,10 @@
         <v>9</v>
       </c>
       <c r="B619" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="C619" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
     </row>
     <row r="620" spans="1:3">
@@ -12255,10 +12280,10 @@
         <v>9</v>
       </c>
       <c r="B620" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="C620" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
     </row>
     <row r="621" spans="1:3">
@@ -12266,10 +12291,10 @@
         <v>9</v>
       </c>
       <c r="B621" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="C621" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
     </row>
     <row r="622" spans="1:3">
@@ -12277,10 +12302,10 @@
         <v>9</v>
       </c>
       <c r="B622" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="C622" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="623" spans="1:3">
@@ -12288,10 +12313,10 @@
         <v>9</v>
       </c>
       <c r="B623" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="C623" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
     </row>
     <row r="624" spans="1:3">
@@ -12299,10 +12324,10 @@
         <v>9</v>
       </c>
       <c r="B624" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="C624" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
     </row>
     <row r="625" spans="1:3">
@@ -12310,10 +12335,10 @@
         <v>9</v>
       </c>
       <c r="B625" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="C625" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
     </row>
     <row r="626" spans="1:3">
@@ -12321,10 +12346,10 @@
         <v>9</v>
       </c>
       <c r="B626" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="C626" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
     </row>
     <row r="627" spans="1:3">
@@ -12332,10 +12357,10 @@
         <v>9</v>
       </c>
       <c r="B627" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="C627" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
     </row>
     <row r="628" spans="1:3">
@@ -12343,10 +12368,10 @@
         <v>9</v>
       </c>
       <c r="B628" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="C628" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
     </row>
     <row r="629" spans="1:3">
@@ -12354,10 +12379,10 @@
         <v>9</v>
       </c>
       <c r="B629" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="C629" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
     </row>
     <row r="630" spans="1:3">
@@ -12365,10 +12390,10 @@
         <v>9</v>
       </c>
       <c r="B630" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="C630" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
     </row>
     <row r="631" spans="1:3">
@@ -12376,10 +12401,10 @@
         <v>9</v>
       </c>
       <c r="B631" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="C631" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
     </row>
     <row r="632" spans="1:3">
@@ -12387,10 +12412,10 @@
         <v>9</v>
       </c>
       <c r="B632" t="s">
-        <v>213</v>
+        <v>194</v>
       </c>
       <c r="C632" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
     </row>
     <row r="633" spans="1:3">
@@ -12398,10 +12423,10 @@
         <v>9</v>
       </c>
       <c r="B633" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="C633" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
     </row>
     <row r="634" spans="1:3">
@@ -12409,10 +12434,10 @@
         <v>9</v>
       </c>
       <c r="B634" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="C634" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
     </row>
     <row r="635" spans="1:3">
@@ -12420,10 +12445,10 @@
         <v>9</v>
       </c>
       <c r="B635" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="C635" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
     </row>
     <row r="636" spans="1:3">
@@ -12431,10 +12456,10 @@
         <v>9</v>
       </c>
       <c r="B636" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="C636" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
     </row>
     <row r="637" spans="1:3">
@@ -12442,10 +12467,10 @@
         <v>9</v>
       </c>
       <c r="B637" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="C637" t="s">
-        <v>19</v>
+        <v>216</v>
       </c>
     </row>
     <row r="638" spans="1:3">
@@ -12453,10 +12478,10 @@
         <v>9</v>
       </c>
       <c r="B638" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="C638" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
     </row>
     <row r="639" spans="1:3">
@@ -12464,10 +12489,10 @@
         <v>9</v>
       </c>
       <c r="B639" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="C639" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
     </row>
     <row r="640" spans="1:3">
@@ -12475,10 +12500,10 @@
         <v>9</v>
       </c>
       <c r="B640" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="C640" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
     </row>
     <row r="641" spans="1:3">
@@ -12486,10 +12511,10 @@
         <v>9</v>
       </c>
       <c r="B641" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="C641" t="s">
-        <v>246</v>
+        <v>19</v>
       </c>
     </row>
     <row r="642" spans="1:3">
@@ -12497,10 +12522,10 @@
         <v>9</v>
       </c>
       <c r="B642" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="C642" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
     </row>
     <row r="643" spans="1:3">
@@ -12508,10 +12533,10 @@
         <v>9</v>
       </c>
       <c r="B643" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="C643" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
     </row>
     <row r="644" spans="1:3">
@@ -12519,10 +12544,10 @@
         <v>9</v>
       </c>
       <c r="B644" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="C644" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
     </row>
     <row r="645" spans="1:3">
@@ -12530,10 +12555,10 @@
         <v>9</v>
       </c>
       <c r="B645" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="C645" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
     </row>
     <row r="646" spans="1:3">
@@ -12541,10 +12566,10 @@
         <v>9</v>
       </c>
       <c r="B646" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="C646" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
     </row>
     <row r="647" spans="1:3">
@@ -12552,10 +12577,10 @@
         <v>9</v>
       </c>
       <c r="B647" t="s">
-        <v>271</v>
+        <v>249</v>
       </c>
       <c r="C647" t="s">
-        <v>272</v>
+        <v>250</v>
       </c>
     </row>
     <row r="648" spans="1:3">
@@ -12563,10 +12588,10 @@
         <v>9</v>
       </c>
       <c r="B648" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="C648" t="s">
-        <v>274</v>
+        <v>256</v>
       </c>
     </row>
     <row r="649" spans="1:3">
@@ -12574,10 +12599,10 @@
         <v>9</v>
       </c>
       <c r="B649" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="C649" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
     </row>
     <row r="650" spans="1:3">
@@ -12585,10 +12610,10 @@
         <v>9</v>
       </c>
       <c r="B650" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="C650" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
     </row>
     <row r="651" spans="1:3">
@@ -12596,10 +12621,10 @@
         <v>9</v>
       </c>
       <c r="B651" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="C651" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
     </row>
     <row r="652" spans="1:3">
@@ -12607,10 +12632,10 @@
         <v>9</v>
       </c>
       <c r="B652" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="C652" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
     </row>
     <row r="653" spans="1:3">
@@ -12618,10 +12643,10 @@
         <v>9</v>
       </c>
       <c r="B653" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="C653" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
     </row>
     <row r="654" spans="1:3">
@@ -12629,10 +12654,10 @@
         <v>9</v>
       </c>
       <c r="B654" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="C654" t="s">
-        <v>292</v>
+        <v>278</v>
       </c>
     </row>
     <row r="655" spans="1:3">
@@ -12640,10 +12665,10 @@
         <v>9</v>
       </c>
       <c r="B655" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="C655" t="s">
-        <v>294</v>
+        <v>280</v>
       </c>
     </row>
     <row r="656" spans="1:3">
@@ -12651,10 +12676,10 @@
         <v>9</v>
       </c>
       <c r="B656" t="s">
-        <v>295</v>
+        <v>281</v>
       </c>
       <c r="C656" t="s">
-        <v>296</v>
+        <v>282</v>
       </c>
     </row>
     <row r="657" spans="1:3">
@@ -12662,10 +12687,10 @@
         <v>9</v>
       </c>
       <c r="B657" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="C657" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
     </row>
     <row r="658" spans="1:3">
@@ -12673,10 +12698,10 @@
         <v>9</v>
       </c>
       <c r="B658" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="C658" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
     </row>
     <row r="659" spans="1:3">
@@ -12684,10 +12709,10 @@
         <v>9</v>
       </c>
       <c r="B659" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="C659" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
     </row>
     <row r="660" spans="1:3">
@@ -12695,10 +12720,10 @@
         <v>9</v>
       </c>
       <c r="B660" t="s">
-        <v>308</v>
+        <v>295</v>
       </c>
       <c r="C660" t="s">
-        <v>309</v>
+        <v>296</v>
       </c>
     </row>
     <row r="661" spans="1:3">
@@ -12706,10 +12731,10 @@
         <v>9</v>
       </c>
       <c r="B661" t="s">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="C661" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
     </row>
     <row r="662" spans="1:3">
@@ -12717,10 +12742,10 @@
         <v>9</v>
       </c>
       <c r="B662" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="C662" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
     </row>
     <row r="663" spans="1:3">
@@ -12728,10 +12753,10 @@
         <v>9</v>
       </c>
       <c r="B663" t="s">
-        <v>36</v>
+        <v>304</v>
       </c>
       <c r="C663" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
     </row>
     <row r="664" spans="1:3">
@@ -12739,10 +12764,10 @@
         <v>9</v>
       </c>
       <c r="B664" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="C664" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
     </row>
     <row r="665" spans="1:3">
@@ -12750,10 +12775,10 @@
         <v>9</v>
       </c>
       <c r="B665" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="C665" t="s">
-        <v>328</v>
+        <v>311</v>
       </c>
     </row>
     <row r="666" spans="1:3">
@@ -12761,10 +12786,10 @@
         <v>9</v>
       </c>
       <c r="B666" t="s">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="C666" t="s">
-        <v>330</v>
+        <v>313</v>
       </c>
     </row>
     <row r="667" spans="1:3">
@@ -12772,10 +12797,10 @@
         <v>9</v>
       </c>
       <c r="B667" t="s">
-        <v>331</v>
+        <v>36</v>
       </c>
       <c r="C667" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
     </row>
     <row r="668" spans="1:3">
@@ -12783,10 +12808,10 @@
         <v>9</v>
       </c>
       <c r="B668" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="C668" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
     </row>
     <row r="669" spans="1:3">
@@ -12794,10 +12819,10 @@
         <v>9</v>
       </c>
       <c r="B669" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="C669" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
     </row>
     <row r="670" spans="1:3">
@@ -12805,10 +12830,10 @@
         <v>9</v>
       </c>
       <c r="B670" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="C670" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
     </row>
     <row r="671" spans="1:3">
@@ -12816,10 +12841,10 @@
         <v>9</v>
       </c>
       <c r="B671" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="C671" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
     </row>
     <row r="672" spans="1:3">
@@ -12827,10 +12852,10 @@
         <v>9</v>
       </c>
       <c r="B672" t="s">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="C672" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
     </row>
     <row r="673" spans="1:3">
@@ -12838,10 +12863,10 @@
         <v>9</v>
       </c>
       <c r="B673" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="C673" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
     </row>
     <row r="674" spans="1:3">
@@ -12849,10 +12874,10 @@
         <v>9</v>
       </c>
       <c r="B674" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="C674" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
     </row>
     <row r="675" spans="1:3">
@@ -12860,10 +12885,10 @@
         <v>9</v>
       </c>
       <c r="B675" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="C675" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
     </row>
     <row r="676" spans="1:3">
@@ -12871,10 +12896,10 @@
         <v>9</v>
       </c>
       <c r="B676" t="s">
-        <v>366</v>
+        <v>348</v>
       </c>
       <c r="C676" t="s">
-        <v>368</v>
+        <v>349</v>
       </c>
     </row>
     <row r="677" spans="1:3">
@@ -12882,10 +12907,10 @@
         <v>9</v>
       </c>
       <c r="B677" t="s">
-        <v>377</v>
+        <v>350</v>
       </c>
       <c r="C677" t="s">
-        <v>378</v>
+        <v>351</v>
       </c>
     </row>
     <row r="678" spans="1:3">
@@ -12893,10 +12918,10 @@
         <v>9</v>
       </c>
       <c r="B678" t="s">
-        <v>377</v>
+        <v>352</v>
       </c>
       <c r="C678" t="s">
-        <v>379</v>
+        <v>353</v>
       </c>
     </row>
     <row r="679" spans="1:3">
@@ -12904,10 +12929,10 @@
         <v>9</v>
       </c>
       <c r="B679" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="C679" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
     </row>
     <row r="680" spans="1:3">
@@ -12915,10 +12940,10 @@
         <v>9</v>
       </c>
       <c r="B680" t="s">
-        <v>388</v>
+        <v>366</v>
       </c>
       <c r="C680" t="s">
-        <v>389</v>
+        <v>368</v>
       </c>
     </row>
     <row r="681" spans="1:3">
@@ -12926,10 +12951,10 @@
         <v>9</v>
       </c>
       <c r="B681" t="s">
-        <v>390</v>
+        <v>377</v>
       </c>
       <c r="C681" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
     </row>
     <row r="682" spans="1:3">
@@ -12937,10 +12962,10 @@
         <v>9</v>
       </c>
       <c r="B682" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="C682" t="s">
-        <v>393</v>
+        <v>379</v>
       </c>
     </row>
     <row r="683" spans="1:3">
@@ -12948,10 +12973,10 @@
         <v>9</v>
       </c>
       <c r="B683" t="s">
-        <v>401</v>
+        <v>380</v>
       </c>
       <c r="C683" t="s">
-        <v>402</v>
+        <v>381</v>
       </c>
     </row>
     <row r="684" spans="1:3">
@@ -12959,10 +12984,10 @@
         <v>9</v>
       </c>
       <c r="B684" t="s">
-        <v>407</v>
+        <v>388</v>
       </c>
       <c r="C684" t="s">
-        <v>409</v>
+        <v>389</v>
       </c>
     </row>
     <row r="685" spans="1:3">
@@ -12970,10 +12995,10 @@
         <v>9</v>
       </c>
       <c r="B685" t="s">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="C685" t="s">
-        <v>411</v>
+        <v>391</v>
       </c>
     </row>
     <row r="686" spans="1:3">
@@ -12981,10 +13006,10 @@
         <v>9</v>
       </c>
       <c r="B686" t="s">
-        <v>412</v>
+        <v>392</v>
       </c>
       <c r="C686" t="s">
-        <v>413</v>
+        <v>393</v>
       </c>
     </row>
     <row r="687" spans="1:3">
@@ -12992,10 +13017,10 @@
         <v>9</v>
       </c>
       <c r="B687" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="C687" t="s">
-        <v>415</v>
+        <v>402</v>
       </c>
     </row>
     <row r="688" spans="1:3">
@@ -13003,10 +13028,10 @@
         <v>9</v>
       </c>
       <c r="B688" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="C688" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
     </row>
     <row r="689" spans="1:3">
@@ -13014,10 +13039,10 @@
         <v>9</v>
       </c>
       <c r="B689" t="s">
-        <v>428</v>
+        <v>410</v>
       </c>
       <c r="C689" t="s">
-        <v>429</v>
+        <v>411</v>
       </c>
     </row>
     <row r="690" spans="1:3">
@@ -13025,10 +13050,10 @@
         <v>9</v>
       </c>
       <c r="B690" t="s">
-        <v>433</v>
+        <v>412</v>
       </c>
       <c r="C690" t="s">
-        <v>435</v>
+        <v>413</v>
       </c>
     </row>
     <row r="691" spans="1:3">
@@ -13036,10 +13061,10 @@
         <v>9</v>
       </c>
       <c r="B691" t="s">
-        <v>436</v>
+        <v>414</v>
       </c>
       <c r="C691" t="s">
-        <v>437</v>
+        <v>415</v>
       </c>
     </row>
     <row r="692" spans="1:3">
@@ -13047,10 +13072,10 @@
         <v>9</v>
       </c>
       <c r="B692" t="s">
-        <v>438</v>
+        <v>416</v>
       </c>
       <c r="C692" t="s">
-        <v>439</v>
+        <v>417</v>
       </c>
     </row>
     <row r="693" spans="1:3">
@@ -13058,10 +13083,10 @@
         <v>9</v>
       </c>
       <c r="B693" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="C693" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
     </row>
     <row r="694" spans="1:3">
@@ -13069,10 +13094,10 @@
         <v>9</v>
       </c>
       <c r="B694" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="C694" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
     </row>
     <row r="695" spans="1:3">
@@ -13080,10 +13105,10 @@
         <v>9</v>
       </c>
       <c r="B695" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="C695" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
     </row>
     <row r="696" spans="1:3">
@@ -13091,10 +13116,10 @@
         <v>9</v>
       </c>
       <c r="B696" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="C696" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
     </row>
     <row r="697" spans="1:3">
@@ -13102,10 +13127,10 @@
         <v>9</v>
       </c>
       <c r="B697" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="C697" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
     </row>
     <row r="698" spans="1:3">
@@ -13113,10 +13138,10 @@
         <v>9</v>
       </c>
       <c r="B698" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="C698" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
     </row>
     <row r="699" spans="1:3">
@@ -13124,10 +13149,10 @@
         <v>9</v>
       </c>
       <c r="B699" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="C699" t="s">
-        <v>457</v>
+        <v>446</v>
       </c>
     </row>
     <row r="700" spans="1:3">
@@ -13135,10 +13160,10 @@
         <v>9</v>
       </c>
       <c r="B700" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="C700" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
     </row>
     <row r="701" spans="1:3">
@@ -13146,10 +13171,10 @@
         <v>9</v>
       </c>
       <c r="B701" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="C701" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
     </row>
     <row r="702" spans="1:3">
@@ -13157,10 +13182,10 @@
         <v>9</v>
       </c>
       <c r="B702" t="s">
-        <v>466</v>
+        <v>454</v>
       </c>
       <c r="C702" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
     </row>
     <row r="703" spans="1:3">
@@ -13168,10 +13193,10 @@
         <v>9</v>
       </c>
       <c r="B703" t="s">
-        <v>470</v>
+        <v>456</v>
       </c>
       <c r="C703" t="s">
-        <v>471</v>
+        <v>457</v>
       </c>
     </row>
     <row r="704" spans="1:3">
@@ -13179,10 +13204,10 @@
         <v>9</v>
       </c>
       <c r="B704" t="s">
-        <v>474</v>
+        <v>458</v>
       </c>
       <c r="C704" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
     </row>
     <row r="705" spans="1:3">
@@ -13190,10 +13215,10 @@
         <v>9</v>
       </c>
       <c r="B705" t="s">
-        <v>476</v>
+        <v>460</v>
       </c>
       <c r="C705" t="s">
-        <v>477</v>
+        <v>461</v>
       </c>
     </row>
     <row r="706" spans="1:3">
@@ -13201,10 +13226,10 @@
         <v>9</v>
       </c>
       <c r="B706" t="s">
-        <v>484</v>
+        <v>466</v>
       </c>
       <c r="C706" t="s">
-        <v>485</v>
+        <v>467</v>
       </c>
     </row>
     <row r="707" spans="1:3">
@@ -13212,10 +13237,10 @@
         <v>9</v>
       </c>
       <c r="B707" t="s">
-        <v>488</v>
+        <v>470</v>
       </c>
       <c r="C707" t="s">
-        <v>489</v>
+        <v>471</v>
       </c>
     </row>
     <row r="708" spans="1:3">
@@ -13223,10 +13248,10 @@
         <v>9</v>
       </c>
       <c r="B708" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="C708" t="s">
-        <v>493</v>
+        <v>475</v>
       </c>
     </row>
     <row r="709" spans="1:3">
@@ -13234,10 +13259,10 @@
         <v>9</v>
       </c>
       <c r="B709" t="s">
-        <v>496</v>
+        <v>476</v>
       </c>
       <c r="C709" t="s">
-        <v>497</v>
+        <v>477</v>
       </c>
     </row>
     <row r="710" spans="1:3">
@@ -13245,10 +13270,10 @@
         <v>9</v>
       </c>
       <c r="B710" t="s">
-        <v>498</v>
+        <v>484</v>
       </c>
       <c r="C710" t="s">
-        <v>499</v>
+        <v>485</v>
       </c>
     </row>
     <row r="711" spans="1:3">
@@ -13256,10 +13281,10 @@
         <v>9</v>
       </c>
       <c r="B711" t="s">
-        <v>507</v>
+        <v>488</v>
       </c>
       <c r="C711" t="s">
-        <v>508</v>
+        <v>489</v>
       </c>
     </row>
     <row r="712" spans="1:3">
@@ -13267,10 +13292,10 @@
         <v>9</v>
       </c>
       <c r="B712" t="s">
-        <v>515</v>
+        <v>492</v>
       </c>
       <c r="C712" t="s">
-        <v>516</v>
+        <v>493</v>
       </c>
     </row>
     <row r="713" spans="1:3">
@@ -13278,10 +13303,10 @@
         <v>9</v>
       </c>
       <c r="B713" t="s">
-        <v>517</v>
+        <v>496</v>
       </c>
       <c r="C713" t="s">
-        <v>518</v>
+        <v>497</v>
       </c>
     </row>
     <row r="714" spans="1:3">
@@ -13289,10 +13314,10 @@
         <v>9</v>
       </c>
       <c r="B714" t="s">
-        <v>8</v>
+        <v>498</v>
       </c>
       <c r="C714" t="s">
-        <v>520</v>
+        <v>499</v>
       </c>
     </row>
     <row r="715" spans="1:3">
@@ -13300,10 +13325,10 @@
         <v>9</v>
       </c>
       <c r="B715" t="s">
-        <v>521</v>
+        <v>507</v>
       </c>
       <c r="C715" t="s">
-        <v>522</v>
+        <v>508</v>
       </c>
     </row>
     <row r="716" spans="1:3">
@@ -13311,10 +13336,10 @@
         <v>9</v>
       </c>
       <c r="B716" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="C716" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
     </row>
     <row r="717" spans="1:3">
@@ -13322,10 +13347,10 @@
         <v>9</v>
       </c>
       <c r="B717" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="C717" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
     </row>
     <row r="718" spans="1:3">
@@ -13333,10 +13358,10 @@
         <v>9</v>
       </c>
       <c r="B718" t="s">
-        <v>533</v>
+        <v>8</v>
       </c>
       <c r="C718" t="s">
-        <v>534</v>
+        <v>520</v>
       </c>
     </row>
     <row r="719" spans="1:3">
@@ -13344,10 +13369,10 @@
         <v>9</v>
       </c>
       <c r="B719" t="s">
-        <v>535</v>
+        <v>521</v>
       </c>
       <c r="C719" t="s">
-        <v>536</v>
+        <v>522</v>
       </c>
     </row>
     <row r="720" spans="1:3">
@@ -13355,10 +13380,10 @@
         <v>9</v>
       </c>
       <c r="B720" t="s">
-        <v>539</v>
+        <v>525</v>
       </c>
       <c r="C720" t="s">
-        <v>540</v>
+        <v>526</v>
       </c>
     </row>
     <row r="721" spans="1:3">
@@ -13366,10 +13391,10 @@
         <v>9</v>
       </c>
       <c r="B721" t="s">
-        <v>541</v>
+        <v>527</v>
       </c>
       <c r="C721" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
     </row>
     <row r="722" spans="1:3">
@@ -13377,10 +13402,10 @@
         <v>9</v>
       </c>
       <c r="B722" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="C722" t="s">
-        <v>544</v>
+        <v>534</v>
       </c>
     </row>
     <row r="723" spans="1:3">
@@ -13388,10 +13413,10 @@
         <v>9</v>
       </c>
       <c r="B723" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="C723" t="s">
-        <v>549</v>
+        <v>536</v>
       </c>
     </row>
     <row r="724" spans="1:3">
@@ -13399,10 +13424,10 @@
         <v>9</v>
       </c>
       <c r="B724" t="s">
-        <v>557</v>
+        <v>539</v>
       </c>
       <c r="C724" t="s">
-        <v>558</v>
+        <v>540</v>
       </c>
     </row>
     <row r="725" spans="1:3">
@@ -13410,10 +13435,10 @@
         <v>9</v>
       </c>
       <c r="B725" t="s">
-        <v>561</v>
+        <v>541</v>
       </c>
       <c r="C725" t="s">
-        <v>563</v>
+        <v>542</v>
       </c>
     </row>
     <row r="726" spans="1:3">
@@ -13421,10 +13446,10 @@
         <v>9</v>
       </c>
       <c r="B726" t="s">
-        <v>564</v>
+        <v>543</v>
       </c>
       <c r="C726" t="s">
-        <v>565</v>
+        <v>544</v>
       </c>
     </row>
     <row r="727" spans="1:3">
@@ -13432,10 +13457,10 @@
         <v>9</v>
       </c>
       <c r="B727" t="s">
-        <v>568</v>
+        <v>547</v>
       </c>
       <c r="C727" t="s">
-        <v>569</v>
+        <v>549</v>
       </c>
     </row>
     <row r="728" spans="1:3">
@@ -13443,10 +13468,10 @@
         <v>9</v>
       </c>
       <c r="B728" t="s">
-        <v>588</v>
+        <v>557</v>
       </c>
       <c r="C728" t="s">
-        <v>589</v>
+        <v>558</v>
       </c>
     </row>
     <row r="729" spans="1:3">
@@ -13454,10 +13479,10 @@
         <v>9</v>
       </c>
       <c r="B729" t="s">
-        <v>600</v>
+        <v>561</v>
       </c>
       <c r="C729" t="s">
-        <v>602</v>
+        <v>563</v>
       </c>
     </row>
     <row r="730" spans="1:3">
@@ -13465,10 +13490,10 @@
         <v>9</v>
       </c>
       <c r="B730" t="s">
-        <v>603</v>
+        <v>564</v>
       </c>
       <c r="C730" t="s">
-        <v>604</v>
+        <v>565</v>
       </c>
     </row>
     <row r="731" spans="1:3">
@@ -13476,10 +13501,10 @@
         <v>9</v>
       </c>
       <c r="B731" t="s">
-        <v>605</v>
+        <v>568</v>
       </c>
       <c r="C731" t="s">
-        <v>607</v>
+        <v>569</v>
       </c>
     </row>
     <row r="732" spans="1:3">
@@ -13487,10 +13512,10 @@
         <v>9</v>
       </c>
       <c r="B732" t="s">
-        <v>608</v>
+        <v>588</v>
       </c>
       <c r="C732" t="s">
-        <v>609</v>
+        <v>589</v>
       </c>
     </row>
     <row r="733" spans="1:3">
@@ -13498,10 +13523,10 @@
         <v>9</v>
       </c>
       <c r="B733" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="C733" t="s">
-        <v>613</v>
+        <v>602</v>
       </c>
     </row>
     <row r="734" spans="1:3">
@@ -13509,10 +13534,10 @@
         <v>9</v>
       </c>
       <c r="B734" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="C734" t="s">
-        <v>617</v>
+        <v>604</v>
       </c>
     </row>
     <row r="735" spans="1:3">
@@ -13520,10 +13545,10 @@
         <v>9</v>
       </c>
       <c r="B735" t="s">
-        <v>628</v>
+        <v>605</v>
       </c>
       <c r="C735" t="s">
-        <v>629</v>
+        <v>607</v>
       </c>
     </row>
     <row r="736" spans="1:3">
@@ -13531,10 +13556,10 @@
         <v>9</v>
       </c>
       <c r="B736" t="s">
-        <v>632</v>
+        <v>608</v>
       </c>
       <c r="C736" t="s">
-        <v>633</v>
+        <v>609</v>
       </c>
     </row>
     <row r="737" spans="1:3">
@@ -13542,10 +13567,10 @@
         <v>9</v>
       </c>
       <c r="B737" t="s">
-        <v>634</v>
+        <v>612</v>
       </c>
       <c r="C737" t="s">
-        <v>635</v>
+        <v>613</v>
       </c>
     </row>
     <row r="738" spans="1:3">
@@ -13553,10 +13578,10 @@
         <v>9</v>
       </c>
       <c r="B738" t="s">
-        <v>642</v>
+        <v>616</v>
       </c>
       <c r="C738" t="s">
-        <v>643</v>
+        <v>617</v>
       </c>
     </row>
     <row r="739" spans="1:3">
@@ -13564,10 +13589,10 @@
         <v>9</v>
       </c>
       <c r="B739" t="s">
-        <v>646</v>
+        <v>628</v>
       </c>
       <c r="C739" t="s">
-        <v>647</v>
+        <v>629</v>
       </c>
     </row>
     <row r="740" spans="1:3">
@@ -13575,10 +13600,10 @@
         <v>9</v>
       </c>
       <c r="B740" t="s">
-        <v>648</v>
+        <v>632</v>
       </c>
       <c r="C740" t="s">
-        <v>649</v>
+        <v>633</v>
       </c>
     </row>
     <row r="741" spans="1:3">
@@ -13586,10 +13611,10 @@
         <v>9</v>
       </c>
       <c r="B741" t="s">
-        <v>652</v>
+        <v>634</v>
       </c>
       <c r="C741" t="s">
-        <v>653</v>
+        <v>635</v>
       </c>
     </row>
     <row r="742" spans="1:3">
@@ -13597,10 +13622,10 @@
         <v>9</v>
       </c>
       <c r="B742" t="s">
-        <v>654</v>
+        <v>642</v>
       </c>
       <c r="C742" t="s">
-        <v>655</v>
+        <v>643</v>
       </c>
     </row>
     <row r="743" spans="1:3">
@@ -13608,10 +13633,10 @@
         <v>9</v>
       </c>
       <c r="B743" t="s">
-        <v>656</v>
+        <v>646</v>
       </c>
       <c r="C743" t="s">
-        <v>657</v>
+        <v>647</v>
       </c>
     </row>
     <row r="744" spans="1:3">
@@ -13619,10 +13644,10 @@
         <v>9</v>
       </c>
       <c r="B744" t="s">
-        <v>658</v>
+        <v>648</v>
       </c>
       <c r="C744" t="s">
-        <v>659</v>
+        <v>649</v>
       </c>
     </row>
     <row r="745" spans="1:3">
@@ -13630,10 +13655,10 @@
         <v>9</v>
       </c>
       <c r="B745" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="C745" t="s">
-        <v>661</v>
+        <v>653</v>
       </c>
     </row>
     <row r="746" spans="1:3">
@@ -13641,10 +13666,10 @@
         <v>9</v>
       </c>
       <c r="B746" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="C746" t="s">
-        <v>665</v>
+        <v>655</v>
       </c>
     </row>
     <row r="747" spans="1:3">
@@ -13652,10 +13677,10 @@
         <v>9</v>
       </c>
       <c r="B747" t="s">
-        <v>666</v>
+        <v>656</v>
       </c>
       <c r="C747" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
     </row>
     <row r="748" spans="1:3">
@@ -13663,10 +13688,10 @@
         <v>9</v>
       </c>
       <c r="B748" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
       <c r="C748" t="s">
-        <v>669</v>
+        <v>659</v>
       </c>
     </row>
     <row r="749" spans="1:3">
@@ -13674,10 +13699,10 @@
         <v>9</v>
       </c>
       <c r="B749" t="s">
-        <v>674</v>
+        <v>660</v>
       </c>
       <c r="C749" t="s">
-        <v>675</v>
+        <v>661</v>
       </c>
     </row>
     <row r="750" spans="1:3">
@@ -13685,10 +13710,10 @@
         <v>9</v>
       </c>
       <c r="B750" t="s">
-        <v>676</v>
+        <v>662</v>
       </c>
       <c r="C750" t="s">
-        <v>678</v>
+        <v>665</v>
       </c>
     </row>
     <row r="751" spans="1:3">
@@ -13696,10 +13721,10 @@
         <v>9</v>
       </c>
       <c r="B751" t="s">
-        <v>679</v>
+        <v>666</v>
       </c>
       <c r="C751" t="s">
-        <v>681</v>
+        <v>667</v>
       </c>
     </row>
     <row r="752" spans="1:3">
@@ -13707,10 +13732,10 @@
         <v>9</v>
       </c>
       <c r="B752" t="s">
-        <v>690</v>
+        <v>668</v>
       </c>
       <c r="C752" t="s">
-        <v>691</v>
+        <v>669</v>
       </c>
     </row>
     <row r="753" spans="1:3">
@@ -13718,10 +13743,10 @@
         <v>9</v>
       </c>
       <c r="B753" t="s">
-        <v>698</v>
+        <v>674</v>
       </c>
       <c r="C753" t="s">
-        <v>699</v>
+        <v>675</v>
       </c>
     </row>
     <row r="754" spans="1:3">
@@ -13729,10 +13754,10 @@
         <v>9</v>
       </c>
       <c r="B754" t="s">
-        <v>700</v>
+        <v>676</v>
       </c>
       <c r="C754" t="s">
-        <v>701</v>
+        <v>678</v>
       </c>
     </row>
     <row r="755" spans="1:3">
@@ -13740,10 +13765,10 @@
         <v>9</v>
       </c>
       <c r="B755" t="s">
-        <v>702</v>
+        <v>679</v>
       </c>
       <c r="C755" t="s">
-        <v>704</v>
+        <v>681</v>
       </c>
     </row>
     <row r="756" spans="1:3">
@@ -13751,10 +13776,10 @@
         <v>9</v>
       </c>
       <c r="B756" t="s">
-        <v>707</v>
+        <v>690</v>
       </c>
       <c r="C756" t="s">
-        <v>708</v>
+        <v>691</v>
       </c>
     </row>
     <row r="757" spans="1:3">
@@ -13762,10 +13787,10 @@
         <v>9</v>
       </c>
       <c r="B757" t="s">
-        <v>709</v>
+        <v>698</v>
       </c>
       <c r="C757" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
     </row>
     <row r="758" spans="1:3">
@@ -13773,10 +13798,10 @@
         <v>9</v>
       </c>
       <c r="B758" t="s">
-        <v>711</v>
+        <v>700</v>
       </c>
       <c r="C758" t="s">
-        <v>712</v>
+        <v>701</v>
       </c>
     </row>
     <row r="759" spans="1:3">
@@ -13784,10 +13809,10 @@
         <v>9</v>
       </c>
       <c r="B759" t="s">
-        <v>723</v>
+        <v>702</v>
       </c>
       <c r="C759" t="s">
-        <v>724</v>
+        <v>704</v>
       </c>
     </row>
     <row r="760" spans="1:3">
@@ -13795,10 +13820,10 @@
         <v>9</v>
       </c>
       <c r="B760" t="s">
-        <v>725</v>
+        <v>707</v>
       </c>
       <c r="C760" t="s">
-        <v>726</v>
+        <v>708</v>
       </c>
     </row>
     <row r="761" spans="1:3">
@@ -13806,10 +13831,10 @@
         <v>9</v>
       </c>
       <c r="B761" t="s">
-        <v>727</v>
+        <v>709</v>
       </c>
       <c r="C761" t="s">
-        <v>728</v>
+        <v>710</v>
       </c>
     </row>
     <row r="762" spans="1:3">
@@ -13817,10 +13842,10 @@
         <v>9</v>
       </c>
       <c r="B762" t="s">
-        <v>729</v>
+        <v>711</v>
       </c>
       <c r="C762" t="s">
-        <v>730</v>
+        <v>712</v>
       </c>
     </row>
     <row r="763" spans="1:3">
@@ -13828,10 +13853,10 @@
         <v>9</v>
       </c>
       <c r="B763" t="s">
-        <v>731</v>
+        <v>723</v>
       </c>
       <c r="C763" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
     </row>
     <row r="764" spans="1:3">
@@ -13839,10 +13864,10 @@
         <v>9</v>
       </c>
       <c r="B764" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
       <c r="C764" t="s">
-        <v>734</v>
+        <v>726</v>
       </c>
     </row>
     <row r="765" spans="1:3">
@@ -13850,10 +13875,10 @@
         <v>9</v>
       </c>
       <c r="B765" t="s">
-        <v>735</v>
+        <v>727</v>
       </c>
       <c r="C765" t="s">
-        <v>736</v>
+        <v>728</v>
       </c>
     </row>
     <row r="766" spans="1:3">
@@ -13861,10 +13886,10 @@
         <v>9</v>
       </c>
       <c r="B766" t="s">
-        <v>737</v>
+        <v>729</v>
       </c>
       <c r="C766" t="s">
-        <v>738</v>
+        <v>730</v>
       </c>
     </row>
     <row r="767" spans="1:3">
@@ -13872,10 +13897,10 @@
         <v>9</v>
       </c>
       <c r="B767" t="s">
-        <v>739</v>
+        <v>731</v>
       </c>
       <c r="C767" t="s">
-        <v>740</v>
+        <v>732</v>
       </c>
     </row>
     <row r="768" spans="1:3">
@@ -13883,10 +13908,10 @@
         <v>9</v>
       </c>
       <c r="B768" t="s">
-        <v>747</v>
+        <v>733</v>
       </c>
       <c r="C768" t="s">
-        <v>749</v>
+        <v>734</v>
       </c>
     </row>
     <row r="769" spans="1:3">
@@ -13894,10 +13919,10 @@
         <v>9</v>
       </c>
       <c r="B769" t="s">
-        <v>750</v>
+        <v>735</v>
       </c>
       <c r="C769" t="s">
-        <v>751</v>
+        <v>736</v>
       </c>
     </row>
     <row r="770" spans="1:3">
@@ -13905,10 +13930,10 @@
         <v>9</v>
       </c>
       <c r="B770" t="s">
-        <v>752</v>
+        <v>737</v>
       </c>
       <c r="C770" t="s">
-        <v>753</v>
+        <v>738</v>
       </c>
     </row>
     <row r="771" spans="1:3">
@@ -13916,10 +13941,10 @@
         <v>9</v>
       </c>
       <c r="B771" t="s">
-        <v>761</v>
+        <v>739</v>
       </c>
       <c r="C771" t="s">
-        <v>762</v>
+        <v>740</v>
       </c>
     </row>
     <row r="772" spans="1:3">
@@ -13927,10 +13952,10 @@
         <v>9</v>
       </c>
       <c r="B772" t="s">
-        <v>765</v>
+        <v>747</v>
       </c>
       <c r="C772" t="s">
-        <v>767</v>
+        <v>749</v>
       </c>
     </row>
     <row r="773" spans="1:3">
@@ -13938,10 +13963,10 @@
         <v>9</v>
       </c>
       <c r="B773" t="s">
-        <v>770</v>
+        <v>750</v>
       </c>
       <c r="C773" t="s">
-        <v>771</v>
+        <v>751</v>
       </c>
     </row>
     <row r="774" spans="1:3">
@@ -13949,10 +13974,10 @@
         <v>9</v>
       </c>
       <c r="B774" t="s">
-        <v>774</v>
+        <v>752</v>
       </c>
       <c r="C774" t="s">
-        <v>775</v>
+        <v>753</v>
       </c>
     </row>
     <row r="775" spans="1:3">
@@ -13960,10 +13985,10 @@
         <v>9</v>
       </c>
       <c r="B775" t="s">
-        <v>776</v>
+        <v>761</v>
       </c>
       <c r="C775" t="s">
-        <v>777</v>
+        <v>762</v>
       </c>
     </row>
     <row r="776" spans="1:3">
@@ -13971,10 +13996,10 @@
         <v>9</v>
       </c>
       <c r="B776" t="s">
-        <v>780</v>
+        <v>765</v>
       </c>
       <c r="C776" t="s">
-        <v>782</v>
+        <v>767</v>
       </c>
     </row>
     <row r="777" spans="1:3">
@@ -13982,10 +14007,10 @@
         <v>9</v>
       </c>
       <c r="B777" t="s">
-        <v>783</v>
+        <v>770</v>
       </c>
       <c r="C777" t="s">
-        <v>784</v>
+        <v>771</v>
       </c>
     </row>
     <row r="778" spans="1:3">
@@ -13993,10 +14018,10 @@
         <v>9</v>
       </c>
       <c r="B778" t="s">
-        <v>785</v>
+        <v>774</v>
       </c>
       <c r="C778" t="s">
-        <v>787</v>
+        <v>775</v>
       </c>
     </row>
     <row r="779" spans="1:3">
@@ -14004,10 +14029,10 @@
         <v>9</v>
       </c>
       <c r="B779" t="s">
-        <v>794</v>
+        <v>776</v>
       </c>
       <c r="C779" t="s">
-        <v>795</v>
+        <v>777</v>
       </c>
     </row>
     <row r="780" spans="1:3">
@@ -14015,10 +14040,10 @@
         <v>9</v>
       </c>
       <c r="B780" t="s">
-        <v>796</v>
+        <v>780</v>
       </c>
       <c r="C780" t="s">
-        <v>797</v>
+        <v>782</v>
       </c>
     </row>
     <row r="781" spans="1:3">
@@ -14026,10 +14051,10 @@
         <v>9</v>
       </c>
       <c r="B781" t="s">
-        <v>800</v>
+        <v>783</v>
       </c>
       <c r="C781" t="s">
-        <v>801</v>
+        <v>784</v>
       </c>
     </row>
     <row r="782" spans="1:3">
@@ -14037,10 +14062,10 @@
         <v>9</v>
       </c>
       <c r="B782" t="s">
-        <v>804</v>
+        <v>785</v>
       </c>
       <c r="C782" t="s">
-        <v>806</v>
+        <v>787</v>
       </c>
     </row>
     <row r="783" spans="1:3">
@@ -14048,10 +14073,10 @@
         <v>9</v>
       </c>
       <c r="B783" t="s">
-        <v>807</v>
+        <v>794</v>
       </c>
       <c r="C783" t="s">
-        <v>808</v>
+        <v>795</v>
       </c>
     </row>
     <row r="784" spans="1:3">
@@ -14059,10 +14084,10 @@
         <v>9</v>
       </c>
       <c r="B784" t="s">
-        <v>818</v>
+        <v>796</v>
       </c>
       <c r="C784" t="s">
-        <v>819</v>
+        <v>797</v>
       </c>
     </row>
     <row r="785" spans="1:3">
@@ -14070,10 +14095,10 @@
         <v>9</v>
       </c>
       <c r="B785" t="s">
-        <v>822</v>
+        <v>800</v>
       </c>
       <c r="C785" t="s">
-        <v>824</v>
+        <v>801</v>
       </c>
     </row>
     <row r="786" spans="1:3">
@@ -14081,10 +14106,10 @@
         <v>9</v>
       </c>
       <c r="B786" t="s">
-        <v>829</v>
+        <v>804</v>
       </c>
       <c r="C786" t="s">
-        <v>830</v>
+        <v>806</v>
       </c>
     </row>
     <row r="787" spans="1:3">
@@ -14092,10 +14117,10 @@
         <v>9</v>
       </c>
       <c r="B787" t="s">
-        <v>833</v>
+        <v>807</v>
       </c>
       <c r="C787" t="s">
-        <v>834</v>
+        <v>808</v>
       </c>
     </row>
     <row r="788" spans="1:3">
@@ -14103,10 +14128,10 @@
         <v>9</v>
       </c>
       <c r="B788" t="s">
-        <v>835</v>
+        <v>818</v>
       </c>
       <c r="C788" t="s">
-        <v>836</v>
+        <v>819</v>
       </c>
     </row>
     <row r="789" spans="1:3">
@@ -14114,10 +14139,10 @@
         <v>9</v>
       </c>
       <c r="B789" t="s">
-        <v>837</v>
+        <v>822</v>
       </c>
       <c r="C789" t="s">
-        <v>838</v>
+        <v>824</v>
       </c>
     </row>
     <row r="790" spans="1:3">
@@ -14125,10 +14150,10 @@
         <v>9</v>
       </c>
       <c r="B790" t="s">
-        <v>839</v>
+        <v>829</v>
       </c>
       <c r="C790" t="s">
-        <v>840</v>
+        <v>830</v>
       </c>
     </row>
     <row r="791" spans="1:3">
@@ -14136,10 +14161,10 @@
         <v>9</v>
       </c>
       <c r="B791" t="s">
-        <v>843</v>
+        <v>833</v>
       </c>
       <c r="C791" t="s">
-        <v>844</v>
+        <v>834</v>
       </c>
     </row>
     <row r="792" spans="1:3">
@@ -14147,10 +14172,10 @@
         <v>9</v>
       </c>
       <c r="B792" t="s">
-        <v>861</v>
+        <v>835</v>
       </c>
       <c r="C792" t="s">
-        <v>862</v>
+        <v>836</v>
       </c>
     </row>
     <row r="793" spans="1:3">
@@ -14158,10 +14183,10 @@
         <v>9</v>
       </c>
       <c r="B793" t="s">
-        <v>865</v>
+        <v>837</v>
       </c>
       <c r="C793" t="s">
-        <v>866</v>
+        <v>838</v>
       </c>
     </row>
     <row r="794" spans="1:3">
@@ -14169,10 +14194,10 @@
         <v>9</v>
       </c>
       <c r="B794" t="s">
-        <v>867</v>
+        <v>839</v>
       </c>
       <c r="C794" t="s">
-        <v>868</v>
+        <v>840</v>
       </c>
     </row>
     <row r="795" spans="1:3">
@@ -14180,10 +14205,10 @@
         <v>9</v>
       </c>
       <c r="B795" t="s">
-        <v>871</v>
+        <v>843</v>
       </c>
       <c r="C795" t="s">
-        <v>872</v>
+        <v>844</v>
       </c>
     </row>
     <row r="796" spans="1:3">
@@ -14191,10 +14216,10 @@
         <v>9</v>
       </c>
       <c r="B796" t="s">
-        <v>879</v>
+        <v>861</v>
       </c>
       <c r="C796" t="s">
-        <v>880</v>
+        <v>862</v>
       </c>
     </row>
     <row r="797" spans="1:3">
@@ -14202,10 +14227,10 @@
         <v>9</v>
       </c>
       <c r="B797" t="s">
-        <v>881</v>
+        <v>865</v>
       </c>
       <c r="C797" t="s">
-        <v>883</v>
+        <v>866</v>
       </c>
     </row>
     <row r="798" spans="1:3">
@@ -14213,10 +14238,10 @@
         <v>9</v>
       </c>
       <c r="B798" t="s">
-        <v>884</v>
+        <v>867</v>
       </c>
       <c r="C798" t="s">
-        <v>885</v>
+        <v>868</v>
       </c>
     </row>
     <row r="799" spans="1:3">
@@ -14224,10 +14249,10 @@
         <v>9</v>
       </c>
       <c r="B799" t="s">
-        <v>888</v>
+        <v>871</v>
       </c>
       <c r="C799" t="s">
-        <v>890</v>
+        <v>872</v>
       </c>
     </row>
     <row r="800" spans="1:3">
@@ -14235,10 +14260,10 @@
         <v>9</v>
       </c>
       <c r="B800" t="s">
-        <v>895</v>
+        <v>879</v>
       </c>
       <c r="C800" t="s">
-        <v>896</v>
+        <v>880</v>
       </c>
     </row>
     <row r="801" spans="1:3">
@@ -14246,10 +14271,10 @@
         <v>9</v>
       </c>
       <c r="B801" t="s">
-        <v>897</v>
+        <v>881</v>
       </c>
       <c r="C801" t="s">
-        <v>898</v>
+        <v>883</v>
       </c>
     </row>
     <row r="802" spans="1:3">
@@ -14257,10 +14282,10 @@
         <v>9</v>
       </c>
       <c r="B802" t="s">
-        <v>899</v>
+        <v>884</v>
       </c>
       <c r="C802" t="s">
-        <v>900</v>
+        <v>885</v>
       </c>
     </row>
     <row r="803" spans="1:3">
@@ -14268,10 +14293,10 @@
         <v>9</v>
       </c>
       <c r="B803" t="s">
-        <v>901</v>
+        <v>888</v>
       </c>
       <c r="C803" t="s">
-        <v>902</v>
+        <v>890</v>
       </c>
     </row>
     <row r="804" spans="1:3">
@@ -14279,10 +14304,10 @@
         <v>9</v>
       </c>
       <c r="B804" t="s">
-        <v>905</v>
+        <v>895</v>
       </c>
       <c r="C804" t="s">
-        <v>906</v>
+        <v>896</v>
       </c>
     </row>
     <row r="805" spans="1:3">
@@ -14290,10 +14315,10 @@
         <v>9</v>
       </c>
       <c r="B805" t="s">
-        <v>907</v>
+        <v>897</v>
       </c>
       <c r="C805" t="s">
-        <v>908</v>
+        <v>898</v>
       </c>
     </row>
     <row r="806" spans="1:3">
@@ -14301,10 +14326,10 @@
         <v>9</v>
       </c>
       <c r="B806" t="s">
-        <v>915</v>
+        <v>899</v>
       </c>
       <c r="C806" t="s">
-        <v>916</v>
+        <v>900</v>
       </c>
     </row>
     <row r="807" spans="1:3">
@@ -14312,10 +14337,10 @@
         <v>9</v>
       </c>
       <c r="B807" t="s">
-        <v>928</v>
+        <v>901</v>
       </c>
       <c r="C807" t="s">
-        <v>929</v>
+        <v>902</v>
       </c>
     </row>
     <row r="808" spans="1:3">
@@ -14323,10 +14348,10 @@
         <v>9</v>
       </c>
       <c r="B808" t="s">
-        <v>930</v>
+        <v>905</v>
       </c>
       <c r="C808" t="s">
-        <v>931</v>
+        <v>906</v>
       </c>
     </row>
     <row r="809" spans="1:3">
@@ -14334,10 +14359,10 @@
         <v>9</v>
       </c>
       <c r="B809" t="s">
-        <v>936</v>
+        <v>907</v>
       </c>
       <c r="C809" t="s">
-        <v>937</v>
+        <v>908</v>
       </c>
     </row>
     <row r="810" spans="1:3">
@@ -14345,10 +14370,10 @@
         <v>9</v>
       </c>
       <c r="B810" t="s">
-        <v>946</v>
+        <v>915</v>
       </c>
       <c r="C810" t="s">
-        <v>947</v>
+        <v>916</v>
       </c>
     </row>
     <row r="811" spans="1:3">
@@ -14356,10 +14381,10 @@
         <v>9</v>
       </c>
       <c r="B811" t="s">
-        <v>950</v>
+        <v>928</v>
       </c>
       <c r="C811" t="s">
-        <v>951</v>
+        <v>929</v>
       </c>
     </row>
     <row r="812" spans="1:3">
@@ -14367,10 +14392,10 @@
         <v>9</v>
       </c>
       <c r="B812" t="s">
-        <v>954</v>
+        <v>930</v>
       </c>
       <c r="C812" t="s">
-        <v>956</v>
+        <v>931</v>
       </c>
     </row>
     <row r="813" spans="1:3">
@@ -14378,10 +14403,10 @@
         <v>9</v>
       </c>
       <c r="B813" t="s">
-        <v>957</v>
+        <v>936</v>
       </c>
       <c r="C813" t="s">
-        <v>958</v>
+        <v>937</v>
       </c>
     </row>
     <row r="814" spans="1:3">
@@ -14389,10 +14414,10 @@
         <v>9</v>
       </c>
       <c r="B814" t="s">
-        <v>963</v>
+        <v>946</v>
       </c>
       <c r="C814" t="s">
-        <v>964</v>
+        <v>947</v>
       </c>
     </row>
     <row r="815" spans="1:3">
@@ -14400,10 +14425,10 @@
         <v>9</v>
       </c>
       <c r="B815" t="s">
-        <v>965</v>
+        <v>950</v>
       </c>
       <c r="C815" t="s">
-        <v>966</v>
+        <v>951</v>
       </c>
     </row>
     <row r="816" spans="1:3">
@@ -14411,10 +14436,10 @@
         <v>9</v>
       </c>
       <c r="B816" t="s">
-        <v>967</v>
+        <v>954</v>
       </c>
       <c r="C816" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
     </row>
     <row r="817" spans="1:3">
@@ -14422,10 +14447,10 @@
         <v>9</v>
       </c>
       <c r="B817" t="s">
-        <v>975</v>
+        <v>957</v>
       </c>
       <c r="C817" t="s">
-        <v>976</v>
+        <v>958</v>
       </c>
     </row>
     <row r="818" spans="1:3">
@@ -14433,10 +14458,10 @@
         <v>9</v>
       </c>
       <c r="B818" t="s">
-        <v>982</v>
+        <v>963</v>
       </c>
       <c r="C818" t="s">
-        <v>983</v>
+        <v>964</v>
       </c>
     </row>
     <row r="819" spans="1:3">
@@ -14444,10 +14469,10 @@
         <v>9</v>
       </c>
       <c r="B819" t="s">
-        <v>984</v>
+        <v>965</v>
       </c>
       <c r="C819" t="s">
-        <v>985</v>
+        <v>966</v>
       </c>
     </row>
     <row r="820" spans="1:3">
@@ -14455,10 +14480,10 @@
         <v>9</v>
       </c>
       <c r="B820" t="s">
-        <v>998</v>
+        <v>967</v>
       </c>
       <c r="C820" t="s">
-        <v>999</v>
+        <v>968</v>
       </c>
     </row>
     <row r="821" spans="1:3">
@@ -14466,10 +14491,10 @@
         <v>9</v>
       </c>
       <c r="B821" t="s">
-        <v>1000</v>
+        <v>975</v>
       </c>
       <c r="C821" t="s">
-        <v>1001</v>
+        <v>976</v>
       </c>
     </row>
     <row r="822" spans="1:3">
@@ -14477,10 +14502,10 @@
         <v>9</v>
       </c>
       <c r="B822" t="s">
-        <v>1002</v>
+        <v>982</v>
       </c>
       <c r="C822" t="s">
-        <v>1003</v>
+        <v>983</v>
       </c>
     </row>
     <row r="823" spans="1:3">
@@ -14488,10 +14513,10 @@
         <v>9</v>
       </c>
       <c r="B823" t="s">
-        <v>1004</v>
+        <v>984</v>
       </c>
       <c r="C823" t="s">
-        <v>1005</v>
+        <v>985</v>
       </c>
     </row>
     <row r="824" spans="1:3">
@@ -14499,10 +14524,10 @@
         <v>9</v>
       </c>
       <c r="B824" t="s">
-        <v>1010</v>
+        <v>998</v>
       </c>
       <c r="C824" t="s">
-        <v>1011</v>
+        <v>999</v>
       </c>
     </row>
     <row r="825" spans="1:3">
@@ -14510,10 +14535,10 @@
         <v>9</v>
       </c>
       <c r="B825" t="s">
-        <v>1012</v>
+        <v>1000</v>
       </c>
       <c r="C825" t="s">
-        <v>1013</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="826" spans="1:3">
@@ -14521,10 +14546,10 @@
         <v>9</v>
       </c>
       <c r="B826" t="s">
-        <v>1014</v>
+        <v>1002</v>
       </c>
       <c r="C826" t="s">
-        <v>1015</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="827" spans="1:3">
@@ -14532,10 +14557,10 @@
         <v>9</v>
       </c>
       <c r="B827" t="s">
-        <v>1018</v>
+        <v>1004</v>
       </c>
       <c r="C827" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="828" spans="1:3">
@@ -14543,10 +14568,10 @@
         <v>9</v>
       </c>
       <c r="B828" t="s">
-        <v>1026</v>
+        <v>1010</v>
       </c>
       <c r="C828" t="s">
-        <v>1027</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="829" spans="1:3">
@@ -14554,10 +14579,10 @@
         <v>9</v>
       </c>
       <c r="B829" t="s">
-        <v>1028</v>
+        <v>1012</v>
       </c>
       <c r="C829" t="s">
-        <v>1029</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="830" spans="1:3">
@@ -14565,10 +14590,10 @@
         <v>9</v>
       </c>
       <c r="B830" t="s">
-        <v>1036</v>
+        <v>1014</v>
       </c>
       <c r="C830" t="s">
-        <v>1037</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="831" spans="1:3">
@@ -14576,10 +14601,10 @@
         <v>9</v>
       </c>
       <c r="B831" t="s">
-        <v>1038</v>
+        <v>1018</v>
       </c>
       <c r="C831" t="s">
-        <v>467</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="832" spans="1:3">
@@ -14587,10 +14612,10 @@
         <v>9</v>
       </c>
       <c r="B832" t="s">
-        <v>1039</v>
+        <v>1026</v>
       </c>
       <c r="C832" t="s">
-        <v>1040</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="833" spans="1:3">
@@ -14598,10 +14623,10 @@
         <v>9</v>
       </c>
       <c r="B833" t="s">
-        <v>1041</v>
+        <v>1028</v>
       </c>
       <c r="C833" t="s">
-        <v>1042</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="834" spans="1:3">
@@ -14609,10 +14634,10 @@
         <v>9</v>
       </c>
       <c r="B834" t="s">
-        <v>1043</v>
+        <v>1036</v>
       </c>
       <c r="C834" t="s">
-        <v>1044</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="835" spans="1:3">
@@ -14620,10 +14645,10 @@
         <v>9</v>
       </c>
       <c r="B835" t="s">
-        <v>1051</v>
+        <v>1038</v>
       </c>
       <c r="C835" t="s">
-        <v>1052</v>
+        <v>467</v>
       </c>
     </row>
     <row r="836" spans="1:3">
@@ -14631,10 +14656,10 @@
         <v>9</v>
       </c>
       <c r="B836" t="s">
-        <v>1057</v>
+        <v>1039</v>
       </c>
       <c r="C836" t="s">
-        <v>1060</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="837" spans="1:3">
@@ -14642,10 +14667,10 @@
         <v>9</v>
       </c>
       <c r="B837" t="s">
-        <v>1061</v>
+        <v>1041</v>
       </c>
       <c r="C837" t="s">
-        <v>1062</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="838" spans="1:3">
@@ -14653,10 +14678,10 @@
         <v>9</v>
       </c>
       <c r="B838" t="s">
-        <v>1063</v>
+        <v>1043</v>
       </c>
       <c r="C838" t="s">
-        <v>1064</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="839" spans="1:3">
@@ -14664,10 +14689,10 @@
         <v>9</v>
       </c>
       <c r="B839" t="s">
-        <v>1065</v>
+        <v>1051</v>
       </c>
       <c r="C839" t="s">
-        <v>1066</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="840" spans="1:3">
@@ -14675,10 +14700,10 @@
         <v>9</v>
       </c>
       <c r="B840" t="s">
-        <v>1067</v>
+        <v>1057</v>
       </c>
       <c r="C840" t="s">
-        <v>1068</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="841" spans="1:3">
@@ -14686,10 +14711,10 @@
         <v>9</v>
       </c>
       <c r="B841" t="s">
-        <v>1069</v>
+        <v>1061</v>
       </c>
       <c r="C841" t="s">
-        <v>1071</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="842" spans="1:3">
@@ -14697,10 +14722,10 @@
         <v>9</v>
       </c>
       <c r="B842" t="s">
-        <v>1082</v>
+        <v>1063</v>
       </c>
       <c r="C842" t="s">
-        <v>1003</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="843" spans="1:3">
@@ -14708,10 +14733,10 @@
         <v>9</v>
       </c>
       <c r="B843" t="s">
-        <v>1083</v>
+        <v>1065</v>
       </c>
       <c r="C843" t="s">
-        <v>1084</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="844" spans="1:3">
@@ -14719,10 +14744,10 @@
         <v>9</v>
       </c>
       <c r="B844" t="s">
-        <v>1085</v>
+        <v>1067</v>
       </c>
       <c r="C844" t="s">
-        <v>1086</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="845" spans="1:3">
@@ -14730,10 +14755,10 @@
         <v>9</v>
       </c>
       <c r="B845" t="s">
-        <v>1089</v>
+        <v>1069</v>
       </c>
       <c r="C845" t="s">
-        <v>1090</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="846" spans="1:3">
@@ -14741,10 +14766,10 @@
         <v>9</v>
       </c>
       <c r="B846" t="s">
-        <v>1091</v>
+        <v>1082</v>
       </c>
       <c r="C846" t="s">
-        <v>1092</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="847" spans="1:3">
@@ -14752,10 +14777,10 @@
         <v>9</v>
       </c>
       <c r="B847" t="s">
-        <v>1095</v>
+        <v>1083</v>
       </c>
       <c r="C847" t="s">
-        <v>1096</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="848" spans="1:3">
@@ -14763,10 +14788,10 @@
         <v>9</v>
       </c>
       <c r="B848" t="s">
-        <v>1097</v>
+        <v>1085</v>
       </c>
       <c r="C848" t="s">
-        <v>1099</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="849" spans="1:3">
@@ -14774,10 +14799,10 @@
         <v>9</v>
       </c>
       <c r="B849" t="s">
-        <v>1106</v>
+        <v>1089</v>
       </c>
       <c r="C849" t="s">
-        <v>1108</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="850" spans="1:3">
@@ -14785,10 +14810,10 @@
         <v>9</v>
       </c>
       <c r="B850" t="s">
-        <v>1109</v>
+        <v>1091</v>
       </c>
       <c r="C850" t="s">
-        <v>1110</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="851" spans="1:3">
@@ -14796,10 +14821,10 @@
         <v>9</v>
       </c>
       <c r="B851" t="s">
-        <v>1122</v>
+        <v>1095</v>
       </c>
       <c r="C851" t="s">
-        <v>1123</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="852" spans="1:3">
@@ -14807,10 +14832,10 @@
         <v>9</v>
       </c>
       <c r="B852" t="s">
-        <v>1134</v>
+        <v>1097</v>
       </c>
       <c r="C852" t="s">
-        <v>1135</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="853" spans="1:3">
@@ -14818,10 +14843,10 @@
         <v>9</v>
       </c>
       <c r="B853" t="s">
-        <v>1136</v>
+        <v>1106</v>
       </c>
       <c r="C853" t="s">
-        <v>1137</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="854" spans="1:3">
@@ -14829,10 +14854,10 @@
         <v>9</v>
       </c>
       <c r="B854" t="s">
-        <v>1140</v>
+        <v>1109</v>
       </c>
       <c r="C854" t="s">
-        <v>1141</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="855" spans="1:3">
@@ -14840,10 +14865,10 @@
         <v>9</v>
       </c>
       <c r="B855" t="s">
-        <v>1142</v>
+        <v>1122</v>
       </c>
       <c r="C855" t="s">
-        <v>1143</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="856" spans="1:3">
@@ -14851,10 +14876,10 @@
         <v>9</v>
       </c>
       <c r="B856" t="s">
-        <v>1144</v>
+        <v>1134</v>
       </c>
       <c r="C856" t="s">
-        <v>1145</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="857" spans="1:3">
@@ -14862,10 +14887,10 @@
         <v>9</v>
       </c>
       <c r="B857" t="s">
-        <v>1152</v>
+        <v>1136</v>
       </c>
       <c r="C857" t="s">
-        <v>1154</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="858" spans="1:3">
@@ -14873,10 +14898,10 @@
         <v>9</v>
       </c>
       <c r="B858" t="s">
-        <v>1155</v>
+        <v>1140</v>
       </c>
       <c r="C858" t="s">
-        <v>1156</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="859" spans="1:3">
@@ -14884,10 +14909,10 @@
         <v>9</v>
       </c>
       <c r="B859" t="s">
-        <v>1157</v>
+        <v>1142</v>
       </c>
       <c r="C859" t="s">
-        <v>1158</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="860" spans="1:3">
@@ -14895,10 +14920,10 @@
         <v>9</v>
       </c>
       <c r="B860" t="s">
-        <v>1161</v>
+        <v>1144</v>
       </c>
       <c r="C860" t="s">
-        <v>1162</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="861" spans="1:3">
@@ -14906,10 +14931,10 @@
         <v>9</v>
       </c>
       <c r="B861" t="s">
-        <v>1163</v>
+        <v>1152</v>
       </c>
       <c r="C861" t="s">
-        <v>1164</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="862" spans="1:3">
@@ -14917,10 +14942,10 @@
         <v>9</v>
       </c>
       <c r="B862" t="s">
-        <v>1165</v>
+        <v>1155</v>
       </c>
       <c r="C862" t="s">
-        <v>1166</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="863" spans="1:3">
@@ -14928,10 +14953,10 @@
         <v>9</v>
       </c>
       <c r="B863" t="s">
-        <v>1167</v>
+        <v>1157</v>
       </c>
       <c r="C863" t="s">
-        <v>1168</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="864" spans="1:3">
@@ -14939,10 +14964,10 @@
         <v>9</v>
       </c>
       <c r="B864" t="s">
-        <v>1169</v>
+        <v>1161</v>
       </c>
       <c r="C864" t="s">
-        <v>1170</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="865" spans="1:3">
@@ -14950,10 +14975,10 @@
         <v>9</v>
       </c>
       <c r="B865" t="s">
-        <v>1171</v>
+        <v>1163</v>
       </c>
       <c r="C865" t="s">
-        <v>1172</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="866" spans="1:3">
@@ -14961,10 +14986,10 @@
         <v>9</v>
       </c>
       <c r="B866" t="s">
-        <v>1173</v>
+        <v>1165</v>
       </c>
       <c r="C866" t="s">
-        <v>1174</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="867" spans="1:3">
@@ -14972,10 +14997,10 @@
         <v>9</v>
       </c>
       <c r="B867" t="s">
-        <v>1175</v>
+        <v>1167</v>
       </c>
       <c r="C867" t="s">
-        <v>1176</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="868" spans="1:3">
@@ -14983,10 +15008,10 @@
         <v>9</v>
       </c>
       <c r="B868" t="s">
-        <v>1177</v>
+        <v>1169</v>
       </c>
       <c r="C868" t="s">
-        <v>1178</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="869" spans="1:3">
@@ -14994,10 +15019,10 @@
         <v>9</v>
       </c>
       <c r="B869" t="s">
-        <v>1179</v>
+        <v>1171</v>
       </c>
       <c r="C869" t="s">
-        <v>1180</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="870" spans="1:3">
@@ -15005,10 +15030,10 @@
         <v>9</v>
       </c>
       <c r="B870" t="s">
-        <v>1183</v>
+        <v>1173</v>
       </c>
       <c r="C870" t="s">
-        <v>1184</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="871" spans="1:3">
@@ -15016,10 +15041,10 @@
         <v>9</v>
       </c>
       <c r="B871" t="s">
-        <v>1185</v>
+        <v>1175</v>
       </c>
       <c r="C871" t="s">
-        <v>1186</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="872" spans="1:3">
@@ -15027,10 +15052,10 @@
         <v>9</v>
       </c>
       <c r="B872" t="s">
-        <v>1195</v>
+        <v>1177</v>
       </c>
       <c r="C872" t="s">
-        <v>1196</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="873" spans="1:3">
@@ -15038,10 +15063,10 @@
         <v>9</v>
       </c>
       <c r="B873" t="s">
-        <v>1197</v>
+        <v>1179</v>
       </c>
       <c r="C873" t="s">
-        <v>1198</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="874" spans="1:3">
@@ -15049,10 +15074,10 @@
         <v>9</v>
       </c>
       <c r="B874" t="s">
-        <v>1199</v>
+        <v>1183</v>
       </c>
       <c r="C874" t="s">
-        <v>1201</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="875" spans="1:3">
@@ -15060,10 +15085,10 @@
         <v>9</v>
       </c>
       <c r="B875" t="s">
-        <v>1204</v>
+        <v>1185</v>
       </c>
       <c r="C875" t="s">
-        <v>1205</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="876" spans="1:3">
@@ -15071,10 +15096,10 @@
         <v>9</v>
       </c>
       <c r="B876" t="s">
-        <v>1206</v>
+        <v>1195</v>
       </c>
       <c r="C876" t="s">
-        <v>1207</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="877" spans="1:3">
@@ -15082,10 +15107,10 @@
         <v>9</v>
       </c>
       <c r="B877" t="s">
-        <v>1220</v>
+        <v>1197</v>
       </c>
       <c r="C877" t="s">
-        <v>1221</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="878" spans="1:3">
@@ -15093,10 +15118,10 @@
         <v>9</v>
       </c>
       <c r="B878" t="s">
-        <v>1222</v>
+        <v>1199</v>
       </c>
       <c r="C878" t="s">
-        <v>1223</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="879" spans="1:3">
@@ -15104,10 +15129,10 @@
         <v>9</v>
       </c>
       <c r="B879" t="s">
-        <v>1226</v>
+        <v>1204</v>
       </c>
       <c r="C879" t="s">
-        <v>1227</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="880" spans="1:3">
@@ -15115,10 +15140,10 @@
         <v>9</v>
       </c>
       <c r="B880" t="s">
-        <v>1228</v>
+        <v>1206</v>
       </c>
       <c r="C880" t="s">
-        <v>1229</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="881" spans="1:3">
@@ -15126,10 +15151,10 @@
         <v>9</v>
       </c>
       <c r="B881" t="s">
-        <v>1230</v>
+        <v>1220</v>
       </c>
       <c r="C881" t="s">
-        <v>1231</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="882" spans="1:3">
@@ -15137,10 +15162,10 @@
         <v>9</v>
       </c>
       <c r="B882" t="s">
-        <v>1240</v>
+        <v>1222</v>
       </c>
       <c r="C882" t="s">
-        <v>1241</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="883" spans="1:3">
@@ -15148,10 +15173,10 @@
         <v>9</v>
       </c>
       <c r="B883" t="s">
-        <v>1242</v>
+        <v>1226</v>
       </c>
       <c r="C883" t="s">
-        <v>1243</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="884" spans="1:3">
@@ -15159,10 +15184,10 @@
         <v>9</v>
       </c>
       <c r="B884" t="s">
-        <v>1244</v>
+        <v>1228</v>
       </c>
       <c r="C884" t="s">
-        <v>1245</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="885" spans="1:3">
@@ -15170,10 +15195,10 @@
         <v>9</v>
       </c>
       <c r="B885" t="s">
-        <v>1250</v>
+        <v>1230</v>
       </c>
       <c r="C885" t="s">
-        <v>1251</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="886" spans="1:3">
@@ -15181,10 +15206,10 @@
         <v>9</v>
       </c>
       <c r="B886" t="s">
-        <v>1262</v>
+        <v>1240</v>
       </c>
       <c r="C886" t="s">
-        <v>1263</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="887" spans="1:3">
@@ -15192,10 +15217,10 @@
         <v>9</v>
       </c>
       <c r="B887" t="s">
-        <v>1264</v>
+        <v>1242</v>
       </c>
       <c r="C887" t="s">
-        <v>1266</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="888" spans="1:3">
@@ -15203,10 +15228,10 @@
         <v>9</v>
       </c>
       <c r="B888" t="s">
-        <v>1277</v>
+        <v>1244</v>
       </c>
       <c r="C888" t="s">
-        <v>1278</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="889" spans="1:3">
@@ -15214,10 +15239,10 @@
         <v>9</v>
       </c>
       <c r="B889" t="s">
-        <v>1286</v>
+        <v>1250</v>
       </c>
       <c r="C889" t="s">
-        <v>1287</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="890" spans="1:3">
@@ -15225,10 +15250,10 @@
         <v>9</v>
       </c>
       <c r="B890" t="s">
-        <v>1293</v>
+        <v>1262</v>
       </c>
       <c r="C890" t="s">
-        <v>1294</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="891" spans="1:3">
@@ -15236,10 +15261,10 @@
         <v>9</v>
       </c>
       <c r="B891" t="s">
-        <v>1299</v>
+        <v>1264</v>
       </c>
       <c r="C891" t="s">
-        <v>1300</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="892" spans="1:3">
@@ -15247,10 +15272,10 @@
         <v>9</v>
       </c>
       <c r="B892" t="s">
-        <v>1304</v>
+        <v>1277</v>
       </c>
       <c r="C892" t="s">
-        <v>1306</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="893" spans="1:3">
@@ -15258,10 +15283,10 @@
         <v>9</v>
       </c>
       <c r="B893" t="s">
-        <v>1313</v>
+        <v>1286</v>
       </c>
       <c r="C893" t="s">
-        <v>1314</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="894" spans="1:3">
@@ -15269,10 +15294,10 @@
         <v>9</v>
       </c>
       <c r="B894" t="s">
-        <v>1317</v>
+        <v>1293</v>
       </c>
       <c r="C894" t="s">
-        <v>1318</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="895" spans="1:3">
@@ -15280,10 +15305,10 @@
         <v>9</v>
       </c>
       <c r="B895" t="s">
-        <v>1319</v>
+        <v>1299</v>
       </c>
       <c r="C895" t="s">
-        <v>1320</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="896" spans="1:3">
@@ -15291,10 +15316,10 @@
         <v>9</v>
       </c>
       <c r="B896" t="s">
-        <v>1329</v>
+        <v>1304</v>
       </c>
       <c r="C896" t="s">
-        <v>1330</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="897" spans="1:3">
@@ -15302,10 +15327,10 @@
         <v>9</v>
       </c>
       <c r="B897" t="s">
-        <v>1331</v>
+        <v>1313</v>
       </c>
       <c r="C897" t="s">
-        <v>1332</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="898" spans="1:3">
@@ -15313,10 +15338,10 @@
         <v>9</v>
       </c>
       <c r="B898" t="s">
-        <v>1335</v>
+        <v>1317</v>
       </c>
       <c r="C898" t="s">
-        <v>1336</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="899" spans="1:3">
@@ -15324,10 +15349,10 @@
         <v>9</v>
       </c>
       <c r="B899" t="s">
-        <v>1337</v>
+        <v>1319</v>
       </c>
       <c r="C899" t="s">
-        <v>1338</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="900" spans="1:3">
@@ -15335,10 +15360,10 @@
         <v>9</v>
       </c>
       <c r="B900" t="s">
-        <v>1345</v>
+        <v>1329</v>
       </c>
       <c r="C900" t="s">
-        <v>1346</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="901" spans="1:3">
@@ -15346,10 +15371,10 @@
         <v>9</v>
       </c>
       <c r="B901" t="s">
-        <v>1347</v>
+        <v>1331</v>
       </c>
       <c r="C901" t="s">
-        <v>1348</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="902" spans="1:3">
@@ -15357,10 +15382,10 @@
         <v>9</v>
       </c>
       <c r="B902" t="s">
-        <v>1349</v>
+        <v>1335</v>
       </c>
       <c r="C902" t="s">
-        <v>1350</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="903" spans="1:3">
@@ -15368,10 +15393,10 @@
         <v>9</v>
       </c>
       <c r="B903" t="s">
-        <v>1351</v>
+        <v>1337</v>
       </c>
       <c r="C903" t="s">
-        <v>1352</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="904" spans="1:3">
@@ -15379,10 +15404,10 @@
         <v>9</v>
       </c>
       <c r="B904" t="s">
-        <v>1353</v>
+        <v>1345</v>
       </c>
       <c r="C904" t="s">
-        <v>1354</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="905" spans="1:3">
@@ -15390,10 +15415,10 @@
         <v>9</v>
       </c>
       <c r="B905" t="s">
-        <v>1355</v>
+        <v>1347</v>
       </c>
       <c r="C905" t="s">
-        <v>1356</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="906" spans="1:3">
@@ -15401,10 +15426,10 @@
         <v>9</v>
       </c>
       <c r="B906" t="s">
-        <v>1363</v>
+        <v>1349</v>
       </c>
       <c r="C906" t="s">
-        <v>1364</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="907" spans="1:3">
@@ -15412,10 +15437,10 @@
         <v>9</v>
       </c>
       <c r="B907" t="s">
-        <v>1367</v>
+        <v>1351</v>
       </c>
       <c r="C907" t="s">
-        <v>1369</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="908" spans="1:3">
@@ -15423,10 +15448,10 @@
         <v>9</v>
       </c>
       <c r="B908" t="s">
-        <v>1374</v>
+        <v>1353</v>
       </c>
       <c r="C908" t="s">
-        <v>1377</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="909" spans="1:3">
@@ -15434,10 +15459,10 @@
         <v>9</v>
       </c>
       <c r="B909" t="s">
-        <v>1390</v>
+        <v>1355</v>
       </c>
       <c r="C909" t="s">
-        <v>1391</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="910" spans="1:3">
@@ -15445,10 +15470,10 @@
         <v>9</v>
       </c>
       <c r="B910" t="s">
-        <v>1392</v>
+        <v>1363</v>
       </c>
       <c r="C910" t="s">
-        <v>1393</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="911" spans="1:3">
@@ -15456,10 +15481,10 @@
         <v>9</v>
       </c>
       <c r="B911" t="s">
-        <v>1394</v>
+        <v>1367</v>
       </c>
       <c r="C911" t="s">
-        <v>1395</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="912" spans="1:3">
@@ -15467,10 +15492,10 @@
         <v>9</v>
       </c>
       <c r="B912" t="s">
-        <v>1400</v>
+        <v>1374</v>
       </c>
       <c r="C912" t="s">
-        <v>1401</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="913" spans="1:3">
@@ -15478,10 +15503,10 @@
         <v>9</v>
       </c>
       <c r="B913" t="s">
-        <v>1402</v>
+        <v>1390</v>
       </c>
       <c r="C913" t="s">
-        <v>1403</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="914" spans="1:3">
@@ -15489,10 +15514,10 @@
         <v>9</v>
       </c>
       <c r="B914" t="s">
-        <v>1404</v>
+        <v>1392</v>
       </c>
       <c r="C914" t="s">
-        <v>1405</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="915" spans="1:3">
@@ -15500,10 +15525,10 @@
         <v>9</v>
       </c>
       <c r="B915" t="s">
-        <v>1406</v>
+        <v>1394</v>
       </c>
       <c r="C915" t="s">
-        <v>1408</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="916" spans="1:3">
@@ -15511,54 +15536,54 @@
         <v>9</v>
       </c>
       <c r="B916" t="s">
-        <v>1422</v>
+        <v>1400</v>
       </c>
       <c r="C916" t="s">
-        <v>1423</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="917" spans="1:3">
       <c r="A917" t="s">
-        <v>7</v>
-      </c>
-      <c r="B917">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="B917" t="s">
+        <v>1402</v>
       </c>
       <c r="C917" t="s">
-        <v>1433</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="918" spans="1:3">
       <c r="A918" t="s">
-        <v>7</v>
-      </c>
-      <c r="B918">
-        <v>2</v>
+        <v>9</v>
+      </c>
+      <c r="B918" t="s">
+        <v>1404</v>
       </c>
       <c r="C918" t="s">
-        <v>1439</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="919" spans="1:3">
       <c r="A919" t="s">
-        <v>7</v>
-      </c>
-      <c r="B919">
-        <v>3</v>
+        <v>9</v>
+      </c>
+      <c r="B919" t="s">
+        <v>1406</v>
       </c>
       <c r="C919" t="s">
-        <v>1447</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="920" spans="1:3">
       <c r="A920" t="s">
-        <v>7</v>
-      </c>
-      <c r="B920">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="B920" t="s">
+        <v>1422</v>
       </c>
       <c r="C920" t="s">
-        <v>1453</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="921" spans="1:3">
@@ -15566,54 +15591,54 @@
         <v>7</v>
       </c>
       <c r="B921">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C921" t="s">
-        <v>1461</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="922" spans="1:3">
       <c r="A922" t="s">
         <v>7</v>
       </c>
-      <c r="B922" t="s">
-        <v>257</v>
+      <c r="B922">
+        <v>2</v>
       </c>
       <c r="C922" t="s">
-        <v>259</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="923" spans="1:3">
       <c r="A923" t="s">
         <v>7</v>
       </c>
-      <c r="B923" t="s">
-        <v>339</v>
+      <c r="B923">
+        <v>3</v>
       </c>
       <c r="C923" t="s">
-        <v>340</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="924" spans="1:3">
       <c r="A924" t="s">
         <v>7</v>
       </c>
-      <c r="B924" t="s">
-        <v>375</v>
+      <c r="B924">
+        <v>4</v>
       </c>
       <c r="C924" t="s">
-        <v>376</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="925" spans="1:3">
       <c r="A925" t="s">
         <v>7</v>
       </c>
-      <c r="B925" t="s">
-        <v>399</v>
+      <c r="B925">
+        <v>5</v>
       </c>
       <c r="C925" t="s">
-        <v>400</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="926" spans="1:3">
@@ -15621,10 +15646,10 @@
         <v>7</v>
       </c>
       <c r="B926" t="s">
-        <v>422</v>
+        <v>257</v>
       </c>
       <c r="C926" t="s">
-        <v>423</v>
+        <v>259</v>
       </c>
     </row>
     <row r="927" spans="1:3">
@@ -15632,10 +15657,10 @@
         <v>7</v>
       </c>
       <c r="B927" t="s">
-        <v>582</v>
+        <v>339</v>
       </c>
       <c r="C927" t="s">
-        <v>583</v>
+        <v>340</v>
       </c>
     </row>
     <row r="928" spans="1:3">
@@ -15643,10 +15668,10 @@
         <v>7</v>
       </c>
       <c r="B928" t="s">
-        <v>745</v>
+        <v>375</v>
       </c>
       <c r="C928" t="s">
-        <v>746</v>
+        <v>376</v>
       </c>
     </row>
     <row r="929" spans="1:3">
@@ -15654,10 +15679,10 @@
         <v>7</v>
       </c>
       <c r="B929" t="s">
-        <v>909</v>
+        <v>399</v>
       </c>
       <c r="C929" t="s">
-        <v>910</v>
+        <v>400</v>
       </c>
     </row>
     <row r="930" spans="1:3">
@@ -15665,10 +15690,10 @@
         <v>7</v>
       </c>
       <c r="B930" t="s">
-        <v>1076</v>
+        <v>422</v>
       </c>
       <c r="C930" t="s">
-        <v>1077</v>
+        <v>423</v>
       </c>
     </row>
     <row r="931" spans="1:3">
@@ -15676,10 +15701,10 @@
         <v>7</v>
       </c>
       <c r="B931" t="s">
-        <v>1159</v>
+        <v>582</v>
       </c>
       <c r="C931" t="s">
-        <v>1160</v>
+        <v>583</v>
       </c>
     </row>
     <row r="932" spans="1:3">
@@ -15687,54 +15712,54 @@
         <v>7</v>
       </c>
       <c r="B932" t="s">
-        <v>1409</v>
+        <v>745</v>
       </c>
       <c r="C932" t="s">
-        <v>1410</v>
+        <v>746</v>
       </c>
     </row>
     <row r="933" spans="1:3">
       <c r="A933" t="s">
-        <v>1649</v>
-      </c>
-      <c r="B933">
-        <v>302</v>
+        <v>7</v>
+      </c>
+      <c r="B933" t="s">
+        <v>909</v>
       </c>
       <c r="C933" t="s">
-        <v>1650</v>
+        <v>910</v>
       </c>
     </row>
     <row r="934" spans="1:3">
       <c r="A934" t="s">
-        <v>1649</v>
-      </c>
-      <c r="B934">
-        <v>303</v>
+        <v>7</v>
+      </c>
+      <c r="B934" t="s">
+        <v>1076</v>
       </c>
       <c r="C934" t="s">
-        <v>1651</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="935" spans="1:3">
       <c r="A935" t="s">
-        <v>1649</v>
-      </c>
-      <c r="B935">
-        <v>304</v>
+        <v>7</v>
+      </c>
+      <c r="B935" t="s">
+        <v>1159</v>
       </c>
       <c r="C935" t="s">
-        <v>1652</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="936" spans="1:3">
       <c r="A936" t="s">
-        <v>1649</v>
-      </c>
-      <c r="B936">
-        <v>305</v>
+        <v>7</v>
+      </c>
+      <c r="B936" t="s">
+        <v>1409</v>
       </c>
       <c r="C936" t="s">
-        <v>1653</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="937" spans="1:3">
@@ -15742,10 +15767,10 @@
         <v>1649</v>
       </c>
       <c r="B937">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C937" t="s">
-        <v>1654</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="938" spans="1:3">
@@ -15753,10 +15778,10 @@
         <v>1649</v>
       </c>
       <c r="B938">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C938" t="s">
-        <v>1655</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="939" spans="1:3">
@@ -15764,10 +15789,10 @@
         <v>1649</v>
       </c>
       <c r="B939">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C939" t="s">
-        <v>1656</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="940" spans="1:3">
@@ -15775,10 +15800,10 @@
         <v>1649</v>
       </c>
       <c r="B940">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C940" t="s">
-        <v>1657</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="941" spans="1:3">
@@ -15786,10 +15811,10 @@
         <v>1649</v>
       </c>
       <c r="B941">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C941" t="s">
-        <v>1658</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="942" spans="1:3">
@@ -15797,10 +15822,10 @@
         <v>1649</v>
       </c>
       <c r="B942">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C942" t="s">
-        <v>1659</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="943" spans="1:3">
@@ -15808,10 +15833,10 @@
         <v>1649</v>
       </c>
       <c r="B943">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C943" t="s">
-        <v>1660</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="944" spans="1:3">
@@ -15819,10 +15844,10 @@
         <v>1649</v>
       </c>
       <c r="B944">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C944" t="s">
-        <v>1661</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="945" spans="1:3">
@@ -15830,10 +15855,10 @@
         <v>1649</v>
       </c>
       <c r="B945">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C945" t="s">
-        <v>1662</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="946" spans="1:3">
@@ -15841,10 +15866,10 @@
         <v>1649</v>
       </c>
       <c r="B946">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C946" t="s">
-        <v>1663</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="947" spans="1:3">
@@ -15852,10 +15877,10 @@
         <v>1649</v>
       </c>
       <c r="B947">
-        <v>401</v>
+        <v>312</v>
       </c>
       <c r="C947" t="s">
-        <v>1664</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="948" spans="1:3">
@@ -15863,10 +15888,10 @@
         <v>1649</v>
       </c>
       <c r="B948">
-        <v>402</v>
+        <v>313</v>
       </c>
       <c r="C948" t="s">
-        <v>1665</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="949" spans="1:3">
@@ -15874,54 +15899,54 @@
         <v>1649</v>
       </c>
       <c r="B949">
-        <v>403</v>
+        <v>314</v>
       </c>
       <c r="C949" t="s">
-        <v>1666</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="950" spans="1:3">
       <c r="A950" t="s">
-        <v>1607</v>
+        <v>1649</v>
       </c>
       <c r="B950">
-        <v>102</v>
+        <v>315</v>
       </c>
       <c r="C950" t="s">
-        <v>1608</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="951" spans="1:3">
       <c r="A951" t="s">
-        <v>1607</v>
+        <v>1649</v>
       </c>
       <c r="B951">
-        <v>103</v>
+        <v>401</v>
       </c>
       <c r="C951" t="s">
-        <v>1609</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="952" spans="1:3">
       <c r="A952" t="s">
-        <v>1607</v>
+        <v>1649</v>
       </c>
       <c r="B952">
-        <v>104</v>
+        <v>402</v>
       </c>
       <c r="C952" t="s">
-        <v>1610</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="953" spans="1:3">
       <c r="A953" t="s">
-        <v>1607</v>
+        <v>1649</v>
       </c>
       <c r="B953">
-        <v>105</v>
+        <v>403</v>
       </c>
       <c r="C953" t="s">
-        <v>1611</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="954" spans="1:3">
@@ -15929,10 +15954,10 @@
         <v>1607</v>
       </c>
       <c r="B954">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C954" t="s">
-        <v>1613</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="955" spans="1:3">
@@ -15940,10 +15965,10 @@
         <v>1607</v>
       </c>
       <c r="B955">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C955" t="s">
-        <v>1614</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="956" spans="1:3">
@@ -15951,10 +15976,10 @@
         <v>1607</v>
       </c>
       <c r="B956">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C956" t="s">
-        <v>1615</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="957" spans="1:3">
@@ -15962,10 +15987,10 @@
         <v>1607</v>
       </c>
       <c r="B957">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C957" t="s">
-        <v>1617</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="958" spans="1:3">
@@ -15973,10 +15998,10 @@
         <v>1607</v>
       </c>
       <c r="B958">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C958" t="s">
-        <v>1620</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="959" spans="1:3">
@@ -15984,10 +16009,10 @@
         <v>1607</v>
       </c>
       <c r="B959">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C959" t="s">
-        <v>1621</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="960" spans="1:3">
@@ -15995,10 +16020,10 @@
         <v>1607</v>
       </c>
       <c r="B960">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C960" t="s">
-        <v>1622</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="961" spans="1:3">
@@ -16006,10 +16031,10 @@
         <v>1607</v>
       </c>
       <c r="B961">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C961" t="s">
-        <v>1623</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="962" spans="1:3">
@@ -16017,10 +16042,10 @@
         <v>1607</v>
       </c>
       <c r="B962">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C962" t="s">
-        <v>1625</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="963" spans="1:3">
@@ -16028,10 +16053,10 @@
         <v>1607</v>
       </c>
       <c r="B963">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C963" t="s">
-        <v>1626</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="964" spans="1:3">
@@ -16039,10 +16064,10 @@
         <v>1607</v>
       </c>
       <c r="B964">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C964" t="s">
-        <v>1627</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="965" spans="1:3">
@@ -16050,10 +16075,10 @@
         <v>1607</v>
       </c>
       <c r="B965">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C965" t="s">
-        <v>1629</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="966" spans="1:3">
@@ -16061,10 +16086,10 @@
         <v>1607</v>
       </c>
       <c r="B966">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C966" t="s">
-        <v>1630</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="967" spans="1:3">
@@ -16072,10 +16097,10 @@
         <v>1607</v>
       </c>
       <c r="B967">
-        <v>201</v>
+        <v>116</v>
       </c>
       <c r="C967" t="s">
-        <v>1635</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="968" spans="1:3">
@@ -16083,10 +16108,10 @@
         <v>1607</v>
       </c>
       <c r="B968">
-        <v>202</v>
+        <v>117</v>
       </c>
       <c r="C968" t="s">
-        <v>1637</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="969" spans="1:3">
@@ -16094,10 +16119,10 @@
         <v>1607</v>
       </c>
       <c r="B969">
-        <v>203</v>
+        <v>118</v>
       </c>
       <c r="C969" t="s">
-        <v>1638</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="970" spans="1:3">
@@ -16105,10 +16130,10 @@
         <v>1607</v>
       </c>
       <c r="B970">
-        <v>204</v>
+        <v>119</v>
       </c>
       <c r="C970" t="s">
-        <v>1639</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="971" spans="1:3">
@@ -16116,10 +16141,10 @@
         <v>1607</v>
       </c>
       <c r="B971">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C971" t="s">
-        <v>1640</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="972" spans="1:3">
@@ -16127,10 +16152,10 @@
         <v>1607</v>
       </c>
       <c r="B972">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C972" t="s">
-        <v>1641</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="973" spans="1:3">
@@ -16138,10 +16163,10 @@
         <v>1607</v>
       </c>
       <c r="B973">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C973" t="s">
-        <v>1642</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="974" spans="1:3">
@@ -16149,10 +16174,10 @@
         <v>1607</v>
       </c>
       <c r="B974">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C974" t="s">
-        <v>1643</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="975" spans="1:3">
@@ -16160,10 +16185,10 @@
         <v>1607</v>
       </c>
       <c r="B975">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C975" t="s">
-        <v>1644</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="976" spans="1:3">
@@ -16171,10 +16196,10 @@
         <v>1607</v>
       </c>
       <c r="B976">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C976" t="s">
-        <v>1645</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="977" spans="1:3">
@@ -16182,10 +16207,10 @@
         <v>1607</v>
       </c>
       <c r="B977">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C977" t="s">
-        <v>1646</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="978" spans="1:3">
@@ -16193,10 +16218,10 @@
         <v>1607</v>
       </c>
       <c r="B978">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C978" t="s">
-        <v>1647</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="979" spans="1:3">
@@ -16204,54 +16229,54 @@
         <v>1607</v>
       </c>
       <c r="B979">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C979" t="s">
-        <v>1648</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="980" spans="1:3">
       <c r="A980" t="s">
-        <v>151</v>
-      </c>
-      <c r="B980" t="s">
-        <v>149</v>
+        <v>1607</v>
+      </c>
+      <c r="B980">
+        <v>210</v>
       </c>
       <c r="C980" t="s">
-        <v>152</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="981" spans="1:3">
       <c r="A981" t="s">
-        <v>151</v>
-      </c>
-      <c r="B981" t="s">
-        <v>260</v>
+        <v>1607</v>
+      </c>
+      <c r="B981">
+        <v>211</v>
       </c>
       <c r="C981" t="s">
-        <v>261</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="982" spans="1:3">
       <c r="A982" t="s">
-        <v>151</v>
-      </c>
-      <c r="B982" t="s">
-        <v>713</v>
+        <v>1607</v>
+      </c>
+      <c r="B982">
+        <v>212</v>
       </c>
       <c r="C982" t="s">
-        <v>714</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="983" spans="1:3">
       <c r="A983" t="s">
-        <v>151</v>
-      </c>
-      <c r="B983" t="s">
-        <v>923</v>
+        <v>1607</v>
+      </c>
+      <c r="B983">
+        <v>213</v>
       </c>
       <c r="C983" t="s">
-        <v>925</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="984" spans="1:3">
@@ -16259,10 +16284,10 @@
         <v>151</v>
       </c>
       <c r="B984" t="s">
-        <v>1214</v>
+        <v>149</v>
       </c>
       <c r="C984" t="s">
-        <v>1215</v>
+        <v>152</v>
       </c>
     </row>
     <row r="985" spans="1:3">
@@ -16270,10 +16295,10 @@
         <v>151</v>
       </c>
       <c r="B985" t="s">
-        <v>151</v>
+        <v>260</v>
       </c>
       <c r="C985" t="s">
-        <v>1413</v>
+        <v>261</v>
       </c>
     </row>
     <row r="986" spans="1:3">
@@ -16281,16 +16306,60 @@
         <v>151</v>
       </c>
       <c r="B986" t="s">
+        <v>713</v>
+      </c>
+      <c r="C986" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="987" spans="1:3">
+      <c r="A987" t="s">
+        <v>151</v>
+      </c>
+      <c r="B987" t="s">
+        <v>923</v>
+      </c>
+      <c r="C987" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="988" spans="1:3">
+      <c r="A988" t="s">
+        <v>151</v>
+      </c>
+      <c r="B988" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C988" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="989" spans="1:3">
+      <c r="A989" t="s">
+        <v>151</v>
+      </c>
+      <c r="B989" t="s">
+        <v>151</v>
+      </c>
+      <c r="C989" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="990" spans="1:3">
+      <c r="A990" t="s">
+        <v>151</v>
+      </c>
+      <c r="B990" t="s">
         <v>1414</v>
       </c>
-      <c r="C986" t="s">
+      <c r="C990" t="s">
         <v>1415</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A1:C986">
-    <sortCondition ref="A1:A986"/>
-    <sortCondition ref="B1:B986"/>
+  <sortState ref="A1:D990">
+    <sortCondition ref="A1:A990"/>
+    <sortCondition ref="B1:B990"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/src/data/ruse-blocks.xlsx
+++ b/src/data/ruse-blocks.xlsx
@@ -9103,7 +9103,7 @@
       <c r="A331" t="s">
         <v>117</v>
       </c>
-      <c r="B331" t="s">
+      <c r="B331" s="1" t="s">
         <v>118</v>
       </c>
       <c r="C331" t="s">
@@ -9114,7 +9114,7 @@
       <c r="A332" t="s">
         <v>117</v>
       </c>
-      <c r="B332" t="s">
+      <c r="B332" s="1" t="s">
         <v>394</v>
       </c>
       <c r="C332" t="s">
@@ -9125,7 +9125,7 @@
       <c r="A333" t="s">
         <v>117</v>
       </c>
-      <c r="B333" t="s">
+      <c r="B333" s="1" t="s">
         <v>816</v>
       </c>
       <c r="C333" t="s">
@@ -9136,7 +9136,7 @@
       <c r="A334" t="s">
         <v>117</v>
       </c>
-      <c r="B334" t="s">
+      <c r="B334" s="1" t="s">
         <v>888</v>
       </c>
       <c r="C334" t="s">
@@ -9147,7 +9147,7 @@
       <c r="A335" t="s">
         <v>117</v>
       </c>
-      <c r="B335" t="s">
+      <c r="B335" s="1" t="s">
         <v>990</v>
       </c>
       <c r="C335" t="s">
@@ -9158,7 +9158,7 @@
       <c r="A336" t="s">
         <v>117</v>
       </c>
-      <c r="B336" t="s">
+      <c r="B336" s="1" t="s">
         <v>1018</v>
       </c>
       <c r="C336" t="s">
@@ -9169,7 +9169,7 @@
       <c r="A337" t="s">
         <v>117</v>
       </c>
-      <c r="B337" t="s">
+      <c r="B337" s="1" t="s">
         <v>1102</v>
       </c>
       <c r="C337" t="s">
@@ -9180,7 +9180,7 @@
       <c r="A338" t="s">
         <v>117</v>
       </c>
-      <c r="B338" t="s">
+      <c r="B338" s="1" t="s">
         <v>1106</v>
       </c>
       <c r="C338" t="s">
@@ -9191,7 +9191,7 @@
       <c r="A339" t="s">
         <v>117</v>
       </c>
-      <c r="B339" t="s">
+      <c r="B339" s="1" t="s">
         <v>1126</v>
       </c>
       <c r="C339" t="s">
@@ -9202,7 +9202,7 @@
       <c r="A340" t="s">
         <v>117</v>
       </c>
-      <c r="B340" t="s">
+      <c r="B340" s="1" t="s">
         <v>1130</v>
       </c>
       <c r="C340" t="s">
@@ -9213,7 +9213,7 @@
       <c r="A341" t="s">
         <v>117</v>
       </c>
-      <c r="B341" t="s">
+      <c r="B341" s="1" t="s">
         <v>1386</v>
       </c>
       <c r="C341" t="s">
@@ -9224,7 +9224,7 @@
       <c r="A342" t="s">
         <v>550</v>
       </c>
-      <c r="B342" t="s">
+      <c r="B342" s="1" t="s">
         <v>551</v>
       </c>
       <c r="C342" t="s">
@@ -9235,7 +9235,7 @@
       <c r="A343" t="s">
         <v>550</v>
       </c>
-      <c r="B343" t="s">
+      <c r="B343" s="1" t="s">
         <v>553</v>
       </c>
       <c r="C343" t="s">
@@ -9246,7 +9246,7 @@
       <c r="A344" t="s">
         <v>550</v>
       </c>
-      <c r="B344" t="s">
+      <c r="B344" s="1" t="s">
         <v>692</v>
       </c>
       <c r="C344" t="s">
@@ -9257,7 +9257,7 @@
       <c r="A345" t="s">
         <v>550</v>
       </c>
-      <c r="B345" t="s">
+      <c r="B345" s="1" t="s">
         <v>1016</v>
       </c>
       <c r="C345" t="s">
@@ -9268,7 +9268,7 @@
       <c r="A346" t="s">
         <v>550</v>
       </c>
-      <c r="B346" t="s">
+      <c r="B346" s="1" t="s">
         <v>1047</v>
       </c>
       <c r="C346" t="s">
@@ -9279,7 +9279,7 @@
       <c r="A347" t="s">
         <v>550</v>
       </c>
-      <c r="B347" t="s">
+      <c r="B347" s="1" t="s">
         <v>1049</v>
       </c>
       <c r="C347" t="s">
@@ -9290,7 +9290,7 @@
       <c r="A348" t="s">
         <v>550</v>
       </c>
-      <c r="B348" t="s">
+      <c r="B348" s="1" t="s">
         <v>1074</v>
       </c>
       <c r="C348" t="s">

--- a/src/data/ruse-blocks.xlsx
+++ b/src/data/ruse-blocks.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2732" uniqueCount="1682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2738" uniqueCount="1684">
   <si>
     <t>Дружба 1</t>
   </si>
@@ -5060,6 +5060,12 @@
   </si>
   <si>
     <t>ул. Бели хризантеми 9</t>
+  </si>
+  <si>
+    <t>ул. Солун 25</t>
+  </si>
+  <si>
+    <t>ул. Мехомия 7</t>
   </si>
 </sst>
 </file>
@@ -5451,10 +5457,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D991"/>
+  <dimension ref="A1:D993"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="15.5" customWidth="1"/>
+    <col min="1" max="1" width="17.8984375" customWidth="1"/>
     <col min="2" max="2" width="22.09765625" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
     <col min="4" max="4" width="12.09765625" customWidth="1"/>
@@ -16308,7 +16314,7 @@
       <c r="A986" t="s">
         <v>151</v>
       </c>
-      <c r="B986" t="s">
+      <c r="B986" s="1" t="s">
         <v>260</v>
       </c>
       <c r="C986" t="s">
@@ -16341,7 +16347,7 @@
       <c r="A989" t="s">
         <v>151</v>
       </c>
-      <c r="B989" t="s">
+      <c r="B989" s="1" t="s">
         <v>1214</v>
       </c>
       <c r="C989" t="s">
@@ -16352,7 +16358,7 @@
       <c r="A990" t="s">
         <v>151</v>
       </c>
-      <c r="B990" t="s">
+      <c r="B990" s="1" t="s">
         <v>151</v>
       </c>
       <c r="C990" t="s">
@@ -16368,6 +16374,28 @@
       </c>
       <c r="C991" t="s">
         <v>1415</v>
+      </c>
+    </row>
+    <row r="992" spans="1:3">
+      <c r="A992" t="s">
+        <v>151</v>
+      </c>
+      <c r="B992" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="C992" t="s">
+        <v>1682</v>
+      </c>
+    </row>
+    <row r="993" spans="1:3">
+      <c r="A993" t="s">
+        <v>151</v>
+      </c>
+      <c r="B993" s="1" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C993" t="s">
+        <v>1683</v>
       </c>
     </row>
   </sheetData>

--- a/src/data/ruse-blocks.xlsx
+++ b/src/data/ruse-blocks.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2732" uniqueCount="1682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2738" uniqueCount="1684">
   <si>
     <t>Дружба 1</t>
   </si>
@@ -5060,6 +5060,12 @@
   </si>
   <si>
     <t>ул. Бели хризантеми 9</t>
+  </si>
+  <si>
+    <t>ул. Солун 25</t>
+  </si>
+  <si>
+    <t>ул. Мехомия 7</t>
   </si>
 </sst>
 </file>
@@ -5451,10 +5457,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D991"/>
+  <dimension ref="A1:D993"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="15.5" customWidth="1"/>
+    <col min="1" max="1" width="17.8984375" customWidth="1"/>
     <col min="2" max="2" width="22.09765625" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
     <col min="4" max="4" width="12.09765625" customWidth="1"/>
@@ -16308,7 +16314,7 @@
       <c r="A986" t="s">
         <v>151</v>
       </c>
-      <c r="B986" t="s">
+      <c r="B986" s="1" t="s">
         <v>260</v>
       </c>
       <c r="C986" t="s">
@@ -16330,7 +16336,7 @@
       <c r="A988" t="s">
         <v>151</v>
       </c>
-      <c r="B988" t="s">
+      <c r="B988" s="1" t="s">
         <v>923</v>
       </c>
       <c r="C988" t="s">
@@ -16341,7 +16347,7 @@
       <c r="A989" t="s">
         <v>151</v>
       </c>
-      <c r="B989" t="s">
+      <c r="B989" s="1" t="s">
         <v>1214</v>
       </c>
       <c r="C989" t="s">
@@ -16352,7 +16358,7 @@
       <c r="A990" t="s">
         <v>151</v>
       </c>
-      <c r="B990" t="s">
+      <c r="B990" s="1" t="s">
         <v>151</v>
       </c>
       <c r="C990" t="s">
@@ -16368,6 +16374,28 @@
       </c>
       <c r="C991" t="s">
         <v>1415</v>
+      </c>
+    </row>
+    <row r="992" spans="1:3">
+      <c r="A992" t="s">
+        <v>151</v>
+      </c>
+      <c r="B992" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="C992" t="s">
+        <v>1682</v>
+      </c>
+    </row>
+    <row r="993" spans="1:3">
+      <c r="A993" t="s">
+        <v>151</v>
+      </c>
+      <c r="B993" s="1" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C993" t="s">
+        <v>1683</v>
       </c>
     </row>
   </sheetData>

--- a/src/data/ruse-blocks.xlsx
+++ b/src/data/ruse-blocks.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2738" uniqueCount="1684">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2741" uniqueCount="1686">
   <si>
     <t>Дружба 1</t>
   </si>
@@ -5066,6 +5066,12 @@
   </si>
   <si>
     <t>ул. Мехомия 7</t>
+  </si>
+  <si>
+    <t>ул. Тича 20</t>
+  </si>
+  <si>
+    <t>Колос</t>
   </si>
 </sst>
 </file>
@@ -5457,7 +5463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D993"/>
+  <dimension ref="A1:D994"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="17.8984375" customWidth="1"/>
@@ -10572,7 +10578,7 @@
       <c r="A464" t="s">
         <v>113</v>
       </c>
-      <c r="B464" t="s">
+      <c r="B464" s="1" t="s">
         <v>136</v>
       </c>
       <c r="C464" t="s">
@@ -10594,7 +10600,7 @@
       <c r="A466" t="s">
         <v>113</v>
       </c>
-      <c r="B466" t="s">
+      <c r="B466" s="1" t="s">
         <v>251</v>
       </c>
       <c r="C466" t="s">
@@ -10605,7 +10611,7 @@
       <c r="A467" t="s">
         <v>113</v>
       </c>
-      <c r="B467" t="s">
+      <c r="B467" s="1" t="s">
         <v>267</v>
       </c>
       <c r="C467" t="s">
@@ -10616,7 +10622,7 @@
       <c r="A468" t="s">
         <v>113</v>
       </c>
-      <c r="B468" t="s">
+      <c r="B468" s="1" t="s">
         <v>364</v>
       </c>
       <c r="C468" t="s">
@@ -10638,7 +10644,7 @@
       <c r="A470" t="s">
         <v>113</v>
       </c>
-      <c r="B470" t="s">
+      <c r="B470" s="1" t="s">
         <v>624</v>
       </c>
       <c r="C470" t="s">
@@ -10649,7 +10655,7 @@
       <c r="A471" t="s">
         <v>113</v>
       </c>
-      <c r="B471" t="s">
+      <c r="B471" s="1" t="s">
         <v>626</v>
       </c>
       <c r="C471" t="s">
@@ -10660,11 +10666,11 @@
       <c r="A472" t="s">
         <v>113</v>
       </c>
-      <c r="B472" t="s">
-        <v>630</v>
+      <c r="B472" s="1" t="s">
+        <v>1685</v>
       </c>
       <c r="C472" t="s">
-        <v>631</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="473" spans="1:3">
@@ -10672,21 +10678,21 @@
         <v>113</v>
       </c>
       <c r="B473" t="s">
-        <v>650</v>
+        <v>630</v>
       </c>
       <c r="C473" t="s">
-        <v>651</v>
+        <v>631</v>
       </c>
     </row>
     <row r="474" spans="1:3">
       <c r="A474" t="s">
         <v>113</v>
       </c>
-      <c r="B474" t="s">
-        <v>747</v>
+      <c r="B474" s="1" t="s">
+        <v>650</v>
       </c>
       <c r="C474" t="s">
-        <v>748</v>
+        <v>651</v>
       </c>
     </row>
     <row r="475" spans="1:3">
@@ -10694,10 +10700,10 @@
         <v>113</v>
       </c>
       <c r="B475" t="s">
-        <v>757</v>
+        <v>747</v>
       </c>
       <c r="C475" t="s">
-        <v>758</v>
+        <v>748</v>
       </c>
     </row>
     <row r="476" spans="1:3">
@@ -10705,32 +10711,32 @@
         <v>113</v>
       </c>
       <c r="B476" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="C476" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
     </row>
     <row r="477" spans="1:3">
       <c r="A477" t="s">
         <v>113</v>
       </c>
-      <c r="B477" t="s">
-        <v>780</v>
+      <c r="B477" s="1" t="s">
+        <v>763</v>
       </c>
       <c r="C477" t="s">
-        <v>781</v>
+        <v>764</v>
       </c>
     </row>
     <row r="478" spans="1:3">
       <c r="A478" t="s">
         <v>113</v>
       </c>
-      <c r="B478" t="s">
-        <v>802</v>
+      <c r="B478" s="1" t="s">
+        <v>780</v>
       </c>
       <c r="C478" t="s">
-        <v>803</v>
+        <v>781</v>
       </c>
     </row>
     <row r="479" spans="1:3">
@@ -10738,10 +10744,10 @@
         <v>113</v>
       </c>
       <c r="B479" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C479" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
     </row>
     <row r="480" spans="1:3">
@@ -10749,10 +10755,10 @@
         <v>113</v>
       </c>
       <c r="B480" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="C480" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
     </row>
     <row r="481" spans="1:3">
@@ -10760,21 +10766,21 @@
         <v>113</v>
       </c>
       <c r="B481" t="s">
-        <v>940</v>
+        <v>809</v>
       </c>
       <c r="C481" t="s">
-        <v>941</v>
+        <v>810</v>
       </c>
     </row>
     <row r="482" spans="1:3">
       <c r="A482" t="s">
         <v>113</v>
       </c>
-      <c r="B482" t="s">
-        <v>973</v>
+      <c r="B482" s="1" t="s">
+        <v>940</v>
       </c>
       <c r="C482" t="s">
-        <v>974</v>
+        <v>941</v>
       </c>
     </row>
     <row r="483" spans="1:3">
@@ -10782,21 +10788,21 @@
         <v>113</v>
       </c>
       <c r="B483" t="s">
-        <v>1148</v>
+        <v>973</v>
       </c>
       <c r="C483" t="s">
-        <v>1149</v>
+        <v>974</v>
       </c>
     </row>
     <row r="484" spans="1:3">
       <c r="A484" t="s">
         <v>113</v>
       </c>
-      <c r="B484" t="s">
-        <v>1193</v>
+      <c r="B484" s="1" t="s">
+        <v>1148</v>
       </c>
       <c r="C484" t="s">
-        <v>1194</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="485" spans="1:3">
@@ -10804,43 +10810,43 @@
         <v>113</v>
       </c>
       <c r="B485" t="s">
-        <v>1232</v>
+        <v>1193</v>
       </c>
       <c r="C485" t="s">
-        <v>1233</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="486" spans="1:3">
       <c r="A486" t="s">
         <v>113</v>
       </c>
-      <c r="B486" t="s">
-        <v>1252</v>
+      <c r="B486" s="1" t="s">
+        <v>1232</v>
       </c>
       <c r="C486" t="s">
-        <v>1253</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="487" spans="1:3">
       <c r="A487" t="s">
         <v>113</v>
       </c>
-      <c r="B487" t="s">
-        <v>1267</v>
+      <c r="B487" s="1" t="s">
+        <v>1252</v>
       </c>
       <c r="C487" t="s">
-        <v>1268</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="488" spans="1:3">
       <c r="A488" t="s">
-        <v>24</v>
+        <v>113</v>
       </c>
       <c r="B488" t="s">
-        <v>25</v>
+        <v>1267</v>
       </c>
       <c r="C488" t="s">
-        <v>26</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="489" spans="1:3">
@@ -10848,10 +10854,10 @@
         <v>24</v>
       </c>
       <c r="B489" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C489" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="490" spans="1:3">
@@ -10859,10 +10865,10 @@
         <v>24</v>
       </c>
       <c r="B490" t="s">
-        <v>120</v>
+        <v>27</v>
       </c>
       <c r="C490" t="s">
-        <v>121</v>
+        <v>28</v>
       </c>
     </row>
     <row r="491" spans="1:3">
@@ -10870,10 +10876,10 @@
         <v>24</v>
       </c>
       <c r="B491" t="s">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="C491" t="s">
-        <v>176</v>
+        <v>121</v>
       </c>
     </row>
     <row r="492" spans="1:3">
@@ -10881,10 +10887,10 @@
         <v>24</v>
       </c>
       <c r="B492" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="C492" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
     </row>
     <row r="493" spans="1:3">
@@ -10892,10 +10898,10 @@
         <v>24</v>
       </c>
       <c r="B493" t="s">
-        <v>221</v>
+        <v>196</v>
       </c>
       <c r="C493" t="s">
-        <v>222</v>
+        <v>197</v>
       </c>
     </row>
     <row r="494" spans="1:3">
@@ -10903,10 +10909,10 @@
         <v>24</v>
       </c>
       <c r="B494" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C494" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
     </row>
     <row r="495" spans="1:3">
@@ -10914,10 +10920,10 @@
         <v>24</v>
       </c>
       <c r="B495" t="s">
-        <v>283</v>
+        <v>227</v>
       </c>
       <c r="C495" t="s">
-        <v>284</v>
+        <v>228</v>
       </c>
     </row>
     <row r="496" spans="1:3">
@@ -10925,10 +10931,10 @@
         <v>24</v>
       </c>
       <c r="B496" t="s">
-        <v>346</v>
+        <v>283</v>
       </c>
       <c r="C496" t="s">
-        <v>347</v>
+        <v>284</v>
       </c>
     </row>
     <row r="497" spans="1:3">
@@ -10936,10 +10942,10 @@
         <v>24</v>
       </c>
       <c r="B497" t="s">
-        <v>369</v>
+        <v>346</v>
       </c>
       <c r="C497" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
     </row>
     <row r="498" spans="1:3">
@@ -10947,10 +10953,10 @@
         <v>24</v>
       </c>
       <c r="B498" t="s">
-        <v>464</v>
+        <v>369</v>
       </c>
       <c r="C498" t="s">
-        <v>465</v>
+        <v>370</v>
       </c>
     </row>
     <row r="499" spans="1:3">
@@ -10958,10 +10964,10 @@
         <v>24</v>
       </c>
       <c r="B499" t="s">
-        <v>494</v>
+        <v>464</v>
       </c>
       <c r="C499" t="s">
-        <v>495</v>
+        <v>465</v>
       </c>
     </row>
     <row r="500" spans="1:3">
@@ -10969,10 +10975,10 @@
         <v>24</v>
       </c>
       <c r="B500" t="s">
-        <v>545</v>
+        <v>494</v>
       </c>
       <c r="C500" t="s">
-        <v>546</v>
+        <v>495</v>
       </c>
     </row>
     <row r="501" spans="1:3">
@@ -10980,10 +10986,10 @@
         <v>24</v>
       </c>
       <c r="B501" t="s">
-        <v>605</v>
+        <v>545</v>
       </c>
       <c r="C501" t="s">
-        <v>606</v>
+        <v>546</v>
       </c>
     </row>
     <row r="502" spans="1:3">
@@ -10991,10 +10997,10 @@
         <v>24</v>
       </c>
       <c r="B502" t="s">
-        <v>618</v>
+        <v>605</v>
       </c>
       <c r="C502" t="s">
-        <v>619</v>
+        <v>606</v>
       </c>
     </row>
     <row r="503" spans="1:3">
@@ -11002,10 +11008,10 @@
         <v>24</v>
       </c>
       <c r="B503" t="s">
-        <v>662</v>
+        <v>618</v>
       </c>
       <c r="C503" t="s">
-        <v>663</v>
+        <v>619</v>
       </c>
     </row>
     <row r="504" spans="1:3">
@@ -11013,10 +11019,10 @@
         <v>24</v>
       </c>
       <c r="B504" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="C504" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
     </row>
     <row r="505" spans="1:3">
@@ -11024,10 +11030,10 @@
         <v>24</v>
       </c>
       <c r="B505" t="s">
-        <v>903</v>
+        <v>670</v>
       </c>
       <c r="C505" t="s">
-        <v>904</v>
+        <v>671</v>
       </c>
     </row>
     <row r="506" spans="1:3">
@@ -11035,10 +11041,10 @@
         <v>24</v>
       </c>
       <c r="B506" t="s">
-        <v>986</v>
+        <v>903</v>
       </c>
       <c r="C506" t="s">
-        <v>987</v>
+        <v>904</v>
       </c>
     </row>
     <row r="507" spans="1:3">
@@ -11046,10 +11052,10 @@
         <v>24</v>
       </c>
       <c r="B507" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="C507" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
     </row>
     <row r="508" spans="1:3">
@@ -11057,10 +11063,10 @@
         <v>24</v>
       </c>
       <c r="B508" t="s">
-        <v>1006</v>
+        <v>992</v>
       </c>
       <c r="C508" t="s">
-        <v>1007</v>
+        <v>993</v>
       </c>
     </row>
     <row r="509" spans="1:3">
@@ -11068,10 +11074,10 @@
         <v>24</v>
       </c>
       <c r="B509" t="s">
-        <v>1111</v>
+        <v>1006</v>
       </c>
       <c r="C509" t="s">
-        <v>1112</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="510" spans="1:3">
@@ -11079,10 +11085,10 @@
         <v>24</v>
       </c>
       <c r="B510" t="s">
-        <v>1132</v>
+        <v>1111</v>
       </c>
       <c r="C510" t="s">
-        <v>1133</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="511" spans="1:3">
@@ -11090,10 +11096,10 @@
         <v>24</v>
       </c>
       <c r="B511" t="s">
-        <v>1202</v>
+        <v>1132</v>
       </c>
       <c r="C511" t="s">
-        <v>1203</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="512" spans="1:3">
@@ -11101,10 +11107,10 @@
         <v>24</v>
       </c>
       <c r="B512" t="s">
-        <v>1234</v>
+        <v>1202</v>
       </c>
       <c r="C512" t="s">
-        <v>1235</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="513" spans="1:3">
@@ -11112,10 +11118,10 @@
         <v>24</v>
       </c>
       <c r="B513" t="s">
-        <v>1248</v>
+        <v>1234</v>
       </c>
       <c r="C513" t="s">
-        <v>1249</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="514" spans="1:3">
@@ -11123,10 +11129,10 @@
         <v>24</v>
       </c>
       <c r="B514" t="s">
-        <v>1260</v>
+        <v>1248</v>
       </c>
       <c r="C514" t="s">
-        <v>1261</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="515" spans="1:3">
@@ -11134,10 +11140,10 @@
         <v>24</v>
       </c>
       <c r="B515" t="s">
-        <v>1304</v>
+        <v>1260</v>
       </c>
       <c r="C515" t="s">
-        <v>1305</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="516" spans="1:3">
@@ -11145,10 +11151,10 @@
         <v>24</v>
       </c>
       <c r="B516" t="s">
-        <v>1321</v>
+        <v>1304</v>
       </c>
       <c r="C516" t="s">
-        <v>1322</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="517" spans="1:3">
@@ -11156,10 +11162,10 @@
         <v>24</v>
       </c>
       <c r="B517" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="C517" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="518" spans="1:3">
@@ -11167,10 +11173,10 @@
         <v>24</v>
       </c>
       <c r="B518" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="C518" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="519" spans="1:3">
@@ -11178,10 +11184,10 @@
         <v>24</v>
       </c>
       <c r="B519" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="C519" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="520" spans="1:3">
@@ -11189,21 +11195,21 @@
         <v>24</v>
       </c>
       <c r="B520" t="s">
-        <v>1380</v>
+        <v>1327</v>
       </c>
       <c r="C520" t="s">
-        <v>1381</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="521" spans="1:3">
       <c r="A521" t="s">
-        <v>5</v>
-      </c>
-      <c r="B521">
-        <v>1</v>
+        <v>24</v>
+      </c>
+      <c r="B521" t="s">
+        <v>1380</v>
       </c>
       <c r="C521" t="s">
-        <v>1431</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="522" spans="1:3">
@@ -11211,10 +11217,10 @@
         <v>5</v>
       </c>
       <c r="B522">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C522" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="523" spans="1:3">
@@ -11222,10 +11228,10 @@
         <v>5</v>
       </c>
       <c r="B523">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C523" t="s">
-        <v>1445</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="524" spans="1:3">
@@ -11233,32 +11239,32 @@
         <v>5</v>
       </c>
       <c r="B524">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C524" t="s">
-        <v>1477</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="525" spans="1:3">
       <c r="A525" t="s">
         <v>5</v>
       </c>
-      <c r="B525" t="s">
-        <v>1341</v>
+      <c r="B525">
+        <v>8</v>
       </c>
       <c r="C525" t="s">
-        <v>1342</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="526" spans="1:3">
       <c r="A526" t="s">
-        <v>530</v>
+        <v>5</v>
       </c>
       <c r="B526" t="s">
-        <v>531</v>
+        <v>1341</v>
       </c>
       <c r="C526" t="s">
-        <v>532</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="527" spans="1:3">
@@ -11266,10 +11272,10 @@
         <v>530</v>
       </c>
       <c r="B527" t="s">
-        <v>977</v>
+        <v>531</v>
       </c>
       <c r="C527" t="s">
-        <v>978</v>
+        <v>532</v>
       </c>
     </row>
     <row r="528" spans="1:3">
@@ -11277,7 +11283,7 @@
         <v>530</v>
       </c>
       <c r="B528" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="C528" t="s">
         <v>978</v>
@@ -11288,10 +11294,10 @@
         <v>530</v>
       </c>
       <c r="B529" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="C529" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
     </row>
     <row r="530" spans="1:3">
@@ -11299,21 +11305,21 @@
         <v>530</v>
       </c>
       <c r="B530" t="s">
-        <v>1189</v>
+        <v>980</v>
       </c>
       <c r="C530" t="s">
-        <v>1190</v>
+        <v>981</v>
       </c>
     </row>
     <row r="531" spans="1:3">
       <c r="A531" t="s">
-        <v>6</v>
-      </c>
-      <c r="B531">
-        <v>1</v>
+        <v>530</v>
+      </c>
+      <c r="B531" t="s">
+        <v>1189</v>
       </c>
       <c r="C531" t="s">
-        <v>1432</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="532" spans="1:3">
@@ -11321,10 +11327,10 @@
         <v>6</v>
       </c>
       <c r="B532">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C532" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="533" spans="1:3">
@@ -11332,10 +11338,10 @@
         <v>6</v>
       </c>
       <c r="B533">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C533" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="534" spans="1:3">
@@ -11343,10 +11349,10 @@
         <v>6</v>
       </c>
       <c r="B534">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C534" t="s">
-        <v>1452</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="535" spans="1:3">
@@ -11354,10 +11360,10 @@
         <v>6</v>
       </c>
       <c r="B535">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C535" t="s">
-        <v>1460</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="536" spans="1:3">
@@ -11365,10 +11371,10 @@
         <v>6</v>
       </c>
       <c r="B536">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C536" t="s">
-        <v>1467</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="537" spans="1:3">
@@ -11376,10 +11382,10 @@
         <v>6</v>
       </c>
       <c r="B537">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C537" t="s">
-        <v>1478</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="538" spans="1:3">
@@ -11387,10 +11393,10 @@
         <v>6</v>
       </c>
       <c r="B538">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C538" t="s">
-        <v>1487</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="539" spans="1:3">
@@ -11398,10 +11404,10 @@
         <v>6</v>
       </c>
       <c r="B539">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C539" t="s">
-        <v>1494</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="540" spans="1:3">
@@ -11409,10 +11415,10 @@
         <v>6</v>
       </c>
       <c r="B540">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C540" t="s">
-        <v>1527</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="541" spans="1:3">
@@ -11420,10 +11426,10 @@
         <v>6</v>
       </c>
       <c r="B541">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C541" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="542" spans="1:3">
@@ -11431,10 +11437,10 @@
         <v>6</v>
       </c>
       <c r="B542">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C542" t="s">
-        <v>1533</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="543" spans="1:3">
@@ -11442,10 +11448,10 @@
         <v>6</v>
       </c>
       <c r="B543">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C543" t="s">
-        <v>1536</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="544" spans="1:3">
@@ -11453,10 +11459,10 @@
         <v>6</v>
       </c>
       <c r="B544">
-        <v>118</v>
+        <v>29</v>
       </c>
       <c r="C544" t="s">
-        <v>1628</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="545" spans="1:3">
@@ -11464,21 +11470,21 @@
         <v>6</v>
       </c>
       <c r="B545">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C545" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="546" spans="1:3">
       <c r="A546" t="s">
         <v>6</v>
       </c>
-      <c r="B546" t="s">
-        <v>14</v>
+      <c r="B546">
+        <v>120</v>
       </c>
       <c r="C546" t="s">
-        <v>15</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="547" spans="1:3">
@@ -11486,10 +11492,10 @@
         <v>6</v>
       </c>
       <c r="B547" t="s">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="C547" t="s">
-        <v>68</v>
+        <v>15</v>
       </c>
     </row>
     <row r="548" spans="1:3">
@@ -11497,10 +11503,10 @@
         <v>6</v>
       </c>
       <c r="B548" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C548" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="549" spans="1:3">
@@ -11508,10 +11514,10 @@
         <v>6</v>
       </c>
       <c r="B549" t="s">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="C549" t="s">
-        <v>133</v>
+        <v>73</v>
       </c>
     </row>
     <row r="550" spans="1:3">
@@ -11519,10 +11525,10 @@
         <v>6</v>
       </c>
       <c r="B550" t="s">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="C550" t="s">
-        <v>164</v>
+        <v>133</v>
       </c>
     </row>
     <row r="551" spans="1:3">
@@ -11530,10 +11536,10 @@
         <v>6</v>
       </c>
       <c r="B551" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C551" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="552" spans="1:3">
@@ -11541,10 +11547,10 @@
         <v>6</v>
       </c>
       <c r="B552" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C552" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="553" spans="1:3">
@@ -11552,10 +11558,10 @@
         <v>6</v>
       </c>
       <c r="B553" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C553" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="554" spans="1:3">
@@ -11563,10 +11569,10 @@
         <v>6</v>
       </c>
       <c r="B554" t="s">
-        <v>287</v>
+        <v>169</v>
       </c>
       <c r="C554" t="s">
-        <v>288</v>
+        <v>170</v>
       </c>
     </row>
     <row r="555" spans="1:3">
@@ -11574,10 +11580,10 @@
         <v>6</v>
       </c>
       <c r="B555" t="s">
-        <v>490</v>
+        <v>287</v>
       </c>
       <c r="C555" t="s">
-        <v>491</v>
+        <v>288</v>
       </c>
     </row>
     <row r="556" spans="1:3">
@@ -11585,10 +11591,10 @@
         <v>6</v>
       </c>
       <c r="B556" t="s">
-        <v>511</v>
+        <v>490</v>
       </c>
       <c r="C556" t="s">
-        <v>512</v>
+        <v>491</v>
       </c>
     </row>
     <row r="557" spans="1:3">
@@ -11596,10 +11602,10 @@
         <v>6</v>
       </c>
       <c r="B557" t="s">
-        <v>662</v>
+        <v>511</v>
       </c>
       <c r="C557" t="s">
-        <v>664</v>
+        <v>512</v>
       </c>
     </row>
     <row r="558" spans="1:3">
@@ -11607,10 +11613,10 @@
         <v>6</v>
       </c>
       <c r="B558" t="s">
-        <v>694</v>
+        <v>662</v>
       </c>
       <c r="C558" t="s">
-        <v>695</v>
+        <v>664</v>
       </c>
     </row>
     <row r="559" spans="1:3">
@@ -11618,10 +11624,10 @@
         <v>6</v>
       </c>
       <c r="B559" t="s">
-        <v>715</v>
+        <v>694</v>
       </c>
       <c r="C559" t="s">
-        <v>716</v>
+        <v>695</v>
       </c>
     </row>
     <row r="560" spans="1:3">
@@ -11629,10 +11635,10 @@
         <v>6</v>
       </c>
       <c r="B560" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="C560" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
     </row>
     <row r="561" spans="1:3">
@@ -11640,10 +11646,10 @@
         <v>6</v>
       </c>
       <c r="B561" t="s">
-        <v>741</v>
+        <v>721</v>
       </c>
       <c r="C561" t="s">
-        <v>742</v>
+        <v>722</v>
       </c>
     </row>
     <row r="562" spans="1:3">
@@ -11651,10 +11657,10 @@
         <v>6</v>
       </c>
       <c r="B562" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C562" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
     </row>
     <row r="563" spans="1:3">
@@ -11662,10 +11668,10 @@
         <v>6</v>
       </c>
       <c r="B563" t="s">
-        <v>754</v>
+        <v>743</v>
       </c>
       <c r="C563" t="s">
-        <v>756</v>
+        <v>744</v>
       </c>
     </row>
     <row r="564" spans="1:3">
@@ -11673,10 +11679,10 @@
         <v>6</v>
       </c>
       <c r="B564" t="s">
-        <v>942</v>
+        <v>754</v>
       </c>
       <c r="C564" t="s">
-        <v>943</v>
+        <v>756</v>
       </c>
     </row>
     <row r="565" spans="1:3">
@@ -11684,10 +11690,10 @@
         <v>6</v>
       </c>
       <c r="B565" t="s">
-        <v>1018</v>
+        <v>942</v>
       </c>
       <c r="C565" t="s">
-        <v>1020</v>
+        <v>943</v>
       </c>
     </row>
     <row r="566" spans="1:3">
@@ -11695,10 +11701,10 @@
         <v>6</v>
       </c>
       <c r="B566" t="s">
-        <v>1104</v>
+        <v>1018</v>
       </c>
       <c r="C566" t="s">
-        <v>1105</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="567" spans="1:3">
@@ -11706,10 +11712,10 @@
         <v>6</v>
       </c>
       <c r="B567" t="s">
-        <v>1273</v>
+        <v>1104</v>
       </c>
       <c r="C567" t="s">
-        <v>1274</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="568" spans="1:3">
@@ -11717,10 +11723,10 @@
         <v>6</v>
       </c>
       <c r="B568" t="s">
-        <v>1288</v>
+        <v>1273</v>
       </c>
       <c r="C568" t="s">
-        <v>1290</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="569" spans="1:3">
@@ -11728,10 +11734,10 @@
         <v>6</v>
       </c>
       <c r="B569" t="s">
-        <v>1297</v>
+        <v>1288</v>
       </c>
       <c r="C569" t="s">
-        <v>1298</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="570" spans="1:3">
@@ -11739,21 +11745,21 @@
         <v>6</v>
       </c>
       <c r="B570" t="s">
-        <v>1301</v>
+        <v>1297</v>
       </c>
       <c r="C570" t="s">
-        <v>1303</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="571" spans="1:3">
       <c r="A571" t="s">
-        <v>9</v>
-      </c>
-      <c r="B571">
         <v>6</v>
       </c>
+      <c r="B571" t="s">
+        <v>1301</v>
+      </c>
       <c r="C571" t="s">
-        <v>1468</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="572" spans="1:3">
@@ -11761,10 +11767,10 @@
         <v>9</v>
       </c>
       <c r="B572">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C572" t="s">
-        <v>1474</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="573" spans="1:3">
@@ -11772,10 +11778,10 @@
         <v>9</v>
       </c>
       <c r="B573">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C573" t="s">
-        <v>1479</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="574" spans="1:3">
@@ -11783,10 +11789,10 @@
         <v>9</v>
       </c>
       <c r="B574">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C574" t="s">
-        <v>1483</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="575" spans="1:3">
@@ -11794,10 +11800,10 @@
         <v>9</v>
       </c>
       <c r="B575">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C575" t="s">
-        <v>1491</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="576" spans="1:3">
@@ -11805,10 +11811,10 @@
         <v>9</v>
       </c>
       <c r="B576">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C576" t="s">
-        <v>1495</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="577" spans="1:3">
@@ -11816,10 +11822,10 @@
         <v>9</v>
       </c>
       <c r="B577">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C577" t="s">
-        <v>1498</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="578" spans="1:3">
@@ -11827,10 +11833,10 @@
         <v>9</v>
       </c>
       <c r="B578">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C578" t="s">
-        <v>1501</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="579" spans="1:3">
@@ -11838,10 +11844,10 @@
         <v>9</v>
       </c>
       <c r="B579">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C579" t="s">
-        <v>1504</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="580" spans="1:3">
@@ -11849,10 +11855,10 @@
         <v>9</v>
       </c>
       <c r="B580">
-        <v>106</v>
+        <v>15</v>
       </c>
       <c r="C580" t="s">
-        <v>1612</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="581" spans="1:3">
@@ -11860,10 +11866,10 @@
         <v>9</v>
       </c>
       <c r="B581">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="C581" t="s">
-        <v>1624</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="582" spans="1:3">
@@ -11871,21 +11877,21 @@
         <v>9</v>
       </c>
       <c r="B582">
-        <v>202</v>
+        <v>115</v>
       </c>
       <c r="C582" t="s">
-        <v>1636</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="583" spans="1:3">
       <c r="A583" t="s">
         <v>9</v>
       </c>
-      <c r="B583" t="s">
-        <v>1667</v>
+      <c r="B583">
+        <v>202</v>
       </c>
       <c r="C583" t="s">
-        <v>1668</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="584" spans="1:3">
@@ -11893,10 +11899,10 @@
         <v>9</v>
       </c>
       <c r="B584" t="s">
-        <v>1669</v>
+        <v>1667</v>
       </c>
       <c r="C584" t="s">
-        <v>1670</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="585" spans="1:3">
@@ -11904,10 +11910,10 @@
         <v>9</v>
       </c>
       <c r="B585" t="s">
-        <v>10</v>
+        <v>1669</v>
       </c>
       <c r="C585" t="s">
-        <v>11</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="586" spans="1:3">
@@ -11915,10 +11921,10 @@
         <v>9</v>
       </c>
       <c r="B586" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C586" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="587" spans="1:3">
@@ -11926,10 +11932,10 @@
         <v>9</v>
       </c>
       <c r="B587" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C587" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="588" spans="1:3">
@@ -11937,10 +11943,10 @@
         <v>9</v>
       </c>
       <c r="B588" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C588" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="589" spans="1:3">
@@ -11948,10 +11954,10 @@
         <v>9</v>
       </c>
       <c r="B589" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C589" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="590" spans="1:3">
@@ -11959,10 +11965,10 @@
         <v>9</v>
       </c>
       <c r="B590" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C590" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="591" spans="1:3">
@@ -11970,10 +11976,10 @@
         <v>9</v>
       </c>
       <c r="B591" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C591" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="592" spans="1:3">
@@ -11981,10 +11987,10 @@
         <v>9</v>
       </c>
       <c r="B592" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C592" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="593" spans="1:3">
@@ -11992,10 +11998,10 @@
         <v>9</v>
       </c>
       <c r="B593" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C593" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="594" spans="1:3">
@@ -12003,10 +12009,10 @@
         <v>9</v>
       </c>
       <c r="B594" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C594" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="595" spans="1:3">
@@ -12014,10 +12020,10 @@
         <v>9</v>
       </c>
       <c r="B595" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C595" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="596" spans="1:3">
@@ -12025,10 +12031,10 @@
         <v>9</v>
       </c>
       <c r="B596" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C596" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="597" spans="1:3">
@@ -12036,10 +12042,10 @@
         <v>9</v>
       </c>
       <c r="B597" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C597" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="598" spans="1:3">
@@ -12047,10 +12053,10 @@
         <v>9</v>
       </c>
       <c r="B598" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C598" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="599" spans="1:3">
@@ -12058,10 +12064,10 @@
         <v>9</v>
       </c>
       <c r="B599" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C599" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="600" spans="1:3">
@@ -12069,10 +12075,10 @@
         <v>9</v>
       </c>
       <c r="B600" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C600" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="601" spans="1:3">
@@ -12080,10 +12086,10 @@
         <v>9</v>
       </c>
       <c r="B601" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C601" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="602" spans="1:3">
@@ -12091,10 +12097,10 @@
         <v>9</v>
       </c>
       <c r="B602" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C602" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="603" spans="1:3">
@@ -12102,10 +12108,10 @@
         <v>9</v>
       </c>
       <c r="B603" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C603" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="604" spans="1:3">
@@ -12113,10 +12119,10 @@
         <v>9</v>
       </c>
       <c r="B604" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C604" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
     </row>
     <row r="605" spans="1:3">
@@ -12124,10 +12130,10 @@
         <v>9</v>
       </c>
       <c r="B605" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C605" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="606" spans="1:3">
@@ -12135,10 +12141,10 @@
         <v>9</v>
       </c>
       <c r="B606" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C606" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="607" spans="1:3">
@@ -12146,10 +12152,10 @@
         <v>9</v>
       </c>
       <c r="B607" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C607" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="608" spans="1:3">
@@ -12157,10 +12163,10 @@
         <v>9</v>
       </c>
       <c r="B608" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C608" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="609" spans="1:3">
@@ -12168,10 +12174,10 @@
         <v>9</v>
       </c>
       <c r="B609" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C609" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="610" spans="1:3">
@@ -12179,10 +12185,10 @@
         <v>9</v>
       </c>
       <c r="B610" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C610" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="611" spans="1:3">
@@ -12190,10 +12196,10 @@
         <v>9</v>
       </c>
       <c r="B611" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C611" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="612" spans="1:3">
@@ -12201,10 +12207,10 @@
         <v>9</v>
       </c>
       <c r="B612" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C612" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="613" spans="1:3">
@@ -12212,10 +12218,10 @@
         <v>9</v>
       </c>
       <c r="B613" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C613" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="614" spans="1:3">
@@ -12223,10 +12229,10 @@
         <v>9</v>
       </c>
       <c r="B614" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C614" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="615" spans="1:3">
@@ -12234,10 +12240,10 @@
         <v>9</v>
       </c>
       <c r="B615" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C615" t="s">
-        <v>19</v>
+        <v>111</v>
       </c>
     </row>
     <row r="616" spans="1:3">
@@ -12245,10 +12251,10 @@
         <v>9</v>
       </c>
       <c r="B616" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C616" t="s">
-        <v>116</v>
+        <v>19</v>
       </c>
     </row>
     <row r="617" spans="1:3">
@@ -12256,10 +12262,10 @@
         <v>9</v>
       </c>
       <c r="B617" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C617" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
     </row>
     <row r="618" spans="1:3">
@@ -12267,10 +12273,10 @@
         <v>9</v>
       </c>
       <c r="B618" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C618" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="619" spans="1:3">
@@ -12278,10 +12284,10 @@
         <v>9</v>
       </c>
       <c r="B619" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C619" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="620" spans="1:3">
@@ -12289,10 +12295,10 @@
         <v>9</v>
       </c>
       <c r="B620" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C620" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
     </row>
     <row r="621" spans="1:3">
@@ -12300,10 +12306,10 @@
         <v>9</v>
       </c>
       <c r="B621" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C621" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="622" spans="1:3">
@@ -12311,10 +12317,10 @@
         <v>9</v>
       </c>
       <c r="B622" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C622" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
     </row>
     <row r="623" spans="1:3">
@@ -12322,10 +12328,10 @@
         <v>9</v>
       </c>
       <c r="B623" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C623" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="624" spans="1:3">
@@ -12333,10 +12339,10 @@
         <v>9</v>
       </c>
       <c r="B624" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C624" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="625" spans="1:3">
@@ -12344,10 +12350,10 @@
         <v>9</v>
       </c>
       <c r="B625" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C625" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="626" spans="1:3">
@@ -12355,10 +12361,10 @@
         <v>9</v>
       </c>
       <c r="B626" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C626" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="627" spans="1:3">
@@ -12366,10 +12372,10 @@
         <v>9</v>
       </c>
       <c r="B627" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="C627" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
     </row>
     <row r="628" spans="1:3">
@@ -12377,10 +12383,10 @@
         <v>9</v>
       </c>
       <c r="B628" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C628" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="629" spans="1:3">
@@ -12388,10 +12394,10 @@
         <v>9</v>
       </c>
       <c r="B629" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C629" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="630" spans="1:3">
@@ -12399,10 +12405,10 @@
         <v>9</v>
       </c>
       <c r="B630" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C630" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
     </row>
     <row r="631" spans="1:3">
@@ -12410,10 +12416,10 @@
         <v>9</v>
       </c>
       <c r="B631" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C631" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="632" spans="1:3">
@@ -12421,10 +12427,10 @@
         <v>9</v>
       </c>
       <c r="B632" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C632" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="633" spans="1:3">
@@ -12432,10 +12438,10 @@
         <v>9</v>
       </c>
       <c r="B633" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C633" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="634" spans="1:3">
@@ -12443,10 +12449,10 @@
         <v>9</v>
       </c>
       <c r="B634" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C634" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
     </row>
     <row r="635" spans="1:3">
@@ -12454,10 +12460,10 @@
         <v>9</v>
       </c>
       <c r="B635" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C635" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="636" spans="1:3">
@@ -12465,10 +12471,10 @@
         <v>9</v>
       </c>
       <c r="B636" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C636" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="637" spans="1:3">
@@ -12476,10 +12482,10 @@
         <v>9</v>
       </c>
       <c r="B637" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="C637" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
     </row>
     <row r="638" spans="1:3">
@@ -12487,10 +12493,10 @@
         <v>9</v>
       </c>
       <c r="B638" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C638" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="639" spans="1:3">
@@ -12498,10 +12504,10 @@
         <v>9</v>
       </c>
       <c r="B639" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="C639" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
     </row>
     <row r="640" spans="1:3">
@@ -12509,10 +12515,10 @@
         <v>9</v>
       </c>
       <c r="B640" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C640" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="641" spans="1:3">
@@ -12520,10 +12526,10 @@
         <v>9</v>
       </c>
       <c r="B641" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C641" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="642" spans="1:3">
@@ -12531,10 +12537,10 @@
         <v>9</v>
       </c>
       <c r="B642" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C642" t="s">
-        <v>19</v>
+        <v>230</v>
       </c>
     </row>
     <row r="643" spans="1:3">
@@ -12542,10 +12548,10 @@
         <v>9</v>
       </c>
       <c r="B643" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C643" t="s">
-        <v>233</v>
+        <v>19</v>
       </c>
     </row>
     <row r="644" spans="1:3">
@@ -12553,10 +12559,10 @@
         <v>9</v>
       </c>
       <c r="B644" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C644" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="645" spans="1:3">
@@ -12564,10 +12570,10 @@
         <v>9</v>
       </c>
       <c r="B645" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="C645" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
     </row>
     <row r="646" spans="1:3">
@@ -12575,10 +12581,10 @@
         <v>9</v>
       </c>
       <c r="B646" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C646" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="647" spans="1:3">
@@ -12586,10 +12592,10 @@
         <v>9</v>
       </c>
       <c r="B647" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C647" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="648" spans="1:3">
@@ -12597,10 +12603,10 @@
         <v>9</v>
       </c>
       <c r="B648" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C648" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="649" spans="1:3">
@@ -12608,10 +12614,10 @@
         <v>9</v>
       </c>
       <c r="B649" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C649" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
     </row>
     <row r="650" spans="1:3">
@@ -12619,10 +12625,10 @@
         <v>9</v>
       </c>
       <c r="B650" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="C650" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
     </row>
     <row r="651" spans="1:3">
@@ -12630,10 +12636,10 @@
         <v>9</v>
       </c>
       <c r="B651" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C651" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="652" spans="1:3">
@@ -12641,10 +12647,10 @@
         <v>9</v>
       </c>
       <c r="B652" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="C652" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
     </row>
     <row r="653" spans="1:3">
@@ -12652,10 +12658,10 @@
         <v>9</v>
       </c>
       <c r="B653" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C653" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="654" spans="1:3">
@@ -12663,10 +12669,10 @@
         <v>9</v>
       </c>
       <c r="B654" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C654" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="655" spans="1:3">
@@ -12674,10 +12680,10 @@
         <v>9</v>
       </c>
       <c r="B655" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C655" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="656" spans="1:3">
@@ -12685,10 +12691,10 @@
         <v>9</v>
       </c>
       <c r="B656" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C656" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="657" spans="1:3">
@@ -12696,10 +12702,10 @@
         <v>9</v>
       </c>
       <c r="B657" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C657" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="658" spans="1:3">
@@ -12707,10 +12713,10 @@
         <v>9</v>
       </c>
       <c r="B658" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="C658" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
     </row>
     <row r="659" spans="1:3">
@@ -12718,10 +12724,10 @@
         <v>9</v>
       </c>
       <c r="B659" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C659" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="660" spans="1:3">
@@ -12729,10 +12735,10 @@
         <v>9</v>
       </c>
       <c r="B660" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C660" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="661" spans="1:3">
@@ -12740,10 +12746,10 @@
         <v>9</v>
       </c>
       <c r="B661" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C661" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="662" spans="1:3">
@@ -12754,7 +12760,7 @@
         <v>295</v>
       </c>
       <c r="C662" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="663" spans="1:3">
@@ -12762,10 +12768,10 @@
         <v>9</v>
       </c>
       <c r="B663" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="C663" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="664" spans="1:3">
@@ -12773,10 +12779,10 @@
         <v>9</v>
       </c>
       <c r="B664" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C664" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="665" spans="1:3">
@@ -12784,10 +12790,10 @@
         <v>9</v>
       </c>
       <c r="B665" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C665" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="666" spans="1:3">
@@ -12795,10 +12801,10 @@
         <v>9</v>
       </c>
       <c r="B666" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C666" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="667" spans="1:3">
@@ -12806,10 +12812,10 @@
         <v>9</v>
       </c>
       <c r="B667" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C667" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="668" spans="1:3">
@@ -12817,10 +12823,10 @@
         <v>9</v>
       </c>
       <c r="B668" t="s">
-        <v>36</v>
+        <v>312</v>
       </c>
       <c r="C668" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="669" spans="1:3">
@@ -12828,10 +12834,10 @@
         <v>9</v>
       </c>
       <c r="B669" t="s">
-        <v>325</v>
+        <v>36</v>
       </c>
       <c r="C669" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
     </row>
     <row r="670" spans="1:3">
@@ -12839,10 +12845,10 @@
         <v>9</v>
       </c>
       <c r="B670" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C670" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="671" spans="1:3">
@@ -12850,10 +12856,10 @@
         <v>9</v>
       </c>
       <c r="B671" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C671" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="672" spans="1:3">
@@ -12861,10 +12867,10 @@
         <v>9</v>
       </c>
       <c r="B672" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C672" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="673" spans="1:3">
@@ -12872,10 +12878,10 @@
         <v>9</v>
       </c>
       <c r="B673" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C673" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="674" spans="1:3">
@@ -12883,10 +12889,10 @@
         <v>9</v>
       </c>
       <c r="B674" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C674" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="675" spans="1:3">
@@ -12894,10 +12900,10 @@
         <v>9</v>
       </c>
       <c r="B675" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="C675" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
     </row>
     <row r="676" spans="1:3">
@@ -12905,10 +12911,10 @@
         <v>9</v>
       </c>
       <c r="B676" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C676" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="677" spans="1:3">
@@ -12916,10 +12922,10 @@
         <v>9</v>
       </c>
       <c r="B677" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C677" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
     </row>
     <row r="678" spans="1:3">
@@ -12927,10 +12933,10 @@
         <v>9</v>
       </c>
       <c r="B678" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C678" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="679" spans="1:3">
@@ -12938,10 +12944,10 @@
         <v>9</v>
       </c>
       <c r="B679" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C679" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="680" spans="1:3">
@@ -12949,10 +12955,10 @@
         <v>9</v>
       </c>
       <c r="B680" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="C680" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
     </row>
     <row r="681" spans="1:3">
@@ -12960,10 +12966,10 @@
         <v>9</v>
       </c>
       <c r="B681" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C681" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="682" spans="1:3">
@@ -12971,10 +12977,10 @@
         <v>9</v>
       </c>
       <c r="B682" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="C682" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
     </row>
     <row r="683" spans="1:3">
@@ -12985,7 +12991,7 @@
         <v>377</v>
       </c>
       <c r="C683" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="684" spans="1:3">
@@ -12993,10 +12999,10 @@
         <v>9</v>
       </c>
       <c r="B684" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C684" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="685" spans="1:3">
@@ -13004,10 +13010,10 @@
         <v>9</v>
       </c>
       <c r="B685" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="C685" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
     </row>
     <row r="686" spans="1:3">
@@ -13015,10 +13021,10 @@
         <v>9</v>
       </c>
       <c r="B686" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C686" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="687" spans="1:3">
@@ -13026,10 +13032,10 @@
         <v>9</v>
       </c>
       <c r="B687" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C687" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="688" spans="1:3">
@@ -13037,10 +13043,10 @@
         <v>9</v>
       </c>
       <c r="B688" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="C688" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
     </row>
     <row r="689" spans="1:3">
@@ -13048,10 +13054,10 @@
         <v>9</v>
       </c>
       <c r="B689" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="C689" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
     </row>
     <row r="690" spans="1:3">
@@ -13059,10 +13065,10 @@
         <v>9</v>
       </c>
       <c r="B690" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C690" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="691" spans="1:3">
@@ -13070,10 +13076,10 @@
         <v>9</v>
       </c>
       <c r="B691" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C691" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="692" spans="1:3">
@@ -13081,10 +13087,10 @@
         <v>9</v>
       </c>
       <c r="B692" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C692" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="693" spans="1:3">
@@ -13092,10 +13098,10 @@
         <v>9</v>
       </c>
       <c r="B693" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C693" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="694" spans="1:3">
@@ -13103,10 +13109,10 @@
         <v>9</v>
       </c>
       <c r="B694" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="C694" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
     </row>
     <row r="695" spans="1:3">
@@ -13114,10 +13120,10 @@
         <v>9</v>
       </c>
       <c r="B695" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="C695" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
     </row>
     <row r="696" spans="1:3">
@@ -13125,10 +13131,10 @@
         <v>9</v>
       </c>
       <c r="B696" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C696" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="697" spans="1:3">
@@ -13136,10 +13142,10 @@
         <v>9</v>
       </c>
       <c r="B697" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C697" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="698" spans="1:3">
@@ -13147,10 +13153,10 @@
         <v>9</v>
       </c>
       <c r="B698" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C698" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="699" spans="1:3">
@@ -13158,10 +13164,10 @@
         <v>9</v>
       </c>
       <c r="B699" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C699" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="700" spans="1:3">
@@ -13169,10 +13175,10 @@
         <v>9</v>
       </c>
       <c r="B700" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C700" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="701" spans="1:3">
@@ -13180,10 +13186,10 @@
         <v>9</v>
       </c>
       <c r="B701" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="C701" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
     </row>
     <row r="702" spans="1:3">
@@ -13191,10 +13197,10 @@
         <v>9</v>
       </c>
       <c r="B702" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C702" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="703" spans="1:3">
@@ -13202,10 +13208,10 @@
         <v>9</v>
       </c>
       <c r="B703" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C703" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="704" spans="1:3">
@@ -13213,10 +13219,10 @@
         <v>9</v>
       </c>
       <c r="B704" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C704" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="705" spans="1:3">
@@ -13224,10 +13230,10 @@
         <v>9</v>
       </c>
       <c r="B705" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C705" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="706" spans="1:3">
@@ -13235,10 +13241,10 @@
         <v>9</v>
       </c>
       <c r="B706" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C706" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="707" spans="1:3">
@@ -13246,10 +13252,10 @@
         <v>9</v>
       </c>
       <c r="B707" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="C707" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
     </row>
     <row r="708" spans="1:3">
@@ -13257,10 +13263,10 @@
         <v>9</v>
       </c>
       <c r="B708" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="C708" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
     </row>
     <row r="709" spans="1:3">
@@ -13268,10 +13274,10 @@
         <v>9</v>
       </c>
       <c r="B709" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="C709" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
     </row>
     <row r="710" spans="1:3">
@@ -13279,10 +13285,10 @@
         <v>9</v>
       </c>
       <c r="B710" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C710" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="711" spans="1:3">
@@ -13290,10 +13296,10 @@
         <v>9</v>
       </c>
       <c r="B711" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="C711" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
     </row>
     <row r="712" spans="1:3">
@@ -13301,10 +13307,10 @@
         <v>9</v>
       </c>
       <c r="B712" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="C712" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
     </row>
     <row r="713" spans="1:3">
@@ -13312,10 +13318,10 @@
         <v>9</v>
       </c>
       <c r="B713" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="C713" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
     </row>
     <row r="714" spans="1:3">
@@ -13323,10 +13329,10 @@
         <v>9</v>
       </c>
       <c r="B714" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="C714" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
     </row>
     <row r="715" spans="1:3">
@@ -13334,10 +13340,10 @@
         <v>9</v>
       </c>
       <c r="B715" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C715" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="716" spans="1:3">
@@ -13345,10 +13351,10 @@
         <v>9</v>
       </c>
       <c r="B716" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="C716" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
     </row>
     <row r="717" spans="1:3">
@@ -13356,10 +13362,10 @@
         <v>9</v>
       </c>
       <c r="B717" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="C717" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
     </row>
     <row r="718" spans="1:3">
@@ -13367,10 +13373,10 @@
         <v>9</v>
       </c>
       <c r="B718" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C718" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="719" spans="1:3">
@@ -13378,10 +13384,10 @@
         <v>9</v>
       </c>
       <c r="B719" t="s">
-        <v>8</v>
+        <v>517</v>
       </c>
       <c r="C719" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="720" spans="1:3">
@@ -13389,10 +13395,10 @@
         <v>9</v>
       </c>
       <c r="B720" t="s">
-        <v>521</v>
+        <v>8</v>
       </c>
       <c r="C720" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="721" spans="1:3">
@@ -13400,10 +13406,10 @@
         <v>9</v>
       </c>
       <c r="B721" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="C721" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
     </row>
     <row r="722" spans="1:3">
@@ -13411,10 +13417,10 @@
         <v>9</v>
       </c>
       <c r="B722" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C722" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="723" spans="1:3">
@@ -13422,10 +13428,10 @@
         <v>9</v>
       </c>
       <c r="B723" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="C723" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
     </row>
     <row r="724" spans="1:3">
@@ -13433,10 +13439,10 @@
         <v>9</v>
       </c>
       <c r="B724" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C724" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="725" spans="1:3">
@@ -13444,10 +13450,10 @@
         <v>9</v>
       </c>
       <c r="B725" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="C725" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
     </row>
     <row r="726" spans="1:3">
@@ -13455,10 +13461,10 @@
         <v>9</v>
       </c>
       <c r="B726" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C726" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="727" spans="1:3">
@@ -13466,10 +13472,10 @@
         <v>9</v>
       </c>
       <c r="B727" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C727" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="728" spans="1:3">
@@ -13477,10 +13483,10 @@
         <v>9</v>
       </c>
       <c r="B728" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="C728" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
     </row>
     <row r="729" spans="1:3">
@@ -13488,10 +13494,10 @@
         <v>9</v>
       </c>
       <c r="B729" t="s">
-        <v>557</v>
+        <v>547</v>
       </c>
       <c r="C729" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
     </row>
     <row r="730" spans="1:3">
@@ -13499,10 +13505,10 @@
         <v>9</v>
       </c>
       <c r="B730" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="C730" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
     </row>
     <row r="731" spans="1:3">
@@ -13510,10 +13516,10 @@
         <v>9</v>
       </c>
       <c r="B731" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="C731" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="732" spans="1:3">
@@ -13521,10 +13527,10 @@
         <v>9</v>
       </c>
       <c r="B732" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="C732" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
     </row>
     <row r="733" spans="1:3">
@@ -13532,10 +13538,10 @@
         <v>9</v>
       </c>
       <c r="B733" t="s">
-        <v>588</v>
+        <v>568</v>
       </c>
       <c r="C733" t="s">
-        <v>589</v>
+        <v>569</v>
       </c>
     </row>
     <row r="734" spans="1:3">
@@ -13543,10 +13549,10 @@
         <v>9</v>
       </c>
       <c r="B734" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="C734" t="s">
-        <v>602</v>
+        <v>589</v>
       </c>
     </row>
     <row r="735" spans="1:3">
@@ -13554,10 +13560,10 @@
         <v>9</v>
       </c>
       <c r="B735" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="C735" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="736" spans="1:3">
@@ -13565,10 +13571,10 @@
         <v>9</v>
       </c>
       <c r="B736" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C736" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="737" spans="1:3">
@@ -13576,10 +13582,10 @@
         <v>9</v>
       </c>
       <c r="B737" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="C737" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="738" spans="1:3">
@@ -13587,10 +13593,10 @@
         <v>9</v>
       </c>
       <c r="B738" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="C738" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
     </row>
     <row r="739" spans="1:3">
@@ -13598,10 +13604,10 @@
         <v>9</v>
       </c>
       <c r="B739" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="C739" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
     </row>
     <row r="740" spans="1:3">
@@ -13609,10 +13615,10 @@
         <v>9</v>
       </c>
       <c r="B740" t="s">
-        <v>628</v>
+        <v>616</v>
       </c>
       <c r="C740" t="s">
-        <v>629</v>
+        <v>617</v>
       </c>
     </row>
     <row r="741" spans="1:3">
@@ -13620,10 +13626,10 @@
         <v>9</v>
       </c>
       <c r="B741" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="C741" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
     </row>
     <row r="742" spans="1:3">
@@ -13631,10 +13637,10 @@
         <v>9</v>
       </c>
       <c r="B742" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C742" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
     </row>
     <row r="743" spans="1:3">
@@ -13642,10 +13648,10 @@
         <v>9</v>
       </c>
       <c r="B743" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="C743" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
     </row>
     <row r="744" spans="1:3">
@@ -13653,10 +13659,10 @@
         <v>9</v>
       </c>
       <c r="B744" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="C744" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
     </row>
     <row r="745" spans="1:3">
@@ -13664,10 +13670,10 @@
         <v>9</v>
       </c>
       <c r="B745" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C745" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="746" spans="1:3">
@@ -13675,10 +13681,10 @@
         <v>9</v>
       </c>
       <c r="B746" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="C746" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
     </row>
     <row r="747" spans="1:3">
@@ -13686,10 +13692,10 @@
         <v>9</v>
       </c>
       <c r="B747" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C747" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="748" spans="1:3">
@@ -13697,10 +13703,10 @@
         <v>9</v>
       </c>
       <c r="B748" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C748" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="749" spans="1:3">
@@ -13708,10 +13714,10 @@
         <v>9</v>
       </c>
       <c r="B749" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C749" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="750" spans="1:3">
@@ -13719,10 +13725,10 @@
         <v>9</v>
       </c>
       <c r="B750" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C750" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="751" spans="1:3">
@@ -13730,10 +13736,10 @@
         <v>9</v>
       </c>
       <c r="B751" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C751" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
     </row>
     <row r="752" spans="1:3">
@@ -13741,10 +13747,10 @@
         <v>9</v>
       </c>
       <c r="B752" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="C752" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
     </row>
     <row r="753" spans="1:3">
@@ -13752,10 +13758,10 @@
         <v>9</v>
       </c>
       <c r="B753" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C753" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="754" spans="1:3">
@@ -13763,10 +13769,10 @@
         <v>9</v>
       </c>
       <c r="B754" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="C754" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
     </row>
     <row r="755" spans="1:3">
@@ -13774,10 +13780,10 @@
         <v>9</v>
       </c>
       <c r="B755" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="C755" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
     </row>
     <row r="756" spans="1:3">
@@ -13785,10 +13791,10 @@
         <v>9</v>
       </c>
       <c r="B756" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="C756" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
     </row>
     <row r="757" spans="1:3">
@@ -13796,10 +13802,10 @@
         <v>9</v>
       </c>
       <c r="B757" t="s">
-        <v>690</v>
+        <v>679</v>
       </c>
       <c r="C757" t="s">
-        <v>691</v>
+        <v>681</v>
       </c>
     </row>
     <row r="758" spans="1:3">
@@ -13807,10 +13813,10 @@
         <v>9</v>
       </c>
       <c r="B758" t="s">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="C758" t="s">
-        <v>699</v>
+        <v>691</v>
       </c>
     </row>
     <row r="759" spans="1:3">
@@ -13818,10 +13824,10 @@
         <v>9</v>
       </c>
       <c r="B759" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C759" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="760" spans="1:3">
@@ -13829,10 +13835,10 @@
         <v>9</v>
       </c>
       <c r="B760" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="C760" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="761" spans="1:3">
@@ -13840,10 +13846,10 @@
         <v>9</v>
       </c>
       <c r="B761" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="C761" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
     </row>
     <row r="762" spans="1:3">
@@ -13851,10 +13857,10 @@
         <v>9</v>
       </c>
       <c r="B762" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C762" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
     </row>
     <row r="763" spans="1:3">
@@ -13862,10 +13868,10 @@
         <v>9</v>
       </c>
       <c r="B763" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C763" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="764" spans="1:3">
@@ -13873,10 +13879,10 @@
         <v>9</v>
       </c>
       <c r="B764" t="s">
-        <v>723</v>
+        <v>711</v>
       </c>
       <c r="C764" t="s">
-        <v>724</v>
+        <v>712</v>
       </c>
     </row>
     <row r="765" spans="1:3">
@@ -13884,10 +13890,10 @@
         <v>9</v>
       </c>
       <c r="B765" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C765" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
     </row>
     <row r="766" spans="1:3">
@@ -13895,10 +13901,10 @@
         <v>9</v>
       </c>
       <c r="B766" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C766" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
     </row>
     <row r="767" spans="1:3">
@@ -13906,10 +13912,10 @@
         <v>9</v>
       </c>
       <c r="B767" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="C767" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
     </row>
     <row r="768" spans="1:3">
@@ -13917,10 +13923,10 @@
         <v>9</v>
       </c>
       <c r="B768" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="C768" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="769" spans="1:3">
@@ -13928,10 +13934,10 @@
         <v>9</v>
       </c>
       <c r="B769" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="C769" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="770" spans="1:3">
@@ -13939,10 +13945,10 @@
         <v>9</v>
       </c>
       <c r="B770" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="C770" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
     </row>
     <row r="771" spans="1:3">
@@ -13950,10 +13956,10 @@
         <v>9</v>
       </c>
       <c r="B771" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="C771" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
     </row>
     <row r="772" spans="1:3">
@@ -13961,10 +13967,10 @@
         <v>9</v>
       </c>
       <c r="B772" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C772" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
     </row>
     <row r="773" spans="1:3">
@@ -13972,10 +13978,10 @@
         <v>9</v>
       </c>
       <c r="B773" t="s">
-        <v>747</v>
+        <v>739</v>
       </c>
       <c r="C773" t="s">
-        <v>749</v>
+        <v>740</v>
       </c>
     </row>
     <row r="774" spans="1:3">
@@ -13983,10 +13989,10 @@
         <v>9</v>
       </c>
       <c r="B774" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="C774" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
     </row>
     <row r="775" spans="1:3">
@@ -13994,10 +14000,10 @@
         <v>9</v>
       </c>
       <c r="B775" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="C775" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
     </row>
     <row r="776" spans="1:3">
@@ -14005,10 +14011,10 @@
         <v>9</v>
       </c>
       <c r="B776" t="s">
-        <v>761</v>
+        <v>752</v>
       </c>
       <c r="C776" t="s">
-        <v>762</v>
+        <v>753</v>
       </c>
     </row>
     <row r="777" spans="1:3">
@@ -14016,10 +14022,10 @@
         <v>9</v>
       </c>
       <c r="B777" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="C777" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
     </row>
     <row r="778" spans="1:3">
@@ -14027,10 +14033,10 @@
         <v>9</v>
       </c>
       <c r="B778" t="s">
-        <v>770</v>
+        <v>765</v>
       </c>
       <c r="C778" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
     </row>
     <row r="779" spans="1:3">
@@ -14038,10 +14044,10 @@
         <v>9</v>
       </c>
       <c r="B779" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="C779" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
     </row>
     <row r="780" spans="1:3">
@@ -14049,10 +14055,10 @@
         <v>9</v>
       </c>
       <c r="B780" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C780" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
     </row>
     <row r="781" spans="1:3">
@@ -14060,10 +14066,10 @@
         <v>9</v>
       </c>
       <c r="B781" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="C781" t="s">
-        <v>782</v>
+        <v>777</v>
       </c>
     </row>
     <row r="782" spans="1:3">
@@ -14071,10 +14077,10 @@
         <v>9</v>
       </c>
       <c r="B782" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="C782" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="783" spans="1:3">
@@ -14082,10 +14088,10 @@
         <v>9</v>
       </c>
       <c r="B783" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C783" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
     </row>
     <row r="784" spans="1:3">
@@ -14093,10 +14099,10 @@
         <v>9</v>
       </c>
       <c r="B784" t="s">
-        <v>794</v>
+        <v>785</v>
       </c>
       <c r="C784" t="s">
-        <v>795</v>
+        <v>787</v>
       </c>
     </row>
     <row r="785" spans="1:3">
@@ -14104,10 +14110,10 @@
         <v>9</v>
       </c>
       <c r="B785" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C785" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
     </row>
     <row r="786" spans="1:3">
@@ -14115,10 +14121,10 @@
         <v>9</v>
       </c>
       <c r="B786" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="C786" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
     </row>
     <row r="787" spans="1:3">
@@ -14126,10 +14132,10 @@
         <v>9</v>
       </c>
       <c r="B787" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="C787" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
     </row>
     <row r="788" spans="1:3">
@@ -14137,10 +14143,10 @@
         <v>9</v>
       </c>
       <c r="B788" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="C788" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
     </row>
     <row r="789" spans="1:3">
@@ -14148,10 +14154,10 @@
         <v>9</v>
       </c>
       <c r="B789" t="s">
-        <v>818</v>
+        <v>807</v>
       </c>
       <c r="C789" t="s">
-        <v>819</v>
+        <v>808</v>
       </c>
     </row>
     <row r="790" spans="1:3">
@@ -14159,10 +14165,10 @@
         <v>9</v>
       </c>
       <c r="B790" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="C790" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
     </row>
     <row r="791" spans="1:3">
@@ -14170,10 +14176,10 @@
         <v>9</v>
       </c>
       <c r="B791" t="s">
-        <v>829</v>
+        <v>822</v>
       </c>
       <c r="C791" t="s">
-        <v>830</v>
+        <v>824</v>
       </c>
     </row>
     <row r="792" spans="1:3">
@@ -14181,10 +14187,10 @@
         <v>9</v>
       </c>
       <c r="B792" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="C792" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
     </row>
     <row r="793" spans="1:3">
@@ -14192,10 +14198,10 @@
         <v>9</v>
       </c>
       <c r="B793" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="C793" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="794" spans="1:3">
@@ -14203,10 +14209,10 @@
         <v>9</v>
       </c>
       <c r="B794" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C794" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="795" spans="1:3">
@@ -14214,10 +14220,10 @@
         <v>9</v>
       </c>
       <c r="B795" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="C795" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="796" spans="1:3">
@@ -14225,10 +14231,10 @@
         <v>9</v>
       </c>
       <c r="B796" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="C796" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
     </row>
     <row r="797" spans="1:3">
@@ -14236,10 +14242,10 @@
         <v>9</v>
       </c>
       <c r="B797" t="s">
-        <v>861</v>
+        <v>843</v>
       </c>
       <c r="C797" t="s">
-        <v>862</v>
+        <v>844</v>
       </c>
     </row>
     <row r="798" spans="1:3">
@@ -14247,10 +14253,10 @@
         <v>9</v>
       </c>
       <c r="B798" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="C798" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
     </row>
     <row r="799" spans="1:3">
@@ -14258,10 +14264,10 @@
         <v>9</v>
       </c>
       <c r="B799" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="C799" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
     </row>
     <row r="800" spans="1:3">
@@ -14269,10 +14275,10 @@
         <v>9</v>
       </c>
       <c r="B800" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="C800" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
     </row>
     <row r="801" spans="1:3">
@@ -14280,10 +14286,10 @@
         <v>9</v>
       </c>
       <c r="B801" t="s">
-        <v>879</v>
+        <v>871</v>
       </c>
       <c r="C801" t="s">
-        <v>880</v>
+        <v>872</v>
       </c>
     </row>
     <row r="802" spans="1:3">
@@ -14291,10 +14297,10 @@
         <v>9</v>
       </c>
       <c r="B802" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="C802" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
     </row>
     <row r="803" spans="1:3">
@@ -14302,10 +14308,10 @@
         <v>9</v>
       </c>
       <c r="B803" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="C803" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
     </row>
     <row r="804" spans="1:3">
@@ -14313,10 +14319,10 @@
         <v>9</v>
       </c>
       <c r="B804" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="C804" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
     </row>
     <row r="805" spans="1:3">
@@ -14324,10 +14330,10 @@
         <v>9</v>
       </c>
       <c r="B805" t="s">
-        <v>895</v>
+        <v>888</v>
       </c>
       <c r="C805" t="s">
-        <v>896</v>
+        <v>890</v>
       </c>
     </row>
     <row r="806" spans="1:3">
@@ -14335,10 +14341,10 @@
         <v>9</v>
       </c>
       <c r="B806" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="C806" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
     </row>
     <row r="807" spans="1:3">
@@ -14346,10 +14352,10 @@
         <v>9</v>
       </c>
       <c r="B807" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="C807" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
     </row>
     <row r="808" spans="1:3">
@@ -14357,10 +14363,10 @@
         <v>9</v>
       </c>
       <c r="B808" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="C808" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
     </row>
     <row r="809" spans="1:3">
@@ -14368,10 +14374,10 @@
         <v>9</v>
       </c>
       <c r="B809" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="C809" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
     </row>
     <row r="810" spans="1:3">
@@ -14379,10 +14385,10 @@
         <v>9</v>
       </c>
       <c r="B810" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="C810" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
     </row>
     <row r="811" spans="1:3">
@@ -14390,10 +14396,10 @@
         <v>9</v>
       </c>
       <c r="B811" t="s">
-        <v>915</v>
+        <v>907</v>
       </c>
       <c r="C811" t="s">
-        <v>916</v>
+        <v>908</v>
       </c>
     </row>
     <row r="812" spans="1:3">
@@ -14401,10 +14407,10 @@
         <v>9</v>
       </c>
       <c r="B812" t="s">
-        <v>928</v>
+        <v>915</v>
       </c>
       <c r="C812" t="s">
-        <v>929</v>
+        <v>916</v>
       </c>
     </row>
     <row r="813" spans="1:3">
@@ -14412,10 +14418,10 @@
         <v>9</v>
       </c>
       <c r="B813" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C813" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="814" spans="1:3">
@@ -14423,10 +14429,10 @@
         <v>9</v>
       </c>
       <c r="B814" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C814" t="s">
-        <v>937</v>
+        <v>931</v>
       </c>
     </row>
     <row r="815" spans="1:3">
@@ -14434,10 +14440,10 @@
         <v>9</v>
       </c>
       <c r="B815" t="s">
-        <v>946</v>
+        <v>936</v>
       </c>
       <c r="C815" t="s">
-        <v>947</v>
+        <v>937</v>
       </c>
     </row>
     <row r="816" spans="1:3">
@@ -14445,10 +14451,10 @@
         <v>9</v>
       </c>
       <c r="B816" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="C816" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
     </row>
     <row r="817" spans="1:3">
@@ -14456,10 +14462,10 @@
         <v>9</v>
       </c>
       <c r="B817" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="C817" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
     </row>
     <row r="818" spans="1:3">
@@ -14467,10 +14473,10 @@
         <v>9</v>
       </c>
       <c r="B818" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="C818" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
     </row>
     <row r="819" spans="1:3">
@@ -14478,10 +14484,10 @@
         <v>9</v>
       </c>
       <c r="B819" t="s">
-        <v>963</v>
+        <v>957</v>
       </c>
       <c r="C819" t="s">
-        <v>964</v>
+        <v>958</v>
       </c>
     </row>
     <row r="820" spans="1:3">
@@ -14489,10 +14495,10 @@
         <v>9</v>
       </c>
       <c r="B820" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="C820" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
     </row>
     <row r="821" spans="1:3">
@@ -14500,10 +14506,10 @@
         <v>9</v>
       </c>
       <c r="B821" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C821" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
     </row>
     <row r="822" spans="1:3">
@@ -14511,10 +14517,10 @@
         <v>9</v>
       </c>
       <c r="B822" t="s">
-        <v>975</v>
+        <v>967</v>
       </c>
       <c r="C822" t="s">
-        <v>976</v>
+        <v>968</v>
       </c>
     </row>
     <row r="823" spans="1:3">
@@ -14522,10 +14528,10 @@
         <v>9</v>
       </c>
       <c r="B823" t="s">
-        <v>982</v>
+        <v>975</v>
       </c>
       <c r="C823" t="s">
-        <v>983</v>
+        <v>976</v>
       </c>
     </row>
     <row r="824" spans="1:3">
@@ -14533,10 +14539,10 @@
         <v>9</v>
       </c>
       <c r="B824" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="C824" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="825" spans="1:3">
@@ -14544,10 +14550,10 @@
         <v>9</v>
       </c>
       <c r="B825" t="s">
-        <v>998</v>
+        <v>984</v>
       </c>
       <c r="C825" t="s">
-        <v>999</v>
+        <v>985</v>
       </c>
     </row>
     <row r="826" spans="1:3">
@@ -14555,10 +14561,10 @@
         <v>9</v>
       </c>
       <c r="B826" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="C826" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
     </row>
     <row r="827" spans="1:3">
@@ -14566,10 +14572,10 @@
         <v>9</v>
       </c>
       <c r="B827" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="C827" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="828" spans="1:3">
@@ -14577,10 +14583,10 @@
         <v>9</v>
       </c>
       <c r="B828" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="C828" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="829" spans="1:3">
@@ -14588,10 +14594,10 @@
         <v>9</v>
       </c>
       <c r="B829" t="s">
-        <v>1010</v>
+        <v>1004</v>
       </c>
       <c r="C829" t="s">
-        <v>1011</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="830" spans="1:3">
@@ -14599,10 +14605,10 @@
         <v>9</v>
       </c>
       <c r="B830" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="C830" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="831" spans="1:3">
@@ -14610,10 +14616,10 @@
         <v>9</v>
       </c>
       <c r="B831" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="C831" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="832" spans="1:3">
@@ -14621,10 +14627,10 @@
         <v>9</v>
       </c>
       <c r="B832" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="C832" t="s">
-        <v>1021</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="833" spans="1:3">
@@ -14632,10 +14638,10 @@
         <v>9</v>
       </c>
       <c r="B833" t="s">
-        <v>1026</v>
+        <v>1018</v>
       </c>
       <c r="C833" t="s">
-        <v>1027</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="834" spans="1:3">
@@ -14643,10 +14649,10 @@
         <v>9</v>
       </c>
       <c r="B834" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="C834" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="835" spans="1:3">
@@ -14654,10 +14660,10 @@
         <v>9</v>
       </c>
       <c r="B835" t="s">
-        <v>1036</v>
+        <v>1028</v>
       </c>
       <c r="C835" t="s">
-        <v>1037</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="836" spans="1:3">
@@ -14665,10 +14671,10 @@
         <v>9</v>
       </c>
       <c r="B836" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C836" t="s">
-        <v>467</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="837" spans="1:3">
@@ -14676,10 +14682,10 @@
         <v>9</v>
       </c>
       <c r="B837" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="C837" t="s">
-        <v>1040</v>
+        <v>467</v>
       </c>
     </row>
     <row r="838" spans="1:3">
@@ -14687,10 +14693,10 @@
         <v>9</v>
       </c>
       <c r="B838" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="C838" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="839" spans="1:3">
@@ -14698,10 +14704,10 @@
         <v>9</v>
       </c>
       <c r="B839" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="C839" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="840" spans="1:3">
@@ -14709,10 +14715,10 @@
         <v>9</v>
       </c>
       <c r="B840" t="s">
-        <v>1051</v>
+        <v>1043</v>
       </c>
       <c r="C840" t="s">
-        <v>1052</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="841" spans="1:3">
@@ -14720,10 +14726,10 @@
         <v>9</v>
       </c>
       <c r="B841" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="C841" t="s">
-        <v>1060</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="842" spans="1:3">
@@ -14731,10 +14737,10 @@
         <v>9</v>
       </c>
       <c r="B842" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
       <c r="C842" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="843" spans="1:3">
@@ -14742,10 +14748,10 @@
         <v>9</v>
       </c>
       <c r="B843" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="C843" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="844" spans="1:3">
@@ -14753,10 +14759,10 @@
         <v>9</v>
       </c>
       <c r="B844" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="C844" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="845" spans="1:3">
@@ -14764,10 +14770,10 @@
         <v>9</v>
       </c>
       <c r="B845" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C845" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="846" spans="1:3">
@@ -14775,10 +14781,10 @@
         <v>9</v>
       </c>
       <c r="B846" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="C846" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="847" spans="1:3">
@@ -14786,10 +14792,10 @@
         <v>9</v>
       </c>
       <c r="B847" t="s">
-        <v>1082</v>
+        <v>1069</v>
       </c>
       <c r="C847" t="s">
-        <v>1003</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="848" spans="1:3">
@@ -14797,10 +14803,10 @@
         <v>9</v>
       </c>
       <c r="B848" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C848" t="s">
-        <v>1084</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="849" spans="1:3">
@@ -14808,10 +14814,10 @@
         <v>9</v>
       </c>
       <c r="B849" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="C849" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="850" spans="1:3">
@@ -14819,10 +14825,10 @@
         <v>9</v>
       </c>
       <c r="B850" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="C850" t="s">
-        <v>1090</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="851" spans="1:3">
@@ -14830,10 +14836,10 @@
         <v>9</v>
       </c>
       <c r="B851" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="C851" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="852" spans="1:3">
@@ -14841,10 +14847,10 @@
         <v>9</v>
       </c>
       <c r="B852" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="C852" t="s">
-        <v>1096</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="853" spans="1:3">
@@ -14852,10 +14858,10 @@
         <v>9</v>
       </c>
       <c r="B853" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="C853" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="854" spans="1:3">
@@ -14863,10 +14869,10 @@
         <v>9</v>
       </c>
       <c r="B854" t="s">
-        <v>1106</v>
+        <v>1097</v>
       </c>
       <c r="C854" t="s">
-        <v>1108</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="855" spans="1:3">
@@ -14874,10 +14880,10 @@
         <v>9</v>
       </c>
       <c r="B855" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
       <c r="C855" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="856" spans="1:3">
@@ -14885,10 +14891,10 @@
         <v>9</v>
       </c>
       <c r="B856" t="s">
-        <v>1122</v>
+        <v>1109</v>
       </c>
       <c r="C856" t="s">
-        <v>1123</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="857" spans="1:3">
@@ -14896,10 +14902,10 @@
         <v>9</v>
       </c>
       <c r="B857" t="s">
-        <v>1134</v>
+        <v>1122</v>
       </c>
       <c r="C857" t="s">
-        <v>1135</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="858" spans="1:3">
@@ -14907,10 +14913,10 @@
         <v>9</v>
       </c>
       <c r="B858" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="C858" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="859" spans="1:3">
@@ -14918,10 +14924,10 @@
         <v>9</v>
       </c>
       <c r="B859" t="s">
-        <v>1140</v>
+        <v>1136</v>
       </c>
       <c r="C859" t="s">
-        <v>1141</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="860" spans="1:3">
@@ -14929,10 +14935,10 @@
         <v>9</v>
       </c>
       <c r="B860" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="C860" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="861" spans="1:3">
@@ -14940,10 +14946,10 @@
         <v>9</v>
       </c>
       <c r="B861" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="C861" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="862" spans="1:3">
@@ -14951,10 +14957,10 @@
         <v>9</v>
       </c>
       <c r="B862" t="s">
-        <v>1152</v>
+        <v>1144</v>
       </c>
       <c r="C862" t="s">
-        <v>1154</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="863" spans="1:3">
@@ -14962,10 +14968,10 @@
         <v>9</v>
       </c>
       <c r="B863" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
       <c r="C863" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="864" spans="1:3">
@@ -14973,10 +14979,10 @@
         <v>9</v>
       </c>
       <c r="B864" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="C864" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="865" spans="1:3">
@@ -14984,10 +14990,10 @@
         <v>9</v>
       </c>
       <c r="B865" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="C865" t="s">
-        <v>1162</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="866" spans="1:3">
@@ -14995,10 +15001,10 @@
         <v>9</v>
       </c>
       <c r="B866" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="C866" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="867" spans="1:3">
@@ -15006,10 +15012,10 @@
         <v>9</v>
       </c>
       <c r="B867" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="C867" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="868" spans="1:3">
@@ -15017,10 +15023,10 @@
         <v>9</v>
       </c>
       <c r="B868" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="C868" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="869" spans="1:3">
@@ -15028,10 +15034,10 @@
         <v>9</v>
       </c>
       <c r="B869" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="C869" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="870" spans="1:3">
@@ -15039,10 +15045,10 @@
         <v>9</v>
       </c>
       <c r="B870" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="C870" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="871" spans="1:3">
@@ -15050,10 +15056,10 @@
         <v>9</v>
       </c>
       <c r="B871" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="C871" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="872" spans="1:3">
@@ -15061,10 +15067,10 @@
         <v>9</v>
       </c>
       <c r="B872" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="C872" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="873" spans="1:3">
@@ -15072,10 +15078,10 @@
         <v>9</v>
       </c>
       <c r="B873" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="C873" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="874" spans="1:3">
@@ -15083,10 +15089,10 @@
         <v>9</v>
       </c>
       <c r="B874" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="C874" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="875" spans="1:3">
@@ -15094,10 +15100,10 @@
         <v>9</v>
       </c>
       <c r="B875" t="s">
-        <v>1183</v>
+        <v>1179</v>
       </c>
       <c r="C875" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="876" spans="1:3">
@@ -15105,10 +15111,10 @@
         <v>9</v>
       </c>
       <c r="B876" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="C876" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="877" spans="1:3">
@@ -15116,10 +15122,10 @@
         <v>9</v>
       </c>
       <c r="B877" t="s">
-        <v>1195</v>
+        <v>1185</v>
       </c>
       <c r="C877" t="s">
-        <v>1196</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="878" spans="1:3">
@@ -15127,10 +15133,10 @@
         <v>9</v>
       </c>
       <c r="B878" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="C878" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="879" spans="1:3">
@@ -15138,10 +15144,10 @@
         <v>9</v>
       </c>
       <c r="B879" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="C879" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="880" spans="1:3">
@@ -15149,10 +15155,10 @@
         <v>9</v>
       </c>
       <c r="B880" t="s">
-        <v>1204</v>
+        <v>1199</v>
       </c>
       <c r="C880" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="881" spans="1:3">
@@ -15160,10 +15166,10 @@
         <v>9</v>
       </c>
       <c r="B881" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="C881" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="882" spans="1:3">
@@ -15171,10 +15177,10 @@
         <v>9</v>
       </c>
       <c r="B882" t="s">
-        <v>1220</v>
+        <v>1206</v>
       </c>
       <c r="C882" t="s">
-        <v>1221</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="883" spans="1:3">
@@ -15182,10 +15188,10 @@
         <v>9</v>
       </c>
       <c r="B883" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="C883" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="884" spans="1:3">
@@ -15193,10 +15199,10 @@
         <v>9</v>
       </c>
       <c r="B884" t="s">
-        <v>1226</v>
+        <v>1222</v>
       </c>
       <c r="C884" t="s">
-        <v>1227</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="885" spans="1:3">
@@ -15204,10 +15210,10 @@
         <v>9</v>
       </c>
       <c r="B885" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="C885" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="886" spans="1:3">
@@ -15215,10 +15221,10 @@
         <v>9</v>
       </c>
       <c r="B886" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="C886" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="887" spans="1:3">
@@ -15226,10 +15232,10 @@
         <v>9</v>
       </c>
       <c r="B887" t="s">
-        <v>1240</v>
+        <v>1230</v>
       </c>
       <c r="C887" t="s">
-        <v>1241</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="888" spans="1:3">
@@ -15237,10 +15243,10 @@
         <v>9</v>
       </c>
       <c r="B888" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="C888" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="889" spans="1:3">
@@ -15248,10 +15254,10 @@
         <v>9</v>
       </c>
       <c r="B889" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="C889" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="890" spans="1:3">
@@ -15259,10 +15265,10 @@
         <v>9</v>
       </c>
       <c r="B890" t="s">
-        <v>1250</v>
+        <v>1244</v>
       </c>
       <c r="C890" t="s">
-        <v>1251</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="891" spans="1:3">
@@ -15270,10 +15276,10 @@
         <v>9</v>
       </c>
       <c r="B891" t="s">
-        <v>1262</v>
+        <v>1250</v>
       </c>
       <c r="C891" t="s">
-        <v>1263</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="892" spans="1:3">
@@ -15281,10 +15287,10 @@
         <v>9</v>
       </c>
       <c r="B892" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="C892" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="893" spans="1:3">
@@ -15292,10 +15298,10 @@
         <v>9</v>
       </c>
       <c r="B893" t="s">
-        <v>1277</v>
+        <v>1264</v>
       </c>
       <c r="C893" t="s">
-        <v>1278</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="894" spans="1:3">
@@ -15303,10 +15309,10 @@
         <v>9</v>
       </c>
       <c r="B894" t="s">
-        <v>1286</v>
+        <v>1277</v>
       </c>
       <c r="C894" t="s">
-        <v>1287</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="895" spans="1:3">
@@ -15314,10 +15320,10 @@
         <v>9</v>
       </c>
       <c r="B895" t="s">
-        <v>1293</v>
+        <v>1286</v>
       </c>
       <c r="C895" t="s">
-        <v>1294</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="896" spans="1:3">
@@ -15325,10 +15331,10 @@
         <v>9</v>
       </c>
       <c r="B896" t="s">
-        <v>1299</v>
+        <v>1293</v>
       </c>
       <c r="C896" t="s">
-        <v>1300</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="897" spans="1:3">
@@ -15336,10 +15342,10 @@
         <v>9</v>
       </c>
       <c r="B897" t="s">
-        <v>1304</v>
+        <v>1299</v>
       </c>
       <c r="C897" t="s">
-        <v>1306</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="898" spans="1:3">
@@ -15347,10 +15353,10 @@
         <v>9</v>
       </c>
       <c r="B898" t="s">
-        <v>1313</v>
+        <v>1304</v>
       </c>
       <c r="C898" t="s">
-        <v>1314</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="899" spans="1:3">
@@ -15358,10 +15364,10 @@
         <v>9</v>
       </c>
       <c r="B899" t="s">
-        <v>1317</v>
+        <v>1313</v>
       </c>
       <c r="C899" t="s">
-        <v>1318</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="900" spans="1:3">
@@ -15369,10 +15375,10 @@
         <v>9</v>
       </c>
       <c r="B900" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="C900" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="901" spans="1:3">
@@ -15380,10 +15386,10 @@
         <v>9</v>
       </c>
       <c r="B901" t="s">
-        <v>1329</v>
+        <v>1319</v>
       </c>
       <c r="C901" t="s">
-        <v>1330</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="902" spans="1:3">
@@ -15391,10 +15397,10 @@
         <v>9</v>
       </c>
       <c r="B902" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="C902" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="903" spans="1:3">
@@ -15402,10 +15408,10 @@
         <v>9</v>
       </c>
       <c r="B903" t="s">
-        <v>1335</v>
+        <v>1331</v>
       </c>
       <c r="C903" t="s">
-        <v>1336</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="904" spans="1:3">
@@ -15413,10 +15419,10 @@
         <v>9</v>
       </c>
       <c r="B904" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="C904" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="905" spans="1:3">
@@ -15424,10 +15430,10 @@
         <v>9</v>
       </c>
       <c r="B905" t="s">
-        <v>1345</v>
+        <v>1337</v>
       </c>
       <c r="C905" t="s">
-        <v>1346</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="906" spans="1:3">
@@ -15435,10 +15441,10 @@
         <v>9</v>
       </c>
       <c r="B906" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="C906" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="907" spans="1:3">
@@ -15446,10 +15452,10 @@
         <v>9</v>
       </c>
       <c r="B907" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="C907" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="908" spans="1:3">
@@ -15457,10 +15463,10 @@
         <v>9</v>
       </c>
       <c r="B908" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="C908" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="909" spans="1:3">
@@ -15468,10 +15474,10 @@
         <v>9</v>
       </c>
       <c r="B909" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="C909" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="910" spans="1:3">
@@ -15479,10 +15485,10 @@
         <v>9</v>
       </c>
       <c r="B910" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="C910" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="911" spans="1:3">
@@ -15490,10 +15496,10 @@
         <v>9</v>
       </c>
       <c r="B911" t="s">
-        <v>1363</v>
+        <v>1355</v>
       </c>
       <c r="C911" t="s">
-        <v>1364</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="912" spans="1:3">
@@ -15501,10 +15507,10 @@
         <v>9</v>
       </c>
       <c r="B912" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
       <c r="C912" t="s">
-        <v>1369</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="913" spans="1:3">
@@ -15512,10 +15518,10 @@
         <v>9</v>
       </c>
       <c r="B913" t="s">
-        <v>1374</v>
+        <v>1367</v>
       </c>
       <c r="C913" t="s">
-        <v>1377</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="914" spans="1:3">
@@ -15523,10 +15529,10 @@
         <v>9</v>
       </c>
       <c r="B914" t="s">
-        <v>1390</v>
+        <v>1374</v>
       </c>
       <c r="C914" t="s">
-        <v>1391</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="915" spans="1:3">
@@ -15534,10 +15540,10 @@
         <v>9</v>
       </c>
       <c r="B915" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="C915" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="916" spans="1:3">
@@ -15545,10 +15551,10 @@
         <v>9</v>
       </c>
       <c r="B916" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="C916" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="917" spans="1:3">
@@ -15556,10 +15562,10 @@
         <v>9</v>
       </c>
       <c r="B917" t="s">
-        <v>1400</v>
+        <v>1394</v>
       </c>
       <c r="C917" t="s">
-        <v>1401</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="918" spans="1:3">
@@ -15567,10 +15573,10 @@
         <v>9</v>
       </c>
       <c r="B918" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="C918" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="919" spans="1:3">
@@ -15578,10 +15584,10 @@
         <v>9</v>
       </c>
       <c r="B919" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="C919" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="920" spans="1:3">
@@ -15589,10 +15595,10 @@
         <v>9</v>
       </c>
       <c r="B920" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="C920" t="s">
-        <v>1408</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="921" spans="1:3">
@@ -15600,21 +15606,21 @@
         <v>9</v>
       </c>
       <c r="B921" t="s">
-        <v>1422</v>
+        <v>1406</v>
       </c>
       <c r="C921" t="s">
-        <v>1423</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="922" spans="1:3">
       <c r="A922" t="s">
-        <v>7</v>
-      </c>
-      <c r="B922">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="B922" t="s">
+        <v>1422</v>
       </c>
       <c r="C922" t="s">
-        <v>1433</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="923" spans="1:3">
@@ -15622,10 +15628,10 @@
         <v>7</v>
       </c>
       <c r="B923">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C923" t="s">
-        <v>1439</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="924" spans="1:3">
@@ -15633,10 +15639,10 @@
         <v>7</v>
       </c>
       <c r="B924">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C924" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="925" spans="1:3">
@@ -15644,10 +15650,10 @@
         <v>7</v>
       </c>
       <c r="B925">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C925" t="s">
-        <v>1453</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="926" spans="1:3">
@@ -15655,21 +15661,21 @@
         <v>7</v>
       </c>
       <c r="B926">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C926" t="s">
-        <v>1461</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="927" spans="1:3">
       <c r="A927" t="s">
         <v>7</v>
       </c>
-      <c r="B927" t="s">
-        <v>257</v>
+      <c r="B927">
+        <v>5</v>
       </c>
       <c r="C927" t="s">
-        <v>259</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="928" spans="1:3">
@@ -15677,10 +15683,10 @@
         <v>7</v>
       </c>
       <c r="B928" t="s">
-        <v>339</v>
+        <v>257</v>
       </c>
       <c r="C928" t="s">
-        <v>340</v>
+        <v>259</v>
       </c>
     </row>
     <row r="929" spans="1:3">
@@ -15688,10 +15694,10 @@
         <v>7</v>
       </c>
       <c r="B929" t="s">
-        <v>375</v>
+        <v>339</v>
       </c>
       <c r="C929" t="s">
-        <v>376</v>
+        <v>340</v>
       </c>
     </row>
     <row r="930" spans="1:3">
@@ -15699,10 +15705,10 @@
         <v>7</v>
       </c>
       <c r="B930" t="s">
-        <v>399</v>
+        <v>375</v>
       </c>
       <c r="C930" t="s">
-        <v>400</v>
+        <v>376</v>
       </c>
     </row>
     <row r="931" spans="1:3">
@@ -15710,10 +15716,10 @@
         <v>7</v>
       </c>
       <c r="B931" t="s">
-        <v>422</v>
+        <v>399</v>
       </c>
       <c r="C931" t="s">
-        <v>423</v>
+        <v>400</v>
       </c>
     </row>
     <row r="932" spans="1:3">
@@ -15721,10 +15727,10 @@
         <v>7</v>
       </c>
       <c r="B932" t="s">
-        <v>582</v>
+        <v>422</v>
       </c>
       <c r="C932" t="s">
-        <v>583</v>
+        <v>423</v>
       </c>
     </row>
     <row r="933" spans="1:3">
@@ -15732,10 +15738,10 @@
         <v>7</v>
       </c>
       <c r="B933" t="s">
-        <v>745</v>
+        <v>582</v>
       </c>
       <c r="C933" t="s">
-        <v>746</v>
+        <v>583</v>
       </c>
     </row>
     <row r="934" spans="1:3">
@@ -15743,10 +15749,10 @@
         <v>7</v>
       </c>
       <c r="B934" t="s">
-        <v>909</v>
+        <v>745</v>
       </c>
       <c r="C934" t="s">
-        <v>910</v>
+        <v>746</v>
       </c>
     </row>
     <row r="935" spans="1:3">
@@ -15754,10 +15760,10 @@
         <v>7</v>
       </c>
       <c r="B935" t="s">
-        <v>1076</v>
+        <v>909</v>
       </c>
       <c r="C935" t="s">
-        <v>1077</v>
+        <v>910</v>
       </c>
     </row>
     <row r="936" spans="1:3">
@@ -15765,10 +15771,10 @@
         <v>7</v>
       </c>
       <c r="B936" t="s">
-        <v>1159</v>
+        <v>1076</v>
       </c>
       <c r="C936" t="s">
-        <v>1160</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="937" spans="1:3">
@@ -15776,21 +15782,21 @@
         <v>7</v>
       </c>
       <c r="B937" t="s">
-        <v>1409</v>
+        <v>1159</v>
       </c>
       <c r="C937" t="s">
-        <v>1410</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="938" spans="1:3">
       <c r="A938" t="s">
-        <v>1649</v>
-      </c>
-      <c r="B938">
-        <v>302</v>
+        <v>7</v>
+      </c>
+      <c r="B938" t="s">
+        <v>1409</v>
       </c>
       <c r="C938" t="s">
-        <v>1650</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="939" spans="1:3">
@@ -15798,10 +15804,10 @@
         <v>1649</v>
       </c>
       <c r="B939">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C939" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="940" spans="1:3">
@@ -15809,10 +15815,10 @@
         <v>1649</v>
       </c>
       <c r="B940">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C940" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="941" spans="1:3">
@@ -15820,10 +15826,10 @@
         <v>1649</v>
       </c>
       <c r="B941">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C941" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="942" spans="1:3">
@@ -15831,10 +15837,10 @@
         <v>1649</v>
       </c>
       <c r="B942">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C942" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="943" spans="1:3">
@@ -15842,10 +15848,10 @@
         <v>1649</v>
       </c>
       <c r="B943">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C943" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="944" spans="1:3">
@@ -15853,10 +15859,10 @@
         <v>1649</v>
       </c>
       <c r="B944">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C944" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="945" spans="1:3">
@@ -15864,10 +15870,10 @@
         <v>1649</v>
       </c>
       <c r="B945">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C945" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="946" spans="1:3">
@@ -15875,10 +15881,10 @@
         <v>1649</v>
       </c>
       <c r="B946">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C946" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="947" spans="1:3">
@@ -15886,10 +15892,10 @@
         <v>1649</v>
       </c>
       <c r="B947">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C947" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="948" spans="1:3">
@@ -15897,10 +15903,10 @@
         <v>1649</v>
       </c>
       <c r="B948">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C948" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="949" spans="1:3">
@@ -15908,10 +15914,10 @@
         <v>1649</v>
       </c>
       <c r="B949">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C949" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="950" spans="1:3">
@@ -15919,10 +15925,10 @@
         <v>1649</v>
       </c>
       <c r="B950">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C950" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="951" spans="1:3">
@@ -15930,10 +15936,10 @@
         <v>1649</v>
       </c>
       <c r="B951">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C951" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="952" spans="1:3">
@@ -15941,10 +15947,10 @@
         <v>1649</v>
       </c>
       <c r="B952">
-        <v>401</v>
+        <v>315</v>
       </c>
       <c r="C952" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="953" spans="1:3">
@@ -15952,10 +15958,10 @@
         <v>1649</v>
       </c>
       <c r="B953">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C953" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="954" spans="1:3">
@@ -15963,21 +15969,21 @@
         <v>1649</v>
       </c>
       <c r="B954">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C954" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="955" spans="1:3">
       <c r="A955" t="s">
-        <v>1607</v>
+        <v>1649</v>
       </c>
       <c r="B955">
-        <v>102</v>
+        <v>403</v>
       </c>
       <c r="C955" t="s">
-        <v>1608</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="956" spans="1:3">
@@ -15985,10 +15991,10 @@
         <v>1607</v>
       </c>
       <c r="B956">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C956" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="957" spans="1:3">
@@ -15996,10 +16002,10 @@
         <v>1607</v>
       </c>
       <c r="B957">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C957" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="958" spans="1:3">
@@ -16007,10 +16013,10 @@
         <v>1607</v>
       </c>
       <c r="B958">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C958" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="959" spans="1:3">
@@ -16018,10 +16024,10 @@
         <v>1607</v>
       </c>
       <c r="B959">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C959" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="960" spans="1:3">
@@ -16029,10 +16035,10 @@
         <v>1607</v>
       </c>
       <c r="B960">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C960" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="961" spans="1:3">
@@ -16040,10 +16046,10 @@
         <v>1607</v>
       </c>
       <c r="B961">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C961" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="962" spans="1:3">
@@ -16051,10 +16057,10 @@
         <v>1607</v>
       </c>
       <c r="B962">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C962" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="963" spans="1:3">
@@ -16062,10 +16068,10 @@
         <v>1607</v>
       </c>
       <c r="B963">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C963" t="s">
-        <v>1620</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="964" spans="1:3">
@@ -16073,10 +16079,10 @@
         <v>1607</v>
       </c>
       <c r="B964">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C964" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="965" spans="1:3">
@@ -16084,10 +16090,10 @@
         <v>1607</v>
       </c>
       <c r="B965">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C965" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="966" spans="1:3">
@@ -16095,10 +16101,10 @@
         <v>1607</v>
       </c>
       <c r="B966">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C966" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="967" spans="1:3">
@@ -16106,10 +16112,10 @@
         <v>1607</v>
       </c>
       <c r="B967">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C967" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="968" spans="1:3">
@@ -16117,10 +16123,10 @@
         <v>1607</v>
       </c>
       <c r="B968">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C968" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="969" spans="1:3">
@@ -16128,10 +16134,10 @@
         <v>1607</v>
       </c>
       <c r="B969">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C969" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="970" spans="1:3">
@@ -16139,10 +16145,10 @@
         <v>1607</v>
       </c>
       <c r="B970">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C970" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="971" spans="1:3">
@@ -16150,10 +16156,10 @@
         <v>1607</v>
       </c>
       <c r="B971">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C971" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="972" spans="1:3">
@@ -16161,10 +16167,10 @@
         <v>1607</v>
       </c>
       <c r="B972">
-        <v>201</v>
+        <v>119</v>
       </c>
       <c r="C972" t="s">
-        <v>1635</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="973" spans="1:3">
@@ -16172,10 +16178,10 @@
         <v>1607</v>
       </c>
       <c r="B973">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C973" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="974" spans="1:3">
@@ -16183,10 +16189,10 @@
         <v>1607</v>
       </c>
       <c r="B974">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C974" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="975" spans="1:3">
@@ -16194,10 +16200,10 @@
         <v>1607</v>
       </c>
       <c r="B975">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C975" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="976" spans="1:3">
@@ -16205,10 +16211,10 @@
         <v>1607</v>
       </c>
       <c r="B976">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C976" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="977" spans="1:3">
@@ -16216,10 +16222,10 @@
         <v>1607</v>
       </c>
       <c r="B977">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C977" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="978" spans="1:3">
@@ -16227,10 +16233,10 @@
         <v>1607</v>
       </c>
       <c r="B978">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C978" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="979" spans="1:3">
@@ -16238,10 +16244,10 @@
         <v>1607</v>
       </c>
       <c r="B979">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C979" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="980" spans="1:3">
@@ -16249,10 +16255,10 @@
         <v>1607</v>
       </c>
       <c r="B980">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C980" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="981" spans="1:3">
@@ -16260,10 +16266,10 @@
         <v>1607</v>
       </c>
       <c r="B981">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C981" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="982" spans="1:3">
@@ -16271,10 +16277,10 @@
         <v>1607</v>
       </c>
       <c r="B982">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C982" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="983" spans="1:3">
@@ -16282,10 +16288,10 @@
         <v>1607</v>
       </c>
       <c r="B983">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C983" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="984" spans="1:3">
@@ -16293,65 +16299,65 @@
         <v>1607</v>
       </c>
       <c r="B984">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C984" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="985" spans="1:3">
       <c r="A985" t="s">
-        <v>151</v>
-      </c>
-      <c r="B985" t="s">
-        <v>149</v>
+        <v>1607</v>
+      </c>
+      <c r="B985">
+        <v>213</v>
       </c>
       <c r="C985" t="s">
-        <v>152</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="986" spans="1:3">
       <c r="A986" t="s">
         <v>151</v>
       </c>
-      <c r="B986" s="1" t="s">
-        <v>260</v>
+      <c r="B986" t="s">
+        <v>149</v>
       </c>
       <c r="C986" t="s">
-        <v>261</v>
+        <v>152</v>
       </c>
     </row>
     <row r="987" spans="1:3">
       <c r="A987" t="s">
         <v>151</v>
       </c>
-      <c r="B987" t="s">
-        <v>713</v>
+      <c r="B987" s="1" t="s">
+        <v>260</v>
       </c>
       <c r="C987" t="s">
-        <v>714</v>
+        <v>261</v>
       </c>
     </row>
     <row r="988" spans="1:3">
       <c r="A988" t="s">
         <v>151</v>
       </c>
-      <c r="B988" t="s">
-        <v>923</v>
+      <c r="B988" s="1" t="s">
+        <v>382</v>
       </c>
       <c r="C988" t="s">
-        <v>925</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="989" spans="1:3">
       <c r="A989" t="s">
         <v>151</v>
       </c>
-      <c r="B989" s="1" t="s">
-        <v>1214</v>
+      <c r="B989" t="s">
+        <v>713</v>
       </c>
       <c r="C989" t="s">
-        <v>1215</v>
+        <v>714</v>
       </c>
     </row>
     <row r="990" spans="1:3">
@@ -16359,21 +16365,21 @@
         <v>151</v>
       </c>
       <c r="B990" s="1" t="s">
-        <v>151</v>
+        <v>923</v>
       </c>
       <c r="C990" t="s">
-        <v>1413</v>
+        <v>925</v>
       </c>
     </row>
     <row r="991" spans="1:3">
       <c r="A991" t="s">
         <v>151</v>
       </c>
-      <c r="B991" t="s">
-        <v>1414</v>
+      <c r="B991" s="1" t="s">
+        <v>1134</v>
       </c>
       <c r="C991" t="s">
-        <v>1415</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="992" spans="1:3">
@@ -16381,10 +16387,10 @@
         <v>151</v>
       </c>
       <c r="B992" s="1" t="s">
-        <v>382</v>
+        <v>1214</v>
       </c>
       <c r="C992" t="s">
-        <v>1682</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="993" spans="1:3">
@@ -16392,16 +16398,27 @@
         <v>151</v>
       </c>
       <c r="B993" s="1" t="s">
-        <v>1134</v>
+        <v>151</v>
       </c>
       <c r="C993" t="s">
-        <v>1683</v>
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="994" spans="1:3">
+      <c r="A994" t="s">
+        <v>151</v>
+      </c>
+      <c r="B994" t="s">
+        <v>1414</v>
+      </c>
+      <c r="C994" t="s">
+        <v>1415</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A1:D991">
-    <sortCondition ref="A1:A991"/>
-    <sortCondition ref="B1:B991"/>
+  <sortState ref="A1:D994">
+    <sortCondition ref="A1:A994"/>
+    <sortCondition ref="B1:B994"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/src/data/ruse-blocks.xlsx
+++ b/src/data/ruse-blocks.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2741" uniqueCount="1686">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2750" uniqueCount="1691">
   <si>
     <t>Дружба 1</t>
   </si>
@@ -5072,6 +5072,21 @@
   </si>
   <si>
     <t>Колос</t>
+  </si>
+  <si>
+    <t>ул. Сърнена гора 10</t>
+  </si>
+  <si>
+    <t>ул. Стоян Заимов №17</t>
+  </si>
+  <si>
+    <t>Маринета</t>
+  </si>
+  <si>
+    <t>ул. Чипровци №21А</t>
+  </si>
+  <si>
+    <t>Данц</t>
   </si>
 </sst>
 </file>
@@ -5463,7 +5478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D994"/>
+  <dimension ref="A1:D997"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="17.8984375" customWidth="1"/>
@@ -10567,7 +10582,7 @@
       <c r="A463" t="s">
         <v>113</v>
       </c>
-      <c r="B463" t="s">
+      <c r="B463" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C463" t="s">
@@ -10589,7 +10604,7 @@
       <c r="A465" t="s">
         <v>113</v>
       </c>
-      <c r="B465" t="s">
+      <c r="B465" s="1" t="s">
         <v>219</v>
       </c>
       <c r="C465" t="s">
@@ -10633,7 +10648,7 @@
       <c r="A469" t="s">
         <v>113</v>
       </c>
-      <c r="B469" t="s">
+      <c r="B469" s="1" t="s">
         <v>426</v>
       </c>
       <c r="C469" t="s">
@@ -10645,10 +10660,10 @@
         <v>113</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>624</v>
+        <v>568</v>
       </c>
       <c r="C470" t="s">
-        <v>625</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="471" spans="1:3">
@@ -10656,10 +10671,10 @@
         <v>113</v>
       </c>
       <c r="B471" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C471" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="472" spans="1:3">
@@ -10667,21 +10682,21 @@
         <v>113</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>1685</v>
+        <v>626</v>
       </c>
       <c r="C472" t="s">
-        <v>1684</v>
+        <v>627</v>
       </c>
     </row>
     <row r="473" spans="1:3">
       <c r="A473" t="s">
         <v>113</v>
       </c>
-      <c r="B473" t="s">
-        <v>630</v>
+      <c r="B473" s="1" t="s">
+        <v>1685</v>
       </c>
       <c r="C473" t="s">
-        <v>631</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="474" spans="1:3">
@@ -10689,32 +10704,32 @@
         <v>113</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>650</v>
+        <v>630</v>
       </c>
       <c r="C474" t="s">
-        <v>651</v>
+        <v>631</v>
       </c>
     </row>
     <row r="475" spans="1:3">
       <c r="A475" t="s">
         <v>113</v>
       </c>
-      <c r="B475" t="s">
-        <v>747</v>
+      <c r="B475" s="1" t="s">
+        <v>650</v>
       </c>
       <c r="C475" t="s">
-        <v>748</v>
+        <v>651</v>
       </c>
     </row>
     <row r="476" spans="1:3">
       <c r="A476" t="s">
         <v>113</v>
       </c>
-      <c r="B476" t="s">
-        <v>757</v>
+      <c r="B476" s="1" t="s">
+        <v>747</v>
       </c>
       <c r="C476" t="s">
-        <v>758</v>
+        <v>748</v>
       </c>
     </row>
     <row r="477" spans="1:3">
@@ -10722,10 +10737,10 @@
         <v>113</v>
       </c>
       <c r="B477" s="1" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="C477" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
     </row>
     <row r="478" spans="1:3">
@@ -10733,43 +10748,43 @@
         <v>113</v>
       </c>
       <c r="B478" s="1" t="s">
-        <v>780</v>
+        <v>763</v>
       </c>
       <c r="C478" t="s">
-        <v>781</v>
+        <v>764</v>
       </c>
     </row>
     <row r="479" spans="1:3">
       <c r="A479" t="s">
         <v>113</v>
       </c>
-      <c r="B479" t="s">
-        <v>802</v>
+      <c r="B479" s="1" t="s">
+        <v>780</v>
       </c>
       <c r="C479" t="s">
-        <v>803</v>
+        <v>781</v>
       </c>
     </row>
     <row r="480" spans="1:3">
       <c r="A480" t="s">
         <v>113</v>
       </c>
-      <c r="B480" t="s">
-        <v>804</v>
+      <c r="B480" s="1" t="s">
+        <v>802</v>
       </c>
       <c r="C480" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
     </row>
     <row r="481" spans="1:3">
       <c r="A481" t="s">
         <v>113</v>
       </c>
-      <c r="B481" t="s">
-        <v>809</v>
+      <c r="B481" s="1" t="s">
+        <v>804</v>
       </c>
       <c r="C481" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
     </row>
     <row r="482" spans="1:3">
@@ -10777,21 +10792,21 @@
         <v>113</v>
       </c>
       <c r="B482" s="1" t="s">
-        <v>940</v>
+        <v>809</v>
       </c>
       <c r="C482" t="s">
-        <v>941</v>
+        <v>810</v>
       </c>
     </row>
     <row r="483" spans="1:3">
       <c r="A483" t="s">
         <v>113</v>
       </c>
-      <c r="B483" t="s">
-        <v>973</v>
+      <c r="B483" s="1" t="s">
+        <v>1688</v>
       </c>
       <c r="C483" t="s">
-        <v>974</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="484" spans="1:3">
@@ -10799,21 +10814,21 @@
         <v>113</v>
       </c>
       <c r="B484" s="1" t="s">
-        <v>1148</v>
+        <v>940</v>
       </c>
       <c r="C484" t="s">
-        <v>1149</v>
+        <v>941</v>
       </c>
     </row>
     <row r="485" spans="1:3">
       <c r="A485" t="s">
         <v>113</v>
       </c>
-      <c r="B485" t="s">
-        <v>1193</v>
+      <c r="B485" s="1" t="s">
+        <v>973</v>
       </c>
       <c r="C485" t="s">
-        <v>1194</v>
+        <v>974</v>
       </c>
     </row>
     <row r="486" spans="1:3">
@@ -10821,10 +10836,10 @@
         <v>113</v>
       </c>
       <c r="B486" s="1" t="s">
-        <v>1232</v>
+        <v>1148</v>
       </c>
       <c r="C486" t="s">
-        <v>1233</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="487" spans="1:3">
@@ -10832,43 +10847,43 @@
         <v>113</v>
       </c>
       <c r="B487" s="1" t="s">
-        <v>1252</v>
+        <v>1193</v>
       </c>
       <c r="C487" t="s">
-        <v>1253</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="488" spans="1:3">
       <c r="A488" t="s">
         <v>113</v>
       </c>
-      <c r="B488" t="s">
-        <v>1267</v>
+      <c r="B488" s="1" t="s">
+        <v>1232</v>
       </c>
       <c r="C488" t="s">
-        <v>1268</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="489" spans="1:3">
       <c r="A489" t="s">
-        <v>24</v>
-      </c>
-      <c r="B489" t="s">
-        <v>25</v>
+        <v>113</v>
+      </c>
+      <c r="B489" s="1" t="s">
+        <v>1252</v>
       </c>
       <c r="C489" t="s">
-        <v>26</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="490" spans="1:3">
       <c r="A490" t="s">
-        <v>24</v>
-      </c>
-      <c r="B490" t="s">
-        <v>27</v>
+        <v>113</v>
+      </c>
+      <c r="B490" s="1" t="s">
+        <v>1267</v>
       </c>
       <c r="C490" t="s">
-        <v>28</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="491" spans="1:3">
@@ -10876,10 +10891,10 @@
         <v>24</v>
       </c>
       <c r="B491" t="s">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="C491" t="s">
-        <v>121</v>
+        <v>26</v>
       </c>
     </row>
     <row r="492" spans="1:3">
@@ -10887,10 +10902,10 @@
         <v>24</v>
       </c>
       <c r="B492" t="s">
-        <v>175</v>
+        <v>27</v>
       </c>
       <c r="C492" t="s">
-        <v>176</v>
+        <v>28</v>
       </c>
     </row>
     <row r="493" spans="1:3">
@@ -10898,10 +10913,10 @@
         <v>24</v>
       </c>
       <c r="B493" t="s">
-        <v>196</v>
+        <v>120</v>
       </c>
       <c r="C493" t="s">
-        <v>197</v>
+        <v>121</v>
       </c>
     </row>
     <row r="494" spans="1:3">
@@ -10909,10 +10924,10 @@
         <v>24</v>
       </c>
       <c r="B494" t="s">
-        <v>221</v>
+        <v>175</v>
       </c>
       <c r="C494" t="s">
-        <v>222</v>
+        <v>176</v>
       </c>
     </row>
     <row r="495" spans="1:3">
@@ -10920,10 +10935,10 @@
         <v>24</v>
       </c>
       <c r="B495" t="s">
-        <v>227</v>
+        <v>196</v>
       </c>
       <c r="C495" t="s">
-        <v>228</v>
+        <v>197</v>
       </c>
     </row>
     <row r="496" spans="1:3">
@@ -10931,10 +10946,10 @@
         <v>24</v>
       </c>
       <c r="B496" t="s">
-        <v>283</v>
+        <v>221</v>
       </c>
       <c r="C496" t="s">
-        <v>284</v>
+        <v>222</v>
       </c>
     </row>
     <row r="497" spans="1:3">
@@ -10942,10 +10957,10 @@
         <v>24</v>
       </c>
       <c r="B497" t="s">
-        <v>346</v>
+        <v>227</v>
       </c>
       <c r="C497" t="s">
-        <v>347</v>
+        <v>228</v>
       </c>
     </row>
     <row r="498" spans="1:3">
@@ -10953,10 +10968,10 @@
         <v>24</v>
       </c>
       <c r="B498" t="s">
-        <v>369</v>
+        <v>283</v>
       </c>
       <c r="C498" t="s">
-        <v>370</v>
+        <v>284</v>
       </c>
     </row>
     <row r="499" spans="1:3">
@@ -10964,10 +10979,10 @@
         <v>24</v>
       </c>
       <c r="B499" t="s">
-        <v>464</v>
+        <v>346</v>
       </c>
       <c r="C499" t="s">
-        <v>465</v>
+        <v>347</v>
       </c>
     </row>
     <row r="500" spans="1:3">
@@ -10975,10 +10990,10 @@
         <v>24</v>
       </c>
       <c r="B500" t="s">
-        <v>494</v>
+        <v>369</v>
       </c>
       <c r="C500" t="s">
-        <v>495</v>
+        <v>370</v>
       </c>
     </row>
     <row r="501" spans="1:3">
@@ -10986,10 +11001,10 @@
         <v>24</v>
       </c>
       <c r="B501" t="s">
-        <v>545</v>
+        <v>464</v>
       </c>
       <c r="C501" t="s">
-        <v>546</v>
+        <v>465</v>
       </c>
     </row>
     <row r="502" spans="1:3">
@@ -10997,10 +11012,10 @@
         <v>24</v>
       </c>
       <c r="B502" t="s">
-        <v>605</v>
+        <v>494</v>
       </c>
       <c r="C502" t="s">
-        <v>606</v>
+        <v>495</v>
       </c>
     </row>
     <row r="503" spans="1:3">
@@ -11008,10 +11023,10 @@
         <v>24</v>
       </c>
       <c r="B503" t="s">
-        <v>618</v>
+        <v>545</v>
       </c>
       <c r="C503" t="s">
-        <v>619</v>
+        <v>546</v>
       </c>
     </row>
     <row r="504" spans="1:3">
@@ -11019,10 +11034,10 @@
         <v>24</v>
       </c>
       <c r="B504" t="s">
-        <v>662</v>
+        <v>605</v>
       </c>
       <c r="C504" t="s">
-        <v>663</v>
+        <v>606</v>
       </c>
     </row>
     <row r="505" spans="1:3">
@@ -11030,10 +11045,10 @@
         <v>24</v>
       </c>
       <c r="B505" t="s">
-        <v>670</v>
+        <v>618</v>
       </c>
       <c r="C505" t="s">
-        <v>671</v>
+        <v>619</v>
       </c>
     </row>
     <row r="506" spans="1:3">
@@ -11041,10 +11056,10 @@
         <v>24</v>
       </c>
       <c r="B506" t="s">
-        <v>903</v>
+        <v>662</v>
       </c>
       <c r="C506" t="s">
-        <v>904</v>
+        <v>663</v>
       </c>
     </row>
     <row r="507" spans="1:3">
@@ -11052,10 +11067,10 @@
         <v>24</v>
       </c>
       <c r="B507" t="s">
-        <v>986</v>
+        <v>670</v>
       </c>
       <c r="C507" t="s">
-        <v>987</v>
+        <v>671</v>
       </c>
     </row>
     <row r="508" spans="1:3">
@@ -11063,10 +11078,10 @@
         <v>24</v>
       </c>
       <c r="B508" t="s">
-        <v>992</v>
+        <v>903</v>
       </c>
       <c r="C508" t="s">
-        <v>993</v>
+        <v>904</v>
       </c>
     </row>
     <row r="509" spans="1:3">
@@ -11074,10 +11089,10 @@
         <v>24</v>
       </c>
       <c r="B509" t="s">
-        <v>1006</v>
+        <v>986</v>
       </c>
       <c r="C509" t="s">
-        <v>1007</v>
+        <v>987</v>
       </c>
     </row>
     <row r="510" spans="1:3">
@@ -11085,10 +11100,10 @@
         <v>24</v>
       </c>
       <c r="B510" t="s">
-        <v>1111</v>
+        <v>992</v>
       </c>
       <c r="C510" t="s">
-        <v>1112</v>
+        <v>993</v>
       </c>
     </row>
     <row r="511" spans="1:3">
@@ -11096,10 +11111,10 @@
         <v>24</v>
       </c>
       <c r="B511" t="s">
-        <v>1132</v>
+        <v>1006</v>
       </c>
       <c r="C511" t="s">
-        <v>1133</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="512" spans="1:3">
@@ -11107,10 +11122,10 @@
         <v>24</v>
       </c>
       <c r="B512" t="s">
-        <v>1202</v>
+        <v>1111</v>
       </c>
       <c r="C512" t="s">
-        <v>1203</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="513" spans="1:3">
@@ -11118,10 +11133,10 @@
         <v>24</v>
       </c>
       <c r="B513" t="s">
-        <v>1234</v>
+        <v>1132</v>
       </c>
       <c r="C513" t="s">
-        <v>1235</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="514" spans="1:3">
@@ -11129,10 +11144,10 @@
         <v>24</v>
       </c>
       <c r="B514" t="s">
-        <v>1248</v>
+        <v>1202</v>
       </c>
       <c r="C514" t="s">
-        <v>1249</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="515" spans="1:3">
@@ -11140,10 +11155,10 @@
         <v>24</v>
       </c>
       <c r="B515" t="s">
-        <v>1260</v>
+        <v>1234</v>
       </c>
       <c r="C515" t="s">
-        <v>1261</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="516" spans="1:3">
@@ -11151,10 +11166,10 @@
         <v>24</v>
       </c>
       <c r="B516" t="s">
-        <v>1304</v>
+        <v>1248</v>
       </c>
       <c r="C516" t="s">
-        <v>1305</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="517" spans="1:3">
@@ -11162,10 +11177,10 @@
         <v>24</v>
       </c>
       <c r="B517" t="s">
-        <v>1321</v>
+        <v>1260</v>
       </c>
       <c r="C517" t="s">
-        <v>1322</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="518" spans="1:3">
@@ -11173,10 +11188,10 @@
         <v>24</v>
       </c>
       <c r="B518" t="s">
-        <v>1323</v>
+        <v>1304</v>
       </c>
       <c r="C518" t="s">
-        <v>1324</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="519" spans="1:3">
@@ -11184,10 +11199,10 @@
         <v>24</v>
       </c>
       <c r="B519" t="s">
-        <v>1325</v>
+        <v>1321</v>
       </c>
       <c r="C519" t="s">
-        <v>1326</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="520" spans="1:3">
@@ -11195,10 +11210,10 @@
         <v>24</v>
       </c>
       <c r="B520" t="s">
-        <v>1327</v>
+        <v>1323</v>
       </c>
       <c r="C520" t="s">
-        <v>1328</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="521" spans="1:3">
@@ -11206,32 +11221,32 @@
         <v>24</v>
       </c>
       <c r="B521" t="s">
-        <v>1380</v>
+        <v>1325</v>
       </c>
       <c r="C521" t="s">
-        <v>1381</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="522" spans="1:3">
       <c r="A522" t="s">
-        <v>5</v>
-      </c>
-      <c r="B522">
-        <v>1</v>
+        <v>24</v>
+      </c>
+      <c r="B522" t="s">
+        <v>1327</v>
       </c>
       <c r="C522" t="s">
-        <v>1431</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="523" spans="1:3">
       <c r="A523" t="s">
-        <v>5</v>
-      </c>
-      <c r="B523">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="B523" t="s">
+        <v>1380</v>
       </c>
       <c r="C523" t="s">
-        <v>1437</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="524" spans="1:3">
@@ -11239,10 +11254,10 @@
         <v>5</v>
       </c>
       <c r="B524">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C524" t="s">
-        <v>1445</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="525" spans="1:3">
@@ -11250,43 +11265,43 @@
         <v>5</v>
       </c>
       <c r="B525">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C525" t="s">
-        <v>1477</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="526" spans="1:3">
       <c r="A526" t="s">
         <v>5</v>
       </c>
-      <c r="B526" t="s">
-        <v>1341</v>
+      <c r="B526">
+        <v>3</v>
       </c>
       <c r="C526" t="s">
-        <v>1342</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="527" spans="1:3">
       <c r="A527" t="s">
-        <v>530</v>
-      </c>
-      <c r="B527" t="s">
-        <v>531</v>
+        <v>5</v>
+      </c>
+      <c r="B527">
+        <v>8</v>
       </c>
       <c r="C527" t="s">
-        <v>532</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="528" spans="1:3">
       <c r="A528" t="s">
-        <v>530</v>
+        <v>5</v>
       </c>
       <c r="B528" t="s">
-        <v>977</v>
+        <v>1341</v>
       </c>
       <c r="C528" t="s">
-        <v>978</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="529" spans="1:3">
@@ -11294,10 +11309,10 @@
         <v>530</v>
       </c>
       <c r="B529" t="s">
-        <v>979</v>
+        <v>531</v>
       </c>
       <c r="C529" t="s">
-        <v>978</v>
+        <v>532</v>
       </c>
     </row>
     <row r="530" spans="1:3">
@@ -11305,10 +11320,10 @@
         <v>530</v>
       </c>
       <c r="B530" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="C530" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
     </row>
     <row r="531" spans="1:3">
@@ -11316,32 +11331,32 @@
         <v>530</v>
       </c>
       <c r="B531" t="s">
-        <v>1189</v>
+        <v>979</v>
       </c>
       <c r="C531" t="s">
-        <v>1190</v>
+        <v>978</v>
       </c>
     </row>
     <row r="532" spans="1:3">
       <c r="A532" t="s">
-        <v>6</v>
-      </c>
-      <c r="B532">
-        <v>1</v>
+        <v>530</v>
+      </c>
+      <c r="B532" t="s">
+        <v>980</v>
       </c>
       <c r="C532" t="s">
-        <v>1432</v>
+        <v>981</v>
       </c>
     </row>
     <row r="533" spans="1:3">
       <c r="A533" t="s">
-        <v>6</v>
-      </c>
-      <c r="B533">
-        <v>2</v>
+        <v>530</v>
+      </c>
+      <c r="B533" t="s">
+        <v>1189</v>
       </c>
       <c r="C533" t="s">
-        <v>1438</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="534" spans="1:3">
@@ -11349,10 +11364,10 @@
         <v>6</v>
       </c>
       <c r="B534">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C534" t="s">
-        <v>1446</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="535" spans="1:3">
@@ -11360,10 +11375,10 @@
         <v>6</v>
       </c>
       <c r="B535">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C535" t="s">
-        <v>1452</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="536" spans="1:3">
@@ -11371,10 +11386,10 @@
         <v>6</v>
       </c>
       <c r="B536">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C536" t="s">
-        <v>1460</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="537" spans="1:3">
@@ -11382,10 +11397,10 @@
         <v>6</v>
       </c>
       <c r="B537">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C537" t="s">
-        <v>1467</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="538" spans="1:3">
@@ -11393,10 +11408,10 @@
         <v>6</v>
       </c>
       <c r="B538">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C538" t="s">
-        <v>1478</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="539" spans="1:3">
@@ -11404,10 +11419,10 @@
         <v>6</v>
       </c>
       <c r="B539">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C539" t="s">
-        <v>1487</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="540" spans="1:3">
@@ -11415,10 +11430,10 @@
         <v>6</v>
       </c>
       <c r="B540">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C540" t="s">
-        <v>1494</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="541" spans="1:3">
@@ -11426,10 +11441,10 @@
         <v>6</v>
       </c>
       <c r="B541">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C541" t="s">
-        <v>1527</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="542" spans="1:3">
@@ -11437,10 +11452,10 @@
         <v>6</v>
       </c>
       <c r="B542">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C542" t="s">
-        <v>1528</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="543" spans="1:3">
@@ -11448,10 +11463,10 @@
         <v>6</v>
       </c>
       <c r="B543">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C543" t="s">
-        <v>1533</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="544" spans="1:3">
@@ -11459,10 +11474,10 @@
         <v>6</v>
       </c>
       <c r="B544">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C544" t="s">
-        <v>1536</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="545" spans="1:3">
@@ -11470,10 +11485,10 @@
         <v>6</v>
       </c>
       <c r="B545">
-        <v>118</v>
+        <v>28</v>
       </c>
       <c r="C545" t="s">
-        <v>1628</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="546" spans="1:3">
@@ -11481,32 +11496,32 @@
         <v>6</v>
       </c>
       <c r="B546">
-        <v>120</v>
+        <v>29</v>
       </c>
       <c r="C546" t="s">
-        <v>1631</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="547" spans="1:3">
       <c r="A547" t="s">
         <v>6</v>
       </c>
-      <c r="B547" t="s">
-        <v>14</v>
+      <c r="B547">
+        <v>118</v>
       </c>
       <c r="C547" t="s">
-        <v>15</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="548" spans="1:3">
       <c r="A548" t="s">
         <v>6</v>
       </c>
-      <c r="B548" t="s">
-        <v>67</v>
+      <c r="B548">
+        <v>120</v>
       </c>
       <c r="C548" t="s">
-        <v>68</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="549" spans="1:3">
@@ -11514,10 +11529,10 @@
         <v>6</v>
       </c>
       <c r="B549" t="s">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="C549" t="s">
-        <v>73</v>
+        <v>15</v>
       </c>
     </row>
     <row r="550" spans="1:3">
@@ -11525,10 +11540,10 @@
         <v>6</v>
       </c>
       <c r="B550" t="s">
-        <v>132</v>
+        <v>67</v>
       </c>
       <c r="C550" t="s">
-        <v>133</v>
+        <v>68</v>
       </c>
     </row>
     <row r="551" spans="1:3">
@@ -11536,10 +11551,10 @@
         <v>6</v>
       </c>
       <c r="B551" t="s">
-        <v>163</v>
+        <v>72</v>
       </c>
       <c r="C551" t="s">
-        <v>164</v>
+        <v>73</v>
       </c>
     </row>
     <row r="552" spans="1:3">
@@ -11547,10 +11562,10 @@
         <v>6</v>
       </c>
       <c r="B552" t="s">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="C552" t="s">
-        <v>166</v>
+        <v>133</v>
       </c>
     </row>
     <row r="553" spans="1:3">
@@ -11558,10 +11573,10 @@
         <v>6</v>
       </c>
       <c r="B553" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C553" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="554" spans="1:3">
@@ -11569,10 +11584,10 @@
         <v>6</v>
       </c>
       <c r="B554" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C554" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="555" spans="1:3">
@@ -11580,10 +11595,10 @@
         <v>6</v>
       </c>
       <c r="B555" t="s">
-        <v>287</v>
+        <v>167</v>
       </c>
       <c r="C555" t="s">
-        <v>288</v>
+        <v>168</v>
       </c>
     </row>
     <row r="556" spans="1:3">
@@ -11591,10 +11606,10 @@
         <v>6</v>
       </c>
       <c r="B556" t="s">
-        <v>490</v>
+        <v>169</v>
       </c>
       <c r="C556" t="s">
-        <v>491</v>
+        <v>170</v>
       </c>
     </row>
     <row r="557" spans="1:3">
@@ -11602,10 +11617,10 @@
         <v>6</v>
       </c>
       <c r="B557" t="s">
-        <v>511</v>
+        <v>287</v>
       </c>
       <c r="C557" t="s">
-        <v>512</v>
+        <v>288</v>
       </c>
     </row>
     <row r="558" spans="1:3">
@@ -11613,10 +11628,10 @@
         <v>6</v>
       </c>
       <c r="B558" t="s">
-        <v>662</v>
+        <v>490</v>
       </c>
       <c r="C558" t="s">
-        <v>664</v>
+        <v>491</v>
       </c>
     </row>
     <row r="559" spans="1:3">
@@ -11624,10 +11639,10 @@
         <v>6</v>
       </c>
       <c r="B559" t="s">
-        <v>694</v>
+        <v>511</v>
       </c>
       <c r="C559" t="s">
-        <v>695</v>
+        <v>512</v>
       </c>
     </row>
     <row r="560" spans="1:3">
@@ -11635,10 +11650,10 @@
         <v>6</v>
       </c>
       <c r="B560" t="s">
-        <v>715</v>
+        <v>662</v>
       </c>
       <c r="C560" t="s">
-        <v>716</v>
+        <v>664</v>
       </c>
     </row>
     <row r="561" spans="1:3">
@@ -11646,10 +11661,10 @@
         <v>6</v>
       </c>
       <c r="B561" t="s">
-        <v>721</v>
+        <v>694</v>
       </c>
       <c r="C561" t="s">
-        <v>722</v>
+        <v>695</v>
       </c>
     </row>
     <row r="562" spans="1:3">
@@ -11657,10 +11672,10 @@
         <v>6</v>
       </c>
       <c r="B562" t="s">
-        <v>741</v>
+        <v>715</v>
       </c>
       <c r="C562" t="s">
-        <v>742</v>
+        <v>716</v>
       </c>
     </row>
     <row r="563" spans="1:3">
@@ -11668,10 +11683,10 @@
         <v>6</v>
       </c>
       <c r="B563" t="s">
-        <v>743</v>
+        <v>721</v>
       </c>
       <c r="C563" t="s">
-        <v>744</v>
+        <v>722</v>
       </c>
     </row>
     <row r="564" spans="1:3">
@@ -11679,10 +11694,10 @@
         <v>6</v>
       </c>
       <c r="B564" t="s">
-        <v>754</v>
+        <v>741</v>
       </c>
       <c r="C564" t="s">
-        <v>756</v>
+        <v>742</v>
       </c>
     </row>
     <row r="565" spans="1:3">
@@ -11690,10 +11705,10 @@
         <v>6</v>
       </c>
       <c r="B565" t="s">
-        <v>942</v>
+        <v>743</v>
       </c>
       <c r="C565" t="s">
-        <v>943</v>
+        <v>744</v>
       </c>
     </row>
     <row r="566" spans="1:3">
@@ -11701,10 +11716,10 @@
         <v>6</v>
       </c>
       <c r="B566" t="s">
-        <v>1018</v>
+        <v>754</v>
       </c>
       <c r="C566" t="s">
-        <v>1020</v>
+        <v>756</v>
       </c>
     </row>
     <row r="567" spans="1:3">
@@ -11712,10 +11727,10 @@
         <v>6</v>
       </c>
       <c r="B567" t="s">
-        <v>1104</v>
+        <v>942</v>
       </c>
       <c r="C567" t="s">
-        <v>1105</v>
+        <v>943</v>
       </c>
     </row>
     <row r="568" spans="1:3">
@@ -11723,10 +11738,10 @@
         <v>6</v>
       </c>
       <c r="B568" t="s">
-        <v>1273</v>
+        <v>1018</v>
       </c>
       <c r="C568" t="s">
-        <v>1274</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="569" spans="1:3">
@@ -11734,10 +11749,10 @@
         <v>6</v>
       </c>
       <c r="B569" t="s">
-        <v>1288</v>
+        <v>1104</v>
       </c>
       <c r="C569" t="s">
-        <v>1290</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="570" spans="1:3">
@@ -11745,10 +11760,10 @@
         <v>6</v>
       </c>
       <c r="B570" t="s">
-        <v>1297</v>
+        <v>1273</v>
       </c>
       <c r="C570" t="s">
-        <v>1298</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="571" spans="1:3">
@@ -11756,32 +11771,32 @@
         <v>6</v>
       </c>
       <c r="B571" t="s">
-        <v>1301</v>
+        <v>1288</v>
       </c>
       <c r="C571" t="s">
-        <v>1303</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="572" spans="1:3">
       <c r="A572" t="s">
-        <v>9</v>
-      </c>
-      <c r="B572">
         <v>6</v>
       </c>
+      <c r="B572" t="s">
+        <v>1297</v>
+      </c>
       <c r="C572" t="s">
-        <v>1468</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="573" spans="1:3">
       <c r="A573" t="s">
-        <v>9</v>
-      </c>
-      <c r="B573">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="B573" t="s">
+        <v>1301</v>
       </c>
       <c r="C573" t="s">
-        <v>1474</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="574" spans="1:3">
@@ -11789,10 +11804,10 @@
         <v>9</v>
       </c>
       <c r="B574">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C574" t="s">
-        <v>1479</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="575" spans="1:3">
@@ -11800,10 +11815,10 @@
         <v>9</v>
       </c>
       <c r="B575">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C575" t="s">
-        <v>1483</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="576" spans="1:3">
@@ -11811,10 +11826,10 @@
         <v>9</v>
       </c>
       <c r="B576">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C576" t="s">
-        <v>1491</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="577" spans="1:3">
@@ -11822,10 +11837,10 @@
         <v>9</v>
       </c>
       <c r="B577">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C577" t="s">
-        <v>1495</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="578" spans="1:3">
@@ -11833,10 +11848,10 @@
         <v>9</v>
       </c>
       <c r="B578">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C578" t="s">
-        <v>1498</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="579" spans="1:3">
@@ -11844,10 +11859,10 @@
         <v>9</v>
       </c>
       <c r="B579">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C579" t="s">
-        <v>1501</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="580" spans="1:3">
@@ -11855,10 +11870,10 @@
         <v>9</v>
       </c>
       <c r="B580">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C580" t="s">
-        <v>1504</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="581" spans="1:3">
@@ -11866,10 +11881,10 @@
         <v>9</v>
       </c>
       <c r="B581">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="C581" t="s">
-        <v>1612</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="582" spans="1:3">
@@ -11877,10 +11892,10 @@
         <v>9</v>
       </c>
       <c r="B582">
-        <v>115</v>
+        <v>15</v>
       </c>
       <c r="C582" t="s">
-        <v>1624</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="583" spans="1:3">
@@ -11888,32 +11903,32 @@
         <v>9</v>
       </c>
       <c r="B583">
-        <v>202</v>
+        <v>106</v>
       </c>
       <c r="C583" t="s">
-        <v>1636</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="584" spans="1:3">
       <c r="A584" t="s">
         <v>9</v>
       </c>
-      <c r="B584" t="s">
-        <v>1667</v>
+      <c r="B584">
+        <v>115</v>
       </c>
       <c r="C584" t="s">
-        <v>1668</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="585" spans="1:3">
       <c r="A585" t="s">
         <v>9</v>
       </c>
-      <c r="B585" t="s">
-        <v>1669</v>
+      <c r="B585">
+        <v>202</v>
       </c>
       <c r="C585" t="s">
-        <v>1670</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="586" spans="1:3">
@@ -11921,10 +11936,10 @@
         <v>9</v>
       </c>
       <c r="B586" t="s">
-        <v>10</v>
+        <v>1667</v>
       </c>
       <c r="C586" t="s">
-        <v>11</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="587" spans="1:3">
@@ -11932,10 +11947,10 @@
         <v>9</v>
       </c>
       <c r="B587" t="s">
-        <v>12</v>
+        <v>1669</v>
       </c>
       <c r="C587" t="s">
-        <v>13</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="588" spans="1:3">
@@ -11943,10 +11958,10 @@
         <v>9</v>
       </c>
       <c r="B588" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C588" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="589" spans="1:3">
@@ -11954,10 +11969,10 @@
         <v>9</v>
       </c>
       <c r="B589" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C589" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="590" spans="1:3">
@@ -11965,10 +11980,10 @@
         <v>9</v>
       </c>
       <c r="B590" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C590" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="591" spans="1:3">
@@ -11976,10 +11991,10 @@
         <v>9</v>
       </c>
       <c r="B591" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C591" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="592" spans="1:3">
@@ -11987,10 +12002,10 @@
         <v>9</v>
       </c>
       <c r="B592" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C592" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
     </row>
     <row r="593" spans="1:3">
@@ -11998,10 +12013,10 @@
         <v>9</v>
       </c>
       <c r="B593" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C593" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="594" spans="1:3">
@@ -12009,10 +12024,10 @@
         <v>9</v>
       </c>
       <c r="B594" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C594" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="595" spans="1:3">
@@ -12020,10 +12035,10 @@
         <v>9</v>
       </c>
       <c r="B595" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C595" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="596" spans="1:3">
@@ -12031,10 +12046,10 @@
         <v>9</v>
       </c>
       <c r="B596" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C596" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="597" spans="1:3">
@@ -12042,10 +12057,10 @@
         <v>9</v>
       </c>
       <c r="B597" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C597" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="598" spans="1:3">
@@ -12053,10 +12068,10 @@
         <v>9</v>
       </c>
       <c r="B598" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C598" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="599" spans="1:3">
@@ -12064,10 +12079,10 @@
         <v>9</v>
       </c>
       <c r="B599" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C599" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="600" spans="1:3">
@@ -12075,10 +12090,10 @@
         <v>9</v>
       </c>
       <c r="B600" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C600" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="601" spans="1:3">
@@ -12086,10 +12101,10 @@
         <v>9</v>
       </c>
       <c r="B601" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C601" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="602" spans="1:3">
@@ -12097,10 +12112,10 @@
         <v>9</v>
       </c>
       <c r="B602" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C602" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="603" spans="1:3">
@@ -12108,10 +12123,10 @@
         <v>9</v>
       </c>
       <c r="B603" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C603" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="604" spans="1:3">
@@ -12119,10 +12134,10 @@
         <v>9</v>
       </c>
       <c r="B604" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C604" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="605" spans="1:3">
@@ -12130,10 +12145,10 @@
         <v>9</v>
       </c>
       <c r="B605" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="C605" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
     </row>
     <row r="606" spans="1:3">
@@ -12141,10 +12156,10 @@
         <v>9</v>
       </c>
       <c r="B606" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="C606" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
     </row>
     <row r="607" spans="1:3">
@@ -12152,10 +12167,10 @@
         <v>9</v>
       </c>
       <c r="B607" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C607" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="608" spans="1:3">
@@ -12163,10 +12178,10 @@
         <v>9</v>
       </c>
       <c r="B608" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C608" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="609" spans="1:3">
@@ -12174,10 +12189,10 @@
         <v>9</v>
       </c>
       <c r="B609" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C609" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="610" spans="1:3">
@@ -12185,10 +12200,10 @@
         <v>9</v>
       </c>
       <c r="B610" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C610" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="611" spans="1:3">
@@ -12196,10 +12211,10 @@
         <v>9</v>
       </c>
       <c r="B611" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C611" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="612" spans="1:3">
@@ -12207,10 +12222,10 @@
         <v>9</v>
       </c>
       <c r="B612" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C612" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="613" spans="1:3">
@@ -12218,10 +12233,10 @@
         <v>9</v>
       </c>
       <c r="B613" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C613" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="614" spans="1:3">
@@ -12229,10 +12244,10 @@
         <v>9</v>
       </c>
       <c r="B614" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C614" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="615" spans="1:3">
@@ -12240,10 +12255,10 @@
         <v>9</v>
       </c>
       <c r="B615" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C615" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="616" spans="1:3">
@@ -12251,10 +12266,10 @@
         <v>9</v>
       </c>
       <c r="B616" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C616" t="s">
-        <v>19</v>
+        <v>105</v>
       </c>
     </row>
     <row r="617" spans="1:3">
@@ -12262,10 +12277,10 @@
         <v>9</v>
       </c>
       <c r="B617" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C617" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="618" spans="1:3">
@@ -12273,10 +12288,10 @@
         <v>9</v>
       </c>
       <c r="B618" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="C618" t="s">
-        <v>123</v>
+        <v>19</v>
       </c>
     </row>
     <row r="619" spans="1:3">
@@ -12284,10 +12299,10 @@
         <v>9</v>
       </c>
       <c r="B619" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="C619" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
     </row>
     <row r="620" spans="1:3">
@@ -12295,10 +12310,10 @@
         <v>9</v>
       </c>
       <c r="B620" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C620" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="621" spans="1:3">
@@ -12306,10 +12321,10 @@
         <v>9</v>
       </c>
       <c r="B621" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="C621" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
     </row>
     <row r="622" spans="1:3">
@@ -12317,10 +12332,10 @@
         <v>9</v>
       </c>
       <c r="B622" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C622" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
     </row>
     <row r="623" spans="1:3">
@@ -12328,10 +12343,10 @@
         <v>9</v>
       </c>
       <c r="B623" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C623" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="624" spans="1:3">
@@ -12339,10 +12354,10 @@
         <v>9</v>
       </c>
       <c r="B624" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="C624" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
     </row>
     <row r="625" spans="1:3">
@@ -12350,10 +12365,10 @@
         <v>9</v>
       </c>
       <c r="B625" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="C625" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
     </row>
     <row r="626" spans="1:3">
@@ -12361,10 +12376,10 @@
         <v>9</v>
       </c>
       <c r="B626" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C626" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="627" spans="1:3">
@@ -12372,10 +12387,10 @@
         <v>9</v>
       </c>
       <c r="B627" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C627" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="628" spans="1:3">
@@ -12383,10 +12398,10 @@
         <v>9</v>
       </c>
       <c r="B628" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="C628" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
     </row>
     <row r="629" spans="1:3">
@@ -12394,10 +12409,10 @@
         <v>9</v>
       </c>
       <c r="B629" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="C629" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
     </row>
     <row r="630" spans="1:3">
@@ -12405,10 +12420,10 @@
         <v>9</v>
       </c>
       <c r="B630" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="C630" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="631" spans="1:3">
@@ -12416,10 +12431,10 @@
         <v>9</v>
       </c>
       <c r="B631" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="C631" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
     </row>
     <row r="632" spans="1:3">
@@ -12427,10 +12442,10 @@
         <v>9</v>
       </c>
       <c r="B632" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="C632" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
     </row>
     <row r="633" spans="1:3">
@@ -12438,10 +12453,10 @@
         <v>9</v>
       </c>
       <c r="B633" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C633" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="634" spans="1:3">
@@ -12449,10 +12464,10 @@
         <v>9</v>
       </c>
       <c r="B634" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C634" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
     </row>
     <row r="635" spans="1:3">
@@ -12460,10 +12475,10 @@
         <v>9</v>
       </c>
       <c r="B635" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="C635" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
     </row>
     <row r="636" spans="1:3">
@@ -12471,10 +12486,10 @@
         <v>9</v>
       </c>
       <c r="B636" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="C636" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="637" spans="1:3">
@@ -12482,10 +12497,10 @@
         <v>9</v>
       </c>
       <c r="B637" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="C637" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="638" spans="1:3">
@@ -12493,10 +12508,10 @@
         <v>9</v>
       </c>
       <c r="B638" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="C638" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
     </row>
     <row r="639" spans="1:3">
@@ -12504,10 +12519,10 @@
         <v>9</v>
       </c>
       <c r="B639" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="C639" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
     </row>
     <row r="640" spans="1:3">
@@ -12515,10 +12530,10 @@
         <v>9</v>
       </c>
       <c r="B640" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="C640" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
     </row>
     <row r="641" spans="1:3">
@@ -12526,10 +12541,10 @@
         <v>9</v>
       </c>
       <c r="B641" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="C641" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
     </row>
     <row r="642" spans="1:3">
@@ -12537,10 +12552,10 @@
         <v>9</v>
       </c>
       <c r="B642" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C642" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
     </row>
     <row r="643" spans="1:3">
@@ -12548,10 +12563,10 @@
         <v>9</v>
       </c>
       <c r="B643" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C643" t="s">
-        <v>19</v>
+        <v>226</v>
       </c>
     </row>
     <row r="644" spans="1:3">
@@ -12559,10 +12574,10 @@
         <v>9</v>
       </c>
       <c r="B644" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C644" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="645" spans="1:3">
@@ -12570,10 +12585,10 @@
         <v>9</v>
       </c>
       <c r="B645" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C645" t="s">
-        <v>235</v>
+        <v>19</v>
       </c>
     </row>
     <row r="646" spans="1:3">
@@ -12581,10 +12596,10 @@
         <v>9</v>
       </c>
       <c r="B646" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="C646" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="647" spans="1:3">
@@ -12592,10 +12607,10 @@
         <v>9</v>
       </c>
       <c r="B647" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="C647" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
     </row>
     <row r="648" spans="1:3">
@@ -12603,10 +12618,10 @@
         <v>9</v>
       </c>
       <c r="B648" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C648" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="649" spans="1:3">
@@ -12614,10 +12629,10 @@
         <v>9</v>
       </c>
       <c r="B649" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C649" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="650" spans="1:3">
@@ -12625,10 +12640,10 @@
         <v>9</v>
       </c>
       <c r="B650" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="C650" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
     </row>
     <row r="651" spans="1:3">
@@ -12636,10 +12651,10 @@
         <v>9</v>
       </c>
       <c r="B651" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="C651" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
     </row>
     <row r="652" spans="1:3">
@@ -12647,10 +12662,10 @@
         <v>9</v>
       </c>
       <c r="B652" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="C652" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
     </row>
     <row r="653" spans="1:3">
@@ -12658,10 +12673,10 @@
         <v>9</v>
       </c>
       <c r="B653" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="C653" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
     </row>
     <row r="654" spans="1:3">
@@ -12669,10 +12684,10 @@
         <v>9</v>
       </c>
       <c r="B654" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="C654" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
     </row>
     <row r="655" spans="1:3">
@@ -12680,10 +12695,10 @@
         <v>9</v>
       </c>
       <c r="B655" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C655" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="656" spans="1:3">
@@ -12691,10 +12706,10 @@
         <v>9</v>
       </c>
       <c r="B656" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C656" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="657" spans="1:3">
@@ -12702,10 +12717,10 @@
         <v>9</v>
       </c>
       <c r="B657" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C657" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="658" spans="1:3">
@@ -12713,10 +12728,10 @@
         <v>9</v>
       </c>
       <c r="B658" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C658" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="659" spans="1:3">
@@ -12724,10 +12739,10 @@
         <v>9</v>
       </c>
       <c r="B659" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="C659" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
     </row>
     <row r="660" spans="1:3">
@@ -12735,10 +12750,10 @@
         <v>9</v>
       </c>
       <c r="B660" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="C660" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
     </row>
     <row r="661" spans="1:3">
@@ -12746,10 +12761,10 @@
         <v>9</v>
       </c>
       <c r="B661" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C661" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="662" spans="1:3">
@@ -12757,10 +12772,10 @@
         <v>9</v>
       </c>
       <c r="B662" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C662" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="663" spans="1:3">
@@ -12768,10 +12783,10 @@
         <v>9</v>
       </c>
       <c r="B663" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C663" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="664" spans="1:3">
@@ -12779,10 +12794,10 @@
         <v>9</v>
       </c>
       <c r="B664" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="C664" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
     </row>
     <row r="665" spans="1:3">
@@ -12790,10 +12805,10 @@
         <v>9</v>
       </c>
       <c r="B665" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="C665" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
     </row>
     <row r="666" spans="1:3">
@@ -12801,10 +12816,10 @@
         <v>9</v>
       </c>
       <c r="B666" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="C666" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
     </row>
     <row r="667" spans="1:3">
@@ -12812,10 +12827,10 @@
         <v>9</v>
       </c>
       <c r="B667" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C667" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
     </row>
     <row r="668" spans="1:3">
@@ -12823,10 +12838,10 @@
         <v>9</v>
       </c>
       <c r="B668" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C668" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="669" spans="1:3">
@@ -12834,10 +12849,10 @@
         <v>9</v>
       </c>
       <c r="B669" t="s">
-        <v>36</v>
+        <v>310</v>
       </c>
       <c r="C669" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="670" spans="1:3">
@@ -12845,10 +12860,10 @@
         <v>9</v>
       </c>
       <c r="B670" t="s">
-        <v>325</v>
+        <v>312</v>
       </c>
       <c r="C670" t="s">
-        <v>326</v>
+        <v>313</v>
       </c>
     </row>
     <row r="671" spans="1:3">
@@ -12856,10 +12871,10 @@
         <v>9</v>
       </c>
       <c r="B671" t="s">
-        <v>327</v>
+        <v>36</v>
       </c>
       <c r="C671" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
     </row>
     <row r="672" spans="1:3">
@@ -12867,10 +12882,10 @@
         <v>9</v>
       </c>
       <c r="B672" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C672" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="673" spans="1:3">
@@ -12878,10 +12893,10 @@
         <v>9</v>
       </c>
       <c r="B673" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C673" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="674" spans="1:3">
@@ -12889,10 +12904,10 @@
         <v>9</v>
       </c>
       <c r="B674" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C674" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="675" spans="1:3">
@@ -12900,10 +12915,10 @@
         <v>9</v>
       </c>
       <c r="B675" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="C675" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
     </row>
     <row r="676" spans="1:3">
@@ -12911,10 +12926,10 @@
         <v>9</v>
       </c>
       <c r="B676" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="C676" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
     </row>
     <row r="677" spans="1:3">
@@ -12922,10 +12937,10 @@
         <v>9</v>
       </c>
       <c r="B677" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="C677" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
     </row>
     <row r="678" spans="1:3">
@@ -12933,10 +12948,10 @@
         <v>9</v>
       </c>
       <c r="B678" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="C678" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
     </row>
     <row r="679" spans="1:3">
@@ -12944,10 +12959,10 @@
         <v>9</v>
       </c>
       <c r="B679" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="C679" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
     </row>
     <row r="680" spans="1:3">
@@ -12955,10 +12970,10 @@
         <v>9</v>
       </c>
       <c r="B680" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C680" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="681" spans="1:3">
@@ -12966,10 +12981,10 @@
         <v>9</v>
       </c>
       <c r="B681" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="C681" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
     </row>
     <row r="682" spans="1:3">
@@ -12977,10 +12992,10 @@
         <v>9</v>
       </c>
       <c r="B682" t="s">
-        <v>366</v>
+        <v>352</v>
       </c>
       <c r="C682" t="s">
-        <v>368</v>
+        <v>353</v>
       </c>
     </row>
     <row r="683" spans="1:3">
@@ -12988,10 +13003,10 @@
         <v>9</v>
       </c>
       <c r="B683" t="s">
-        <v>377</v>
+        <v>362</v>
       </c>
       <c r="C683" t="s">
-        <v>378</v>
+        <v>363</v>
       </c>
     </row>
     <row r="684" spans="1:3">
@@ -12999,10 +13014,10 @@
         <v>9</v>
       </c>
       <c r="B684" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="C684" t="s">
-        <v>379</v>
+        <v>368</v>
       </c>
     </row>
     <row r="685" spans="1:3">
@@ -13010,10 +13025,10 @@
         <v>9</v>
       </c>
       <c r="B685" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C685" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="686" spans="1:3">
@@ -13021,10 +13036,10 @@
         <v>9</v>
       </c>
       <c r="B686" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="C686" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
     </row>
     <row r="687" spans="1:3">
@@ -13032,10 +13047,10 @@
         <v>9</v>
       </c>
       <c r="B687" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C687" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
     </row>
     <row r="688" spans="1:3">
@@ -13043,10 +13058,10 @@
         <v>9</v>
       </c>
       <c r="B688" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C688" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
     </row>
     <row r="689" spans="1:3">
@@ -13054,10 +13069,10 @@
         <v>9</v>
       </c>
       <c r="B689" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="C689" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
     </row>
     <row r="690" spans="1:3">
@@ -13065,10 +13080,10 @@
         <v>9</v>
       </c>
       <c r="B690" t="s">
-        <v>407</v>
+        <v>392</v>
       </c>
       <c r="C690" t="s">
-        <v>409</v>
+        <v>393</v>
       </c>
     </row>
     <row r="691" spans="1:3">
@@ -13076,10 +13091,10 @@
         <v>9</v>
       </c>
       <c r="B691" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="C691" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
     </row>
     <row r="692" spans="1:3">
@@ -13087,10 +13102,10 @@
         <v>9</v>
       </c>
       <c r="B692" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="C692" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
     </row>
     <row r="693" spans="1:3">
@@ -13098,10 +13113,10 @@
         <v>9</v>
       </c>
       <c r="B693" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C693" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
     </row>
     <row r="694" spans="1:3">
@@ -13109,10 +13124,10 @@
         <v>9</v>
       </c>
       <c r="B694" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="C694" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="695" spans="1:3">
@@ -13120,10 +13135,10 @@
         <v>9</v>
       </c>
       <c r="B695" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="C695" t="s">
-        <v>429</v>
+        <v>415</v>
       </c>
     </row>
     <row r="696" spans="1:3">
@@ -13131,10 +13146,10 @@
         <v>9</v>
       </c>
       <c r="B696" t="s">
-        <v>433</v>
+        <v>416</v>
       </c>
       <c r="C696" t="s">
-        <v>435</v>
+        <v>417</v>
       </c>
     </row>
     <row r="697" spans="1:3">
@@ -13142,10 +13157,10 @@
         <v>9</v>
       </c>
       <c r="B697" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="C697" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
     </row>
     <row r="698" spans="1:3">
@@ -13153,10 +13168,10 @@
         <v>9</v>
       </c>
       <c r="B698" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="C698" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="699" spans="1:3">
@@ -13164,10 +13179,10 @@
         <v>9</v>
       </c>
       <c r="B699" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="C699" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
     </row>
     <row r="700" spans="1:3">
@@ -13175,10 +13190,10 @@
         <v>9</v>
       </c>
       <c r="B700" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="C700" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
     </row>
     <row r="701" spans="1:3">
@@ -13186,10 +13201,10 @@
         <v>9</v>
       </c>
       <c r="B701" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C701" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
     </row>
     <row r="702" spans="1:3">
@@ -13197,10 +13212,10 @@
         <v>9</v>
       </c>
       <c r="B702" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="C702" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
     </row>
     <row r="703" spans="1:3">
@@ -13208,10 +13223,10 @@
         <v>9</v>
       </c>
       <c r="B703" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="C703" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
     </row>
     <row r="704" spans="1:3">
@@ -13219,10 +13234,10 @@
         <v>9</v>
       </c>
       <c r="B704" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="C704" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="705" spans="1:3">
@@ -13230,10 +13245,10 @@
         <v>9</v>
       </c>
       <c r="B705" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="C705" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
     </row>
     <row r="706" spans="1:3">
@@ -13241,10 +13256,10 @@
         <v>9</v>
       </c>
       <c r="B706" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="C706" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
     </row>
     <row r="707" spans="1:3">
@@ -13252,10 +13267,10 @@
         <v>9</v>
       </c>
       <c r="B707" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="C707" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
     </row>
     <row r="708" spans="1:3">
@@ -13263,10 +13278,10 @@
         <v>9</v>
       </c>
       <c r="B708" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="C708" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
     </row>
     <row r="709" spans="1:3">
@@ -13274,10 +13289,10 @@
         <v>9</v>
       </c>
       <c r="B709" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="C709" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
     </row>
     <row r="710" spans="1:3">
@@ -13285,10 +13300,10 @@
         <v>9</v>
       </c>
       <c r="B710" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="C710" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
     </row>
     <row r="711" spans="1:3">
@@ -13296,10 +13311,10 @@
         <v>9</v>
       </c>
       <c r="B711" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="C711" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
     </row>
     <row r="712" spans="1:3">
@@ -13307,10 +13322,10 @@
         <v>9</v>
       </c>
       <c r="B712" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="C712" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
     </row>
     <row r="713" spans="1:3">
@@ -13318,10 +13333,10 @@
         <v>9</v>
       </c>
       <c r="B713" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="C713" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
     </row>
     <row r="714" spans="1:3">
@@ -13329,10 +13344,10 @@
         <v>9</v>
       </c>
       <c r="B714" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="C714" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
     </row>
     <row r="715" spans="1:3">
@@ -13340,10 +13355,10 @@
         <v>9</v>
       </c>
       <c r="B715" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="C715" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
     </row>
     <row r="716" spans="1:3">
@@ -13351,10 +13366,10 @@
         <v>9</v>
       </c>
       <c r="B716" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="C716" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
     </row>
     <row r="717" spans="1:3">
@@ -13362,10 +13377,10 @@
         <v>9</v>
       </c>
       <c r="B717" t="s">
-        <v>507</v>
+        <v>496</v>
       </c>
       <c r="C717" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="718" spans="1:3">
@@ -13373,10 +13388,10 @@
         <v>9</v>
       </c>
       <c r="B718" t="s">
-        <v>515</v>
+        <v>498</v>
       </c>
       <c r="C718" t="s">
-        <v>516</v>
+        <v>499</v>
       </c>
     </row>
     <row r="719" spans="1:3">
@@ -13384,10 +13399,10 @@
         <v>9</v>
       </c>
       <c r="B719" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="C719" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
     </row>
     <row r="720" spans="1:3">
@@ -13395,10 +13410,10 @@
         <v>9</v>
       </c>
       <c r="B720" t="s">
-        <v>8</v>
+        <v>515</v>
       </c>
       <c r="C720" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
     </row>
     <row r="721" spans="1:3">
@@ -13406,10 +13421,10 @@
         <v>9</v>
       </c>
       <c r="B721" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="C721" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
     </row>
     <row r="722" spans="1:3">
@@ -13417,10 +13432,10 @@
         <v>9</v>
       </c>
       <c r="B722" t="s">
-        <v>525</v>
+        <v>8</v>
       </c>
       <c r="C722" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
     </row>
     <row r="723" spans="1:3">
@@ -13428,10 +13443,10 @@
         <v>9</v>
       </c>
       <c r="B723" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="C723" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
     </row>
     <row r="724" spans="1:3">
@@ -13439,10 +13454,10 @@
         <v>9</v>
       </c>
       <c r="B724" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="C724" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
     </row>
     <row r="725" spans="1:3">
@@ -13450,10 +13465,10 @@
         <v>9</v>
       </c>
       <c r="B725" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="C725" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
     </row>
     <row r="726" spans="1:3">
@@ -13461,10 +13476,10 @@
         <v>9</v>
       </c>
       <c r="B726" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="C726" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
     </row>
     <row r="727" spans="1:3">
@@ -13472,10 +13487,10 @@
         <v>9</v>
       </c>
       <c r="B727" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="C727" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
     </row>
     <row r="728" spans="1:3">
@@ -13483,10 +13498,10 @@
         <v>9</v>
       </c>
       <c r="B728" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="C728" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
     </row>
     <row r="729" spans="1:3">
@@ -13494,10 +13509,10 @@
         <v>9</v>
       </c>
       <c r="B729" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="C729" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
     </row>
     <row r="730" spans="1:3">
@@ -13505,10 +13520,10 @@
         <v>9</v>
       </c>
       <c r="B730" t="s">
-        <v>557</v>
+        <v>543</v>
       </c>
       <c r="C730" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
     </row>
     <row r="731" spans="1:3">
@@ -13516,10 +13531,10 @@
         <v>9</v>
       </c>
       <c r="B731" t="s">
-        <v>561</v>
+        <v>547</v>
       </c>
       <c r="C731" t="s">
-        <v>563</v>
+        <v>549</v>
       </c>
     </row>
     <row r="732" spans="1:3">
@@ -13527,10 +13542,10 @@
         <v>9</v>
       </c>
       <c r="B732" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="C732" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
     </row>
     <row r="733" spans="1:3">
@@ -13538,10 +13553,10 @@
         <v>9</v>
       </c>
       <c r="B733" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="C733" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
     </row>
     <row r="734" spans="1:3">
@@ -13549,10 +13564,10 @@
         <v>9</v>
       </c>
       <c r="B734" t="s">
-        <v>588</v>
+        <v>564</v>
       </c>
       <c r="C734" t="s">
-        <v>589</v>
+        <v>565</v>
       </c>
     </row>
     <row r="735" spans="1:3">
@@ -13560,10 +13575,10 @@
         <v>9</v>
       </c>
       <c r="B735" t="s">
-        <v>600</v>
+        <v>568</v>
       </c>
       <c r="C735" t="s">
-        <v>602</v>
+        <v>569</v>
       </c>
     </row>
     <row r="736" spans="1:3">
@@ -13571,10 +13586,10 @@
         <v>9</v>
       </c>
       <c r="B736" t="s">
-        <v>603</v>
+        <v>588</v>
       </c>
       <c r="C736" t="s">
-        <v>604</v>
+        <v>589</v>
       </c>
     </row>
     <row r="737" spans="1:3">
@@ -13582,10 +13597,10 @@
         <v>9</v>
       </c>
       <c r="B737" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="C737" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
     </row>
     <row r="738" spans="1:3">
@@ -13593,10 +13608,10 @@
         <v>9</v>
       </c>
       <c r="B738" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="C738" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
     </row>
     <row r="739" spans="1:3">
@@ -13604,10 +13619,10 @@
         <v>9</v>
       </c>
       <c r="B739" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="C739" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
     </row>
     <row r="740" spans="1:3">
@@ -13615,10 +13630,10 @@
         <v>9</v>
       </c>
       <c r="B740" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="C740" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
     </row>
     <row r="741" spans="1:3">
@@ -13626,10 +13641,10 @@
         <v>9</v>
       </c>
       <c r="B741" t="s">
-        <v>628</v>
+        <v>612</v>
       </c>
       <c r="C741" t="s">
-        <v>629</v>
+        <v>613</v>
       </c>
     </row>
     <row r="742" spans="1:3">
@@ -13637,10 +13652,10 @@
         <v>9</v>
       </c>
       <c r="B742" t="s">
-        <v>632</v>
+        <v>616</v>
       </c>
       <c r="C742" t="s">
-        <v>633</v>
+        <v>617</v>
       </c>
     </row>
     <row r="743" spans="1:3">
@@ -13648,10 +13663,10 @@
         <v>9</v>
       </c>
       <c r="B743" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="C743" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
     </row>
     <row r="744" spans="1:3">
@@ -13659,10 +13674,10 @@
         <v>9</v>
       </c>
       <c r="B744" t="s">
-        <v>642</v>
+        <v>632</v>
       </c>
       <c r="C744" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
     </row>
     <row r="745" spans="1:3">
@@ -13670,10 +13685,10 @@
         <v>9</v>
       </c>
       <c r="B745" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="C745" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
     </row>
     <row r="746" spans="1:3">
@@ -13681,10 +13696,10 @@
         <v>9</v>
       </c>
       <c r="B746" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="C746" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
     </row>
     <row r="747" spans="1:3">
@@ -13692,10 +13707,10 @@
         <v>9</v>
       </c>
       <c r="B747" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="C747" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
     </row>
     <row r="748" spans="1:3">
@@ -13703,10 +13718,10 @@
         <v>9</v>
       </c>
       <c r="B748" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="C748" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
     </row>
     <row r="749" spans="1:3">
@@ -13714,10 +13729,10 @@
         <v>9</v>
       </c>
       <c r="B749" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="C749" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
     </row>
     <row r="750" spans="1:3">
@@ -13725,10 +13740,10 @@
         <v>9</v>
       </c>
       <c r="B750" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="C750" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
     </row>
     <row r="751" spans="1:3">
@@ -13736,10 +13751,10 @@
         <v>9</v>
       </c>
       <c r="B751" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="C751" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
     </row>
     <row r="752" spans="1:3">
@@ -13747,10 +13762,10 @@
         <v>9</v>
       </c>
       <c r="B752" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="C752" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
     </row>
     <row r="753" spans="1:3">
@@ -13758,10 +13773,10 @@
         <v>9</v>
       </c>
       <c r="B753" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="C753" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
     </row>
     <row r="754" spans="1:3">
@@ -13769,10 +13784,10 @@
         <v>9</v>
       </c>
       <c r="B754" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="C754" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
     </row>
     <row r="755" spans="1:3">
@@ -13780,10 +13795,10 @@
         <v>9</v>
       </c>
       <c r="B755" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="C755" t="s">
-        <v>675</v>
+        <v>667</v>
       </c>
     </row>
     <row r="756" spans="1:3">
@@ -13791,10 +13806,10 @@
         <v>9</v>
       </c>
       <c r="B756" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="C756" t="s">
-        <v>678</v>
+        <v>669</v>
       </c>
     </row>
     <row r="757" spans="1:3">
@@ -13802,10 +13817,10 @@
         <v>9</v>
       </c>
       <c r="B757" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="C757" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
     </row>
     <row r="758" spans="1:3">
@@ -13813,10 +13828,10 @@
         <v>9</v>
       </c>
       <c r="B758" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="C758" t="s">
-        <v>691</v>
+        <v>678</v>
       </c>
     </row>
     <row r="759" spans="1:3">
@@ -13824,10 +13839,10 @@
         <v>9</v>
       </c>
       <c r="B759" t="s">
-        <v>698</v>
+        <v>679</v>
       </c>
       <c r="C759" t="s">
-        <v>699</v>
+        <v>681</v>
       </c>
     </row>
     <row r="760" spans="1:3">
@@ -13835,10 +13850,10 @@
         <v>9</v>
       </c>
       <c r="B760" t="s">
-        <v>700</v>
+        <v>690</v>
       </c>
       <c r="C760" t="s">
-        <v>701</v>
+        <v>691</v>
       </c>
     </row>
     <row r="761" spans="1:3">
@@ -13846,10 +13861,10 @@
         <v>9</v>
       </c>
       <c r="B761" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="C761" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
     </row>
     <row r="762" spans="1:3">
@@ -13857,10 +13872,10 @@
         <v>9</v>
       </c>
       <c r="B762" t="s">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="C762" t="s">
-        <v>708</v>
+        <v>701</v>
       </c>
     </row>
     <row r="763" spans="1:3">
@@ -13868,10 +13883,10 @@
         <v>9</v>
       </c>
       <c r="B763" t="s">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="C763" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
     </row>
     <row r="764" spans="1:3">
@@ -13879,10 +13894,10 @@
         <v>9</v>
       </c>
       <c r="B764" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="C764" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
     </row>
     <row r="765" spans="1:3">
@@ -13890,10 +13905,10 @@
         <v>9</v>
       </c>
       <c r="B765" t="s">
-        <v>723</v>
+        <v>709</v>
       </c>
       <c r="C765" t="s">
-        <v>724</v>
+        <v>710</v>
       </c>
     </row>
     <row r="766" spans="1:3">
@@ -13901,10 +13916,10 @@
         <v>9</v>
       </c>
       <c r="B766" t="s">
-        <v>725</v>
+        <v>711</v>
       </c>
       <c r="C766" t="s">
-        <v>726</v>
+        <v>712</v>
       </c>
     </row>
     <row r="767" spans="1:3">
@@ -13912,10 +13927,10 @@
         <v>9</v>
       </c>
       <c r="B767" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="C767" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
     </row>
     <row r="768" spans="1:3">
@@ -13923,10 +13938,10 @@
         <v>9</v>
       </c>
       <c r="B768" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="C768" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
     </row>
     <row r="769" spans="1:3">
@@ -13934,10 +13949,10 @@
         <v>9</v>
       </c>
       <c r="B769" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="C769" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
     </row>
     <row r="770" spans="1:3">
@@ -13945,10 +13960,10 @@
         <v>9</v>
       </c>
       <c r="B770" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="C770" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
     </row>
     <row r="771" spans="1:3">
@@ -13956,10 +13971,10 @@
         <v>9</v>
       </c>
       <c r="B771" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="C771" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
     </row>
     <row r="772" spans="1:3">
@@ -13967,10 +13982,10 @@
         <v>9</v>
       </c>
       <c r="B772" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="C772" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
     </row>
     <row r="773" spans="1:3">
@@ -13978,10 +13993,10 @@
         <v>9</v>
       </c>
       <c r="B773" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="C773" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
     </row>
     <row r="774" spans="1:3">
@@ -13989,10 +14004,10 @@
         <v>9</v>
       </c>
       <c r="B774" t="s">
-        <v>747</v>
+        <v>737</v>
       </c>
       <c r="C774" t="s">
-        <v>749</v>
+        <v>738</v>
       </c>
     </row>
     <row r="775" spans="1:3">
@@ -14000,10 +14015,10 @@
         <v>9</v>
       </c>
       <c r="B775" t="s">
-        <v>750</v>
+        <v>739</v>
       </c>
       <c r="C775" t="s">
-        <v>751</v>
+        <v>740</v>
       </c>
     </row>
     <row r="776" spans="1:3">
@@ -14011,10 +14026,10 @@
         <v>9</v>
       </c>
       <c r="B776" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="C776" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
     </row>
     <row r="777" spans="1:3">
@@ -14022,10 +14037,10 @@
         <v>9</v>
       </c>
       <c r="B777" t="s">
-        <v>761</v>
+        <v>750</v>
       </c>
       <c r="C777" t="s">
-        <v>762</v>
+        <v>751</v>
       </c>
     </row>
     <row r="778" spans="1:3">
@@ -14033,10 +14048,10 @@
         <v>9</v>
       </c>
       <c r="B778" t="s">
-        <v>765</v>
+        <v>752</v>
       </c>
       <c r="C778" t="s">
-        <v>767</v>
+        <v>753</v>
       </c>
     </row>
     <row r="779" spans="1:3">
@@ -14044,10 +14059,10 @@
         <v>9</v>
       </c>
       <c r="B779" t="s">
-        <v>770</v>
+        <v>761</v>
       </c>
       <c r="C779" t="s">
-        <v>771</v>
+        <v>762</v>
       </c>
     </row>
     <row r="780" spans="1:3">
@@ -14055,10 +14070,10 @@
         <v>9</v>
       </c>
       <c r="B780" t="s">
-        <v>774</v>
+        <v>765</v>
       </c>
       <c r="C780" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
     </row>
     <row r="781" spans="1:3">
@@ -14066,10 +14081,10 @@
         <v>9</v>
       </c>
       <c r="B781" t="s">
-        <v>776</v>
+        <v>770</v>
       </c>
       <c r="C781" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
     </row>
     <row r="782" spans="1:3">
@@ -14077,10 +14092,10 @@
         <v>9</v>
       </c>
       <c r="B782" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="C782" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
     </row>
     <row r="783" spans="1:3">
@@ -14088,10 +14103,10 @@
         <v>9</v>
       </c>
       <c r="B783" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="C783" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
     </row>
     <row r="784" spans="1:3">
@@ -14099,10 +14114,10 @@
         <v>9</v>
       </c>
       <c r="B784" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="C784" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
     </row>
     <row r="785" spans="1:3">
@@ -14110,10 +14125,10 @@
         <v>9</v>
       </c>
       <c r="B785" t="s">
-        <v>794</v>
+        <v>783</v>
       </c>
       <c r="C785" t="s">
-        <v>795</v>
+        <v>784</v>
       </c>
     </row>
     <row r="786" spans="1:3">
@@ -14121,10 +14136,10 @@
         <v>9</v>
       </c>
       <c r="B786" t="s">
-        <v>796</v>
+        <v>785</v>
       </c>
       <c r="C786" t="s">
-        <v>797</v>
+        <v>787</v>
       </c>
     </row>
     <row r="787" spans="1:3">
@@ -14132,10 +14147,10 @@
         <v>9</v>
       </c>
       <c r="B787" t="s">
-        <v>800</v>
+        <v>794</v>
       </c>
       <c r="C787" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
     </row>
     <row r="788" spans="1:3">
@@ -14143,10 +14158,10 @@
         <v>9</v>
       </c>
       <c r="B788" t="s">
-        <v>804</v>
+        <v>796</v>
       </c>
       <c r="C788" t="s">
-        <v>806</v>
+        <v>797</v>
       </c>
     </row>
     <row r="789" spans="1:3">
@@ -14154,10 +14169,10 @@
         <v>9</v>
       </c>
       <c r="B789" t="s">
-        <v>807</v>
+        <v>800</v>
       </c>
       <c r="C789" t="s">
-        <v>808</v>
+        <v>801</v>
       </c>
     </row>
     <row r="790" spans="1:3">
@@ -14165,10 +14180,10 @@
         <v>9</v>
       </c>
       <c r="B790" t="s">
-        <v>818</v>
+        <v>804</v>
       </c>
       <c r="C790" t="s">
-        <v>819</v>
+        <v>806</v>
       </c>
     </row>
     <row r="791" spans="1:3">
@@ -14176,10 +14191,10 @@
         <v>9</v>
       </c>
       <c r="B791" t="s">
-        <v>822</v>
+        <v>807</v>
       </c>
       <c r="C791" t="s">
-        <v>824</v>
+        <v>808</v>
       </c>
     </row>
     <row r="792" spans="1:3">
@@ -14187,10 +14202,10 @@
         <v>9</v>
       </c>
       <c r="B792" t="s">
-        <v>829</v>
+        <v>818</v>
       </c>
       <c r="C792" t="s">
-        <v>830</v>
+        <v>819</v>
       </c>
     </row>
     <row r="793" spans="1:3">
@@ -14198,10 +14213,10 @@
         <v>9</v>
       </c>
       <c r="B793" t="s">
-        <v>833</v>
+        <v>822</v>
       </c>
       <c r="C793" t="s">
-        <v>834</v>
+        <v>824</v>
       </c>
     </row>
     <row r="794" spans="1:3">
@@ -14209,10 +14224,10 @@
         <v>9</v>
       </c>
       <c r="B794" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="C794" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
     </row>
     <row r="795" spans="1:3">
@@ -14220,10 +14235,10 @@
         <v>9</v>
       </c>
       <c r="B795" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="C795" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
     </row>
     <row r="796" spans="1:3">
@@ -14231,10 +14246,10 @@
         <v>9</v>
       </c>
       <c r="B796" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C796" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
     </row>
     <row r="797" spans="1:3">
@@ -14242,10 +14257,10 @@
         <v>9</v>
       </c>
       <c r="B797" t="s">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="C797" t="s">
-        <v>844</v>
+        <v>838</v>
       </c>
     </row>
     <row r="798" spans="1:3">
@@ -14253,10 +14268,10 @@
         <v>9</v>
       </c>
       <c r="B798" t="s">
-        <v>861</v>
+        <v>839</v>
       </c>
       <c r="C798" t="s">
-        <v>862</v>
+        <v>840</v>
       </c>
     </row>
     <row r="799" spans="1:3">
@@ -14264,10 +14279,10 @@
         <v>9</v>
       </c>
       <c r="B799" t="s">
-        <v>865</v>
+        <v>843</v>
       </c>
       <c r="C799" t="s">
-        <v>866</v>
+        <v>844</v>
       </c>
     </row>
     <row r="800" spans="1:3">
@@ -14275,10 +14290,10 @@
         <v>9</v>
       </c>
       <c r="B800" t="s">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="C800" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
     </row>
     <row r="801" spans="1:3">
@@ -14286,10 +14301,10 @@
         <v>9</v>
       </c>
       <c r="B801" t="s">
-        <v>871</v>
+        <v>865</v>
       </c>
       <c r="C801" t="s">
-        <v>872</v>
+        <v>866</v>
       </c>
     </row>
     <row r="802" spans="1:3">
@@ -14297,10 +14312,10 @@
         <v>9</v>
       </c>
       <c r="B802" t="s">
-        <v>879</v>
+        <v>867</v>
       </c>
       <c r="C802" t="s">
-        <v>880</v>
+        <v>868</v>
       </c>
     </row>
     <row r="803" spans="1:3">
@@ -14308,10 +14323,10 @@
         <v>9</v>
       </c>
       <c r="B803" t="s">
-        <v>881</v>
+        <v>871</v>
       </c>
       <c r="C803" t="s">
-        <v>883</v>
+        <v>872</v>
       </c>
     </row>
     <row r="804" spans="1:3">
@@ -14319,10 +14334,10 @@
         <v>9</v>
       </c>
       <c r="B804" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="C804" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
     </row>
     <row r="805" spans="1:3">
@@ -14330,10 +14345,10 @@
         <v>9</v>
       </c>
       <c r="B805" t="s">
-        <v>888</v>
+        <v>881</v>
       </c>
       <c r="C805" t="s">
-        <v>890</v>
+        <v>883</v>
       </c>
     </row>
     <row r="806" spans="1:3">
@@ -14341,10 +14356,10 @@
         <v>9</v>
       </c>
       <c r="B806" t="s">
-        <v>895</v>
+        <v>884</v>
       </c>
       <c r="C806" t="s">
-        <v>896</v>
+        <v>885</v>
       </c>
     </row>
     <row r="807" spans="1:3">
@@ -14352,10 +14367,10 @@
         <v>9</v>
       </c>
       <c r="B807" t="s">
-        <v>897</v>
+        <v>888</v>
       </c>
       <c r="C807" t="s">
-        <v>898</v>
+        <v>890</v>
       </c>
     </row>
     <row r="808" spans="1:3">
@@ -14363,10 +14378,10 @@
         <v>9</v>
       </c>
       <c r="B808" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="C808" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
     </row>
     <row r="809" spans="1:3">
@@ -14374,10 +14389,10 @@
         <v>9</v>
       </c>
       <c r="B809" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="C809" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
     </row>
     <row r="810" spans="1:3">
@@ -14385,10 +14400,10 @@
         <v>9</v>
       </c>
       <c r="B810" t="s">
-        <v>905</v>
+        <v>899</v>
       </c>
       <c r="C810" t="s">
-        <v>906</v>
+        <v>900</v>
       </c>
     </row>
     <row r="811" spans="1:3">
@@ -14396,10 +14411,10 @@
         <v>9</v>
       </c>
       <c r="B811" t="s">
-        <v>907</v>
+        <v>901</v>
       </c>
       <c r="C811" t="s">
-        <v>908</v>
+        <v>902</v>
       </c>
     </row>
     <row r="812" spans="1:3">
@@ -14407,10 +14422,10 @@
         <v>9</v>
       </c>
       <c r="B812" t="s">
-        <v>915</v>
+        <v>905</v>
       </c>
       <c r="C812" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
     </row>
     <row r="813" spans="1:3">
@@ -14418,10 +14433,10 @@
         <v>9</v>
       </c>
       <c r="B813" t="s">
-        <v>928</v>
+        <v>907</v>
       </c>
       <c r="C813" t="s">
-        <v>929</v>
+        <v>908</v>
       </c>
     </row>
     <row r="814" spans="1:3">
@@ -14429,10 +14444,10 @@
         <v>9</v>
       </c>
       <c r="B814" t="s">
-        <v>930</v>
+        <v>915</v>
       </c>
       <c r="C814" t="s">
-        <v>931</v>
+        <v>916</v>
       </c>
     </row>
     <row r="815" spans="1:3">
@@ -14440,10 +14455,10 @@
         <v>9</v>
       </c>
       <c r="B815" t="s">
-        <v>936</v>
+        <v>928</v>
       </c>
       <c r="C815" t="s">
-        <v>937</v>
+        <v>929</v>
       </c>
     </row>
     <row r="816" spans="1:3">
@@ -14451,10 +14466,10 @@
         <v>9</v>
       </c>
       <c r="B816" t="s">
-        <v>946</v>
+        <v>930</v>
       </c>
       <c r="C816" t="s">
-        <v>947</v>
+        <v>931</v>
       </c>
     </row>
     <row r="817" spans="1:3">
@@ -14462,10 +14477,10 @@
         <v>9</v>
       </c>
       <c r="B817" t="s">
-        <v>950</v>
+        <v>936</v>
       </c>
       <c r="C817" t="s">
-        <v>951</v>
+        <v>937</v>
       </c>
     </row>
     <row r="818" spans="1:3">
@@ -14473,10 +14488,10 @@
         <v>9</v>
       </c>
       <c r="B818" t="s">
-        <v>954</v>
+        <v>946</v>
       </c>
       <c r="C818" t="s">
-        <v>956</v>
+        <v>947</v>
       </c>
     </row>
     <row r="819" spans="1:3">
@@ -14484,10 +14499,10 @@
         <v>9</v>
       </c>
       <c r="B819" t="s">
-        <v>957</v>
+        <v>950</v>
       </c>
       <c r="C819" t="s">
-        <v>958</v>
+        <v>951</v>
       </c>
     </row>
     <row r="820" spans="1:3">
@@ -14495,10 +14510,10 @@
         <v>9</v>
       </c>
       <c r="B820" t="s">
-        <v>963</v>
+        <v>954</v>
       </c>
       <c r="C820" t="s">
-        <v>964</v>
+        <v>956</v>
       </c>
     </row>
     <row r="821" spans="1:3">
@@ -14506,10 +14521,10 @@
         <v>9</v>
       </c>
       <c r="B821" t="s">
-        <v>965</v>
+        <v>957</v>
       </c>
       <c r="C821" t="s">
-        <v>966</v>
+        <v>958</v>
       </c>
     </row>
     <row r="822" spans="1:3">
@@ -14517,10 +14532,10 @@
         <v>9</v>
       </c>
       <c r="B822" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="C822" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
     </row>
     <row r="823" spans="1:3">
@@ -14528,10 +14543,10 @@
         <v>9</v>
       </c>
       <c r="B823" t="s">
-        <v>975</v>
+        <v>965</v>
       </c>
       <c r="C823" t="s">
-        <v>976</v>
+        <v>966</v>
       </c>
     </row>
     <row r="824" spans="1:3">
@@ -14539,10 +14554,10 @@
         <v>9</v>
       </c>
       <c r="B824" t="s">
-        <v>982</v>
+        <v>967</v>
       </c>
       <c r="C824" t="s">
-        <v>983</v>
+        <v>968</v>
       </c>
     </row>
     <row r="825" spans="1:3">
@@ -14550,10 +14565,10 @@
         <v>9</v>
       </c>
       <c r="B825" t="s">
-        <v>984</v>
+        <v>975</v>
       </c>
       <c r="C825" t="s">
-        <v>985</v>
+        <v>976</v>
       </c>
     </row>
     <row r="826" spans="1:3">
@@ -14561,10 +14576,10 @@
         <v>9</v>
       </c>
       <c r="B826" t="s">
-        <v>998</v>
+        <v>982</v>
       </c>
       <c r="C826" t="s">
-        <v>999</v>
+        <v>983</v>
       </c>
     </row>
     <row r="827" spans="1:3">
@@ -14572,10 +14587,10 @@
         <v>9</v>
       </c>
       <c r="B827" t="s">
-        <v>1000</v>
+        <v>984</v>
       </c>
       <c r="C827" t="s">
-        <v>1001</v>
+        <v>985</v>
       </c>
     </row>
     <row r="828" spans="1:3">
@@ -14583,10 +14598,10 @@
         <v>9</v>
       </c>
       <c r="B828" t="s">
-        <v>1002</v>
+        <v>998</v>
       </c>
       <c r="C828" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
     </row>
     <row r="829" spans="1:3">
@@ -14594,10 +14609,10 @@
         <v>9</v>
       </c>
       <c r="B829" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="C829" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="830" spans="1:3">
@@ -14605,10 +14620,10 @@
         <v>9</v>
       </c>
       <c r="B830" t="s">
-        <v>1010</v>
+        <v>1002</v>
       </c>
       <c r="C830" t="s">
-        <v>1011</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="831" spans="1:3">
@@ -14616,10 +14631,10 @@
         <v>9</v>
       </c>
       <c r="B831" t="s">
-        <v>1012</v>
+        <v>1004</v>
       </c>
       <c r="C831" t="s">
-        <v>1013</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="832" spans="1:3">
@@ -14627,10 +14642,10 @@
         <v>9</v>
       </c>
       <c r="B832" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="C832" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="833" spans="1:3">
@@ -14638,10 +14653,10 @@
         <v>9</v>
       </c>
       <c r="B833" t="s">
-        <v>1018</v>
+        <v>1012</v>
       </c>
       <c r="C833" t="s">
-        <v>1021</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="834" spans="1:3">
@@ -14649,10 +14664,10 @@
         <v>9</v>
       </c>
       <c r="B834" t="s">
-        <v>1026</v>
+        <v>1014</v>
       </c>
       <c r="C834" t="s">
-        <v>1027</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="835" spans="1:3">
@@ -14660,10 +14675,10 @@
         <v>9</v>
       </c>
       <c r="B835" t="s">
-        <v>1028</v>
+        <v>1018</v>
       </c>
       <c r="C835" t="s">
-        <v>1029</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="836" spans="1:3">
@@ -14671,10 +14686,10 @@
         <v>9</v>
       </c>
       <c r="B836" t="s">
-        <v>1036</v>
+        <v>1026</v>
       </c>
       <c r="C836" t="s">
-        <v>1037</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="837" spans="1:3">
@@ -14682,10 +14697,10 @@
         <v>9</v>
       </c>
       <c r="B837" t="s">
-        <v>1038</v>
+        <v>1028</v>
       </c>
       <c r="C837" t="s">
-        <v>467</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="838" spans="1:3">
@@ -14693,10 +14708,10 @@
         <v>9</v>
       </c>
       <c r="B838" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="C838" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="839" spans="1:3">
@@ -14704,10 +14719,10 @@
         <v>9</v>
       </c>
       <c r="B839" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="C839" t="s">
-        <v>1042</v>
+        <v>467</v>
       </c>
     </row>
     <row r="840" spans="1:3">
@@ -14715,10 +14730,10 @@
         <v>9</v>
       </c>
       <c r="B840" t="s">
-        <v>1043</v>
+        <v>1039</v>
       </c>
       <c r="C840" t="s">
-        <v>1044</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="841" spans="1:3">
@@ -14726,10 +14741,10 @@
         <v>9</v>
       </c>
       <c r="B841" t="s">
-        <v>1051</v>
+        <v>1041</v>
       </c>
       <c r="C841" t="s">
-        <v>1052</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="842" spans="1:3">
@@ -14737,10 +14752,10 @@
         <v>9</v>
       </c>
       <c r="B842" t="s">
-        <v>1057</v>
+        <v>1043</v>
       </c>
       <c r="C842" t="s">
-        <v>1060</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="843" spans="1:3">
@@ -14748,10 +14763,10 @@
         <v>9</v>
       </c>
       <c r="B843" t="s">
-        <v>1061</v>
+        <v>1051</v>
       </c>
       <c r="C843" t="s">
-        <v>1062</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="844" spans="1:3">
@@ -14759,10 +14774,10 @@
         <v>9</v>
       </c>
       <c r="B844" t="s">
-        <v>1063</v>
+        <v>1057</v>
       </c>
       <c r="C844" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="845" spans="1:3">
@@ -14770,10 +14785,10 @@
         <v>9</v>
       </c>
       <c r="B845" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
       <c r="C845" t="s">
-        <v>1066</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="846" spans="1:3">
@@ -14781,10 +14796,10 @@
         <v>9</v>
       </c>
       <c r="B846" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="C846" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="847" spans="1:3">
@@ -14792,10 +14807,10 @@
         <v>9</v>
       </c>
       <c r="B847" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="C847" t="s">
-        <v>1071</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="848" spans="1:3">
@@ -14803,10 +14818,10 @@
         <v>9</v>
       </c>
       <c r="B848" t="s">
-        <v>1082</v>
+        <v>1067</v>
       </c>
       <c r="C848" t="s">
-        <v>1003</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="849" spans="1:3">
@@ -14814,10 +14829,10 @@
         <v>9</v>
       </c>
       <c r="B849" t="s">
-        <v>1083</v>
+        <v>1069</v>
       </c>
       <c r="C849" t="s">
-        <v>1084</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="850" spans="1:3">
@@ -14825,10 +14840,10 @@
         <v>9</v>
       </c>
       <c r="B850" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="C850" t="s">
-        <v>1086</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="851" spans="1:3">
@@ -14836,10 +14851,10 @@
         <v>9</v>
       </c>
       <c r="B851" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="C851" t="s">
-        <v>1090</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="852" spans="1:3">
@@ -14847,10 +14862,10 @@
         <v>9</v>
       </c>
       <c r="B852" t="s">
-        <v>1091</v>
+        <v>1085</v>
       </c>
       <c r="C852" t="s">
-        <v>1092</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="853" spans="1:3">
@@ -14858,10 +14873,10 @@
         <v>9</v>
       </c>
       <c r="B853" t="s">
-        <v>1095</v>
+        <v>1089</v>
       </c>
       <c r="C853" t="s">
-        <v>1096</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="854" spans="1:3">
@@ -14869,10 +14884,10 @@
         <v>9</v>
       </c>
       <c r="B854" t="s">
-        <v>1097</v>
+        <v>1091</v>
       </c>
       <c r="C854" t="s">
-        <v>1099</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="855" spans="1:3">
@@ -14880,10 +14895,10 @@
         <v>9</v>
       </c>
       <c r="B855" t="s">
-        <v>1106</v>
+        <v>1095</v>
       </c>
       <c r="C855" t="s">
-        <v>1108</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="856" spans="1:3">
@@ -14891,10 +14906,10 @@
         <v>9</v>
       </c>
       <c r="B856" t="s">
-        <v>1109</v>
+        <v>1097</v>
       </c>
       <c r="C856" t="s">
-        <v>1110</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="857" spans="1:3">
@@ -14902,10 +14917,10 @@
         <v>9</v>
       </c>
       <c r="B857" t="s">
-        <v>1122</v>
+        <v>1106</v>
       </c>
       <c r="C857" t="s">
-        <v>1123</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="858" spans="1:3">
@@ -14913,10 +14928,10 @@
         <v>9</v>
       </c>
       <c r="B858" t="s">
-        <v>1134</v>
+        <v>1109</v>
       </c>
       <c r="C858" t="s">
-        <v>1135</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="859" spans="1:3">
@@ -14924,10 +14939,10 @@
         <v>9</v>
       </c>
       <c r="B859" t="s">
-        <v>1136</v>
+        <v>1122</v>
       </c>
       <c r="C859" t="s">
-        <v>1137</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="860" spans="1:3">
@@ -14935,10 +14950,10 @@
         <v>9</v>
       </c>
       <c r="B860" t="s">
-        <v>1140</v>
+        <v>1134</v>
       </c>
       <c r="C860" t="s">
-        <v>1141</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="861" spans="1:3">
@@ -14946,10 +14961,10 @@
         <v>9</v>
       </c>
       <c r="B861" t="s">
-        <v>1142</v>
+        <v>1136</v>
       </c>
       <c r="C861" t="s">
-        <v>1143</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="862" spans="1:3">
@@ -14957,10 +14972,10 @@
         <v>9</v>
       </c>
       <c r="B862" t="s">
-        <v>1144</v>
+        <v>1140</v>
       </c>
       <c r="C862" t="s">
-        <v>1145</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="863" spans="1:3">
@@ -14968,10 +14983,10 @@
         <v>9</v>
       </c>
       <c r="B863" t="s">
-        <v>1152</v>
+        <v>1142</v>
       </c>
       <c r="C863" t="s">
-        <v>1154</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="864" spans="1:3">
@@ -14979,10 +14994,10 @@
         <v>9</v>
       </c>
       <c r="B864" t="s">
-        <v>1155</v>
+        <v>1144</v>
       </c>
       <c r="C864" t="s">
-        <v>1156</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="865" spans="1:3">
@@ -14990,10 +15005,10 @@
         <v>9</v>
       </c>
       <c r="B865" t="s">
-        <v>1157</v>
+        <v>1152</v>
       </c>
       <c r="C865" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="866" spans="1:3">
@@ -15001,10 +15016,10 @@
         <v>9</v>
       </c>
       <c r="B866" t="s">
-        <v>1161</v>
+        <v>1155</v>
       </c>
       <c r="C866" t="s">
-        <v>1162</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="867" spans="1:3">
@@ -15012,10 +15027,10 @@
         <v>9</v>
       </c>
       <c r="B867" t="s">
-        <v>1163</v>
+        <v>1157</v>
       </c>
       <c r="C867" t="s">
-        <v>1164</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="868" spans="1:3">
@@ -15023,10 +15038,10 @@
         <v>9</v>
       </c>
       <c r="B868" t="s">
-        <v>1165</v>
+        <v>1161</v>
       </c>
       <c r="C868" t="s">
-        <v>1166</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="869" spans="1:3">
@@ -15034,10 +15049,10 @@
         <v>9</v>
       </c>
       <c r="B869" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="C869" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="870" spans="1:3">
@@ -15045,10 +15060,10 @@
         <v>9</v>
       </c>
       <c r="B870" t="s">
-        <v>1169</v>
+        <v>1165</v>
       </c>
       <c r="C870" t="s">
-        <v>1170</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="871" spans="1:3">
@@ -15056,10 +15071,10 @@
         <v>9</v>
       </c>
       <c r="B871" t="s">
-        <v>1171</v>
+        <v>1167</v>
       </c>
       <c r="C871" t="s">
-        <v>1172</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="872" spans="1:3">
@@ -15067,10 +15082,10 @@
         <v>9</v>
       </c>
       <c r="B872" t="s">
-        <v>1173</v>
+        <v>1169</v>
       </c>
       <c r="C872" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="873" spans="1:3">
@@ -15078,10 +15093,10 @@
         <v>9</v>
       </c>
       <c r="B873" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="C873" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="874" spans="1:3">
@@ -15089,10 +15104,10 @@
         <v>9</v>
       </c>
       <c r="B874" t="s">
-        <v>1177</v>
+        <v>1173</v>
       </c>
       <c r="C874" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="875" spans="1:3">
@@ -15100,10 +15115,10 @@
         <v>9</v>
       </c>
       <c r="B875" t="s">
-        <v>1179</v>
+        <v>1175</v>
       </c>
       <c r="C875" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="876" spans="1:3">
@@ -15111,10 +15126,10 @@
         <v>9</v>
       </c>
       <c r="B876" t="s">
-        <v>1183</v>
+        <v>1177</v>
       </c>
       <c r="C876" t="s">
-        <v>1184</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="877" spans="1:3">
@@ -15122,10 +15137,10 @@
         <v>9</v>
       </c>
       <c r="B877" t="s">
-        <v>1185</v>
+        <v>1179</v>
       </c>
       <c r="C877" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="878" spans="1:3">
@@ -15133,10 +15148,10 @@
         <v>9</v>
       </c>
       <c r="B878" t="s">
-        <v>1195</v>
+        <v>1183</v>
       </c>
       <c r="C878" t="s">
-        <v>1196</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="879" spans="1:3">
@@ -15144,10 +15159,10 @@
         <v>9</v>
       </c>
       <c r="B879" t="s">
-        <v>1197</v>
+        <v>1185</v>
       </c>
       <c r="C879" t="s">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="880" spans="1:3">
@@ -15155,10 +15170,10 @@
         <v>9</v>
       </c>
       <c r="B880" t="s">
-        <v>1199</v>
+        <v>1195</v>
       </c>
       <c r="C880" t="s">
-        <v>1201</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="881" spans="1:3">
@@ -15166,10 +15181,10 @@
         <v>9</v>
       </c>
       <c r="B881" t="s">
-        <v>1204</v>
+        <v>1197</v>
       </c>
       <c r="C881" t="s">
-        <v>1205</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="882" spans="1:3">
@@ -15177,10 +15192,10 @@
         <v>9</v>
       </c>
       <c r="B882" t="s">
-        <v>1206</v>
+        <v>1199</v>
       </c>
       <c r="C882" t="s">
-        <v>1207</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="883" spans="1:3">
@@ -15188,10 +15203,10 @@
         <v>9</v>
       </c>
       <c r="B883" t="s">
-        <v>1220</v>
+        <v>1204</v>
       </c>
       <c r="C883" t="s">
-        <v>1221</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="884" spans="1:3">
@@ -15199,10 +15214,10 @@
         <v>9</v>
       </c>
       <c r="B884" t="s">
-        <v>1222</v>
+        <v>1206</v>
       </c>
       <c r="C884" t="s">
-        <v>1223</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="885" spans="1:3">
@@ -15210,10 +15225,10 @@
         <v>9</v>
       </c>
       <c r="B885" t="s">
-        <v>1226</v>
+        <v>1220</v>
       </c>
       <c r="C885" t="s">
-        <v>1227</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="886" spans="1:3">
@@ -15221,10 +15236,10 @@
         <v>9</v>
       </c>
       <c r="B886" t="s">
-        <v>1228</v>
+        <v>1222</v>
       </c>
       <c r="C886" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="887" spans="1:3">
@@ -15232,10 +15247,10 @@
         <v>9</v>
       </c>
       <c r="B887" t="s">
-        <v>1230</v>
+        <v>1226</v>
       </c>
       <c r="C887" t="s">
-        <v>1231</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="888" spans="1:3">
@@ -15243,10 +15258,10 @@
         <v>9</v>
       </c>
       <c r="B888" t="s">
-        <v>1240</v>
+        <v>1228</v>
       </c>
       <c r="C888" t="s">
-        <v>1241</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="889" spans="1:3">
@@ -15254,10 +15269,10 @@
         <v>9</v>
       </c>
       <c r="B889" t="s">
-        <v>1242</v>
+        <v>1230</v>
       </c>
       <c r="C889" t="s">
-        <v>1243</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="890" spans="1:3">
@@ -15265,10 +15280,10 @@
         <v>9</v>
       </c>
       <c r="B890" t="s">
-        <v>1244</v>
+        <v>1240</v>
       </c>
       <c r="C890" t="s">
-        <v>1245</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="891" spans="1:3">
@@ -15276,10 +15291,10 @@
         <v>9</v>
       </c>
       <c r="B891" t="s">
-        <v>1250</v>
+        <v>1242</v>
       </c>
       <c r="C891" t="s">
-        <v>1251</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="892" spans="1:3">
@@ -15287,10 +15302,10 @@
         <v>9</v>
       </c>
       <c r="B892" t="s">
-        <v>1262</v>
+        <v>1244</v>
       </c>
       <c r="C892" t="s">
-        <v>1263</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="893" spans="1:3">
@@ -15298,10 +15313,10 @@
         <v>9</v>
       </c>
       <c r="B893" t="s">
-        <v>1264</v>
+        <v>1250</v>
       </c>
       <c r="C893" t="s">
-        <v>1266</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="894" spans="1:3">
@@ -15309,10 +15324,10 @@
         <v>9</v>
       </c>
       <c r="B894" t="s">
-        <v>1277</v>
+        <v>1262</v>
       </c>
       <c r="C894" t="s">
-        <v>1278</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="895" spans="1:3">
@@ -15320,10 +15335,10 @@
         <v>9</v>
       </c>
       <c r="B895" t="s">
-        <v>1286</v>
+        <v>1264</v>
       </c>
       <c r="C895" t="s">
-        <v>1287</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="896" spans="1:3">
@@ -15331,10 +15346,10 @@
         <v>9</v>
       </c>
       <c r="B896" t="s">
-        <v>1293</v>
+        <v>1277</v>
       </c>
       <c r="C896" t="s">
-        <v>1294</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="897" spans="1:3">
@@ -15342,10 +15357,10 @@
         <v>9</v>
       </c>
       <c r="B897" t="s">
-        <v>1299</v>
+        <v>1286</v>
       </c>
       <c r="C897" t="s">
-        <v>1300</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="898" spans="1:3">
@@ -15353,10 +15368,10 @@
         <v>9</v>
       </c>
       <c r="B898" t="s">
-        <v>1304</v>
+        <v>1293</v>
       </c>
       <c r="C898" t="s">
-        <v>1306</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="899" spans="1:3">
@@ -15364,10 +15379,10 @@
         <v>9</v>
       </c>
       <c r="B899" t="s">
-        <v>1313</v>
+        <v>1299</v>
       </c>
       <c r="C899" t="s">
-        <v>1314</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="900" spans="1:3">
@@ -15375,10 +15390,10 @@
         <v>9</v>
       </c>
       <c r="B900" t="s">
-        <v>1317</v>
+        <v>1304</v>
       </c>
       <c r="C900" t="s">
-        <v>1318</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="901" spans="1:3">
@@ -15386,10 +15401,10 @@
         <v>9</v>
       </c>
       <c r="B901" t="s">
-        <v>1319</v>
+        <v>1313</v>
       </c>
       <c r="C901" t="s">
-        <v>1320</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="902" spans="1:3">
@@ -15397,10 +15412,10 @@
         <v>9</v>
       </c>
       <c r="B902" t="s">
-        <v>1329</v>
+        <v>1317</v>
       </c>
       <c r="C902" t="s">
-        <v>1330</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="903" spans="1:3">
@@ -15408,10 +15423,10 @@
         <v>9</v>
       </c>
       <c r="B903" t="s">
-        <v>1331</v>
+        <v>1319</v>
       </c>
       <c r="C903" t="s">
-        <v>1332</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="904" spans="1:3">
@@ -15419,10 +15434,10 @@
         <v>9</v>
       </c>
       <c r="B904" t="s">
-        <v>1335</v>
+        <v>1329</v>
       </c>
       <c r="C904" t="s">
-        <v>1336</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="905" spans="1:3">
@@ -15430,10 +15445,10 @@
         <v>9</v>
       </c>
       <c r="B905" t="s">
-        <v>1337</v>
+        <v>1331</v>
       </c>
       <c r="C905" t="s">
-        <v>1338</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="906" spans="1:3">
@@ -15441,10 +15456,10 @@
         <v>9</v>
       </c>
       <c r="B906" t="s">
-        <v>1345</v>
+        <v>1335</v>
       </c>
       <c r="C906" t="s">
-        <v>1346</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="907" spans="1:3">
@@ -15452,10 +15467,10 @@
         <v>9</v>
       </c>
       <c r="B907" t="s">
-        <v>1347</v>
+        <v>1337</v>
       </c>
       <c r="C907" t="s">
-        <v>1348</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="908" spans="1:3">
@@ -15463,10 +15478,10 @@
         <v>9</v>
       </c>
       <c r="B908" t="s">
-        <v>1349</v>
+        <v>1345</v>
       </c>
       <c r="C908" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="909" spans="1:3">
@@ -15474,10 +15489,10 @@
         <v>9</v>
       </c>
       <c r="B909" t="s">
-        <v>1351</v>
+        <v>1347</v>
       </c>
       <c r="C909" t="s">
-        <v>1352</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="910" spans="1:3">
@@ -15485,10 +15500,10 @@
         <v>9</v>
       </c>
       <c r="B910" t="s">
-        <v>1353</v>
+        <v>1349</v>
       </c>
       <c r="C910" t="s">
-        <v>1354</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="911" spans="1:3">
@@ -15496,10 +15511,10 @@
         <v>9</v>
       </c>
       <c r="B911" t="s">
-        <v>1355</v>
+        <v>1351</v>
       </c>
       <c r="C911" t="s">
-        <v>1356</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="912" spans="1:3">
@@ -15507,10 +15522,10 @@
         <v>9</v>
       </c>
       <c r="B912" t="s">
-        <v>1363</v>
+        <v>1353</v>
       </c>
       <c r="C912" t="s">
-        <v>1364</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="913" spans="1:3">
@@ -15518,10 +15533,10 @@
         <v>9</v>
       </c>
       <c r="B913" t="s">
-        <v>1367</v>
+        <v>1355</v>
       </c>
       <c r="C913" t="s">
-        <v>1369</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="914" spans="1:3">
@@ -15529,10 +15544,10 @@
         <v>9</v>
       </c>
       <c r="B914" t="s">
-        <v>1374</v>
+        <v>1363</v>
       </c>
       <c r="C914" t="s">
-        <v>1377</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="915" spans="1:3">
@@ -15540,10 +15555,10 @@
         <v>9</v>
       </c>
       <c r="B915" t="s">
-        <v>1390</v>
+        <v>1367</v>
       </c>
       <c r="C915" t="s">
-        <v>1391</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="916" spans="1:3">
@@ -15551,10 +15566,10 @@
         <v>9</v>
       </c>
       <c r="B916" t="s">
-        <v>1392</v>
+        <v>1374</v>
       </c>
       <c r="C916" t="s">
-        <v>1393</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="917" spans="1:3">
@@ -15562,10 +15577,10 @@
         <v>9</v>
       </c>
       <c r="B917" t="s">
-        <v>1394</v>
+        <v>1390</v>
       </c>
       <c r="C917" t="s">
-        <v>1395</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="918" spans="1:3">
@@ -15573,10 +15588,10 @@
         <v>9</v>
       </c>
       <c r="B918" t="s">
-        <v>1400</v>
+        <v>1392</v>
       </c>
       <c r="C918" t="s">
-        <v>1401</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="919" spans="1:3">
@@ -15584,10 +15599,10 @@
         <v>9</v>
       </c>
       <c r="B919" t="s">
-        <v>1402</v>
+        <v>1394</v>
       </c>
       <c r="C919" t="s">
-        <v>1403</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="920" spans="1:3">
@@ -15595,10 +15610,10 @@
         <v>9</v>
       </c>
       <c r="B920" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="C920" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="921" spans="1:3">
@@ -15606,10 +15621,10 @@
         <v>9</v>
       </c>
       <c r="B921" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="C921" t="s">
-        <v>1408</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="922" spans="1:3">
@@ -15617,32 +15632,32 @@
         <v>9</v>
       </c>
       <c r="B922" t="s">
-        <v>1422</v>
+        <v>1404</v>
       </c>
       <c r="C922" t="s">
-        <v>1423</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="923" spans="1:3">
       <c r="A923" t="s">
-        <v>7</v>
-      </c>
-      <c r="B923">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="B923" t="s">
+        <v>1406</v>
       </c>
       <c r="C923" t="s">
-        <v>1433</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="924" spans="1:3">
       <c r="A924" t="s">
-        <v>7</v>
-      </c>
-      <c r="B924">
-        <v>2</v>
+        <v>9</v>
+      </c>
+      <c r="B924" t="s">
+        <v>1422</v>
       </c>
       <c r="C924" t="s">
-        <v>1439</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="925" spans="1:3">
@@ -15650,10 +15665,10 @@
         <v>7</v>
       </c>
       <c r="B925">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C925" t="s">
-        <v>1447</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="926" spans="1:3">
@@ -15661,10 +15676,10 @@
         <v>7</v>
       </c>
       <c r="B926">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C926" t="s">
-        <v>1453</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="927" spans="1:3">
@@ -15672,32 +15687,32 @@
         <v>7</v>
       </c>
       <c r="B927">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C927" t="s">
-        <v>1461</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="928" spans="1:3">
       <c r="A928" t="s">
         <v>7</v>
       </c>
-      <c r="B928" t="s">
-        <v>257</v>
+      <c r="B928">
+        <v>4</v>
       </c>
       <c r="C928" t="s">
-        <v>259</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="929" spans="1:3">
       <c r="A929" t="s">
         <v>7</v>
       </c>
-      <c r="B929" t="s">
-        <v>339</v>
+      <c r="B929">
+        <v>5</v>
       </c>
       <c r="C929" t="s">
-        <v>340</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="930" spans="1:3">
@@ -15705,10 +15720,10 @@
         <v>7</v>
       </c>
       <c r="B930" t="s">
-        <v>375</v>
+        <v>257</v>
       </c>
       <c r="C930" t="s">
-        <v>376</v>
+        <v>259</v>
       </c>
     </row>
     <row r="931" spans="1:3">
@@ -15716,10 +15731,10 @@
         <v>7</v>
       </c>
       <c r="B931" t="s">
-        <v>399</v>
+        <v>339</v>
       </c>
       <c r="C931" t="s">
-        <v>400</v>
+        <v>340</v>
       </c>
     </row>
     <row r="932" spans="1:3">
@@ -15727,10 +15742,10 @@
         <v>7</v>
       </c>
       <c r="B932" t="s">
-        <v>422</v>
+        <v>375</v>
       </c>
       <c r="C932" t="s">
-        <v>423</v>
+        <v>376</v>
       </c>
     </row>
     <row r="933" spans="1:3">
@@ -15738,10 +15753,10 @@
         <v>7</v>
       </c>
       <c r="B933" t="s">
-        <v>582</v>
+        <v>399</v>
       </c>
       <c r="C933" t="s">
-        <v>583</v>
+        <v>400</v>
       </c>
     </row>
     <row r="934" spans="1:3">
@@ -15749,10 +15764,10 @@
         <v>7</v>
       </c>
       <c r="B934" t="s">
-        <v>745</v>
+        <v>422</v>
       </c>
       <c r="C934" t="s">
-        <v>746</v>
+        <v>423</v>
       </c>
     </row>
     <row r="935" spans="1:3">
@@ -15760,10 +15775,10 @@
         <v>7</v>
       </c>
       <c r="B935" t="s">
-        <v>909</v>
+        <v>582</v>
       </c>
       <c r="C935" t="s">
-        <v>910</v>
+        <v>583</v>
       </c>
     </row>
     <row r="936" spans="1:3">
@@ -15771,10 +15786,10 @@
         <v>7</v>
       </c>
       <c r="B936" t="s">
-        <v>1076</v>
+        <v>745</v>
       </c>
       <c r="C936" t="s">
-        <v>1077</v>
+        <v>746</v>
       </c>
     </row>
     <row r="937" spans="1:3">
@@ -15782,10 +15797,10 @@
         <v>7</v>
       </c>
       <c r="B937" t="s">
-        <v>1159</v>
+        <v>909</v>
       </c>
       <c r="C937" t="s">
-        <v>1160</v>
+        <v>910</v>
       </c>
     </row>
     <row r="938" spans="1:3">
@@ -15793,32 +15808,32 @@
         <v>7</v>
       </c>
       <c r="B938" t="s">
-        <v>1409</v>
+        <v>1076</v>
       </c>
       <c r="C938" t="s">
-        <v>1410</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="939" spans="1:3">
       <c r="A939" t="s">
-        <v>1649</v>
-      </c>
-      <c r="B939">
-        <v>302</v>
+        <v>7</v>
+      </c>
+      <c r="B939" t="s">
+        <v>1159</v>
       </c>
       <c r="C939" t="s">
-        <v>1650</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="940" spans="1:3">
       <c r="A940" t="s">
-        <v>1649</v>
-      </c>
-      <c r="B940">
-        <v>303</v>
+        <v>7</v>
+      </c>
+      <c r="B940" t="s">
+        <v>1409</v>
       </c>
       <c r="C940" t="s">
-        <v>1651</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="941" spans="1:3">
@@ -15826,10 +15841,10 @@
         <v>1649</v>
       </c>
       <c r="B941">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C941" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="942" spans="1:3">
@@ -15837,10 +15852,10 @@
         <v>1649</v>
       </c>
       <c r="B942">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C942" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="943" spans="1:3">
@@ -15848,10 +15863,10 @@
         <v>1649</v>
       </c>
       <c r="B943">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C943" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="944" spans="1:3">
@@ -15859,10 +15874,10 @@
         <v>1649</v>
       </c>
       <c r="B944">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C944" t="s">
-        <v>1655</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="945" spans="1:3">
@@ -15870,10 +15885,10 @@
         <v>1649</v>
       </c>
       <c r="B945">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C945" t="s">
-        <v>1656</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="946" spans="1:3">
@@ -15881,10 +15896,10 @@
         <v>1649</v>
       </c>
       <c r="B946">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C946" t="s">
-        <v>1657</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="947" spans="1:3">
@@ -15892,10 +15907,10 @@
         <v>1649</v>
       </c>
       <c r="B947">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C947" t="s">
-        <v>1658</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="948" spans="1:3">
@@ -15903,10 +15918,10 @@
         <v>1649</v>
       </c>
       <c r="B948">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C948" t="s">
-        <v>1659</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="949" spans="1:3">
@@ -15914,10 +15929,10 @@
         <v>1649</v>
       </c>
       <c r="B949">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C949" t="s">
-        <v>1660</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="950" spans="1:3">
@@ -15925,10 +15940,10 @@
         <v>1649</v>
       </c>
       <c r="B950">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C950" t="s">
-        <v>1661</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="951" spans="1:3">
@@ -15936,10 +15951,10 @@
         <v>1649</v>
       </c>
       <c r="B951">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C951" t="s">
-        <v>1662</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="952" spans="1:3">
@@ -15947,10 +15962,10 @@
         <v>1649</v>
       </c>
       <c r="B952">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C952" t="s">
-        <v>1663</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="953" spans="1:3">
@@ -15958,10 +15973,10 @@
         <v>1649</v>
       </c>
       <c r="B953">
-        <v>401</v>
+        <v>314</v>
       </c>
       <c r="C953" t="s">
-        <v>1664</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="954" spans="1:3">
@@ -15969,10 +15984,10 @@
         <v>1649</v>
       </c>
       <c r="B954">
-        <v>402</v>
+        <v>315</v>
       </c>
       <c r="C954" t="s">
-        <v>1665</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="955" spans="1:3">
@@ -15980,32 +15995,32 @@
         <v>1649</v>
       </c>
       <c r="B955">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C955" t="s">
-        <v>1666</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="956" spans="1:3">
       <c r="A956" t="s">
-        <v>1607</v>
+        <v>1649</v>
       </c>
       <c r="B956">
-        <v>102</v>
+        <v>402</v>
       </c>
       <c r="C956" t="s">
-        <v>1608</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="957" spans="1:3">
       <c r="A957" t="s">
-        <v>1607</v>
+        <v>1649</v>
       </c>
       <c r="B957">
-        <v>103</v>
+        <v>403</v>
       </c>
       <c r="C957" t="s">
-        <v>1609</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="958" spans="1:3">
@@ -16013,10 +16028,10 @@
         <v>1607</v>
       </c>
       <c r="B958">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C958" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="959" spans="1:3">
@@ -16024,10 +16039,10 @@
         <v>1607</v>
       </c>
       <c r="B959">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C959" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="960" spans="1:3">
@@ -16035,10 +16050,10 @@
         <v>1607</v>
       </c>
       <c r="B960">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C960" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="961" spans="1:3">
@@ -16046,10 +16061,10 @@
         <v>1607</v>
       </c>
       <c r="B961">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C961" t="s">
-        <v>1614</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="962" spans="1:3">
@@ -16057,10 +16072,10 @@
         <v>1607</v>
       </c>
       <c r="B962">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C962" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="963" spans="1:3">
@@ -16068,10 +16083,10 @@
         <v>1607</v>
       </c>
       <c r="B963">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C963" t="s">
-        <v>1617</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="964" spans="1:3">
@@ -16079,10 +16094,10 @@
         <v>1607</v>
       </c>
       <c r="B964">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C964" t="s">
-        <v>1620</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="965" spans="1:3">
@@ -16090,10 +16105,10 @@
         <v>1607</v>
       </c>
       <c r="B965">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C965" t="s">
-        <v>1621</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="966" spans="1:3">
@@ -16101,10 +16116,10 @@
         <v>1607</v>
       </c>
       <c r="B966">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C966" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="967" spans="1:3">
@@ -16112,10 +16127,10 @@
         <v>1607</v>
       </c>
       <c r="B967">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C967" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="968" spans="1:3">
@@ -16123,10 +16138,10 @@
         <v>1607</v>
       </c>
       <c r="B968">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C968" t="s">
-        <v>1625</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="969" spans="1:3">
@@ -16134,10 +16149,10 @@
         <v>1607</v>
       </c>
       <c r="B969">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C969" t="s">
-        <v>1626</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="970" spans="1:3">
@@ -16145,10 +16160,10 @@
         <v>1607</v>
       </c>
       <c r="B970">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C970" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="971" spans="1:3">
@@ -16156,10 +16171,10 @@
         <v>1607</v>
       </c>
       <c r="B971">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C971" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="972" spans="1:3">
@@ -16167,10 +16182,10 @@
         <v>1607</v>
       </c>
       <c r="B972">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C972" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="973" spans="1:3">
@@ -16178,10 +16193,10 @@
         <v>1607</v>
       </c>
       <c r="B973">
-        <v>201</v>
+        <v>118</v>
       </c>
       <c r="C973" t="s">
-        <v>1635</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="974" spans="1:3">
@@ -16189,10 +16204,10 @@
         <v>1607</v>
       </c>
       <c r="B974">
-        <v>202</v>
+        <v>119</v>
       </c>
       <c r="C974" t="s">
-        <v>1637</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="975" spans="1:3">
@@ -16200,10 +16215,10 @@
         <v>1607</v>
       </c>
       <c r="B975">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C975" t="s">
-        <v>1638</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="976" spans="1:3">
@@ -16211,10 +16226,10 @@
         <v>1607</v>
       </c>
       <c r="B976">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C976" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="977" spans="1:3">
@@ -16222,10 +16237,10 @@
         <v>1607</v>
       </c>
       <c r="B977">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C977" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="978" spans="1:3">
@@ -16233,10 +16248,10 @@
         <v>1607</v>
       </c>
       <c r="B978">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C978" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="979" spans="1:3">
@@ -16244,10 +16259,10 @@
         <v>1607</v>
       </c>
       <c r="B979">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C979" t="s">
-        <v>1642</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="980" spans="1:3">
@@ -16255,10 +16270,10 @@
         <v>1607</v>
       </c>
       <c r="B980">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C980" t="s">
-        <v>1643</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="981" spans="1:3">
@@ -16266,10 +16281,10 @@
         <v>1607</v>
       </c>
       <c r="B981">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C981" t="s">
-        <v>1644</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="982" spans="1:3">
@@ -16277,10 +16292,10 @@
         <v>1607</v>
       </c>
       <c r="B982">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C982" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="983" spans="1:3">
@@ -16288,10 +16303,10 @@
         <v>1607</v>
       </c>
       <c r="B983">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C983" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="984" spans="1:3">
@@ -16299,10 +16314,10 @@
         <v>1607</v>
       </c>
       <c r="B984">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C984" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="985" spans="1:3">
@@ -16310,54 +16325,54 @@
         <v>1607</v>
       </c>
       <c r="B985">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C985" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="986" spans="1:3">
       <c r="A986" t="s">
-        <v>151</v>
-      </c>
-      <c r="B986" t="s">
-        <v>149</v>
+        <v>1607</v>
+      </c>
+      <c r="B986">
+        <v>212</v>
       </c>
       <c r="C986" t="s">
-        <v>152</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="987" spans="1:3">
       <c r="A987" t="s">
-        <v>151</v>
-      </c>
-      <c r="B987" s="1" t="s">
-        <v>260</v>
+        <v>1607</v>
+      </c>
+      <c r="B987">
+        <v>213</v>
       </c>
       <c r="C987" t="s">
-        <v>261</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="988" spans="1:3">
       <c r="A988" t="s">
         <v>151</v>
       </c>
-      <c r="B988" s="1" t="s">
-        <v>382</v>
+      <c r="B988" t="s">
+        <v>149</v>
       </c>
       <c r="C988" t="s">
-        <v>1682</v>
+        <v>152</v>
       </c>
     </row>
     <row r="989" spans="1:3">
       <c r="A989" t="s">
         <v>151</v>
       </c>
-      <c r="B989" t="s">
-        <v>713</v>
+      <c r="B989" s="1" t="s">
+        <v>260</v>
       </c>
       <c r="C989" t="s">
-        <v>714</v>
+        <v>261</v>
       </c>
     </row>
     <row r="990" spans="1:3">
@@ -16365,21 +16380,21 @@
         <v>151</v>
       </c>
       <c r="B990" s="1" t="s">
-        <v>923</v>
+        <v>382</v>
       </c>
       <c r="C990" t="s">
-        <v>925</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="991" spans="1:3">
       <c r="A991" t="s">
         <v>151</v>
       </c>
-      <c r="B991" s="1" t="s">
-        <v>1134</v>
+      <c r="B991" t="s">
+        <v>713</v>
       </c>
       <c r="C991" t="s">
-        <v>1683</v>
+        <v>714</v>
       </c>
     </row>
     <row r="992" spans="1:3">
@@ -16387,10 +16402,10 @@
         <v>151</v>
       </c>
       <c r="B992" s="1" t="s">
-        <v>1214</v>
+        <v>923</v>
       </c>
       <c r="C992" t="s">
-        <v>1215</v>
+        <v>925</v>
       </c>
     </row>
     <row r="993" spans="1:3">
@@ -16398,27 +16413,60 @@
         <v>151</v>
       </c>
       <c r="B993" s="1" t="s">
-        <v>151</v>
+        <v>1134</v>
       </c>
       <c r="C993" t="s">
-        <v>1413</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="994" spans="1:3">
       <c r="A994" t="s">
         <v>151</v>
       </c>
-      <c r="B994" t="s">
+      <c r="B994" s="1" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C994" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="995" spans="1:3">
+      <c r="A995" t="s">
+        <v>151</v>
+      </c>
+      <c r="B995" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C995" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="996" spans="1:3">
+      <c r="A996" t="s">
+        <v>151</v>
+      </c>
+      <c r="B996" t="s">
         <v>1414</v>
       </c>
-      <c r="C994" t="s">
+      <c r="C996" t="s">
         <v>1415</v>
       </c>
     </row>
+    <row r="997" spans="1:3">
+      <c r="A997" t="s">
+        <v>113</v>
+      </c>
+      <c r="B997" s="1" t="s">
+        <v>1690</v>
+      </c>
+      <c r="C997" t="s">
+        <v>1689</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState ref="A1:D994">
-    <sortCondition ref="A1:A994"/>
-    <sortCondition ref="B1:B994"/>
+  <sortState ref="A1:D996">
+    <sortCondition ref="A1:A996"/>
+    <sortCondition ref="B1:B996"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/src/data/ruse-blocks.xlsx
+++ b/src/data/ruse-blocks.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2738" uniqueCount="1684">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2750" uniqueCount="1691">
   <si>
     <t>Дружба 1</t>
   </si>
@@ -5066,6 +5066,27 @@
   </si>
   <si>
     <t>ул. Мехомия 7</t>
+  </si>
+  <si>
+    <t>ул. Тича 20</t>
+  </si>
+  <si>
+    <t>Колос</t>
+  </si>
+  <si>
+    <t>ул. Сърнена гора 10</t>
+  </si>
+  <si>
+    <t>ул. Стоян Заимов №17</t>
+  </si>
+  <si>
+    <t>Маринета</t>
+  </si>
+  <si>
+    <t>ул. Чипровци №21А</t>
+  </si>
+  <si>
+    <t>Данц</t>
   </si>
 </sst>
 </file>
@@ -5457,7 +5478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D993"/>
+  <dimension ref="A1:D997"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="17.8984375" customWidth="1"/>
@@ -10561,7 +10582,7 @@
       <c r="A463" t="s">
         <v>113</v>
       </c>
-      <c r="B463" t="s">
+      <c r="B463" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C463" t="s">
@@ -10572,7 +10593,7 @@
       <c r="A464" t="s">
         <v>113</v>
       </c>
-      <c r="B464" t="s">
+      <c r="B464" s="1" t="s">
         <v>136</v>
       </c>
       <c r="C464" t="s">
@@ -10583,7 +10604,7 @@
       <c r="A465" t="s">
         <v>113</v>
       </c>
-      <c r="B465" t="s">
+      <c r="B465" s="1" t="s">
         <v>219</v>
       </c>
       <c r="C465" t="s">
@@ -10594,7 +10615,7 @@
       <c r="A466" t="s">
         <v>113</v>
       </c>
-      <c r="B466" t="s">
+      <c r="B466" s="1" t="s">
         <v>251</v>
       </c>
       <c r="C466" t="s">
@@ -10605,7 +10626,7 @@
       <c r="A467" t="s">
         <v>113</v>
       </c>
-      <c r="B467" t="s">
+      <c r="B467" s="1" t="s">
         <v>267</v>
       </c>
       <c r="C467" t="s">
@@ -10616,7 +10637,7 @@
       <c r="A468" t="s">
         <v>113</v>
       </c>
-      <c r="B468" t="s">
+      <c r="B468" s="1" t="s">
         <v>364</v>
       </c>
       <c r="C468" t="s">
@@ -10627,253 +10648,253 @@
       <c r="A469" t="s">
         <v>113</v>
       </c>
-      <c r="B469" t="s">
-        <v>426</v>
+      <c r="B469" s="1" t="s">
+        <v>1690</v>
       </c>
       <c r="C469" t="s">
-        <v>427</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="470" spans="1:3">
       <c r="A470" t="s">
         <v>113</v>
       </c>
-      <c r="B470" t="s">
-        <v>624</v>
+      <c r="B470" s="1" t="s">
+        <v>426</v>
       </c>
       <c r="C470" t="s">
-        <v>625</v>
+        <v>427</v>
       </c>
     </row>
     <row r="471" spans="1:3">
       <c r="A471" t="s">
         <v>113</v>
       </c>
-      <c r="B471" t="s">
-        <v>626</v>
+      <c r="B471" s="1" t="s">
+        <v>568</v>
       </c>
       <c r="C471" t="s">
-        <v>627</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="472" spans="1:3">
       <c r="A472" t="s">
         <v>113</v>
       </c>
-      <c r="B472" t="s">
-        <v>630</v>
+      <c r="B472" s="1" t="s">
+        <v>624</v>
       </c>
       <c r="C472" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
     </row>
     <row r="473" spans="1:3">
       <c r="A473" t="s">
         <v>113</v>
       </c>
-      <c r="B473" t="s">
-        <v>650</v>
+      <c r="B473" s="1" t="s">
+        <v>626</v>
       </c>
       <c r="C473" t="s">
-        <v>651</v>
+        <v>627</v>
       </c>
     </row>
     <row r="474" spans="1:3">
       <c r="A474" t="s">
         <v>113</v>
       </c>
-      <c r="B474" t="s">
-        <v>747</v>
+      <c r="B474" s="1" t="s">
+        <v>1685</v>
       </c>
       <c r="C474" t="s">
-        <v>748</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="475" spans="1:3">
       <c r="A475" t="s">
         <v>113</v>
       </c>
-      <c r="B475" t="s">
-        <v>757</v>
+      <c r="B475" s="1" t="s">
+        <v>630</v>
       </c>
       <c r="C475" t="s">
-        <v>758</v>
+        <v>631</v>
       </c>
     </row>
     <row r="476" spans="1:3">
       <c r="A476" t="s">
         <v>113</v>
       </c>
-      <c r="B476" t="s">
-        <v>763</v>
+      <c r="B476" s="1" t="s">
+        <v>650</v>
       </c>
       <c r="C476" t="s">
-        <v>764</v>
+        <v>651</v>
       </c>
     </row>
     <row r="477" spans="1:3">
       <c r="A477" t="s">
         <v>113</v>
       </c>
-      <c r="B477" t="s">
-        <v>780</v>
+      <c r="B477" s="1" t="s">
+        <v>747</v>
       </c>
       <c r="C477" t="s">
-        <v>781</v>
+        <v>748</v>
       </c>
     </row>
     <row r="478" spans="1:3">
       <c r="A478" t="s">
         <v>113</v>
       </c>
-      <c r="B478" t="s">
-        <v>802</v>
+      <c r="B478" s="1" t="s">
+        <v>757</v>
       </c>
       <c r="C478" t="s">
-        <v>803</v>
+        <v>758</v>
       </c>
     </row>
     <row r="479" spans="1:3">
       <c r="A479" t="s">
         <v>113</v>
       </c>
-      <c r="B479" t="s">
-        <v>804</v>
+      <c r="B479" s="1" t="s">
+        <v>763</v>
       </c>
       <c r="C479" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
     </row>
     <row r="480" spans="1:3">
       <c r="A480" t="s">
         <v>113</v>
       </c>
-      <c r="B480" t="s">
-        <v>809</v>
+      <c r="B480" s="1" t="s">
+        <v>780</v>
       </c>
       <c r="C480" t="s">
-        <v>810</v>
+        <v>781</v>
       </c>
     </row>
     <row r="481" spans="1:3">
       <c r="A481" t="s">
         <v>113</v>
       </c>
-      <c r="B481" t="s">
-        <v>940</v>
+      <c r="B481" s="1" t="s">
+        <v>802</v>
       </c>
       <c r="C481" t="s">
-        <v>941</v>
+        <v>803</v>
       </c>
     </row>
     <row r="482" spans="1:3">
       <c r="A482" t="s">
         <v>113</v>
       </c>
-      <c r="B482" t="s">
-        <v>973</v>
+      <c r="B482" s="1" t="s">
+        <v>804</v>
       </c>
       <c r="C482" t="s">
-        <v>974</v>
+        <v>805</v>
       </c>
     </row>
     <row r="483" spans="1:3">
       <c r="A483" t="s">
         <v>113</v>
       </c>
-      <c r="B483" t="s">
-        <v>1148</v>
+      <c r="B483" s="1" t="s">
+        <v>809</v>
       </c>
       <c r="C483" t="s">
-        <v>1149</v>
+        <v>810</v>
       </c>
     </row>
     <row r="484" spans="1:3">
       <c r="A484" t="s">
         <v>113</v>
       </c>
-      <c r="B484" t="s">
-        <v>1193</v>
+      <c r="B484" s="1" t="s">
+        <v>1688</v>
       </c>
       <c r="C484" t="s">
-        <v>1194</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="485" spans="1:3">
       <c r="A485" t="s">
         <v>113</v>
       </c>
-      <c r="B485" t="s">
-        <v>1232</v>
+      <c r="B485" s="1" t="s">
+        <v>940</v>
       </c>
       <c r="C485" t="s">
-        <v>1233</v>
+        <v>941</v>
       </c>
     </row>
     <row r="486" spans="1:3">
       <c r="A486" t="s">
         <v>113</v>
       </c>
-      <c r="B486" t="s">
-        <v>1252</v>
+      <c r="B486" s="1" t="s">
+        <v>973</v>
       </c>
       <c r="C486" t="s">
-        <v>1253</v>
+        <v>974</v>
       </c>
     </row>
     <row r="487" spans="1:3">
       <c r="A487" t="s">
         <v>113</v>
       </c>
-      <c r="B487" t="s">
-        <v>1267</v>
+      <c r="B487" s="1" t="s">
+        <v>1148</v>
       </c>
       <c r="C487" t="s">
-        <v>1268</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="488" spans="1:3">
       <c r="A488" t="s">
-        <v>24</v>
-      </c>
-      <c r="B488" t="s">
-        <v>25</v>
+        <v>113</v>
+      </c>
+      <c r="B488" s="1" t="s">
+        <v>1193</v>
       </c>
       <c r="C488" t="s">
-        <v>26</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="489" spans="1:3">
       <c r="A489" t="s">
-        <v>24</v>
-      </c>
-      <c r="B489" t="s">
-        <v>27</v>
+        <v>113</v>
+      </c>
+      <c r="B489" s="1" t="s">
+        <v>1232</v>
       </c>
       <c r="C489" t="s">
-        <v>28</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="490" spans="1:3">
       <c r="A490" t="s">
-        <v>24</v>
-      </c>
-      <c r="B490" t="s">
-        <v>120</v>
+        <v>113</v>
+      </c>
+      <c r="B490" s="1" t="s">
+        <v>1252</v>
       </c>
       <c r="C490" t="s">
-        <v>121</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="491" spans="1:3">
       <c r="A491" t="s">
-        <v>24</v>
-      </c>
-      <c r="B491" t="s">
-        <v>175</v>
+        <v>113</v>
+      </c>
+      <c r="B491" s="1" t="s">
+        <v>1267</v>
       </c>
       <c r="C491" t="s">
-        <v>176</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="492" spans="1:3">
@@ -10881,10 +10902,10 @@
         <v>24</v>
       </c>
       <c r="B492" t="s">
-        <v>196</v>
+        <v>25</v>
       </c>
       <c r="C492" t="s">
-        <v>197</v>
+        <v>26</v>
       </c>
     </row>
     <row r="493" spans="1:3">
@@ -10892,10 +10913,10 @@
         <v>24</v>
       </c>
       <c r="B493" t="s">
-        <v>221</v>
+        <v>27</v>
       </c>
       <c r="C493" t="s">
-        <v>222</v>
+        <v>28</v>
       </c>
     </row>
     <row r="494" spans="1:3">
@@ -10903,10 +10924,10 @@
         <v>24</v>
       </c>
       <c r="B494" t="s">
-        <v>227</v>
+        <v>120</v>
       </c>
       <c r="C494" t="s">
-        <v>228</v>
+        <v>121</v>
       </c>
     </row>
     <row r="495" spans="1:3">
@@ -10914,10 +10935,10 @@
         <v>24</v>
       </c>
       <c r="B495" t="s">
-        <v>283</v>
+        <v>175</v>
       </c>
       <c r="C495" t="s">
-        <v>284</v>
+        <v>176</v>
       </c>
     </row>
     <row r="496" spans="1:3">
@@ -10925,10 +10946,10 @@
         <v>24</v>
       </c>
       <c r="B496" t="s">
-        <v>346</v>
+        <v>196</v>
       </c>
       <c r="C496" t="s">
-        <v>347</v>
+        <v>197</v>
       </c>
     </row>
     <row r="497" spans="1:3">
@@ -10936,10 +10957,10 @@
         <v>24</v>
       </c>
       <c r="B497" t="s">
-        <v>369</v>
+        <v>221</v>
       </c>
       <c r="C497" t="s">
-        <v>370</v>
+        <v>222</v>
       </c>
     </row>
     <row r="498" spans="1:3">
@@ -10947,10 +10968,10 @@
         <v>24</v>
       </c>
       <c r="B498" t="s">
-        <v>464</v>
+        <v>227</v>
       </c>
       <c r="C498" t="s">
-        <v>465</v>
+        <v>228</v>
       </c>
     </row>
     <row r="499" spans="1:3">
@@ -10958,10 +10979,10 @@
         <v>24</v>
       </c>
       <c r="B499" t="s">
-        <v>494</v>
+        <v>283</v>
       </c>
       <c r="C499" t="s">
-        <v>495</v>
+        <v>284</v>
       </c>
     </row>
     <row r="500" spans="1:3">
@@ -10969,10 +10990,10 @@
         <v>24</v>
       </c>
       <c r="B500" t="s">
-        <v>545</v>
+        <v>346</v>
       </c>
       <c r="C500" t="s">
-        <v>546</v>
+        <v>347</v>
       </c>
     </row>
     <row r="501" spans="1:3">
@@ -10980,10 +11001,10 @@
         <v>24</v>
       </c>
       <c r="B501" t="s">
-        <v>605</v>
+        <v>369</v>
       </c>
       <c r="C501" t="s">
-        <v>606</v>
+        <v>370</v>
       </c>
     </row>
     <row r="502" spans="1:3">
@@ -10991,10 +11012,10 @@
         <v>24</v>
       </c>
       <c r="B502" t="s">
-        <v>618</v>
+        <v>464</v>
       </c>
       <c r="C502" t="s">
-        <v>619</v>
+        <v>465</v>
       </c>
     </row>
     <row r="503" spans="1:3">
@@ -11002,10 +11023,10 @@
         <v>24</v>
       </c>
       <c r="B503" t="s">
-        <v>662</v>
+        <v>494</v>
       </c>
       <c r="C503" t="s">
-        <v>663</v>
+        <v>495</v>
       </c>
     </row>
     <row r="504" spans="1:3">
@@ -11013,10 +11034,10 @@
         <v>24</v>
       </c>
       <c r="B504" t="s">
-        <v>670</v>
+        <v>545</v>
       </c>
       <c r="C504" t="s">
-        <v>671</v>
+        <v>546</v>
       </c>
     </row>
     <row r="505" spans="1:3">
@@ -11024,10 +11045,10 @@
         <v>24</v>
       </c>
       <c r="B505" t="s">
-        <v>903</v>
+        <v>605</v>
       </c>
       <c r="C505" t="s">
-        <v>904</v>
+        <v>606</v>
       </c>
     </row>
     <row r="506" spans="1:3">
@@ -11035,10 +11056,10 @@
         <v>24</v>
       </c>
       <c r="B506" t="s">
-        <v>986</v>
+        <v>618</v>
       </c>
       <c r="C506" t="s">
-        <v>987</v>
+        <v>619</v>
       </c>
     </row>
     <row r="507" spans="1:3">
@@ -11046,10 +11067,10 @@
         <v>24</v>
       </c>
       <c r="B507" t="s">
-        <v>992</v>
+        <v>662</v>
       </c>
       <c r="C507" t="s">
-        <v>993</v>
+        <v>663</v>
       </c>
     </row>
     <row r="508" spans="1:3">
@@ -11057,10 +11078,10 @@
         <v>24</v>
       </c>
       <c r="B508" t="s">
-        <v>1006</v>
+        <v>670</v>
       </c>
       <c r="C508" t="s">
-        <v>1007</v>
+        <v>671</v>
       </c>
     </row>
     <row r="509" spans="1:3">
@@ -11068,10 +11089,10 @@
         <v>24</v>
       </c>
       <c r="B509" t="s">
-        <v>1111</v>
+        <v>903</v>
       </c>
       <c r="C509" t="s">
-        <v>1112</v>
+        <v>904</v>
       </c>
     </row>
     <row r="510" spans="1:3">
@@ -11079,10 +11100,10 @@
         <v>24</v>
       </c>
       <c r="B510" t="s">
-        <v>1132</v>
+        <v>986</v>
       </c>
       <c r="C510" t="s">
-        <v>1133</v>
+        <v>987</v>
       </c>
     </row>
     <row r="511" spans="1:3">
@@ -11090,10 +11111,10 @@
         <v>24</v>
       </c>
       <c r="B511" t="s">
-        <v>1202</v>
+        <v>992</v>
       </c>
       <c r="C511" t="s">
-        <v>1203</v>
+        <v>993</v>
       </c>
     </row>
     <row r="512" spans="1:3">
@@ -11101,10 +11122,10 @@
         <v>24</v>
       </c>
       <c r="B512" t="s">
-        <v>1234</v>
+        <v>1006</v>
       </c>
       <c r="C512" t="s">
-        <v>1235</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="513" spans="1:3">
@@ -11112,10 +11133,10 @@
         <v>24</v>
       </c>
       <c r="B513" t="s">
-        <v>1248</v>
+        <v>1111</v>
       </c>
       <c r="C513" t="s">
-        <v>1249</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="514" spans="1:3">
@@ -11123,10 +11144,10 @@
         <v>24</v>
       </c>
       <c r="B514" t="s">
-        <v>1260</v>
+        <v>1132</v>
       </c>
       <c r="C514" t="s">
-        <v>1261</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="515" spans="1:3">
@@ -11134,10 +11155,10 @@
         <v>24</v>
       </c>
       <c r="B515" t="s">
-        <v>1304</v>
+        <v>1202</v>
       </c>
       <c r="C515" t="s">
-        <v>1305</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="516" spans="1:3">
@@ -11145,10 +11166,10 @@
         <v>24</v>
       </c>
       <c r="B516" t="s">
-        <v>1321</v>
+        <v>1234</v>
       </c>
       <c r="C516" t="s">
-        <v>1322</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="517" spans="1:3">
@@ -11156,10 +11177,10 @@
         <v>24</v>
       </c>
       <c r="B517" t="s">
-        <v>1323</v>
+        <v>1248</v>
       </c>
       <c r="C517" t="s">
-        <v>1324</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="518" spans="1:3">
@@ -11167,10 +11188,10 @@
         <v>24</v>
       </c>
       <c r="B518" t="s">
-        <v>1325</v>
+        <v>1260</v>
       </c>
       <c r="C518" t="s">
-        <v>1326</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="519" spans="1:3">
@@ -11178,10 +11199,10 @@
         <v>24</v>
       </c>
       <c r="B519" t="s">
-        <v>1327</v>
+        <v>1304</v>
       </c>
       <c r="C519" t="s">
-        <v>1328</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="520" spans="1:3">
@@ -11189,109 +11210,109 @@
         <v>24</v>
       </c>
       <c r="B520" t="s">
-        <v>1380</v>
+        <v>1321</v>
       </c>
       <c r="C520" t="s">
-        <v>1381</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="521" spans="1:3">
       <c r="A521" t="s">
-        <v>5</v>
-      </c>
-      <c r="B521">
-        <v>1</v>
+        <v>24</v>
+      </c>
+      <c r="B521" t="s">
+        <v>1323</v>
       </c>
       <c r="C521" t="s">
-        <v>1431</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="522" spans="1:3">
       <c r="A522" t="s">
-        <v>5</v>
-      </c>
-      <c r="B522">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="B522" t="s">
+        <v>1325</v>
       </c>
       <c r="C522" t="s">
-        <v>1437</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="523" spans="1:3">
       <c r="A523" t="s">
-        <v>5</v>
-      </c>
-      <c r="B523">
-        <v>3</v>
+        <v>24</v>
+      </c>
+      <c r="B523" t="s">
+        <v>1327</v>
       </c>
       <c r="C523" t="s">
-        <v>1445</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="524" spans="1:3">
       <c r="A524" t="s">
-        <v>5</v>
-      </c>
-      <c r="B524">
-        <v>8</v>
+        <v>24</v>
+      </c>
+      <c r="B524" t="s">
+        <v>1380</v>
       </c>
       <c r="C524" t="s">
-        <v>1477</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="525" spans="1:3">
       <c r="A525" t="s">
         <v>5</v>
       </c>
-      <c r="B525" t="s">
-        <v>1341</v>
+      <c r="B525">
+        <v>1</v>
       </c>
       <c r="C525" t="s">
-        <v>1342</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="526" spans="1:3">
       <c r="A526" t="s">
-        <v>530</v>
-      </c>
-      <c r="B526" t="s">
-        <v>531</v>
+        <v>5</v>
+      </c>
+      <c r="B526">
+        <v>2</v>
       </c>
       <c r="C526" t="s">
-        <v>532</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="527" spans="1:3">
       <c r="A527" t="s">
-        <v>530</v>
-      </c>
-      <c r="B527" t="s">
-        <v>977</v>
+        <v>5</v>
+      </c>
+      <c r="B527">
+        <v>3</v>
       </c>
       <c r="C527" t="s">
-        <v>978</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="528" spans="1:3">
       <c r="A528" t="s">
-        <v>530</v>
-      </c>
-      <c r="B528" t="s">
-        <v>979</v>
+        <v>5</v>
+      </c>
+      <c r="B528">
+        <v>8</v>
       </c>
       <c r="C528" t="s">
-        <v>978</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="529" spans="1:3">
       <c r="A529" t="s">
-        <v>530</v>
+        <v>5</v>
       </c>
       <c r="B529" t="s">
-        <v>980</v>
+        <v>1341</v>
       </c>
       <c r="C529" t="s">
-        <v>981</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="530" spans="1:3">
@@ -11299,54 +11320,54 @@
         <v>530</v>
       </c>
       <c r="B530" t="s">
-        <v>1189</v>
+        <v>531</v>
       </c>
       <c r="C530" t="s">
-        <v>1190</v>
+        <v>532</v>
       </c>
     </row>
     <row r="531" spans="1:3">
       <c r="A531" t="s">
-        <v>6</v>
-      </c>
-      <c r="B531">
-        <v>1</v>
+        <v>530</v>
+      </c>
+      <c r="B531" t="s">
+        <v>977</v>
       </c>
       <c r="C531" t="s">
-        <v>1432</v>
+        <v>978</v>
       </c>
     </row>
     <row r="532" spans="1:3">
       <c r="A532" t="s">
-        <v>6</v>
-      </c>
-      <c r="B532">
-        <v>2</v>
+        <v>530</v>
+      </c>
+      <c r="B532" t="s">
+        <v>979</v>
       </c>
       <c r="C532" t="s">
-        <v>1438</v>
+        <v>978</v>
       </c>
     </row>
     <row r="533" spans="1:3">
       <c r="A533" t="s">
-        <v>6</v>
-      </c>
-      <c r="B533">
-        <v>3</v>
+        <v>530</v>
+      </c>
+      <c r="B533" t="s">
+        <v>980</v>
       </c>
       <c r="C533" t="s">
-        <v>1446</v>
+        <v>981</v>
       </c>
     </row>
     <row r="534" spans="1:3">
       <c r="A534" t="s">
-        <v>6</v>
-      </c>
-      <c r="B534">
-        <v>4</v>
+        <v>530</v>
+      </c>
+      <c r="B534" t="s">
+        <v>1189</v>
       </c>
       <c r="C534" t="s">
-        <v>1452</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="535" spans="1:3">
@@ -11354,10 +11375,10 @@
         <v>6</v>
       </c>
       <c r="B535">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C535" t="s">
-        <v>1460</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="536" spans="1:3">
@@ -11365,10 +11386,10 @@
         <v>6</v>
       </c>
       <c r="B536">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C536" t="s">
-        <v>1467</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="537" spans="1:3">
@@ -11376,10 +11397,10 @@
         <v>6</v>
       </c>
       <c r="B537">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C537" t="s">
-        <v>1478</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="538" spans="1:3">
@@ -11387,10 +11408,10 @@
         <v>6</v>
       </c>
       <c r="B538">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C538" t="s">
-        <v>1487</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="539" spans="1:3">
@@ -11398,10 +11419,10 @@
         <v>6</v>
       </c>
       <c r="B539">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C539" t="s">
-        <v>1494</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="540" spans="1:3">
@@ -11409,10 +11430,10 @@
         <v>6</v>
       </c>
       <c r="B540">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="C540" t="s">
-        <v>1527</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="541" spans="1:3">
@@ -11420,10 +11441,10 @@
         <v>6</v>
       </c>
       <c r="B541">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="C541" t="s">
-        <v>1528</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="542" spans="1:3">
@@ -11431,10 +11452,10 @@
         <v>6</v>
       </c>
       <c r="B542">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="C542" t="s">
-        <v>1533</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="543" spans="1:3">
@@ -11442,10 +11463,10 @@
         <v>6</v>
       </c>
       <c r="B543">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C543" t="s">
-        <v>1536</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="544" spans="1:3">
@@ -11453,10 +11474,10 @@
         <v>6</v>
       </c>
       <c r="B544">
-        <v>118</v>
+        <v>25</v>
       </c>
       <c r="C544" t="s">
-        <v>1628</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="545" spans="1:3">
@@ -11464,54 +11485,54 @@
         <v>6</v>
       </c>
       <c r="B545">
-        <v>120</v>
+        <v>26</v>
       </c>
       <c r="C545" t="s">
-        <v>1631</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="546" spans="1:3">
       <c r="A546" t="s">
         <v>6</v>
       </c>
-      <c r="B546" t="s">
-        <v>14</v>
+      <c r="B546">
+        <v>28</v>
       </c>
       <c r="C546" t="s">
-        <v>15</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="547" spans="1:3">
       <c r="A547" t="s">
         <v>6</v>
       </c>
-      <c r="B547" t="s">
-        <v>67</v>
+      <c r="B547">
+        <v>29</v>
       </c>
       <c r="C547" t="s">
-        <v>68</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="548" spans="1:3">
       <c r="A548" t="s">
         <v>6</v>
       </c>
-      <c r="B548" t="s">
-        <v>72</v>
+      <c r="B548">
+        <v>118</v>
       </c>
       <c r="C548" t="s">
-        <v>73</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="549" spans="1:3">
       <c r="A549" t="s">
         <v>6</v>
       </c>
-      <c r="B549" t="s">
-        <v>132</v>
+      <c r="B549">
+        <v>120</v>
       </c>
       <c r="C549" t="s">
-        <v>133</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="550" spans="1:3">
@@ -11519,10 +11540,10 @@
         <v>6</v>
       </c>
       <c r="B550" t="s">
-        <v>163</v>
+        <v>14</v>
       </c>
       <c r="C550" t="s">
-        <v>164</v>
+        <v>15</v>
       </c>
     </row>
     <row r="551" spans="1:3">
@@ -11530,10 +11551,10 @@
         <v>6</v>
       </c>
       <c r="B551" t="s">
-        <v>165</v>
+        <v>67</v>
       </c>
       <c r="C551" t="s">
-        <v>166</v>
+        <v>68</v>
       </c>
     </row>
     <row r="552" spans="1:3">
@@ -11541,10 +11562,10 @@
         <v>6</v>
       </c>
       <c r="B552" t="s">
-        <v>167</v>
+        <v>72</v>
       </c>
       <c r="C552" t="s">
-        <v>168</v>
+        <v>73</v>
       </c>
     </row>
     <row r="553" spans="1:3">
@@ -11552,10 +11573,10 @@
         <v>6</v>
       </c>
       <c r="B553" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="C553" t="s">
-        <v>170</v>
+        <v>133</v>
       </c>
     </row>
     <row r="554" spans="1:3">
@@ -11563,10 +11584,10 @@
         <v>6</v>
       </c>
       <c r="B554" t="s">
-        <v>287</v>
+        <v>163</v>
       </c>
       <c r="C554" t="s">
-        <v>288</v>
+        <v>164</v>
       </c>
     </row>
     <row r="555" spans="1:3">
@@ -11574,10 +11595,10 @@
         <v>6</v>
       </c>
       <c r="B555" t="s">
-        <v>490</v>
+        <v>165</v>
       </c>
       <c r="C555" t="s">
-        <v>491</v>
+        <v>166</v>
       </c>
     </row>
     <row r="556" spans="1:3">
@@ -11585,10 +11606,10 @@
         <v>6</v>
       </c>
       <c r="B556" t="s">
-        <v>511</v>
+        <v>167</v>
       </c>
       <c r="C556" t="s">
-        <v>512</v>
+        <v>168</v>
       </c>
     </row>
     <row r="557" spans="1:3">
@@ -11596,10 +11617,10 @@
         <v>6</v>
       </c>
       <c r="B557" t="s">
-        <v>662</v>
+        <v>169</v>
       </c>
       <c r="C557" t="s">
-        <v>664</v>
+        <v>170</v>
       </c>
     </row>
     <row r="558" spans="1:3">
@@ -11607,10 +11628,10 @@
         <v>6</v>
       </c>
       <c r="B558" t="s">
-        <v>694</v>
+        <v>287</v>
       </c>
       <c r="C558" t="s">
-        <v>695</v>
+        <v>288</v>
       </c>
     </row>
     <row r="559" spans="1:3">
@@ -11618,10 +11639,10 @@
         <v>6</v>
       </c>
       <c r="B559" t="s">
-        <v>715</v>
+        <v>490</v>
       </c>
       <c r="C559" t="s">
-        <v>716</v>
+        <v>491</v>
       </c>
     </row>
     <row r="560" spans="1:3">
@@ -11629,10 +11650,10 @@
         <v>6</v>
       </c>
       <c r="B560" t="s">
-        <v>721</v>
+        <v>511</v>
       </c>
       <c r="C560" t="s">
-        <v>722</v>
+        <v>512</v>
       </c>
     </row>
     <row r="561" spans="1:3">
@@ -11640,10 +11661,10 @@
         <v>6</v>
       </c>
       <c r="B561" t="s">
-        <v>741</v>
+        <v>662</v>
       </c>
       <c r="C561" t="s">
-        <v>742</v>
+        <v>664</v>
       </c>
     </row>
     <row r="562" spans="1:3">
@@ -11651,10 +11672,10 @@
         <v>6</v>
       </c>
       <c r="B562" t="s">
-        <v>743</v>
+        <v>694</v>
       </c>
       <c r="C562" t="s">
-        <v>744</v>
+        <v>695</v>
       </c>
     </row>
     <row r="563" spans="1:3">
@@ -11662,10 +11683,10 @@
         <v>6</v>
       </c>
       <c r="B563" t="s">
-        <v>754</v>
+        <v>715</v>
       </c>
       <c r="C563" t="s">
-        <v>756</v>
+        <v>716</v>
       </c>
     </row>
     <row r="564" spans="1:3">
@@ -11673,10 +11694,10 @@
         <v>6</v>
       </c>
       <c r="B564" t="s">
-        <v>942</v>
+        <v>721</v>
       </c>
       <c r="C564" t="s">
-        <v>943</v>
+        <v>722</v>
       </c>
     </row>
     <row r="565" spans="1:3">
@@ -11684,10 +11705,10 @@
         <v>6</v>
       </c>
       <c r="B565" t="s">
-        <v>1018</v>
+        <v>741</v>
       </c>
       <c r="C565" t="s">
-        <v>1020</v>
+        <v>742</v>
       </c>
     </row>
     <row r="566" spans="1:3">
@@ -11695,10 +11716,10 @@
         <v>6</v>
       </c>
       <c r="B566" t="s">
-        <v>1104</v>
+        <v>743</v>
       </c>
       <c r="C566" t="s">
-        <v>1105</v>
+        <v>744</v>
       </c>
     </row>
     <row r="567" spans="1:3">
@@ -11706,10 +11727,10 @@
         <v>6</v>
       </c>
       <c r="B567" t="s">
-        <v>1273</v>
+        <v>754</v>
       </c>
       <c r="C567" t="s">
-        <v>1274</v>
+        <v>756</v>
       </c>
     </row>
     <row r="568" spans="1:3">
@@ -11717,10 +11738,10 @@
         <v>6</v>
       </c>
       <c r="B568" t="s">
-        <v>1288</v>
+        <v>942</v>
       </c>
       <c r="C568" t="s">
-        <v>1290</v>
+        <v>943</v>
       </c>
     </row>
     <row r="569" spans="1:3">
@@ -11728,10 +11749,10 @@
         <v>6</v>
       </c>
       <c r="B569" t="s">
-        <v>1297</v>
+        <v>1018</v>
       </c>
       <c r="C569" t="s">
-        <v>1298</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="570" spans="1:3">
@@ -11739,54 +11760,54 @@
         <v>6</v>
       </c>
       <c r="B570" t="s">
-        <v>1301</v>
+        <v>1104</v>
       </c>
       <c r="C570" t="s">
-        <v>1303</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="571" spans="1:3">
       <c r="A571" t="s">
-        <v>9</v>
-      </c>
-      <c r="B571">
         <v>6</v>
       </c>
+      <c r="B571" t="s">
+        <v>1273</v>
+      </c>
       <c r="C571" t="s">
-        <v>1468</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="572" spans="1:3">
       <c r="A572" t="s">
-        <v>9</v>
-      </c>
-      <c r="B572">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="B572" t="s">
+        <v>1288</v>
       </c>
       <c r="C572" t="s">
-        <v>1474</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="573" spans="1:3">
       <c r="A573" t="s">
-        <v>9</v>
-      </c>
-      <c r="B573">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="B573" t="s">
+        <v>1297</v>
       </c>
       <c r="C573" t="s">
-        <v>1479</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="574" spans="1:3">
       <c r="A574" t="s">
-        <v>9</v>
-      </c>
-      <c r="B574">
-        <v>9</v>
+        <v>6</v>
+      </c>
+      <c r="B574" t="s">
+        <v>1301</v>
       </c>
       <c r="C574" t="s">
-        <v>1483</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="575" spans="1:3">
@@ -11794,10 +11815,10 @@
         <v>9</v>
       </c>
       <c r="B575">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C575" t="s">
-        <v>1491</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="576" spans="1:3">
@@ -11805,10 +11826,10 @@
         <v>9</v>
       </c>
       <c r="B576">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C576" t="s">
-        <v>1495</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="577" spans="1:3">
@@ -11816,10 +11837,10 @@
         <v>9</v>
       </c>
       <c r="B577">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C577" t="s">
-        <v>1498</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="578" spans="1:3">
@@ -11827,10 +11848,10 @@
         <v>9</v>
       </c>
       <c r="B578">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C578" t="s">
-        <v>1501</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="579" spans="1:3">
@@ -11838,10 +11859,10 @@
         <v>9</v>
       </c>
       <c r="B579">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C579" t="s">
-        <v>1504</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="580" spans="1:3">
@@ -11849,10 +11870,10 @@
         <v>9</v>
       </c>
       <c r="B580">
-        <v>106</v>
+        <v>12</v>
       </c>
       <c r="C580" t="s">
-        <v>1612</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="581" spans="1:3">
@@ -11860,10 +11881,10 @@
         <v>9</v>
       </c>
       <c r="B581">
-        <v>115</v>
+        <v>13</v>
       </c>
       <c r="C581" t="s">
-        <v>1624</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="582" spans="1:3">
@@ -11871,54 +11892,54 @@
         <v>9</v>
       </c>
       <c r="B582">
-        <v>202</v>
+        <v>14</v>
       </c>
       <c r="C582" t="s">
-        <v>1636</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="583" spans="1:3">
       <c r="A583" t="s">
         <v>9</v>
       </c>
-      <c r="B583" t="s">
-        <v>1667</v>
+      <c r="B583">
+        <v>15</v>
       </c>
       <c r="C583" t="s">
-        <v>1668</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="584" spans="1:3">
       <c r="A584" t="s">
         <v>9</v>
       </c>
-      <c r="B584" t="s">
-        <v>1669</v>
+      <c r="B584">
+        <v>106</v>
       </c>
       <c r="C584" t="s">
-        <v>1670</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="585" spans="1:3">
       <c r="A585" t="s">
         <v>9</v>
       </c>
-      <c r="B585" t="s">
-        <v>10</v>
+      <c r="B585">
+        <v>115</v>
       </c>
       <c r="C585" t="s">
-        <v>11</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="586" spans="1:3">
       <c r="A586" t="s">
         <v>9</v>
       </c>
-      <c r="B586" t="s">
-        <v>12</v>
+      <c r="B586">
+        <v>202</v>
       </c>
       <c r="C586" t="s">
-        <v>13</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="587" spans="1:3">
@@ -11926,10 +11947,10 @@
         <v>9</v>
       </c>
       <c r="B587" t="s">
-        <v>18</v>
+        <v>1667</v>
       </c>
       <c r="C587" t="s">
-        <v>19</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="588" spans="1:3">
@@ -11937,10 +11958,10 @@
         <v>9</v>
       </c>
       <c r="B588" t="s">
-        <v>20</v>
+        <v>1669</v>
       </c>
       <c r="C588" t="s">
-        <v>21</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="589" spans="1:3">
@@ -11948,10 +11969,10 @@
         <v>9</v>
       </c>
       <c r="B589" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C589" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="590" spans="1:3">
@@ -11959,10 +11980,10 @@
         <v>9</v>
       </c>
       <c r="B590" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C590" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="591" spans="1:3">
@@ -11970,10 +11991,10 @@
         <v>9</v>
       </c>
       <c r="B591" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="C591" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="592" spans="1:3">
@@ -11981,10 +12002,10 @@
         <v>9</v>
       </c>
       <c r="B592" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="C592" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
     <row r="593" spans="1:3">
@@ -11992,10 +12013,10 @@
         <v>9</v>
       </c>
       <c r="B593" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="C593" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
     </row>
     <row r="594" spans="1:3">
@@ -12003,10 +12024,10 @@
         <v>9</v>
       </c>
       <c r="B594" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="C594" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
     </row>
     <row r="595" spans="1:3">
@@ -12014,10 +12035,10 @@
         <v>9</v>
       </c>
       <c r="B595" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C595" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
     </row>
     <row r="596" spans="1:3">
@@ -12025,10 +12046,10 @@
         <v>9</v>
       </c>
       <c r="B596" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C596" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="597" spans="1:3">
@@ -12036,10 +12057,10 @@
         <v>9</v>
       </c>
       <c r="B597" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C597" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
     </row>
     <row r="598" spans="1:3">
@@ -12047,10 +12068,10 @@
         <v>9</v>
       </c>
       <c r="B598" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="C598" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
     </row>
     <row r="599" spans="1:3">
@@ -12058,10 +12079,10 @@
         <v>9</v>
       </c>
       <c r="B599" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C599" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="600" spans="1:3">
@@ -12069,10 +12090,10 @@
         <v>9</v>
       </c>
       <c r="B600" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C600" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="601" spans="1:3">
@@ -12080,10 +12101,10 @@
         <v>9</v>
       </c>
       <c r="B601" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="C601" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
     </row>
     <row r="602" spans="1:3">
@@ -12091,10 +12112,10 @@
         <v>9</v>
       </c>
       <c r="B602" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C602" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="603" spans="1:3">
@@ -12102,10 +12123,10 @@
         <v>9</v>
       </c>
       <c r="B603" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C603" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="604" spans="1:3">
@@ -12113,10 +12134,10 @@
         <v>9</v>
       </c>
       <c r="B604" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="C604" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
     </row>
     <row r="605" spans="1:3">
@@ -12124,10 +12145,10 @@
         <v>9</v>
       </c>
       <c r="B605" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="C605" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
     </row>
     <row r="606" spans="1:3">
@@ -12135,10 +12156,10 @@
         <v>9</v>
       </c>
       <c r="B606" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="C606" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
     </row>
     <row r="607" spans="1:3">
@@ -12146,10 +12167,10 @@
         <v>9</v>
       </c>
       <c r="B607" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="C607" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
     </row>
     <row r="608" spans="1:3">
@@ -12157,10 +12178,10 @@
         <v>9</v>
       </c>
       <c r="B608" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="C608" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
     </row>
     <row r="609" spans="1:3">
@@ -12168,10 +12189,10 @@
         <v>9</v>
       </c>
       <c r="B609" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="C609" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
     </row>
     <row r="610" spans="1:3">
@@ -12179,10 +12200,10 @@
         <v>9</v>
       </c>
       <c r="B610" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="C610" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
     </row>
     <row r="611" spans="1:3">
@@ -12190,10 +12211,10 @@
         <v>9</v>
       </c>
       <c r="B611" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="C611" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="612" spans="1:3">
@@ -12201,10 +12222,10 @@
         <v>9</v>
       </c>
       <c r="B612" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="C612" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
     </row>
     <row r="613" spans="1:3">
@@ -12212,10 +12233,10 @@
         <v>9</v>
       </c>
       <c r="B613" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C613" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
     </row>
     <row r="614" spans="1:3">
@@ -12223,10 +12244,10 @@
         <v>9</v>
       </c>
       <c r="B614" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="C614" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
     </row>
     <row r="615" spans="1:3">
@@ -12234,10 +12255,10 @@
         <v>9</v>
       </c>
       <c r="B615" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="C615" t="s">
-        <v>19</v>
+        <v>101</v>
       </c>
     </row>
     <row r="616" spans="1:3">
@@ -12245,10 +12266,10 @@
         <v>9</v>
       </c>
       <c r="B616" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="C616" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
     </row>
     <row r="617" spans="1:3">
@@ -12256,10 +12277,10 @@
         <v>9</v>
       </c>
       <c r="B617" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="C617" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
     </row>
     <row r="618" spans="1:3">
@@ -12267,10 +12288,10 @@
         <v>9</v>
       </c>
       <c r="B618" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="C618" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
     </row>
     <row r="619" spans="1:3">
@@ -12278,10 +12299,10 @@
         <v>9</v>
       </c>
       <c r="B619" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="C619" t="s">
-        <v>131</v>
+        <v>19</v>
       </c>
     </row>
     <row r="620" spans="1:3">
@@ -12289,10 +12310,10 @@
         <v>9</v>
       </c>
       <c r="B620" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="C620" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
     </row>
     <row r="621" spans="1:3">
@@ -12300,10 +12321,10 @@
         <v>9</v>
       </c>
       <c r="B621" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="C621" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
     </row>
     <row r="622" spans="1:3">
@@ -12311,10 +12332,10 @@
         <v>9</v>
       </c>
       <c r="B622" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="C622" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
     </row>
     <row r="623" spans="1:3">
@@ -12322,10 +12343,10 @@
         <v>9</v>
       </c>
       <c r="B623" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="C623" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
     </row>
     <row r="624" spans="1:3">
@@ -12333,10 +12354,10 @@
         <v>9</v>
       </c>
       <c r="B624" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="C624" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
     </row>
     <row r="625" spans="1:3">
@@ -12344,10 +12365,10 @@
         <v>9</v>
       </c>
       <c r="B625" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="C625" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
     </row>
     <row r="626" spans="1:3">
@@ -12355,10 +12376,10 @@
         <v>9</v>
       </c>
       <c r="B626" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="C626" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
     </row>
     <row r="627" spans="1:3">
@@ -12366,10 +12387,10 @@
         <v>9</v>
       </c>
       <c r="B627" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="C627" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="628" spans="1:3">
@@ -12377,10 +12398,10 @@
         <v>9</v>
       </c>
       <c r="B628" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="C628" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
     </row>
     <row r="629" spans="1:3">
@@ -12388,10 +12409,10 @@
         <v>9</v>
       </c>
       <c r="B629" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="C629" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
     </row>
     <row r="630" spans="1:3">
@@ -12399,10 +12420,10 @@
         <v>9</v>
       </c>
       <c r="B630" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="C630" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
     </row>
     <row r="631" spans="1:3">
@@ -12410,10 +12431,10 @@
         <v>9</v>
       </c>
       <c r="B631" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="C631" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
     </row>
     <row r="632" spans="1:3">
@@ -12421,10 +12442,10 @@
         <v>9</v>
       </c>
       <c r="B632" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="C632" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
     </row>
     <row r="633" spans="1:3">
@@ -12432,10 +12453,10 @@
         <v>9</v>
       </c>
       <c r="B633" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="C633" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
     </row>
     <row r="634" spans="1:3">
@@ -12443,10 +12464,10 @@
         <v>9</v>
       </c>
       <c r="B634" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="C634" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
     </row>
     <row r="635" spans="1:3">
@@ -12454,10 +12475,10 @@
         <v>9</v>
       </c>
       <c r="B635" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="C635" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
     </row>
     <row r="636" spans="1:3">
@@ -12465,10 +12486,10 @@
         <v>9</v>
       </c>
       <c r="B636" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="C636" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
     </row>
     <row r="637" spans="1:3">
@@ -12476,10 +12497,10 @@
         <v>9</v>
       </c>
       <c r="B637" t="s">
-        <v>213</v>
+        <v>194</v>
       </c>
       <c r="C637" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
     </row>
     <row r="638" spans="1:3">
@@ -12487,10 +12508,10 @@
         <v>9</v>
       </c>
       <c r="B638" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="C638" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
     </row>
     <row r="639" spans="1:3">
@@ -12498,10 +12519,10 @@
         <v>9</v>
       </c>
       <c r="B639" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="C639" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
     </row>
     <row r="640" spans="1:3">
@@ -12509,10 +12530,10 @@
         <v>9</v>
       </c>
       <c r="B640" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="C640" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
     </row>
     <row r="641" spans="1:3">
@@ -12520,10 +12541,10 @@
         <v>9</v>
       </c>
       <c r="B641" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="C641" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
     </row>
     <row r="642" spans="1:3">
@@ -12531,10 +12552,10 @@
         <v>9</v>
       </c>
       <c r="B642" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="C642" t="s">
-        <v>19</v>
+        <v>216</v>
       </c>
     </row>
     <row r="643" spans="1:3">
@@ -12542,10 +12563,10 @@
         <v>9</v>
       </c>
       <c r="B643" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="C643" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
     </row>
     <row r="644" spans="1:3">
@@ -12553,10 +12574,10 @@
         <v>9</v>
       </c>
       <c r="B644" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="C644" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
     </row>
     <row r="645" spans="1:3">
@@ -12564,10 +12585,10 @@
         <v>9</v>
       </c>
       <c r="B645" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="C645" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
     </row>
     <row r="646" spans="1:3">
@@ -12575,10 +12596,10 @@
         <v>9</v>
       </c>
       <c r="B646" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="C646" t="s">
-        <v>246</v>
+        <v>19</v>
       </c>
     </row>
     <row r="647" spans="1:3">
@@ -12586,10 +12607,10 @@
         <v>9</v>
       </c>
       <c r="B647" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="C647" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
     </row>
     <row r="648" spans="1:3">
@@ -12597,10 +12618,10 @@
         <v>9</v>
       </c>
       <c r="B648" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="C648" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
     </row>
     <row r="649" spans="1:3">
@@ -12608,10 +12629,10 @@
         <v>9</v>
       </c>
       <c r="B649" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="C649" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
     </row>
     <row r="650" spans="1:3">
@@ -12619,10 +12640,10 @@
         <v>9</v>
       </c>
       <c r="B650" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="C650" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
     </row>
     <row r="651" spans="1:3">
@@ -12630,10 +12651,10 @@
         <v>9</v>
       </c>
       <c r="B651" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="C651" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
     </row>
     <row r="652" spans="1:3">
@@ -12641,10 +12662,10 @@
         <v>9</v>
       </c>
       <c r="B652" t="s">
-        <v>271</v>
+        <v>249</v>
       </c>
       <c r="C652" t="s">
-        <v>272</v>
+        <v>250</v>
       </c>
     </row>
     <row r="653" spans="1:3">
@@ -12652,10 +12673,10 @@
         <v>9</v>
       </c>
       <c r="B653" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="C653" t="s">
-        <v>274</v>
+        <v>256</v>
       </c>
     </row>
     <row r="654" spans="1:3">
@@ -12663,10 +12684,10 @@
         <v>9</v>
       </c>
       <c r="B654" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="C654" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
     </row>
     <row r="655" spans="1:3">
@@ -12674,10 +12695,10 @@
         <v>9</v>
       </c>
       <c r="B655" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="C655" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
     </row>
     <row r="656" spans="1:3">
@@ -12685,10 +12706,10 @@
         <v>9</v>
       </c>
       <c r="B656" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="C656" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
     </row>
     <row r="657" spans="1:3">
@@ -12696,10 +12717,10 @@
         <v>9</v>
       </c>
       <c r="B657" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="C657" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
     </row>
     <row r="658" spans="1:3">
@@ -12707,10 +12728,10 @@
         <v>9</v>
       </c>
       <c r="B658" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="C658" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
     </row>
     <row r="659" spans="1:3">
@@ -12718,10 +12739,10 @@
         <v>9</v>
       </c>
       <c r="B659" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="C659" t="s">
-        <v>292</v>
+        <v>278</v>
       </c>
     </row>
     <row r="660" spans="1:3">
@@ -12729,10 +12750,10 @@
         <v>9</v>
       </c>
       <c r="B660" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="C660" t="s">
-        <v>294</v>
+        <v>280</v>
       </c>
     </row>
     <row r="661" spans="1:3">
@@ -12740,10 +12761,10 @@
         <v>9</v>
       </c>
       <c r="B661" t="s">
-        <v>295</v>
+        <v>281</v>
       </c>
       <c r="C661" t="s">
-        <v>296</v>
+        <v>282</v>
       </c>
     </row>
     <row r="662" spans="1:3">
@@ -12751,10 +12772,10 @@
         <v>9</v>
       </c>
       <c r="B662" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="C662" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
     </row>
     <row r="663" spans="1:3">
@@ -12762,10 +12783,10 @@
         <v>9</v>
       </c>
       <c r="B663" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="C663" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
     </row>
     <row r="664" spans="1:3">
@@ -12773,10 +12794,10 @@
         <v>9</v>
       </c>
       <c r="B664" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="C664" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
     </row>
     <row r="665" spans="1:3">
@@ -12784,10 +12805,10 @@
         <v>9</v>
       </c>
       <c r="B665" t="s">
-        <v>308</v>
+        <v>295</v>
       </c>
       <c r="C665" t="s">
-        <v>309</v>
+        <v>296</v>
       </c>
     </row>
     <row r="666" spans="1:3">
@@ -12795,10 +12816,10 @@
         <v>9</v>
       </c>
       <c r="B666" t="s">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="C666" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
     </row>
     <row r="667" spans="1:3">
@@ -12806,10 +12827,10 @@
         <v>9</v>
       </c>
       <c r="B667" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="C667" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
     </row>
     <row r="668" spans="1:3">
@@ -12817,10 +12838,10 @@
         <v>9</v>
       </c>
       <c r="B668" t="s">
-        <v>36</v>
+        <v>304</v>
       </c>
       <c r="C668" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
     </row>
     <row r="669" spans="1:3">
@@ -12828,10 +12849,10 @@
         <v>9</v>
       </c>
       <c r="B669" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="C669" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
     </row>
     <row r="670" spans="1:3">
@@ -12839,10 +12860,10 @@
         <v>9</v>
       </c>
       <c r="B670" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="C670" t="s">
-        <v>328</v>
+        <v>311</v>
       </c>
     </row>
     <row r="671" spans="1:3">
@@ -12850,10 +12871,10 @@
         <v>9</v>
       </c>
       <c r="B671" t="s">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="C671" t="s">
-        <v>330</v>
+        <v>313</v>
       </c>
     </row>
     <row r="672" spans="1:3">
@@ -12861,10 +12882,10 @@
         <v>9</v>
       </c>
       <c r="B672" t="s">
-        <v>331</v>
+        <v>36</v>
       </c>
       <c r="C672" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
     </row>
     <row r="673" spans="1:3">
@@ -12872,10 +12893,10 @@
         <v>9</v>
       </c>
       <c r="B673" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="C673" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
     </row>
     <row r="674" spans="1:3">
@@ -12883,10 +12904,10 @@
         <v>9</v>
       </c>
       <c r="B674" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="C674" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
     </row>
     <row r="675" spans="1:3">
@@ -12894,10 +12915,10 @@
         <v>9</v>
       </c>
       <c r="B675" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="C675" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
     </row>
     <row r="676" spans="1:3">
@@ -12905,10 +12926,10 @@
         <v>9</v>
       </c>
       <c r="B676" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="C676" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
     </row>
     <row r="677" spans="1:3">
@@ -12916,10 +12937,10 @@
         <v>9</v>
       </c>
       <c r="B677" t="s">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="C677" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
     </row>
     <row r="678" spans="1:3">
@@ -12927,10 +12948,10 @@
         <v>9</v>
       </c>
       <c r="B678" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="C678" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
     </row>
     <row r="679" spans="1:3">
@@ -12938,10 +12959,10 @@
         <v>9</v>
       </c>
       <c r="B679" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="C679" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
     </row>
     <row r="680" spans="1:3">
@@ -12949,10 +12970,10 @@
         <v>9</v>
       </c>
       <c r="B680" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="C680" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
     </row>
     <row r="681" spans="1:3">
@@ -12960,10 +12981,10 @@
         <v>9</v>
       </c>
       <c r="B681" t="s">
-        <v>366</v>
+        <v>348</v>
       </c>
       <c r="C681" t="s">
-        <v>368</v>
+        <v>349</v>
       </c>
     </row>
     <row r="682" spans="1:3">
@@ -12971,10 +12992,10 @@
         <v>9</v>
       </c>
       <c r="B682" t="s">
-        <v>377</v>
+        <v>350</v>
       </c>
       <c r="C682" t="s">
-        <v>378</v>
+        <v>351</v>
       </c>
     </row>
     <row r="683" spans="1:3">
@@ -12982,10 +13003,10 @@
         <v>9</v>
       </c>
       <c r="B683" t="s">
-        <v>377</v>
+        <v>352</v>
       </c>
       <c r="C683" t="s">
-        <v>379</v>
+        <v>353</v>
       </c>
     </row>
     <row r="684" spans="1:3">
@@ -12993,10 +13014,10 @@
         <v>9</v>
       </c>
       <c r="B684" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="C684" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
     </row>
     <row r="685" spans="1:3">
@@ -13004,10 +13025,10 @@
         <v>9</v>
       </c>
       <c r="B685" t="s">
-        <v>388</v>
+        <v>366</v>
       </c>
       <c r="C685" t="s">
-        <v>389</v>
+        <v>368</v>
       </c>
     </row>
     <row r="686" spans="1:3">
@@ -13015,10 +13036,10 @@
         <v>9</v>
       </c>
       <c r="B686" t="s">
-        <v>390</v>
+        <v>377</v>
       </c>
       <c r="C686" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
     </row>
     <row r="687" spans="1:3">
@@ -13026,10 +13047,10 @@
         <v>9</v>
       </c>
       <c r="B687" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="C687" t="s">
-        <v>393</v>
+        <v>379</v>
       </c>
     </row>
     <row r="688" spans="1:3">
@@ -13037,10 +13058,10 @@
         <v>9</v>
       </c>
       <c r="B688" t="s">
-        <v>401</v>
+        <v>380</v>
       </c>
       <c r="C688" t="s">
-        <v>402</v>
+        <v>381</v>
       </c>
     </row>
     <row r="689" spans="1:3">
@@ -13048,10 +13069,10 @@
         <v>9</v>
       </c>
       <c r="B689" t="s">
-        <v>407</v>
+        <v>388</v>
       </c>
       <c r="C689" t="s">
-        <v>409</v>
+        <v>389</v>
       </c>
     </row>
     <row r="690" spans="1:3">
@@ -13059,10 +13080,10 @@
         <v>9</v>
       </c>
       <c r="B690" t="s">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="C690" t="s">
-        <v>411</v>
+        <v>391</v>
       </c>
     </row>
     <row r="691" spans="1:3">
@@ -13070,10 +13091,10 @@
         <v>9</v>
       </c>
       <c r="B691" t="s">
-        <v>412</v>
+        <v>392</v>
       </c>
       <c r="C691" t="s">
-        <v>413</v>
+        <v>393</v>
       </c>
     </row>
     <row r="692" spans="1:3">
@@ -13081,10 +13102,10 @@
         <v>9</v>
       </c>
       <c r="B692" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="C692" t="s">
-        <v>415</v>
+        <v>402</v>
       </c>
     </row>
     <row r="693" spans="1:3">
@@ -13092,10 +13113,10 @@
         <v>9</v>
       </c>
       <c r="B693" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="C693" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
     </row>
     <row r="694" spans="1:3">
@@ -13103,10 +13124,10 @@
         <v>9</v>
       </c>
       <c r="B694" t="s">
-        <v>428</v>
+        <v>410</v>
       </c>
       <c r="C694" t="s">
-        <v>429</v>
+        <v>411</v>
       </c>
     </row>
     <row r="695" spans="1:3">
@@ -13114,10 +13135,10 @@
         <v>9</v>
       </c>
       <c r="B695" t="s">
-        <v>433</v>
+        <v>412</v>
       </c>
       <c r="C695" t="s">
-        <v>435</v>
+        <v>413</v>
       </c>
     </row>
     <row r="696" spans="1:3">
@@ -13125,10 +13146,10 @@
         <v>9</v>
       </c>
       <c r="B696" t="s">
-        <v>436</v>
+        <v>414</v>
       </c>
       <c r="C696" t="s">
-        <v>437</v>
+        <v>415</v>
       </c>
     </row>
     <row r="697" spans="1:3">
@@ -13136,10 +13157,10 @@
         <v>9</v>
       </c>
       <c r="B697" t="s">
-        <v>438</v>
+        <v>416</v>
       </c>
       <c r="C697" t="s">
-        <v>439</v>
+        <v>417</v>
       </c>
     </row>
     <row r="698" spans="1:3">
@@ -13147,10 +13168,10 @@
         <v>9</v>
       </c>
       <c r="B698" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="C698" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
     </row>
     <row r="699" spans="1:3">
@@ -13158,10 +13179,10 @@
         <v>9</v>
       </c>
       <c r="B699" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="C699" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
     </row>
     <row r="700" spans="1:3">
@@ -13169,10 +13190,10 @@
         <v>9</v>
       </c>
       <c r="B700" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="C700" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
     </row>
     <row r="701" spans="1:3">
@@ -13180,10 +13201,10 @@
         <v>9</v>
       </c>
       <c r="B701" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="C701" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
     </row>
     <row r="702" spans="1:3">
@@ -13191,10 +13212,10 @@
         <v>9</v>
       </c>
       <c r="B702" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="C702" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
     </row>
     <row r="703" spans="1:3">
@@ -13202,10 +13223,10 @@
         <v>9</v>
       </c>
       <c r="B703" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="C703" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
     </row>
     <row r="704" spans="1:3">
@@ -13213,10 +13234,10 @@
         <v>9</v>
       </c>
       <c r="B704" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="C704" t="s">
-        <v>457</v>
+        <v>446</v>
       </c>
     </row>
     <row r="705" spans="1:3">
@@ -13224,10 +13245,10 @@
         <v>9</v>
       </c>
       <c r="B705" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="C705" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
     </row>
     <row r="706" spans="1:3">
@@ -13235,10 +13256,10 @@
         <v>9</v>
       </c>
       <c r="B706" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="C706" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
     </row>
     <row r="707" spans="1:3">
@@ -13246,10 +13267,10 @@
         <v>9</v>
       </c>
       <c r="B707" t="s">
-        <v>466</v>
+        <v>454</v>
       </c>
       <c r="C707" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
     </row>
     <row r="708" spans="1:3">
@@ -13257,10 +13278,10 @@
         <v>9</v>
       </c>
       <c r="B708" t="s">
-        <v>470</v>
+        <v>456</v>
       </c>
       <c r="C708" t="s">
-        <v>471</v>
+        <v>457</v>
       </c>
     </row>
     <row r="709" spans="1:3">
@@ -13268,10 +13289,10 @@
         <v>9</v>
       </c>
       <c r="B709" t="s">
-        <v>474</v>
+        <v>458</v>
       </c>
       <c r="C709" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
     </row>
     <row r="710" spans="1:3">
@@ -13279,10 +13300,10 @@
         <v>9</v>
       </c>
       <c r="B710" t="s">
-        <v>476</v>
+        <v>460</v>
       </c>
       <c r="C710" t="s">
-        <v>477</v>
+        <v>461</v>
       </c>
     </row>
     <row r="711" spans="1:3">
@@ -13290,10 +13311,10 @@
         <v>9</v>
       </c>
       <c r="B711" t="s">
-        <v>484</v>
+        <v>466</v>
       </c>
       <c r="C711" t="s">
-        <v>485</v>
+        <v>467</v>
       </c>
     </row>
     <row r="712" spans="1:3">
@@ -13301,10 +13322,10 @@
         <v>9</v>
       </c>
       <c r="B712" t="s">
-        <v>488</v>
+        <v>470</v>
       </c>
       <c r="C712" t="s">
-        <v>489</v>
+        <v>471</v>
       </c>
     </row>
     <row r="713" spans="1:3">
@@ -13312,10 +13333,10 @@
         <v>9</v>
       </c>
       <c r="B713" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="C713" t="s">
-        <v>493</v>
+        <v>475</v>
       </c>
     </row>
     <row r="714" spans="1:3">
@@ -13323,10 +13344,10 @@
         <v>9</v>
       </c>
       <c r="B714" t="s">
-        <v>496</v>
+        <v>476</v>
       </c>
       <c r="C714" t="s">
-        <v>497</v>
+        <v>477</v>
       </c>
     </row>
     <row r="715" spans="1:3">
@@ -13334,10 +13355,10 @@
         <v>9</v>
       </c>
       <c r="B715" t="s">
-        <v>498</v>
+        <v>484</v>
       </c>
       <c r="C715" t="s">
-        <v>499</v>
+        <v>485</v>
       </c>
     </row>
     <row r="716" spans="1:3">
@@ -13345,10 +13366,10 @@
         <v>9</v>
       </c>
       <c r="B716" t="s">
-        <v>507</v>
+        <v>488</v>
       </c>
       <c r="C716" t="s">
-        <v>508</v>
+        <v>489</v>
       </c>
     </row>
     <row r="717" spans="1:3">
@@ -13356,10 +13377,10 @@
         <v>9</v>
       </c>
       <c r="B717" t="s">
-        <v>515</v>
+        <v>492</v>
       </c>
       <c r="C717" t="s">
-        <v>516</v>
+        <v>493</v>
       </c>
     </row>
     <row r="718" spans="1:3">
@@ -13367,10 +13388,10 @@
         <v>9</v>
       </c>
       <c r="B718" t="s">
-        <v>517</v>
+        <v>496</v>
       </c>
       <c r="C718" t="s">
-        <v>518</v>
+        <v>497</v>
       </c>
     </row>
     <row r="719" spans="1:3">
@@ -13378,10 +13399,10 @@
         <v>9</v>
       </c>
       <c r="B719" t="s">
-        <v>8</v>
+        <v>498</v>
       </c>
       <c r="C719" t="s">
-        <v>520</v>
+        <v>499</v>
       </c>
     </row>
     <row r="720" spans="1:3">
@@ -13389,10 +13410,10 @@
         <v>9</v>
       </c>
       <c r="B720" t="s">
-        <v>521</v>
+        <v>507</v>
       </c>
       <c r="C720" t="s">
-        <v>522</v>
+        <v>508</v>
       </c>
     </row>
     <row r="721" spans="1:3">
@@ -13400,10 +13421,10 @@
         <v>9</v>
       </c>
       <c r="B721" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="C721" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
     </row>
     <row r="722" spans="1:3">
@@ -13411,10 +13432,10 @@
         <v>9</v>
       </c>
       <c r="B722" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="C722" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
     </row>
     <row r="723" spans="1:3">
@@ -13422,10 +13443,10 @@
         <v>9</v>
       </c>
       <c r="B723" t="s">
-        <v>533</v>
+        <v>8</v>
       </c>
       <c r="C723" t="s">
-        <v>534</v>
+        <v>520</v>
       </c>
     </row>
     <row r="724" spans="1:3">
@@ -13433,10 +13454,10 @@
         <v>9</v>
       </c>
       <c r="B724" t="s">
-        <v>535</v>
+        <v>521</v>
       </c>
       <c r="C724" t="s">
-        <v>536</v>
+        <v>522</v>
       </c>
     </row>
     <row r="725" spans="1:3">
@@ -13444,10 +13465,10 @@
         <v>9</v>
       </c>
       <c r="B725" t="s">
-        <v>539</v>
+        <v>525</v>
       </c>
       <c r="C725" t="s">
-        <v>540</v>
+        <v>526</v>
       </c>
     </row>
     <row r="726" spans="1:3">
@@ -13455,10 +13476,10 @@
         <v>9</v>
       </c>
       <c r="B726" t="s">
-        <v>541</v>
+        <v>527</v>
       </c>
       <c r="C726" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
     </row>
     <row r="727" spans="1:3">
@@ -13466,10 +13487,10 @@
         <v>9</v>
       </c>
       <c r="B727" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="C727" t="s">
-        <v>544</v>
+        <v>534</v>
       </c>
     </row>
     <row r="728" spans="1:3">
@@ -13477,10 +13498,10 @@
         <v>9</v>
       </c>
       <c r="B728" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="C728" t="s">
-        <v>549</v>
+        <v>536</v>
       </c>
     </row>
     <row r="729" spans="1:3">
@@ -13488,10 +13509,10 @@
         <v>9</v>
       </c>
       <c r="B729" t="s">
-        <v>557</v>
+        <v>539</v>
       </c>
       <c r="C729" t="s">
-        <v>558</v>
+        <v>540</v>
       </c>
     </row>
     <row r="730" spans="1:3">
@@ -13499,10 +13520,10 @@
         <v>9</v>
       </c>
       <c r="B730" t="s">
-        <v>561</v>
+        <v>541</v>
       </c>
       <c r="C730" t="s">
-        <v>563</v>
+        <v>542</v>
       </c>
     </row>
     <row r="731" spans="1:3">
@@ -13510,10 +13531,10 @@
         <v>9</v>
       </c>
       <c r="B731" t="s">
-        <v>564</v>
+        <v>543</v>
       </c>
       <c r="C731" t="s">
-        <v>565</v>
+        <v>544</v>
       </c>
     </row>
     <row r="732" spans="1:3">
@@ -13521,10 +13542,10 @@
         <v>9</v>
       </c>
       <c r="B732" t="s">
-        <v>568</v>
+        <v>547</v>
       </c>
       <c r="C732" t="s">
-        <v>569</v>
+        <v>549</v>
       </c>
     </row>
     <row r="733" spans="1:3">
@@ -13532,10 +13553,10 @@
         <v>9</v>
       </c>
       <c r="B733" t="s">
-        <v>588</v>
+        <v>557</v>
       </c>
       <c r="C733" t="s">
-        <v>589</v>
+        <v>558</v>
       </c>
     </row>
     <row r="734" spans="1:3">
@@ -13543,10 +13564,10 @@
         <v>9</v>
       </c>
       <c r="B734" t="s">
-        <v>600</v>
+        <v>561</v>
       </c>
       <c r="C734" t="s">
-        <v>602</v>
+        <v>563</v>
       </c>
     </row>
     <row r="735" spans="1:3">
@@ -13554,10 +13575,10 @@
         <v>9</v>
       </c>
       <c r="B735" t="s">
-        <v>603</v>
+        <v>564</v>
       </c>
       <c r="C735" t="s">
-        <v>604</v>
+        <v>565</v>
       </c>
     </row>
     <row r="736" spans="1:3">
@@ -13565,10 +13586,10 @@
         <v>9</v>
       </c>
       <c r="B736" t="s">
-        <v>605</v>
+        <v>568</v>
       </c>
       <c r="C736" t="s">
-        <v>607</v>
+        <v>569</v>
       </c>
     </row>
     <row r="737" spans="1:3">
@@ -13576,10 +13597,10 @@
         <v>9</v>
       </c>
       <c r="B737" t="s">
-        <v>608</v>
+        <v>588</v>
       </c>
       <c r="C737" t="s">
-        <v>609</v>
+        <v>589</v>
       </c>
     </row>
     <row r="738" spans="1:3">
@@ -13587,10 +13608,10 @@
         <v>9</v>
       </c>
       <c r="B738" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="C738" t="s">
-        <v>613</v>
+        <v>602</v>
       </c>
     </row>
     <row r="739" spans="1:3">
@@ -13598,10 +13619,10 @@
         <v>9</v>
       </c>
       <c r="B739" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="C739" t="s">
-        <v>617</v>
+        <v>604</v>
       </c>
     </row>
     <row r="740" spans="1:3">
@@ -13609,10 +13630,10 @@
         <v>9</v>
       </c>
       <c r="B740" t="s">
-        <v>628</v>
+        <v>605</v>
       </c>
       <c r="C740" t="s">
-        <v>629</v>
+        <v>607</v>
       </c>
     </row>
     <row r="741" spans="1:3">
@@ -13620,10 +13641,10 @@
         <v>9</v>
       </c>
       <c r="B741" t="s">
-        <v>632</v>
+        <v>608</v>
       </c>
       <c r="C741" t="s">
-        <v>633</v>
+        <v>609</v>
       </c>
     </row>
     <row r="742" spans="1:3">
@@ -13631,10 +13652,10 @@
         <v>9</v>
       </c>
       <c r="B742" t="s">
-        <v>634</v>
+        <v>612</v>
       </c>
       <c r="C742" t="s">
-        <v>635</v>
+        <v>613</v>
       </c>
     </row>
     <row r="743" spans="1:3">
@@ -13642,10 +13663,10 @@
         <v>9</v>
       </c>
       <c r="B743" t="s">
-        <v>642</v>
+        <v>616</v>
       </c>
       <c r="C743" t="s">
-        <v>643</v>
+        <v>617</v>
       </c>
     </row>
     <row r="744" spans="1:3">
@@ -13653,10 +13674,10 @@
         <v>9</v>
       </c>
       <c r="B744" t="s">
-        <v>646</v>
+        <v>628</v>
       </c>
       <c r="C744" t="s">
-        <v>647</v>
+        <v>629</v>
       </c>
     </row>
     <row r="745" spans="1:3">
@@ -13664,10 +13685,10 @@
         <v>9</v>
       </c>
       <c r="B745" t="s">
-        <v>648</v>
+        <v>632</v>
       </c>
       <c r="C745" t="s">
-        <v>649</v>
+        <v>633</v>
       </c>
     </row>
     <row r="746" spans="1:3">
@@ -13675,10 +13696,10 @@
         <v>9</v>
       </c>
       <c r="B746" t="s">
-        <v>652</v>
+        <v>634</v>
       </c>
       <c r="C746" t="s">
-        <v>653</v>
+        <v>635</v>
       </c>
     </row>
     <row r="747" spans="1:3">
@@ -13686,10 +13707,10 @@
         <v>9</v>
       </c>
       <c r="B747" t="s">
-        <v>654</v>
+        <v>642</v>
       </c>
       <c r="C747" t="s">
-        <v>655</v>
+        <v>643</v>
       </c>
     </row>
     <row r="748" spans="1:3">
@@ -13697,10 +13718,10 @@
         <v>9</v>
       </c>
       <c r="B748" t="s">
-        <v>656</v>
+        <v>646</v>
       </c>
       <c r="C748" t="s">
-        <v>657</v>
+        <v>647</v>
       </c>
     </row>
     <row r="749" spans="1:3">
@@ -13708,10 +13729,10 @@
         <v>9</v>
       </c>
       <c r="B749" t="s">
-        <v>658</v>
+        <v>648</v>
       </c>
       <c r="C749" t="s">
-        <v>659</v>
+        <v>649</v>
       </c>
     </row>
     <row r="750" spans="1:3">
@@ -13719,10 +13740,10 @@
         <v>9</v>
       </c>
       <c r="B750" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="C750" t="s">
-        <v>661</v>
+        <v>653</v>
       </c>
     </row>
     <row r="751" spans="1:3">
@@ -13730,10 +13751,10 @@
         <v>9</v>
       </c>
       <c r="B751" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="C751" t="s">
-        <v>665</v>
+        <v>655</v>
       </c>
     </row>
     <row r="752" spans="1:3">
@@ -13741,10 +13762,10 @@
         <v>9</v>
       </c>
       <c r="B752" t="s">
-        <v>666</v>
+        <v>656</v>
       </c>
       <c r="C752" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
     </row>
     <row r="753" spans="1:3">
@@ -13752,10 +13773,10 @@
         <v>9</v>
       </c>
       <c r="B753" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
       <c r="C753" t="s">
-        <v>669</v>
+        <v>659</v>
       </c>
     </row>
     <row r="754" spans="1:3">
@@ -13763,10 +13784,10 @@
         <v>9</v>
       </c>
       <c r="B754" t="s">
-        <v>674</v>
+        <v>660</v>
       </c>
       <c r="C754" t="s">
-        <v>675</v>
+        <v>661</v>
       </c>
     </row>
     <row r="755" spans="1:3">
@@ -13774,10 +13795,10 @@
         <v>9</v>
       </c>
       <c r="B755" t="s">
-        <v>676</v>
+        <v>662</v>
       </c>
       <c r="C755" t="s">
-        <v>678</v>
+        <v>665</v>
       </c>
     </row>
     <row r="756" spans="1:3">
@@ -13785,10 +13806,10 @@
         <v>9</v>
       </c>
       <c r="B756" t="s">
-        <v>679</v>
+        <v>666</v>
       </c>
       <c r="C756" t="s">
-        <v>681</v>
+        <v>667</v>
       </c>
     </row>
     <row r="757" spans="1:3">
@@ -13796,10 +13817,10 @@
         <v>9</v>
       </c>
       <c r="B757" t="s">
-        <v>690</v>
+        <v>668</v>
       </c>
       <c r="C757" t="s">
-        <v>691</v>
+        <v>669</v>
       </c>
     </row>
     <row r="758" spans="1:3">
@@ -13807,10 +13828,10 @@
         <v>9</v>
       </c>
       <c r="B758" t="s">
-        <v>698</v>
+        <v>674</v>
       </c>
       <c r="C758" t="s">
-        <v>699</v>
+        <v>675</v>
       </c>
     </row>
     <row r="759" spans="1:3">
@@ -13818,10 +13839,10 @@
         <v>9</v>
       </c>
       <c r="B759" t="s">
-        <v>700</v>
+        <v>676</v>
       </c>
       <c r="C759" t="s">
-        <v>701</v>
+        <v>678</v>
       </c>
     </row>
     <row r="760" spans="1:3">
@@ -13829,10 +13850,10 @@
         <v>9</v>
       </c>
       <c r="B760" t="s">
-        <v>702</v>
+        <v>679</v>
       </c>
       <c r="C760" t="s">
-        <v>704</v>
+        <v>681</v>
       </c>
     </row>
     <row r="761" spans="1:3">
@@ -13840,10 +13861,10 @@
         <v>9</v>
       </c>
       <c r="B761" t="s">
-        <v>707</v>
+        <v>690</v>
       </c>
       <c r="C761" t="s">
-        <v>708</v>
+        <v>691</v>
       </c>
     </row>
     <row r="762" spans="1:3">
@@ -13851,10 +13872,10 @@
         <v>9</v>
       </c>
       <c r="B762" t="s">
-        <v>709</v>
+        <v>698</v>
       </c>
       <c r="C762" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
     </row>
     <row r="763" spans="1:3">
@@ -13862,10 +13883,10 @@
         <v>9</v>
       </c>
       <c r="B763" t="s">
-        <v>711</v>
+        <v>700</v>
       </c>
       <c r="C763" t="s">
-        <v>712</v>
+        <v>701</v>
       </c>
     </row>
     <row r="764" spans="1:3">
@@ -13873,10 +13894,10 @@
         <v>9</v>
       </c>
       <c r="B764" t="s">
-        <v>723</v>
+        <v>702</v>
       </c>
       <c r="C764" t="s">
-        <v>724</v>
+        <v>704</v>
       </c>
     </row>
     <row r="765" spans="1:3">
@@ -13884,10 +13905,10 @@
         <v>9</v>
       </c>
       <c r="B765" t="s">
-        <v>725</v>
+        <v>707</v>
       </c>
       <c r="C765" t="s">
-        <v>726</v>
+        <v>708</v>
       </c>
     </row>
     <row r="766" spans="1:3">
@@ -13895,10 +13916,10 @@
         <v>9</v>
       </c>
       <c r="B766" t="s">
-        <v>727</v>
+        <v>709</v>
       </c>
       <c r="C766" t="s">
-        <v>728</v>
+        <v>710</v>
       </c>
     </row>
     <row r="767" spans="1:3">
@@ -13906,10 +13927,10 @@
         <v>9</v>
       </c>
       <c r="B767" t="s">
-        <v>729</v>
+        <v>711</v>
       </c>
       <c r="C767" t="s">
-        <v>730</v>
+        <v>712</v>
       </c>
     </row>
     <row r="768" spans="1:3">
@@ -13917,10 +13938,10 @@
         <v>9</v>
       </c>
       <c r="B768" t="s">
-        <v>731</v>
+        <v>723</v>
       </c>
       <c r="C768" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
     </row>
     <row r="769" spans="1:3">
@@ -13928,10 +13949,10 @@
         <v>9</v>
       </c>
       <c r="B769" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
       <c r="C769" t="s">
-        <v>734</v>
+        <v>726</v>
       </c>
     </row>
     <row r="770" spans="1:3">
@@ -13939,10 +13960,10 @@
         <v>9</v>
       </c>
       <c r="B770" t="s">
-        <v>735</v>
+        <v>727</v>
       </c>
       <c r="C770" t="s">
-        <v>736</v>
+        <v>728</v>
       </c>
     </row>
     <row r="771" spans="1:3">
@@ -13950,10 +13971,10 @@
         <v>9</v>
       </c>
       <c r="B771" t="s">
-        <v>737</v>
+        <v>729</v>
       </c>
       <c r="C771" t="s">
-        <v>738</v>
+        <v>730</v>
       </c>
     </row>
     <row r="772" spans="1:3">
@@ -13961,10 +13982,10 @@
         <v>9</v>
       </c>
       <c r="B772" t="s">
-        <v>739</v>
+        <v>731</v>
       </c>
       <c r="C772" t="s">
-        <v>740</v>
+        <v>732</v>
       </c>
     </row>
     <row r="773" spans="1:3">
@@ -13972,10 +13993,10 @@
         <v>9</v>
       </c>
       <c r="B773" t="s">
-        <v>747</v>
+        <v>733</v>
       </c>
       <c r="C773" t="s">
-        <v>749</v>
+        <v>734</v>
       </c>
     </row>
     <row r="774" spans="1:3">
@@ -13983,10 +14004,10 @@
         <v>9</v>
       </c>
       <c r="B774" t="s">
-        <v>750</v>
+        <v>735</v>
       </c>
       <c r="C774" t="s">
-        <v>751</v>
+        <v>736</v>
       </c>
     </row>
     <row r="775" spans="1:3">
@@ -13994,10 +14015,10 @@
         <v>9</v>
       </c>
       <c r="B775" t="s">
-        <v>752</v>
+        <v>737</v>
       </c>
       <c r="C775" t="s">
-        <v>753</v>
+        <v>738</v>
       </c>
     </row>
     <row r="776" spans="1:3">
@@ -14005,10 +14026,10 @@
         <v>9</v>
       </c>
       <c r="B776" t="s">
-        <v>761</v>
+        <v>739</v>
       </c>
       <c r="C776" t="s">
-        <v>762</v>
+        <v>740</v>
       </c>
     </row>
     <row r="777" spans="1:3">
@@ -14016,10 +14037,10 @@
         <v>9</v>
       </c>
       <c r="B777" t="s">
-        <v>765</v>
+        <v>747</v>
       </c>
       <c r="C777" t="s">
-        <v>767</v>
+        <v>749</v>
       </c>
     </row>
     <row r="778" spans="1:3">
@@ -14027,10 +14048,10 @@
         <v>9</v>
       </c>
       <c r="B778" t="s">
-        <v>770</v>
+        <v>750</v>
       </c>
       <c r="C778" t="s">
-        <v>771</v>
+        <v>751</v>
       </c>
     </row>
     <row r="779" spans="1:3">
@@ -14038,10 +14059,10 @@
         <v>9</v>
       </c>
       <c r="B779" t="s">
-        <v>774</v>
+        <v>752</v>
       </c>
       <c r="C779" t="s">
-        <v>775</v>
+        <v>753</v>
       </c>
     </row>
     <row r="780" spans="1:3">
@@ -14049,10 +14070,10 @@
         <v>9</v>
       </c>
       <c r="B780" t="s">
-        <v>776</v>
+        <v>761</v>
       </c>
       <c r="C780" t="s">
-        <v>777</v>
+        <v>762</v>
       </c>
     </row>
     <row r="781" spans="1:3">
@@ -14060,10 +14081,10 @@
         <v>9</v>
       </c>
       <c r="B781" t="s">
-        <v>780</v>
+        <v>765</v>
       </c>
       <c r="C781" t="s">
-        <v>782</v>
+        <v>767</v>
       </c>
     </row>
     <row r="782" spans="1:3">
@@ -14071,10 +14092,10 @@
         <v>9</v>
       </c>
       <c r="B782" t="s">
-        <v>783</v>
+        <v>770</v>
       </c>
       <c r="C782" t="s">
-        <v>784</v>
+        <v>771</v>
       </c>
     </row>
     <row r="783" spans="1:3">
@@ -14082,10 +14103,10 @@
         <v>9</v>
       </c>
       <c r="B783" t="s">
-        <v>785</v>
+        <v>774</v>
       </c>
       <c r="C783" t="s">
-        <v>787</v>
+        <v>775</v>
       </c>
     </row>
     <row r="784" spans="1:3">
@@ -14093,10 +14114,10 @@
         <v>9</v>
       </c>
       <c r="B784" t="s">
-        <v>794</v>
+        <v>776</v>
       </c>
       <c r="C784" t="s">
-        <v>795</v>
+        <v>777</v>
       </c>
     </row>
     <row r="785" spans="1:3">
@@ -14104,10 +14125,10 @@
         <v>9</v>
       </c>
       <c r="B785" t="s">
-        <v>796</v>
+        <v>780</v>
       </c>
       <c r="C785" t="s">
-        <v>797</v>
+        <v>782</v>
       </c>
     </row>
     <row r="786" spans="1:3">
@@ -14115,10 +14136,10 @@
         <v>9</v>
       </c>
       <c r="B786" t="s">
-        <v>800</v>
+        <v>783</v>
       </c>
       <c r="C786" t="s">
-        <v>801</v>
+        <v>784</v>
       </c>
     </row>
     <row r="787" spans="1:3">
@@ -14126,10 +14147,10 @@
         <v>9</v>
       </c>
       <c r="B787" t="s">
-        <v>804</v>
+        <v>785</v>
       </c>
       <c r="C787" t="s">
-        <v>806</v>
+        <v>787</v>
       </c>
     </row>
     <row r="788" spans="1:3">
@@ -14137,10 +14158,10 @@
         <v>9</v>
       </c>
       <c r="B788" t="s">
-        <v>807</v>
+        <v>794</v>
       </c>
       <c r="C788" t="s">
-        <v>808</v>
+        <v>795</v>
       </c>
     </row>
     <row r="789" spans="1:3">
@@ -14148,10 +14169,10 @@
         <v>9</v>
       </c>
       <c r="B789" t="s">
-        <v>818</v>
+        <v>796</v>
       </c>
       <c r="C789" t="s">
-        <v>819</v>
+        <v>797</v>
       </c>
     </row>
     <row r="790" spans="1:3">
@@ -14159,10 +14180,10 @@
         <v>9</v>
       </c>
       <c r="B790" t="s">
-        <v>822</v>
+        <v>800</v>
       </c>
       <c r="C790" t="s">
-        <v>824</v>
+        <v>801</v>
       </c>
     </row>
     <row r="791" spans="1:3">
@@ -14170,10 +14191,10 @@
         <v>9</v>
       </c>
       <c r="B791" t="s">
-        <v>829</v>
+        <v>804</v>
       </c>
       <c r="C791" t="s">
-        <v>830</v>
+        <v>806</v>
       </c>
     </row>
     <row r="792" spans="1:3">
@@ -14181,10 +14202,10 @@
         <v>9</v>
       </c>
       <c r="B792" t="s">
-        <v>833</v>
+        <v>807</v>
       </c>
       <c r="C792" t="s">
-        <v>834</v>
+        <v>808</v>
       </c>
     </row>
     <row r="793" spans="1:3">
@@ -14192,10 +14213,10 @@
         <v>9</v>
       </c>
       <c r="B793" t="s">
-        <v>835</v>
+        <v>818</v>
       </c>
       <c r="C793" t="s">
-        <v>836</v>
+        <v>819</v>
       </c>
     </row>
     <row r="794" spans="1:3">
@@ -14203,10 +14224,10 @@
         <v>9</v>
       </c>
       <c r="B794" t="s">
-        <v>837</v>
+        <v>822</v>
       </c>
       <c r="C794" t="s">
-        <v>838</v>
+        <v>824</v>
       </c>
     </row>
     <row r="795" spans="1:3">
@@ -14214,10 +14235,10 @@
         <v>9</v>
       </c>
       <c r="B795" t="s">
-        <v>839</v>
+        <v>829</v>
       </c>
       <c r="C795" t="s">
-        <v>840</v>
+        <v>830</v>
       </c>
     </row>
     <row r="796" spans="1:3">
@@ -14225,10 +14246,10 @@
         <v>9</v>
       </c>
       <c r="B796" t="s">
-        <v>843</v>
+        <v>833</v>
       </c>
       <c r="C796" t="s">
-        <v>844</v>
+        <v>834</v>
       </c>
     </row>
     <row r="797" spans="1:3">
@@ -14236,10 +14257,10 @@
         <v>9</v>
       </c>
       <c r="B797" t="s">
-        <v>861</v>
+        <v>835</v>
       </c>
       <c r="C797" t="s">
-        <v>862</v>
+        <v>836</v>
       </c>
     </row>
     <row r="798" spans="1:3">
@@ -14247,10 +14268,10 @@
         <v>9</v>
       </c>
       <c r="B798" t="s">
-        <v>865</v>
+        <v>837</v>
       </c>
       <c r="C798" t="s">
-        <v>866</v>
+        <v>838</v>
       </c>
     </row>
     <row r="799" spans="1:3">
@@ -14258,10 +14279,10 @@
         <v>9</v>
       </c>
       <c r="B799" t="s">
-        <v>867</v>
+        <v>839</v>
       </c>
       <c r="C799" t="s">
-        <v>868</v>
+        <v>840</v>
       </c>
     </row>
     <row r="800" spans="1:3">
@@ -14269,10 +14290,10 @@
         <v>9</v>
       </c>
       <c r="B800" t="s">
-        <v>871</v>
+        <v>843</v>
       </c>
       <c r="C800" t="s">
-        <v>872</v>
+        <v>844</v>
       </c>
     </row>
     <row r="801" spans="1:3">
@@ -14280,10 +14301,10 @@
         <v>9</v>
       </c>
       <c r="B801" t="s">
-        <v>879</v>
+        <v>861</v>
       </c>
       <c r="C801" t="s">
-        <v>880</v>
+        <v>862</v>
       </c>
     </row>
     <row r="802" spans="1:3">
@@ -14291,10 +14312,10 @@
         <v>9</v>
       </c>
       <c r="B802" t="s">
-        <v>881</v>
+        <v>865</v>
       </c>
       <c r="C802" t="s">
-        <v>883</v>
+        <v>866</v>
       </c>
     </row>
     <row r="803" spans="1:3">
@@ -14302,10 +14323,10 @@
         <v>9</v>
       </c>
       <c r="B803" t="s">
-        <v>884</v>
+        <v>867</v>
       </c>
       <c r="C803" t="s">
-        <v>885</v>
+        <v>868</v>
       </c>
     </row>
     <row r="804" spans="1:3">
@@ -14313,10 +14334,10 @@
         <v>9</v>
       </c>
       <c r="B804" t="s">
-        <v>888</v>
+        <v>871</v>
       </c>
       <c r="C804" t="s">
-        <v>890</v>
+        <v>872</v>
       </c>
     </row>
     <row r="805" spans="1:3">
@@ -14324,10 +14345,10 @@
         <v>9</v>
       </c>
       <c r="B805" t="s">
-        <v>895</v>
+        <v>879</v>
       </c>
       <c r="C805" t="s">
-        <v>896</v>
+        <v>880</v>
       </c>
     </row>
     <row r="806" spans="1:3">
@@ -14335,10 +14356,10 @@
         <v>9</v>
       </c>
       <c r="B806" t="s">
-        <v>897</v>
+        <v>881</v>
       </c>
       <c r="C806" t="s">
-        <v>898</v>
+        <v>883</v>
       </c>
     </row>
     <row r="807" spans="1:3">
@@ -14346,10 +14367,10 @@
         <v>9</v>
       </c>
       <c r="B807" t="s">
-        <v>899</v>
+        <v>884</v>
       </c>
       <c r="C807" t="s">
-        <v>900</v>
+        <v>885</v>
       </c>
     </row>
     <row r="808" spans="1:3">
@@ -14357,10 +14378,10 @@
         <v>9</v>
       </c>
       <c r="B808" t="s">
-        <v>901</v>
+        <v>888</v>
       </c>
       <c r="C808" t="s">
-        <v>902</v>
+        <v>890</v>
       </c>
     </row>
     <row r="809" spans="1:3">
@@ -14368,10 +14389,10 @@
         <v>9</v>
       </c>
       <c r="B809" t="s">
-        <v>905</v>
+        <v>895</v>
       </c>
       <c r="C809" t="s">
-        <v>906</v>
+        <v>896</v>
       </c>
     </row>
     <row r="810" spans="1:3">
@@ -14379,10 +14400,10 @@
         <v>9</v>
       </c>
       <c r="B810" t="s">
-        <v>907</v>
+        <v>897</v>
       </c>
       <c r="C810" t="s">
-        <v>908</v>
+        <v>898</v>
       </c>
     </row>
     <row r="811" spans="1:3">
@@ -14390,10 +14411,10 @@
         <v>9</v>
       </c>
       <c r="B811" t="s">
-        <v>915</v>
+        <v>899</v>
       </c>
       <c r="C811" t="s">
-        <v>916</v>
+        <v>900</v>
       </c>
     </row>
     <row r="812" spans="1:3">
@@ -14401,10 +14422,10 @@
         <v>9</v>
       </c>
       <c r="B812" t="s">
-        <v>928</v>
+        <v>901</v>
       </c>
       <c r="C812" t="s">
-        <v>929</v>
+        <v>902</v>
       </c>
     </row>
     <row r="813" spans="1:3">
@@ -14412,10 +14433,10 @@
         <v>9</v>
       </c>
       <c r="B813" t="s">
-        <v>930</v>
+        <v>905</v>
       </c>
       <c r="C813" t="s">
-        <v>931</v>
+        <v>906</v>
       </c>
     </row>
     <row r="814" spans="1:3">
@@ -14423,10 +14444,10 @@
         <v>9</v>
       </c>
       <c r="B814" t="s">
-        <v>936</v>
+        <v>907</v>
       </c>
       <c r="C814" t="s">
-        <v>937</v>
+        <v>908</v>
       </c>
     </row>
     <row r="815" spans="1:3">
@@ -14434,10 +14455,10 @@
         <v>9</v>
       </c>
       <c r="B815" t="s">
-        <v>946</v>
+        <v>915</v>
       </c>
       <c r="C815" t="s">
-        <v>947</v>
+        <v>916</v>
       </c>
     </row>
     <row r="816" spans="1:3">
@@ -14445,10 +14466,10 @@
         <v>9</v>
       </c>
       <c r="B816" t="s">
-        <v>950</v>
+        <v>928</v>
       </c>
       <c r="C816" t="s">
-        <v>951</v>
+        <v>929</v>
       </c>
     </row>
     <row r="817" spans="1:3">
@@ -14456,10 +14477,10 @@
         <v>9</v>
       </c>
       <c r="B817" t="s">
-        <v>954</v>
+        <v>930</v>
       </c>
       <c r="C817" t="s">
-        <v>956</v>
+        <v>931</v>
       </c>
     </row>
     <row r="818" spans="1:3">
@@ -14467,10 +14488,10 @@
         <v>9</v>
       </c>
       <c r="B818" t="s">
-        <v>957</v>
+        <v>936</v>
       </c>
       <c r="C818" t="s">
-        <v>958</v>
+        <v>937</v>
       </c>
     </row>
     <row r="819" spans="1:3">
@@ -14478,10 +14499,10 @@
         <v>9</v>
       </c>
       <c r="B819" t="s">
-        <v>963</v>
+        <v>946</v>
       </c>
       <c r="C819" t="s">
-        <v>964</v>
+        <v>947</v>
       </c>
     </row>
     <row r="820" spans="1:3">
@@ -14489,10 +14510,10 @@
         <v>9</v>
       </c>
       <c r="B820" t="s">
-        <v>965</v>
+        <v>950</v>
       </c>
       <c r="C820" t="s">
-        <v>966</v>
+        <v>951</v>
       </c>
     </row>
     <row r="821" spans="1:3">
@@ -14500,10 +14521,10 @@
         <v>9</v>
       </c>
       <c r="B821" t="s">
-        <v>967</v>
+        <v>954</v>
       </c>
       <c r="C821" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
     </row>
     <row r="822" spans="1:3">
@@ -14511,10 +14532,10 @@
         <v>9</v>
       </c>
       <c r="B822" t="s">
-        <v>975</v>
+        <v>957</v>
       </c>
       <c r="C822" t="s">
-        <v>976</v>
+        <v>958</v>
       </c>
     </row>
     <row r="823" spans="1:3">
@@ -14522,10 +14543,10 @@
         <v>9</v>
       </c>
       <c r="B823" t="s">
-        <v>982</v>
+        <v>963</v>
       </c>
       <c r="C823" t="s">
-        <v>983</v>
+        <v>964</v>
       </c>
     </row>
     <row r="824" spans="1:3">
@@ -14533,10 +14554,10 @@
         <v>9</v>
       </c>
       <c r="B824" t="s">
-        <v>984</v>
+        <v>965</v>
       </c>
       <c r="C824" t="s">
-        <v>985</v>
+        <v>966</v>
       </c>
     </row>
     <row r="825" spans="1:3">
@@ -14544,10 +14565,10 @@
         <v>9</v>
       </c>
       <c r="B825" t="s">
-        <v>998</v>
+        <v>967</v>
       </c>
       <c r="C825" t="s">
-        <v>999</v>
+        <v>968</v>
       </c>
     </row>
     <row r="826" spans="1:3">
@@ -14555,10 +14576,10 @@
         <v>9</v>
       </c>
       <c r="B826" t="s">
-        <v>1000</v>
+        <v>975</v>
       </c>
       <c r="C826" t="s">
-        <v>1001</v>
+        <v>976</v>
       </c>
     </row>
     <row r="827" spans="1:3">
@@ -14566,10 +14587,10 @@
         <v>9</v>
       </c>
       <c r="B827" t="s">
-        <v>1002</v>
+        <v>982</v>
       </c>
       <c r="C827" t="s">
-        <v>1003</v>
+        <v>983</v>
       </c>
     </row>
     <row r="828" spans="1:3">
@@ -14577,10 +14598,10 @@
         <v>9</v>
       </c>
       <c r="B828" t="s">
-        <v>1004</v>
+        <v>984</v>
       </c>
       <c r="C828" t="s">
-        <v>1005</v>
+        <v>985</v>
       </c>
     </row>
     <row r="829" spans="1:3">
@@ -14588,10 +14609,10 @@
         <v>9</v>
       </c>
       <c r="B829" t="s">
-        <v>1010</v>
+        <v>998</v>
       </c>
       <c r="C829" t="s">
-        <v>1011</v>
+        <v>999</v>
       </c>
     </row>
     <row r="830" spans="1:3">
@@ -14599,10 +14620,10 @@
         <v>9</v>
       </c>
       <c r="B830" t="s">
-        <v>1012</v>
+        <v>1000</v>
       </c>
       <c r="C830" t="s">
-        <v>1013</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="831" spans="1:3">
@@ -14610,10 +14631,10 @@
         <v>9</v>
       </c>
       <c r="B831" t="s">
-        <v>1014</v>
+        <v>1002</v>
       </c>
       <c r="C831" t="s">
-        <v>1015</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="832" spans="1:3">
@@ -14621,10 +14642,10 @@
         <v>9</v>
       </c>
       <c r="B832" t="s">
-        <v>1018</v>
+        <v>1004</v>
       </c>
       <c r="C832" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="833" spans="1:3">
@@ -14632,10 +14653,10 @@
         <v>9</v>
       </c>
       <c r="B833" t="s">
-        <v>1026</v>
+        <v>1010</v>
       </c>
       <c r="C833" t="s">
-        <v>1027</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="834" spans="1:3">
@@ -14643,10 +14664,10 @@
         <v>9</v>
       </c>
       <c r="B834" t="s">
-        <v>1028</v>
+        <v>1012</v>
       </c>
       <c r="C834" t="s">
-        <v>1029</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="835" spans="1:3">
@@ -14654,10 +14675,10 @@
         <v>9</v>
       </c>
       <c r="B835" t="s">
-        <v>1036</v>
+        <v>1014</v>
       </c>
       <c r="C835" t="s">
-        <v>1037</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="836" spans="1:3">
@@ -14665,10 +14686,10 @@
         <v>9</v>
       </c>
       <c r="B836" t="s">
-        <v>1038</v>
+        <v>1018</v>
       </c>
       <c r="C836" t="s">
-        <v>467</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="837" spans="1:3">
@@ -14676,10 +14697,10 @@
         <v>9</v>
       </c>
       <c r="B837" t="s">
-        <v>1039</v>
+        <v>1026</v>
       </c>
       <c r="C837" t="s">
-        <v>1040</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="838" spans="1:3">
@@ -14687,10 +14708,10 @@
         <v>9</v>
       </c>
       <c r="B838" t="s">
-        <v>1041</v>
+        <v>1028</v>
       </c>
       <c r="C838" t="s">
-        <v>1042</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="839" spans="1:3">
@@ -14698,10 +14719,10 @@
         <v>9</v>
       </c>
       <c r="B839" t="s">
-        <v>1043</v>
+        <v>1036</v>
       </c>
       <c r="C839" t="s">
-        <v>1044</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="840" spans="1:3">
@@ -14709,10 +14730,10 @@
         <v>9</v>
       </c>
       <c r="B840" t="s">
-        <v>1051</v>
+        <v>1038</v>
       </c>
       <c r="C840" t="s">
-        <v>1052</v>
+        <v>467</v>
       </c>
     </row>
     <row r="841" spans="1:3">
@@ -14720,10 +14741,10 @@
         <v>9</v>
       </c>
       <c r="B841" t="s">
-        <v>1057</v>
+        <v>1039</v>
       </c>
       <c r="C841" t="s">
-        <v>1060</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="842" spans="1:3">
@@ -14731,10 +14752,10 @@
         <v>9</v>
       </c>
       <c r="B842" t="s">
-        <v>1061</v>
+        <v>1041</v>
       </c>
       <c r="C842" t="s">
-        <v>1062</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="843" spans="1:3">
@@ -14742,10 +14763,10 @@
         <v>9</v>
       </c>
       <c r="B843" t="s">
-        <v>1063</v>
+        <v>1043</v>
       </c>
       <c r="C843" t="s">
-        <v>1064</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="844" spans="1:3">
@@ -14753,10 +14774,10 @@
         <v>9</v>
       </c>
       <c r="B844" t="s">
-        <v>1065</v>
+        <v>1051</v>
       </c>
       <c r="C844" t="s">
-        <v>1066</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="845" spans="1:3">
@@ -14764,10 +14785,10 @@
         <v>9</v>
       </c>
       <c r="B845" t="s">
-        <v>1067</v>
+        <v>1057</v>
       </c>
       <c r="C845" t="s">
-        <v>1068</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="846" spans="1:3">
@@ -14775,10 +14796,10 @@
         <v>9</v>
       </c>
       <c r="B846" t="s">
-        <v>1069</v>
+        <v>1061</v>
       </c>
       <c r="C846" t="s">
-        <v>1071</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="847" spans="1:3">
@@ -14786,10 +14807,10 @@
         <v>9</v>
       </c>
       <c r="B847" t="s">
-        <v>1082</v>
+        <v>1063</v>
       </c>
       <c r="C847" t="s">
-        <v>1003</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="848" spans="1:3">
@@ -14797,10 +14818,10 @@
         <v>9</v>
       </c>
       <c r="B848" t="s">
-        <v>1083</v>
+        <v>1065</v>
       </c>
       <c r="C848" t="s">
-        <v>1084</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="849" spans="1:3">
@@ -14808,10 +14829,10 @@
         <v>9</v>
       </c>
       <c r="B849" t="s">
-        <v>1085</v>
+        <v>1067</v>
       </c>
       <c r="C849" t="s">
-        <v>1086</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="850" spans="1:3">
@@ -14819,10 +14840,10 @@
         <v>9</v>
       </c>
       <c r="B850" t="s">
-        <v>1089</v>
+        <v>1069</v>
       </c>
       <c r="C850" t="s">
-        <v>1090</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="851" spans="1:3">
@@ -14830,10 +14851,10 @@
         <v>9</v>
       </c>
       <c r="B851" t="s">
-        <v>1091</v>
+        <v>1082</v>
       </c>
       <c r="C851" t="s">
-        <v>1092</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="852" spans="1:3">
@@ -14841,10 +14862,10 @@
         <v>9</v>
       </c>
       <c r="B852" t="s">
-        <v>1095</v>
+        <v>1083</v>
       </c>
       <c r="C852" t="s">
-        <v>1096</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="853" spans="1:3">
@@ -14852,10 +14873,10 @@
         <v>9</v>
       </c>
       <c r="B853" t="s">
-        <v>1097</v>
+        <v>1085</v>
       </c>
       <c r="C853" t="s">
-        <v>1099</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="854" spans="1:3">
@@ -14863,10 +14884,10 @@
         <v>9</v>
       </c>
       <c r="B854" t="s">
-        <v>1106</v>
+        <v>1089</v>
       </c>
       <c r="C854" t="s">
-        <v>1108</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="855" spans="1:3">
@@ -14874,10 +14895,10 @@
         <v>9</v>
       </c>
       <c r="B855" t="s">
-        <v>1109</v>
+        <v>1091</v>
       </c>
       <c r="C855" t="s">
-        <v>1110</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="856" spans="1:3">
@@ -14885,10 +14906,10 @@
         <v>9</v>
       </c>
       <c r="B856" t="s">
-        <v>1122</v>
+        <v>1095</v>
       </c>
       <c r="C856" t="s">
-        <v>1123</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="857" spans="1:3">
@@ -14896,10 +14917,10 @@
         <v>9</v>
       </c>
       <c r="B857" t="s">
-        <v>1134</v>
+        <v>1097</v>
       </c>
       <c r="C857" t="s">
-        <v>1135</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="858" spans="1:3">
@@ -14907,10 +14928,10 @@
         <v>9</v>
       </c>
       <c r="B858" t="s">
-        <v>1136</v>
+        <v>1106</v>
       </c>
       <c r="C858" t="s">
-        <v>1137</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="859" spans="1:3">
@@ -14918,10 +14939,10 @@
         <v>9</v>
       </c>
       <c r="B859" t="s">
-        <v>1140</v>
+        <v>1109</v>
       </c>
       <c r="C859" t="s">
-        <v>1141</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="860" spans="1:3">
@@ -14929,10 +14950,10 @@
         <v>9</v>
       </c>
       <c r="B860" t="s">
-        <v>1142</v>
+        <v>1122</v>
       </c>
       <c r="C860" t="s">
-        <v>1143</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="861" spans="1:3">
@@ -14940,10 +14961,10 @@
         <v>9</v>
       </c>
       <c r="B861" t="s">
-        <v>1144</v>
+        <v>1134</v>
       </c>
       <c r="C861" t="s">
-        <v>1145</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="862" spans="1:3">
@@ -14951,10 +14972,10 @@
         <v>9</v>
       </c>
       <c r="B862" t="s">
-        <v>1152</v>
+        <v>1136</v>
       </c>
       <c r="C862" t="s">
-        <v>1154</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="863" spans="1:3">
@@ -14962,10 +14983,10 @@
         <v>9</v>
       </c>
       <c r="B863" t="s">
-        <v>1155</v>
+        <v>1140</v>
       </c>
       <c r="C863" t="s">
-        <v>1156</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="864" spans="1:3">
@@ -14973,10 +14994,10 @@
         <v>9</v>
       </c>
       <c r="B864" t="s">
-        <v>1157</v>
+        <v>1142</v>
       </c>
       <c r="C864" t="s">
-        <v>1158</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="865" spans="1:3">
@@ -14984,10 +15005,10 @@
         <v>9</v>
       </c>
       <c r="B865" t="s">
-        <v>1161</v>
+        <v>1144</v>
       </c>
       <c r="C865" t="s">
-        <v>1162</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="866" spans="1:3">
@@ -14995,10 +15016,10 @@
         <v>9</v>
       </c>
       <c r="B866" t="s">
-        <v>1163</v>
+        <v>1152</v>
       </c>
       <c r="C866" t="s">
-        <v>1164</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="867" spans="1:3">
@@ -15006,10 +15027,10 @@
         <v>9</v>
       </c>
       <c r="B867" t="s">
-        <v>1165</v>
+        <v>1155</v>
       </c>
       <c r="C867" t="s">
-        <v>1166</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="868" spans="1:3">
@@ -15017,10 +15038,10 @@
         <v>9</v>
       </c>
       <c r="B868" t="s">
-        <v>1167</v>
+        <v>1157</v>
       </c>
       <c r="C868" t="s">
-        <v>1168</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="869" spans="1:3">
@@ -15028,10 +15049,10 @@
         <v>9</v>
       </c>
       <c r="B869" t="s">
-        <v>1169</v>
+        <v>1161</v>
       </c>
       <c r="C869" t="s">
-        <v>1170</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="870" spans="1:3">
@@ -15039,10 +15060,10 @@
         <v>9</v>
       </c>
       <c r="B870" t="s">
-        <v>1171</v>
+        <v>1163</v>
       </c>
       <c r="C870" t="s">
-        <v>1172</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="871" spans="1:3">
@@ -15050,10 +15071,10 @@
         <v>9</v>
       </c>
       <c r="B871" t="s">
-        <v>1173</v>
+        <v>1165</v>
       </c>
       <c r="C871" t="s">
-        <v>1174</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="872" spans="1:3">
@@ -15061,10 +15082,10 @@
         <v>9</v>
       </c>
       <c r="B872" t="s">
-        <v>1175</v>
+        <v>1167</v>
       </c>
       <c r="C872" t="s">
-        <v>1176</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="873" spans="1:3">
@@ -15072,10 +15093,10 @@
         <v>9</v>
       </c>
       <c r="B873" t="s">
-        <v>1177</v>
+        <v>1169</v>
       </c>
       <c r="C873" t="s">
-        <v>1178</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="874" spans="1:3">
@@ -15083,10 +15104,10 @@
         <v>9</v>
       </c>
       <c r="B874" t="s">
-        <v>1179</v>
+        <v>1171</v>
       </c>
       <c r="C874" t="s">
-        <v>1180</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="875" spans="1:3">
@@ -15094,10 +15115,10 @@
         <v>9</v>
       </c>
       <c r="B875" t="s">
-        <v>1183</v>
+        <v>1173</v>
       </c>
       <c r="C875" t="s">
-        <v>1184</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="876" spans="1:3">
@@ -15105,10 +15126,10 @@
         <v>9</v>
       </c>
       <c r="B876" t="s">
-        <v>1185</v>
+        <v>1175</v>
       </c>
       <c r="C876" t="s">
-        <v>1186</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="877" spans="1:3">
@@ -15116,10 +15137,10 @@
         <v>9</v>
       </c>
       <c r="B877" t="s">
-        <v>1195</v>
+        <v>1177</v>
       </c>
       <c r="C877" t="s">
-        <v>1196</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="878" spans="1:3">
@@ -15127,10 +15148,10 @@
         <v>9</v>
       </c>
       <c r="B878" t="s">
-        <v>1197</v>
+        <v>1179</v>
       </c>
       <c r="C878" t="s">
-        <v>1198</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="879" spans="1:3">
@@ -15138,10 +15159,10 @@
         <v>9</v>
       </c>
       <c r="B879" t="s">
-        <v>1199</v>
+        <v>1183</v>
       </c>
       <c r="C879" t="s">
-        <v>1201</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="880" spans="1:3">
@@ -15149,10 +15170,10 @@
         <v>9</v>
       </c>
       <c r="B880" t="s">
-        <v>1204</v>
+        <v>1185</v>
       </c>
       <c r="C880" t="s">
-        <v>1205</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="881" spans="1:3">
@@ -15160,10 +15181,10 @@
         <v>9</v>
       </c>
       <c r="B881" t="s">
-        <v>1206</v>
+        <v>1195</v>
       </c>
       <c r="C881" t="s">
-        <v>1207</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="882" spans="1:3">
@@ -15171,10 +15192,10 @@
         <v>9</v>
       </c>
       <c r="B882" t="s">
-        <v>1220</v>
+        <v>1197</v>
       </c>
       <c r="C882" t="s">
-        <v>1221</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="883" spans="1:3">
@@ -15182,10 +15203,10 @@
         <v>9</v>
       </c>
       <c r="B883" t="s">
-        <v>1222</v>
+        <v>1199</v>
       </c>
       <c r="C883" t="s">
-        <v>1223</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="884" spans="1:3">
@@ -15193,10 +15214,10 @@
         <v>9</v>
       </c>
       <c r="B884" t="s">
-        <v>1226</v>
+        <v>1204</v>
       </c>
       <c r="C884" t="s">
-        <v>1227</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="885" spans="1:3">
@@ -15204,10 +15225,10 @@
         <v>9</v>
       </c>
       <c r="B885" t="s">
-        <v>1228</v>
+        <v>1206</v>
       </c>
       <c r="C885" t="s">
-        <v>1229</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="886" spans="1:3">
@@ -15215,10 +15236,10 @@
         <v>9</v>
       </c>
       <c r="B886" t="s">
-        <v>1230</v>
+        <v>1220</v>
       </c>
       <c r="C886" t="s">
-        <v>1231</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="887" spans="1:3">
@@ -15226,10 +15247,10 @@
         <v>9</v>
       </c>
       <c r="B887" t="s">
-        <v>1240</v>
+        <v>1222</v>
       </c>
       <c r="C887" t="s">
-        <v>1241</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="888" spans="1:3">
@@ -15237,10 +15258,10 @@
         <v>9</v>
       </c>
       <c r="B888" t="s">
-        <v>1242</v>
+        <v>1226</v>
       </c>
       <c r="C888" t="s">
-        <v>1243</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="889" spans="1:3">
@@ -15248,10 +15269,10 @@
         <v>9</v>
       </c>
       <c r="B889" t="s">
-        <v>1244</v>
+        <v>1228</v>
       </c>
       <c r="C889" t="s">
-        <v>1245</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="890" spans="1:3">
@@ -15259,10 +15280,10 @@
         <v>9</v>
       </c>
       <c r="B890" t="s">
-        <v>1250</v>
+        <v>1230</v>
       </c>
       <c r="C890" t="s">
-        <v>1251</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="891" spans="1:3">
@@ -15270,10 +15291,10 @@
         <v>9</v>
       </c>
       <c r="B891" t="s">
-        <v>1262</v>
+        <v>1240</v>
       </c>
       <c r="C891" t="s">
-        <v>1263</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="892" spans="1:3">
@@ -15281,10 +15302,10 @@
         <v>9</v>
       </c>
       <c r="B892" t="s">
-        <v>1264</v>
+        <v>1242</v>
       </c>
       <c r="C892" t="s">
-        <v>1266</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="893" spans="1:3">
@@ -15292,10 +15313,10 @@
         <v>9</v>
       </c>
       <c r="B893" t="s">
-        <v>1277</v>
+        <v>1244</v>
       </c>
       <c r="C893" t="s">
-        <v>1278</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="894" spans="1:3">
@@ -15303,10 +15324,10 @@
         <v>9</v>
       </c>
       <c r="B894" t="s">
-        <v>1286</v>
+        <v>1250</v>
       </c>
       <c r="C894" t="s">
-        <v>1287</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="895" spans="1:3">
@@ -15314,10 +15335,10 @@
         <v>9</v>
       </c>
       <c r="B895" t="s">
-        <v>1293</v>
+        <v>1262</v>
       </c>
       <c r="C895" t="s">
-        <v>1294</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="896" spans="1:3">
@@ -15325,10 +15346,10 @@
         <v>9</v>
       </c>
       <c r="B896" t="s">
-        <v>1299</v>
+        <v>1264</v>
       </c>
       <c r="C896" t="s">
-        <v>1300</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="897" spans="1:3">
@@ -15336,10 +15357,10 @@
         <v>9</v>
       </c>
       <c r="B897" t="s">
-        <v>1304</v>
+        <v>1277</v>
       </c>
       <c r="C897" t="s">
-        <v>1306</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="898" spans="1:3">
@@ -15347,10 +15368,10 @@
         <v>9</v>
       </c>
       <c r="B898" t="s">
-        <v>1313</v>
+        <v>1286</v>
       </c>
       <c r="C898" t="s">
-        <v>1314</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="899" spans="1:3">
@@ -15358,10 +15379,10 @@
         <v>9</v>
       </c>
       <c r="B899" t="s">
-        <v>1317</v>
+        <v>1293</v>
       </c>
       <c r="C899" t="s">
-        <v>1318</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="900" spans="1:3">
@@ -15369,10 +15390,10 @@
         <v>9</v>
       </c>
       <c r="B900" t="s">
-        <v>1319</v>
+        <v>1299</v>
       </c>
       <c r="C900" t="s">
-        <v>1320</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="901" spans="1:3">
@@ -15380,10 +15401,10 @@
         <v>9</v>
       </c>
       <c r="B901" t="s">
-        <v>1329</v>
+        <v>1304</v>
       </c>
       <c r="C901" t="s">
-        <v>1330</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="902" spans="1:3">
@@ -15391,10 +15412,10 @@
         <v>9</v>
       </c>
       <c r="B902" t="s">
-        <v>1331</v>
+        <v>1313</v>
       </c>
       <c r="C902" t="s">
-        <v>1332</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="903" spans="1:3">
@@ -15402,10 +15423,10 @@
         <v>9</v>
       </c>
       <c r="B903" t="s">
-        <v>1335</v>
+        <v>1317</v>
       </c>
       <c r="C903" t="s">
-        <v>1336</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="904" spans="1:3">
@@ -15413,10 +15434,10 @@
         <v>9</v>
       </c>
       <c r="B904" t="s">
-        <v>1337</v>
+        <v>1319</v>
       </c>
       <c r="C904" t="s">
-        <v>1338</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="905" spans="1:3">
@@ -15424,10 +15445,10 @@
         <v>9</v>
       </c>
       <c r="B905" t="s">
-        <v>1345</v>
+        <v>1329</v>
       </c>
       <c r="C905" t="s">
-        <v>1346</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="906" spans="1:3">
@@ -15435,10 +15456,10 @@
         <v>9</v>
       </c>
       <c r="B906" t="s">
-        <v>1347</v>
+        <v>1331</v>
       </c>
       <c r="C906" t="s">
-        <v>1348</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="907" spans="1:3">
@@ -15446,10 +15467,10 @@
         <v>9</v>
       </c>
       <c r="B907" t="s">
-        <v>1349</v>
+        <v>1335</v>
       </c>
       <c r="C907" t="s">
-        <v>1350</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="908" spans="1:3">
@@ -15457,10 +15478,10 @@
         <v>9</v>
       </c>
       <c r="B908" t="s">
-        <v>1351</v>
+        <v>1337</v>
       </c>
       <c r="C908" t="s">
-        <v>1352</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="909" spans="1:3">
@@ -15468,10 +15489,10 @@
         <v>9</v>
       </c>
       <c r="B909" t="s">
-        <v>1353</v>
+        <v>1345</v>
       </c>
       <c r="C909" t="s">
-        <v>1354</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="910" spans="1:3">
@@ -15479,10 +15500,10 @@
         <v>9</v>
       </c>
       <c r="B910" t="s">
-        <v>1355</v>
+        <v>1347</v>
       </c>
       <c r="C910" t="s">
-        <v>1356</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="911" spans="1:3">
@@ -15490,10 +15511,10 @@
         <v>9</v>
       </c>
       <c r="B911" t="s">
-        <v>1363</v>
+        <v>1349</v>
       </c>
       <c r="C911" t="s">
-        <v>1364</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="912" spans="1:3">
@@ -15501,10 +15522,10 @@
         <v>9</v>
       </c>
       <c r="B912" t="s">
-        <v>1367</v>
+        <v>1351</v>
       </c>
       <c r="C912" t="s">
-        <v>1369</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="913" spans="1:3">
@@ -15512,10 +15533,10 @@
         <v>9</v>
       </c>
       <c r="B913" t="s">
-        <v>1374</v>
+        <v>1353</v>
       </c>
       <c r="C913" t="s">
-        <v>1377</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="914" spans="1:3">
@@ -15523,10 +15544,10 @@
         <v>9</v>
       </c>
       <c r="B914" t="s">
-        <v>1390</v>
+        <v>1355</v>
       </c>
       <c r="C914" t="s">
-        <v>1391</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="915" spans="1:3">
@@ -15534,10 +15555,10 @@
         <v>9</v>
       </c>
       <c r="B915" t="s">
-        <v>1392</v>
+        <v>1363</v>
       </c>
       <c r="C915" t="s">
-        <v>1393</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="916" spans="1:3">
@@ -15545,10 +15566,10 @@
         <v>9</v>
       </c>
       <c r="B916" t="s">
-        <v>1394</v>
+        <v>1367</v>
       </c>
       <c r="C916" t="s">
-        <v>1395</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="917" spans="1:3">
@@ -15556,10 +15577,10 @@
         <v>9</v>
       </c>
       <c r="B917" t="s">
-        <v>1400</v>
+        <v>1374</v>
       </c>
       <c r="C917" t="s">
-        <v>1401</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="918" spans="1:3">
@@ -15567,10 +15588,10 @@
         <v>9</v>
       </c>
       <c r="B918" t="s">
-        <v>1402</v>
+        <v>1390</v>
       </c>
       <c r="C918" t="s">
-        <v>1403</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="919" spans="1:3">
@@ -15578,10 +15599,10 @@
         <v>9</v>
       </c>
       <c r="B919" t="s">
-        <v>1404</v>
+        <v>1392</v>
       </c>
       <c r="C919" t="s">
-        <v>1405</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="920" spans="1:3">
@@ -15589,10 +15610,10 @@
         <v>9</v>
       </c>
       <c r="B920" t="s">
-        <v>1406</v>
+        <v>1394</v>
       </c>
       <c r="C920" t="s">
-        <v>1408</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="921" spans="1:3">
@@ -15600,54 +15621,54 @@
         <v>9</v>
       </c>
       <c r="B921" t="s">
-        <v>1422</v>
+        <v>1400</v>
       </c>
       <c r="C921" t="s">
-        <v>1423</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="922" spans="1:3">
       <c r="A922" t="s">
-        <v>7</v>
-      </c>
-      <c r="B922">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="B922" t="s">
+        <v>1402</v>
       </c>
       <c r="C922" t="s">
-        <v>1433</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="923" spans="1:3">
       <c r="A923" t="s">
-        <v>7</v>
-      </c>
-      <c r="B923">
-        <v>2</v>
+        <v>9</v>
+      </c>
+      <c r="B923" t="s">
+        <v>1404</v>
       </c>
       <c r="C923" t="s">
-        <v>1439</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="924" spans="1:3">
       <c r="A924" t="s">
-        <v>7</v>
-      </c>
-      <c r="B924">
-        <v>3</v>
+        <v>9</v>
+      </c>
+      <c r="B924" t="s">
+        <v>1406</v>
       </c>
       <c r="C924" t="s">
-        <v>1447</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="925" spans="1:3">
       <c r="A925" t="s">
-        <v>7</v>
-      </c>
-      <c r="B925">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="B925" t="s">
+        <v>1422</v>
       </c>
       <c r="C925" t="s">
-        <v>1453</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="926" spans="1:3">
@@ -15655,54 +15676,54 @@
         <v>7</v>
       </c>
       <c r="B926">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C926" t="s">
-        <v>1461</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="927" spans="1:3">
       <c r="A927" t="s">
         <v>7</v>
       </c>
-      <c r="B927" t="s">
-        <v>257</v>
+      <c r="B927">
+        <v>2</v>
       </c>
       <c r="C927" t="s">
-        <v>259</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="928" spans="1:3">
       <c r="A928" t="s">
         <v>7</v>
       </c>
-      <c r="B928" t="s">
-        <v>339</v>
+      <c r="B928">
+        <v>3</v>
       </c>
       <c r="C928" t="s">
-        <v>340</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="929" spans="1:3">
       <c r="A929" t="s">
         <v>7</v>
       </c>
-      <c r="B929" t="s">
-        <v>375</v>
+      <c r="B929">
+        <v>4</v>
       </c>
       <c r="C929" t="s">
-        <v>376</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="930" spans="1:3">
       <c r="A930" t="s">
         <v>7</v>
       </c>
-      <c r="B930" t="s">
-        <v>399</v>
+      <c r="B930">
+        <v>5</v>
       </c>
       <c r="C930" t="s">
-        <v>400</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="931" spans="1:3">
@@ -15710,10 +15731,10 @@
         <v>7</v>
       </c>
       <c r="B931" t="s">
-        <v>422</v>
+        <v>257</v>
       </c>
       <c r="C931" t="s">
-        <v>423</v>
+        <v>259</v>
       </c>
     </row>
     <row r="932" spans="1:3">
@@ -15721,10 +15742,10 @@
         <v>7</v>
       </c>
       <c r="B932" t="s">
-        <v>582</v>
+        <v>339</v>
       </c>
       <c r="C932" t="s">
-        <v>583</v>
+        <v>340</v>
       </c>
     </row>
     <row r="933" spans="1:3">
@@ -15732,10 +15753,10 @@
         <v>7</v>
       </c>
       <c r="B933" t="s">
-        <v>745</v>
+        <v>375</v>
       </c>
       <c r="C933" t="s">
-        <v>746</v>
+        <v>376</v>
       </c>
     </row>
     <row r="934" spans="1:3">
@@ -15743,10 +15764,10 @@
         <v>7</v>
       </c>
       <c r="B934" t="s">
-        <v>909</v>
+        <v>399</v>
       </c>
       <c r="C934" t="s">
-        <v>910</v>
+        <v>400</v>
       </c>
     </row>
     <row r="935" spans="1:3">
@@ -15754,10 +15775,10 @@
         <v>7</v>
       </c>
       <c r="B935" t="s">
-        <v>1076</v>
+        <v>422</v>
       </c>
       <c r="C935" t="s">
-        <v>1077</v>
+        <v>423</v>
       </c>
     </row>
     <row r="936" spans="1:3">
@@ -15765,10 +15786,10 @@
         <v>7</v>
       </c>
       <c r="B936" t="s">
-        <v>1159</v>
+        <v>582</v>
       </c>
       <c r="C936" t="s">
-        <v>1160</v>
+        <v>583</v>
       </c>
     </row>
     <row r="937" spans="1:3">
@@ -15776,54 +15797,54 @@
         <v>7</v>
       </c>
       <c r="B937" t="s">
-        <v>1409</v>
+        <v>745</v>
       </c>
       <c r="C937" t="s">
-        <v>1410</v>
+        <v>746</v>
       </c>
     </row>
     <row r="938" spans="1:3">
       <c r="A938" t="s">
-        <v>1649</v>
-      </c>
-      <c r="B938">
-        <v>302</v>
+        <v>7</v>
+      </c>
+      <c r="B938" t="s">
+        <v>909</v>
       </c>
       <c r="C938" t="s">
-        <v>1650</v>
+        <v>910</v>
       </c>
     </row>
     <row r="939" spans="1:3">
       <c r="A939" t="s">
-        <v>1649</v>
-      </c>
-      <c r="B939">
-        <v>303</v>
+        <v>7</v>
+      </c>
+      <c r="B939" t="s">
+        <v>1076</v>
       </c>
       <c r="C939" t="s">
-        <v>1651</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="940" spans="1:3">
       <c r="A940" t="s">
-        <v>1649</v>
-      </c>
-      <c r="B940">
-        <v>304</v>
+        <v>7</v>
+      </c>
+      <c r="B940" t="s">
+        <v>1159</v>
       </c>
       <c r="C940" t="s">
-        <v>1652</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="941" spans="1:3">
       <c r="A941" t="s">
-        <v>1649</v>
-      </c>
-      <c r="B941">
-        <v>305</v>
+        <v>7</v>
+      </c>
+      <c r="B941" t="s">
+        <v>1409</v>
       </c>
       <c r="C941" t="s">
-        <v>1653</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="942" spans="1:3">
@@ -15831,10 +15852,10 @@
         <v>1649</v>
       </c>
       <c r="B942">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C942" t="s">
-        <v>1654</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="943" spans="1:3">
@@ -15842,10 +15863,10 @@
         <v>1649</v>
       </c>
       <c r="B943">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C943" t="s">
-        <v>1655</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="944" spans="1:3">
@@ -15853,10 +15874,10 @@
         <v>1649</v>
       </c>
       <c r="B944">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C944" t="s">
-        <v>1656</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="945" spans="1:3">
@@ -15864,10 +15885,10 @@
         <v>1649</v>
       </c>
       <c r="B945">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C945" t="s">
-        <v>1657</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="946" spans="1:3">
@@ -15875,10 +15896,10 @@
         <v>1649</v>
       </c>
       <c r="B946">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C946" t="s">
-        <v>1658</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="947" spans="1:3">
@@ -15886,10 +15907,10 @@
         <v>1649</v>
       </c>
       <c r="B947">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C947" t="s">
-        <v>1659</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="948" spans="1:3">
@@ -15897,10 +15918,10 @@
         <v>1649</v>
       </c>
       <c r="B948">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C948" t="s">
-        <v>1660</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="949" spans="1:3">
@@ -15908,10 +15929,10 @@
         <v>1649</v>
       </c>
       <c r="B949">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C949" t="s">
-        <v>1661</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="950" spans="1:3">
@@ -15919,10 +15940,10 @@
         <v>1649</v>
       </c>
       <c r="B950">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C950" t="s">
-        <v>1662</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="951" spans="1:3">
@@ -15930,10 +15951,10 @@
         <v>1649</v>
       </c>
       <c r="B951">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C951" t="s">
-        <v>1663</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="952" spans="1:3">
@@ -15941,10 +15962,10 @@
         <v>1649</v>
       </c>
       <c r="B952">
-        <v>401</v>
+        <v>312</v>
       </c>
       <c r="C952" t="s">
-        <v>1664</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="953" spans="1:3">
@@ -15952,10 +15973,10 @@
         <v>1649</v>
       </c>
       <c r="B953">
-        <v>402</v>
+        <v>313</v>
       </c>
       <c r="C953" t="s">
-        <v>1665</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="954" spans="1:3">
@@ -15963,54 +15984,54 @@
         <v>1649</v>
       </c>
       <c r="B954">
-        <v>403</v>
+        <v>314</v>
       </c>
       <c r="C954" t="s">
-        <v>1666</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="955" spans="1:3">
       <c r="A955" t="s">
-        <v>1607</v>
+        <v>1649</v>
       </c>
       <c r="B955">
-        <v>102</v>
+        <v>315</v>
       </c>
       <c r="C955" t="s">
-        <v>1608</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="956" spans="1:3">
       <c r="A956" t="s">
-        <v>1607</v>
+        <v>1649</v>
       </c>
       <c r="B956">
-        <v>103</v>
+        <v>401</v>
       </c>
       <c r="C956" t="s">
-        <v>1609</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="957" spans="1:3">
       <c r="A957" t="s">
-        <v>1607</v>
+        <v>1649</v>
       </c>
       <c r="B957">
-        <v>104</v>
+        <v>402</v>
       </c>
       <c r="C957" t="s">
-        <v>1610</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="958" spans="1:3">
       <c r="A958" t="s">
-        <v>1607</v>
+        <v>1649</v>
       </c>
       <c r="B958">
-        <v>105</v>
+        <v>403</v>
       </c>
       <c r="C958" t="s">
-        <v>1611</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="959" spans="1:3">
@@ -16018,10 +16039,10 @@
         <v>1607</v>
       </c>
       <c r="B959">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C959" t="s">
-        <v>1613</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="960" spans="1:3">
@@ -16029,10 +16050,10 @@
         <v>1607</v>
       </c>
       <c r="B960">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C960" t="s">
-        <v>1614</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="961" spans="1:3">
@@ -16040,10 +16061,10 @@
         <v>1607</v>
       </c>
       <c r="B961">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C961" t="s">
-        <v>1615</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="962" spans="1:3">
@@ -16051,10 +16072,10 @@
         <v>1607</v>
       </c>
       <c r="B962">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C962" t="s">
-        <v>1617</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="963" spans="1:3">
@@ -16062,10 +16083,10 @@
         <v>1607</v>
       </c>
       <c r="B963">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C963" t="s">
-        <v>1620</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="964" spans="1:3">
@@ -16073,10 +16094,10 @@
         <v>1607</v>
       </c>
       <c r="B964">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C964" t="s">
-        <v>1621</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="965" spans="1:3">
@@ -16084,10 +16105,10 @@
         <v>1607</v>
       </c>
       <c r="B965">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C965" t="s">
-        <v>1622</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="966" spans="1:3">
@@ -16095,10 +16116,10 @@
         <v>1607</v>
       </c>
       <c r="B966">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C966" t="s">
-        <v>1623</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="967" spans="1:3">
@@ -16106,10 +16127,10 @@
         <v>1607</v>
       </c>
       <c r="B967">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C967" t="s">
-        <v>1625</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="968" spans="1:3">
@@ -16117,10 +16138,10 @@
         <v>1607</v>
       </c>
       <c r="B968">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C968" t="s">
-        <v>1626</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="969" spans="1:3">
@@ -16128,10 +16149,10 @@
         <v>1607</v>
       </c>
       <c r="B969">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C969" t="s">
-        <v>1627</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="970" spans="1:3">
@@ -16139,10 +16160,10 @@
         <v>1607</v>
       </c>
       <c r="B970">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C970" t="s">
-        <v>1629</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="971" spans="1:3">
@@ -16150,10 +16171,10 @@
         <v>1607</v>
       </c>
       <c r="B971">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C971" t="s">
-        <v>1630</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="972" spans="1:3">
@@ -16161,10 +16182,10 @@
         <v>1607</v>
       </c>
       <c r="B972">
-        <v>201</v>
+        <v>116</v>
       </c>
       <c r="C972" t="s">
-        <v>1635</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="973" spans="1:3">
@@ -16172,10 +16193,10 @@
         <v>1607</v>
       </c>
       <c r="B973">
-        <v>202</v>
+        <v>117</v>
       </c>
       <c r="C973" t="s">
-        <v>1637</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="974" spans="1:3">
@@ -16183,10 +16204,10 @@
         <v>1607</v>
       </c>
       <c r="B974">
-        <v>203</v>
+        <v>118</v>
       </c>
       <c r="C974" t="s">
-        <v>1638</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="975" spans="1:3">
@@ -16194,10 +16215,10 @@
         <v>1607</v>
       </c>
       <c r="B975">
-        <v>204</v>
+        <v>119</v>
       </c>
       <c r="C975" t="s">
-        <v>1639</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="976" spans="1:3">
@@ -16205,10 +16226,10 @@
         <v>1607</v>
       </c>
       <c r="B976">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C976" t="s">
-        <v>1640</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="977" spans="1:3">
@@ -16216,10 +16237,10 @@
         <v>1607</v>
       </c>
       <c r="B977">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C977" t="s">
-        <v>1641</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="978" spans="1:3">
@@ -16227,10 +16248,10 @@
         <v>1607</v>
       </c>
       <c r="B978">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C978" t="s">
-        <v>1642</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="979" spans="1:3">
@@ -16238,10 +16259,10 @@
         <v>1607</v>
       </c>
       <c r="B979">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C979" t="s">
-        <v>1643</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="980" spans="1:3">
@@ -16249,10 +16270,10 @@
         <v>1607</v>
       </c>
       <c r="B980">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C980" t="s">
-        <v>1644</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="981" spans="1:3">
@@ -16260,10 +16281,10 @@
         <v>1607</v>
       </c>
       <c r="B981">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C981" t="s">
-        <v>1645</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="982" spans="1:3">
@@ -16271,10 +16292,10 @@
         <v>1607</v>
       </c>
       <c r="B982">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C982" t="s">
-        <v>1646</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="983" spans="1:3">
@@ -16282,10 +16303,10 @@
         <v>1607</v>
       </c>
       <c r="B983">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C983" t="s">
-        <v>1647</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="984" spans="1:3">
@@ -16293,65 +16314,65 @@
         <v>1607</v>
       </c>
       <c r="B984">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C984" t="s">
-        <v>1648</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="985" spans="1:3">
       <c r="A985" t="s">
-        <v>151</v>
-      </c>
-      <c r="B985" t="s">
-        <v>149</v>
+        <v>1607</v>
+      </c>
+      <c r="B985">
+        <v>210</v>
       </c>
       <c r="C985" t="s">
-        <v>152</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="986" spans="1:3">
       <c r="A986" t="s">
-        <v>151</v>
-      </c>
-      <c r="B986" s="1" t="s">
-        <v>260</v>
+        <v>1607</v>
+      </c>
+      <c r="B986">
+        <v>211</v>
       </c>
       <c r="C986" t="s">
-        <v>261</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="987" spans="1:3">
       <c r="A987" t="s">
-        <v>151</v>
-      </c>
-      <c r="B987" t="s">
-        <v>713</v>
+        <v>1607</v>
+      </c>
+      <c r="B987">
+        <v>212</v>
       </c>
       <c r="C987" t="s">
-        <v>714</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="988" spans="1:3">
       <c r="A988" t="s">
-        <v>151</v>
-      </c>
-      <c r="B988" s="1" t="s">
-        <v>923</v>
+        <v>1607</v>
+      </c>
+      <c r="B988">
+        <v>213</v>
       </c>
       <c r="C988" t="s">
-        <v>925</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="989" spans="1:3">
       <c r="A989" t="s">
         <v>151</v>
       </c>
-      <c r="B989" s="1" t="s">
-        <v>1214</v>
+      <c r="B989" t="s">
+        <v>149</v>
       </c>
       <c r="C989" t="s">
-        <v>1215</v>
+        <v>152</v>
       </c>
     </row>
     <row r="990" spans="1:3">
@@ -16359,32 +16380,32 @@
         <v>151</v>
       </c>
       <c r="B990" s="1" t="s">
-        <v>151</v>
+        <v>260</v>
       </c>
       <c r="C990" t="s">
-        <v>1413</v>
+        <v>261</v>
       </c>
     </row>
     <row r="991" spans="1:3">
       <c r="A991" t="s">
         <v>151</v>
       </c>
-      <c r="B991" t="s">
-        <v>1414</v>
+      <c r="B991" s="1" t="s">
+        <v>382</v>
       </c>
       <c r="C991" t="s">
-        <v>1415</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="992" spans="1:3">
       <c r="A992" t="s">
         <v>151</v>
       </c>
-      <c r="B992" s="1" t="s">
-        <v>382</v>
+      <c r="B992" t="s">
+        <v>713</v>
       </c>
       <c r="C992" t="s">
-        <v>1682</v>
+        <v>714</v>
       </c>
     </row>
     <row r="993" spans="1:3">
@@ -16392,16 +16413,60 @@
         <v>151</v>
       </c>
       <c r="B993" s="1" t="s">
+        <v>923</v>
+      </c>
+      <c r="C993" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="994" spans="1:3">
+      <c r="A994" t="s">
+        <v>151</v>
+      </c>
+      <c r="B994" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="C993" t="s">
+      <c r="C994" t="s">
         <v>1683</v>
       </c>
     </row>
+    <row r="995" spans="1:3">
+      <c r="A995" t="s">
+        <v>151</v>
+      </c>
+      <c r="B995" s="1" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C995" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="996" spans="1:3">
+      <c r="A996" t="s">
+        <v>151</v>
+      </c>
+      <c r="B996" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C996" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="997" spans="1:3">
+      <c r="A997" t="s">
+        <v>151</v>
+      </c>
+      <c r="B997" t="s">
+        <v>1414</v>
+      </c>
+      <c r="C997" t="s">
+        <v>1415</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState ref="A1:D991">
-    <sortCondition ref="A1:A991"/>
-    <sortCondition ref="B1:B991"/>
+  <sortState ref="A1:D997">
+    <sortCondition ref="A1:A997"/>
+    <sortCondition ref="B1:B997"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
